--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Documents\portal_mariana\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F76A4B3F-6F9B-4AAE-B459-BED541251FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22215E66-84D7-42A9-96D3-75409AD8C8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="720" windowWidth="18435" windowHeight="15480" xr2:uid="{3AC424E5-2774-4F4B-8F6B-ABD290BB5A41}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="19965" windowHeight="15480" xr2:uid="{2F3631AF-8538-4ADF-8DC4-649BE7C373BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <t>Ano</t>
   </si>
   <si>
-    <t>Iniciativa</t>
+    <t>Código Iniciativa</t>
   </si>
   <si>
     <t>Código Órgão</t>
@@ -1177,7 +1177,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6B0E61-D1C2-458D-995B-15BAD48377F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E402307-D42E-4907-8D85-678D3343282B}">
   <dimension ref="A1:AD212"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16289,7 +16289,7 @@
         <v>20401.41</v>
       </c>
       <c r="R174" t="n">
-        <v>12967.76</v>
+        <v>20401.39</v>
       </c>
       <c r="S174" t="n">
         <v>12967.76</v>
@@ -16386,7 +16386,7 @@
         <v>7602.3</v>
       </c>
       <c r="S175" t="n">
-        <v>3551.03</v>
+        <v>7322.73</v>
       </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr"/>
       <c r="AD175" t="n">
-        <v>3551.03</v>
+        <v>7322.73</v>
       </c>
     </row>
     <row r="176">
@@ -16477,7 +16477,7 @@
         <v>56971.47</v>
       </c>
       <c r="R176" t="n">
-        <v>20160.08</v>
+        <v>56971.45</v>
       </c>
       <c r="S176" t="n">
         <v>20160.08</v>
@@ -16574,7 +16574,7 @@
         <v>43093.08</v>
       </c>
       <c r="S177" t="n">
-        <v>32076.63</v>
+        <v>41207.95</v>
       </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
@@ -16593,7 +16593,7 @@
       <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="n">
-        <v>32076.63</v>
+        <v>41207.95</v>
       </c>
     </row>
     <row r="178">
@@ -16665,7 +16665,7 @@
         <v>20845.26</v>
       </c>
       <c r="R178" t="n">
-        <v>15913.42</v>
+        <v>20845.24</v>
       </c>
       <c r="S178" t="n">
         <v>15913.42</v>
@@ -16762,7 +16762,7 @@
         <v>5781.07</v>
       </c>
       <c r="S179" t="n">
-        <v>4197.58</v>
+        <v>5781.07</v>
       </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
@@ -16781,7 +16781,7 @@
       <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="inlineStr"/>
       <c r="AD179" t="n">
-        <v>4197.58</v>
+        <v>5781.07</v>
       </c>
     </row>
     <row r="180">
@@ -17229,10 +17229,10 @@
         <v>271448.09</v>
       </c>
       <c r="R184" t="n">
-        <v>194028.94</v>
+        <v>271408.09</v>
       </c>
       <c r="S184" t="n">
-        <v>172685.76</v>
+        <v>241553.2</v>
       </c>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
@@ -17251,7 +17251,7 @@
       <c r="AB184" t="inlineStr"/>
       <c r="AC184" t="inlineStr"/>
       <c r="AD184" t="n">
-        <v>172685.76</v>
+        <v>241553.2</v>
       </c>
     </row>
     <row r="185">
@@ -17417,10 +17417,10 @@
         <v>1010484.55</v>
       </c>
       <c r="R186" t="n">
-        <v>732187.0600000001</v>
+        <v>1010482.55</v>
       </c>
       <c r="S186" t="n">
-        <v>604916.79</v>
+        <v>852437.58</v>
       </c>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
@@ -17439,7 +17439,7 @@
       <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr"/>
       <c r="AD186" t="n">
-        <v>604916.79</v>
+        <v>852437.58</v>
       </c>
     </row>
     <row r="187">
@@ -17605,10 +17605,10 @@
         <v>212903.3</v>
       </c>
       <c r="R188" t="n">
-        <v>158444.14</v>
+        <v>212899.3</v>
       </c>
       <c r="S188" t="n">
-        <v>141015.29</v>
+        <v>189480.38</v>
       </c>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
@@ -17627,7 +17627,7 @@
       <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="inlineStr"/>
       <c r="AD188" t="n">
-        <v>141015.29</v>
+        <v>189480.38</v>
       </c>
     </row>
     <row r="189">
@@ -18447,7 +18447,7 @@
         <v>1245.84</v>
       </c>
       <c r="R197" t="n">
-        <v>981.89</v>
+        <v>1245.81</v>
       </c>
       <c r="S197" t="n">
         <v>981.89</v>
@@ -18541,7 +18541,7 @@
         <v>51565.56</v>
       </c>
       <c r="R198" t="n">
-        <v>40076.82</v>
+        <v>51565.51</v>
       </c>
       <c r="S198" t="n">
         <v>35668.36</v>
@@ -29375,7 +29375,7 @@
         <v>26315.79</v>
       </c>
       <c r="R317" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S317" t="n">
         <v>0</v>
@@ -29465,7 +29465,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R318" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S318" t="n">
         <v>0</v>
@@ -29555,7 +29555,7 @@
         <v>26315.79</v>
       </c>
       <c r="R319" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S319" t="n">
         <v>0</v>
@@ -29645,7 +29645,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R320" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S320" t="n">
         <v>0</v>
@@ -29735,7 +29735,7 @@
         <v>26315.79</v>
       </c>
       <c r="R321" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S321" t="n">
         <v>0</v>
@@ -29825,7 +29825,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R322" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S322" t="n">
         <v>0</v>
@@ -29915,7 +29915,7 @@
         <v>26315.79</v>
       </c>
       <c r="R323" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S323" t="n">
         <v>0</v>
@@ -30005,7 +30005,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R324" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S324" t="n">
         <v>0</v>
@@ -30095,7 +30095,7 @@
         <v>26315.79</v>
       </c>
       <c r="R325" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S325" t="n">
         <v>0</v>
@@ -30185,7 +30185,7 @@
         <v>75433.53</v>
       </c>
       <c r="R326" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S326" t="n">
         <v>0</v>
@@ -30275,7 +30275,7 @@
         <v>26315.79</v>
       </c>
       <c r="R327" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S327" t="n">
         <v>0</v>
@@ -30365,7 +30365,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R328" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S328" t="n">
         <v>0</v>
@@ -30455,7 +30455,7 @@
         <v>26315.79</v>
       </c>
       <c r="R329" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S329" t="n">
         <v>0</v>
@@ -30545,7 +30545,7 @@
         <v>69075.14</v>
       </c>
       <c r="R330" t="n">
-        <v>0</v>
+        <v>69075.14</v>
       </c>
       <c r="S330" t="n">
         <v>0</v>
@@ -30635,7 +30635,7 @@
         <v>26315.79</v>
       </c>
       <c r="R331" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S331" t="n">
         <v>0</v>
@@ -30725,7 +30725,7 @@
         <v>75433.53</v>
       </c>
       <c r="R332" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S332" t="n">
         <v>0</v>
@@ -30815,7 +30815,7 @@
         <v>26315.79</v>
       </c>
       <c r="R333" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S333" t="n">
         <v>0</v>
@@ -30905,7 +30905,7 @@
         <v>75433.53</v>
       </c>
       <c r="R334" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S334" t="n">
         <v>0</v>
@@ -30995,7 +30995,7 @@
         <v>26315.79</v>
       </c>
       <c r="R335" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S335" t="n">
         <v>0</v>
@@ -31085,7 +31085,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R336" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S336" t="n">
         <v>0</v>
@@ -31175,7 +31175,7 @@
         <v>26315.79</v>
       </c>
       <c r="R337" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S337" t="n">
         <v>0</v>
@@ -31265,7 +31265,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R338" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S338" t="n">
         <v>0</v>
@@ -31355,7 +31355,7 @@
         <v>26315.79</v>
       </c>
       <c r="R339" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S339" t="n">
         <v>0</v>
@@ -31445,7 +31445,7 @@
         <v>75433.53</v>
       </c>
       <c r="R340" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S340" t="n">
         <v>0</v>
@@ -31535,7 +31535,7 @@
         <v>26315.79</v>
       </c>
       <c r="R341" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S341" t="n">
         <v>0</v>
@@ -31625,7 +31625,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R342" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S342" t="n">
         <v>0</v>
@@ -31715,7 +31715,7 @@
         <v>26315.79</v>
       </c>
       <c r="R343" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S343" t="n">
         <v>0</v>
@@ -31805,7 +31805,7 @@
         <v>75433.53</v>
       </c>
       <c r="R344" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S344" t="n">
         <v>0</v>
@@ -31895,7 +31895,7 @@
         <v>26315.79</v>
       </c>
       <c r="R345" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S345" t="n">
         <v>0</v>
@@ -31985,7 +31985,7 @@
         <v>75433.53</v>
       </c>
       <c r="R346" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S346" t="n">
         <v>0</v>
@@ -32075,7 +32075,7 @@
         <v>26315.79</v>
       </c>
       <c r="R347" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S347" t="n">
         <v>0</v>
@@ -32165,7 +32165,7 @@
         <v>75433.53</v>
       </c>
       <c r="R348" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S348" t="n">
         <v>0</v>
@@ -32255,7 +32255,7 @@
         <v>26315.79</v>
       </c>
       <c r="R349" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S349" t="n">
         <v>0</v>
@@ -32345,7 +32345,7 @@
         <v>75433.53</v>
       </c>
       <c r="R350" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S350" t="n">
         <v>0</v>
@@ -32435,7 +32435,7 @@
         <v>26315.79</v>
       </c>
       <c r="R351" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S351" t="n">
         <v>0</v>
@@ -32525,7 +32525,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R352" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S352" t="n">
         <v>0</v>
@@ -32615,7 +32615,7 @@
         <v>26315.79</v>
       </c>
       <c r="R353" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S353" t="n">
         <v>0</v>
@@ -32705,7 +32705,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R354" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S354" t="n">
         <v>0</v>
@@ -32795,7 +32795,7 @@
         <v>26315.79</v>
       </c>
       <c r="R355" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S355" t="n">
         <v>0</v>
@@ -32885,7 +32885,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="R356" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="S356" t="n">
         <v>0</v>
@@ -32975,7 +32975,7 @@
         <v>26315.79</v>
       </c>
       <c r="R357" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S357" t="n">
         <v>0</v>
@@ -33065,7 +33065,7 @@
         <v>81791.91</v>
       </c>
       <c r="R358" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="S358" t="n">
         <v>0</v>
@@ -33155,7 +33155,7 @@
         <v>26315.79</v>
       </c>
       <c r="R359" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S359" t="n">
         <v>0</v>
@@ -33245,7 +33245,7 @@
         <v>75433.53</v>
       </c>
       <c r="R360" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S360" t="n">
         <v>0</v>
@@ -33335,7 +33335,7 @@
         <v>26315.79</v>
       </c>
       <c r="R361" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S361" t="n">
         <v>0</v>
@@ -33425,7 +33425,7 @@
         <v>81791.91</v>
       </c>
       <c r="R362" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="S362" t="n">
         <v>0</v>
@@ -33515,7 +33515,7 @@
         <v>26315.79</v>
       </c>
       <c r="R363" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S363" t="n">
         <v>0</v>
@@ -33605,7 +33605,7 @@
         <v>81791.91</v>
       </c>
       <c r="R364" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="S364" t="n">
         <v>0</v>
@@ -33695,7 +33695,7 @@
         <v>26315.79</v>
       </c>
       <c r="R365" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S365" t="n">
         <v>0</v>
@@ -33785,7 +33785,7 @@
         <v>75433.53</v>
       </c>
       <c r="R366" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S366" t="n">
         <v>0</v>
@@ -33875,7 +33875,7 @@
         <v>26315.79</v>
       </c>
       <c r="R367" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S367" t="n">
         <v>0</v>
@@ -33965,7 +33965,7 @@
         <v>75433.53</v>
       </c>
       <c r="R368" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S368" t="n">
         <v>0</v>
@@ -34055,7 +34055,7 @@
         <v>26315.79</v>
       </c>
       <c r="R369" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S369" t="n">
         <v>0</v>
@@ -34145,7 +34145,7 @@
         <v>81791.91</v>
       </c>
       <c r="R370" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="S370" t="n">
         <v>0</v>
@@ -34235,7 +34235,7 @@
         <v>26315.79</v>
       </c>
       <c r="R371" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S371" t="n">
         <v>0</v>
@@ -34325,7 +34325,7 @@
         <v>75433.53</v>
       </c>
       <c r="R372" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S372" t="n">
         <v>0</v>
@@ -34415,7 +34415,7 @@
         <v>26315.78</v>
       </c>
       <c r="R373" t="n">
-        <v>0</v>
+        <v>26315.78</v>
       </c>
       <c r="S373" t="n">
         <v>0</v>
@@ -34505,7 +34505,7 @@
         <v>88150.28999999999</v>
       </c>
       <c r="R374" t="n">
-        <v>0</v>
+        <v>88150.28999999999</v>
       </c>
       <c r="S374" t="n">
         <v>0</v>
@@ -34595,7 +34595,7 @@
         <v>26315.79</v>
       </c>
       <c r="R375" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S375" t="n">
         <v>0</v>
@@ -34685,7 +34685,7 @@
         <v>81791.91</v>
       </c>
       <c r="R376" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="S376" t="n">
         <v>0</v>
@@ -34775,7 +34775,7 @@
         <v>26315.79</v>
       </c>
       <c r="R377" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S377" t="n">
         <v>0</v>
@@ -34865,7 +34865,7 @@
         <v>81791.91</v>
       </c>
       <c r="R378" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="S378" t="n">
         <v>0</v>
@@ -34955,7 +34955,7 @@
         <v>26315.79</v>
       </c>
       <c r="R379" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S379" t="n">
         <v>0</v>
@@ -35045,7 +35045,7 @@
         <v>75433.53</v>
       </c>
       <c r="R380" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S380" t="n">
         <v>0</v>
@@ -35135,7 +35135,7 @@
         <v>26315.79</v>
       </c>
       <c r="R381" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S381" t="n">
         <v>0</v>
@@ -35225,7 +35225,7 @@
         <v>88150.28999999999</v>
       </c>
       <c r="R382" t="n">
-        <v>0</v>
+        <v>88150.28999999999</v>
       </c>
       <c r="S382" t="n">
         <v>0</v>
@@ -35315,7 +35315,7 @@
         <v>26315.79</v>
       </c>
       <c r="R383" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S383" t="n">
         <v>0</v>
@@ -35405,7 +35405,7 @@
         <v>75433.53</v>
       </c>
       <c r="R384" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S384" t="n">
         <v>0</v>
@@ -35495,7 +35495,7 @@
         <v>26315.78</v>
       </c>
       <c r="R385" t="n">
-        <v>0</v>
+        <v>26315.78</v>
       </c>
       <c r="S385" t="n">
         <v>0</v>
@@ -35585,7 +35585,7 @@
         <v>75433.53</v>
       </c>
       <c r="R386" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S386" t="n">
         <v>0</v>
@@ -35675,7 +35675,7 @@
         <v>26315.79</v>
       </c>
       <c r="R387" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S387" t="n">
         <v>0</v>
@@ -35765,7 +35765,7 @@
         <v>75433.53</v>
       </c>
       <c r="R388" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S388" t="n">
         <v>0</v>
@@ -35855,7 +35855,7 @@
         <v>26315.79</v>
       </c>
       <c r="R389" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S389" t="n">
         <v>0</v>
@@ -35945,7 +35945,7 @@
         <v>81791.91</v>
       </c>
       <c r="R390" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="S390" t="n">
         <v>0</v>
@@ -36035,7 +36035,7 @@
         <v>26315.79</v>
       </c>
       <c r="R391" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="S391" t="n">
         <v>0</v>
@@ -36125,7 +36125,7 @@
         <v>75433.53</v>
       </c>
       <c r="R392" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="S392" t="n">
         <v>0</v>
@@ -36403,7 +36403,7 @@
         <v>1500000</v>
       </c>
       <c r="R395" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="S395" t="n">
         <v>0</v>
@@ -36493,7 +36493,7 @@
         <v>550000</v>
       </c>
       <c r="R396" t="n">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="S396" t="n">
         <v>0</v>
@@ -36583,7 +36583,7 @@
         <v>1583.51</v>
       </c>
       <c r="R397" t="n">
-        <v>0</v>
+        <v>1583.48</v>
       </c>
       <c r="S397" t="n">
         <v>0</v>
@@ -36771,7 +36771,7 @@
         <v>33755.74</v>
       </c>
       <c r="R399" t="n">
-        <v>0</v>
+        <v>33755.73</v>
       </c>
       <c r="S399" t="n">
         <v>0</v>
@@ -36865,10 +36865,10 @@
         <v>20455.24</v>
       </c>
       <c r="R400" t="n">
-        <v>0</v>
+        <v>20455.23</v>
       </c>
       <c r="S400" t="n">
-        <v>0</v>
+        <v>18243.88</v>
       </c>
       <c r="T400" t="inlineStr"/>
       <c r="U400" t="inlineStr"/>
@@ -36887,7 +36887,7 @@
       <c r="AB400" t="inlineStr"/>
       <c r="AC400" t="inlineStr"/>
       <c r="AD400" t="n">
-        <v>0</v>
+        <v>18243.88</v>
       </c>
     </row>
     <row r="401">
@@ -36959,7 +36959,7 @@
         <v>77101.57000000001</v>
       </c>
       <c r="R401" t="n">
-        <v>0</v>
+        <v>77101.56</v>
       </c>
       <c r="S401" t="n">
         <v>0</v>
@@ -37053,10 +37053,10 @@
         <v>75875.06</v>
       </c>
       <c r="R402" t="n">
-        <v>0</v>
+        <v>75875.05</v>
       </c>
       <c r="S402" t="n">
-        <v>0</v>
+        <v>42058.91</v>
       </c>
       <c r="T402" t="inlineStr"/>
       <c r="U402" t="inlineStr"/>
@@ -37075,7 +37075,7 @@
       <c r="AB402" t="inlineStr"/>
       <c r="AC402" t="inlineStr"/>
       <c r="AD402" t="n">
-        <v>0</v>
+        <v>42058.91</v>
       </c>
     </row>
     <row r="403">
@@ -37147,7 +37147,7 @@
         <v>55389.55</v>
       </c>
       <c r="R403" t="n">
-        <v>0</v>
+        <v>55389.54</v>
       </c>
       <c r="S403" t="n">
         <v>0</v>
@@ -37241,10 +37241,10 @@
         <v>12237.7</v>
       </c>
       <c r="R404" t="n">
-        <v>0</v>
+        <v>12237.69</v>
       </c>
       <c r="S404" t="n">
-        <v>0</v>
+        <v>10926.23</v>
       </c>
       <c r="T404" t="inlineStr"/>
       <c r="U404" t="inlineStr"/>
@@ -37263,7 +37263,7 @@
       <c r="AB404" t="inlineStr"/>
       <c r="AC404" t="inlineStr"/>
       <c r="AD404" t="n">
-        <v>0</v>
+        <v>10926.23</v>
       </c>
     </row>
     <row r="405">
@@ -37335,7 +37335,7 @@
         <v>3079.53</v>
       </c>
       <c r="R405" t="n">
-        <v>0</v>
+        <v>3079.52</v>
       </c>
       <c r="S405" t="n">
         <v>0</v>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD405"/>
+  <dimension ref="A1:AD407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13292,7 +13292,7 @@
         <v>60882.72</v>
       </c>
       <c r="S142" t="n">
-        <v>38447.46</v>
+        <v>51263.28</v>
       </c>
       <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr"/>
@@ -13311,7 +13311,7 @@
       <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="n">
-        <v>38447.46</v>
+        <v>51263.28</v>
       </c>
     </row>
     <row r="143">
@@ -17135,7 +17135,7 @@
         <v>489186</v>
       </c>
       <c r="R183" t="n">
-        <v>359889.19</v>
+        <v>489138.54</v>
       </c>
       <c r="S183" t="n">
         <v>271636.02</v>
@@ -17323,7 +17323,7 @@
         <v>1109262.91</v>
       </c>
       <c r="R185" t="n">
-        <v>818445.86</v>
+        <v>1109258.91</v>
       </c>
       <c r="S185" t="n">
         <v>727768.01</v>
@@ -17511,7 +17511,7 @@
         <v>777688.27</v>
       </c>
       <c r="R187" t="n">
-        <v>581654.51</v>
+        <v>777684.27</v>
       </c>
       <c r="S187" t="n">
         <v>468265.2</v>
@@ -36677,7 +36677,7 @@
         <v>57506.47</v>
       </c>
       <c r="R398" t="n">
-        <v>0</v>
+        <v>57506.44</v>
       </c>
       <c r="S398" t="n">
         <v>0</v>
@@ -37360,6 +37360,186 @@
         <v>0</v>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B406" t="n">
+        <v>9480259</v>
+      </c>
+      <c r="C406" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>155</v>
+      </c>
+      <c r="F406" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>37</v>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K406" t="n">
+        <v>3704</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
+        </is>
+      </c>
+      <c r="M406" t="n">
+        <v>80</v>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q406" t="n">
+        <v>45068.98</v>
+      </c>
+      <c r="R406" t="n">
+        <v>0</v>
+      </c>
+      <c r="S406" t="n">
+        <v>0</v>
+      </c>
+      <c r="T406" t="inlineStr"/>
+      <c r="U406" t="inlineStr"/>
+      <c r="V406" t="inlineStr"/>
+      <c r="W406" t="inlineStr"/>
+      <c r="X406" t="inlineStr"/>
+      <c r="Y406" t="inlineStr"/>
+      <c r="Z406" t="n">
+        <v>45068.98</v>
+      </c>
+      <c r="AA406" t="inlineStr"/>
+      <c r="AB406" t="inlineStr"/>
+      <c r="AC406" t="inlineStr"/>
+      <c r="AD406" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B407" t="n">
+        <v>9480259</v>
+      </c>
+      <c r="C407" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>156</v>
+      </c>
+      <c r="F407" s="2" t="n">
+        <v>46175</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>37</v>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K407" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M407" t="n">
+        <v>80</v>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q407" t="n">
+        <v>974.33</v>
+      </c>
+      <c r="R407" t="n">
+        <v>0</v>
+      </c>
+      <c r="S407" t="n">
+        <v>0</v>
+      </c>
+      <c r="T407" t="inlineStr"/>
+      <c r="U407" t="inlineStr"/>
+      <c r="V407" t="inlineStr"/>
+      <c r="W407" t="inlineStr"/>
+      <c r="X407" t="inlineStr"/>
+      <c r="Y407" t="inlineStr"/>
+      <c r="Z407" t="n">
+        <v>974.33</v>
+      </c>
+      <c r="AA407" t="inlineStr"/>
+      <c r="AB407" t="inlineStr"/>
+      <c r="AC407" t="inlineStr"/>
+      <c r="AD407" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD407"/>
+  <dimension ref="A1:AD410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14605,10 +14605,10 @@
         <v>25000</v>
       </c>
       <c r="R156" t="n">
-        <v>9612.799999999999</v>
+        <v>11625.2</v>
       </c>
       <c r="S156" t="n">
-        <v>9612.799999999999</v>
+        <v>11625.2</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14627,7 +14627,7 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>9612.799999999999</v>
+        <v>11625.2</v>
       </c>
     </row>
     <row r="157">
@@ -16199,10 +16199,10 @@
         <v>67763</v>
       </c>
       <c r="R173" t="n">
-        <v>1111</v>
+        <v>3380.8</v>
       </c>
       <c r="S173" t="n">
-        <v>1473</v>
+        <v>3742.8</v>
       </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr"/>
       <c r="AD173" t="n">
-        <v>1473</v>
+        <v>3742.8</v>
       </c>
     </row>
     <row r="174">
@@ -16292,7 +16292,7 @@
         <v>20401.39</v>
       </c>
       <c r="S174" t="n">
-        <v>12967.76</v>
+        <v>20036.2</v>
       </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
@@ -16311,7 +16311,7 @@
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr"/>
       <c r="AD174" t="n">
-        <v>12967.76</v>
+        <v>20036.2</v>
       </c>
     </row>
     <row r="175">
@@ -16480,7 +16480,7 @@
         <v>56971.45</v>
       </c>
       <c r="S176" t="n">
-        <v>20160.08</v>
+        <v>53665.01</v>
       </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
@@ -16499,7 +16499,7 @@
       <c r="AB176" t="inlineStr"/>
       <c r="AC176" t="inlineStr"/>
       <c r="AD176" t="n">
-        <v>20160.08</v>
+        <v>53665.01</v>
       </c>
     </row>
     <row r="177">
@@ -16668,7 +16668,7 @@
         <v>20845.24</v>
       </c>
       <c r="S178" t="n">
-        <v>15913.42</v>
+        <v>20845.24</v>
       </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
@@ -16687,7 +16687,7 @@
       <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="inlineStr"/>
       <c r="AD178" t="n">
-        <v>15913.42</v>
+        <v>20845.24</v>
       </c>
     </row>
     <row r="179">
@@ -17138,7 +17138,7 @@
         <v>489138.54</v>
       </c>
       <c r="S183" t="n">
-        <v>271636.02</v>
+        <v>386505.74</v>
       </c>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
@@ -17157,7 +17157,7 @@
       <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="inlineStr"/>
       <c r="AD183" t="n">
-        <v>271636.02</v>
+        <v>386505.74</v>
       </c>
     </row>
     <row r="184">
@@ -17326,7 +17326,7 @@
         <v>1109258.91</v>
       </c>
       <c r="S185" t="n">
-        <v>727768.01</v>
+        <v>986429.4300000001</v>
       </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="inlineStr"/>
       <c r="AD185" t="n">
-        <v>727768.01</v>
+        <v>986429.4300000001</v>
       </c>
     </row>
     <row r="186">
@@ -17514,7 +17514,7 @@
         <v>777684.27</v>
       </c>
       <c r="S187" t="n">
-        <v>468265.2</v>
+        <v>642569.49</v>
       </c>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
@@ -17533,7 +17533,7 @@
       <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="n">
-        <v>468265.2</v>
+        <v>642569.49</v>
       </c>
     </row>
     <row r="188">
@@ -18450,7 +18450,7 @@
         <v>1245.81</v>
       </c>
       <c r="S197" t="n">
-        <v>981.89</v>
+        <v>1245.81</v>
       </c>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
@@ -18469,7 +18469,7 @@
       <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="n">
-        <v>981.89</v>
+        <v>1245.81</v>
       </c>
     </row>
     <row r="198">
@@ -18544,7 +18544,7 @@
         <v>51565.51</v>
       </c>
       <c r="S198" t="n">
-        <v>35668.36</v>
+        <v>45893.29</v>
       </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
@@ -18563,7 +18563,7 @@
       <c r="AB198" t="inlineStr"/>
       <c r="AC198" t="inlineStr"/>
       <c r="AD198" t="n">
-        <v>35668.36</v>
+        <v>45893.29</v>
       </c>
     </row>
     <row r="199">
@@ -21322,7 +21322,7 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>2380952.38</v>
+        <v>2173913.04</v>
       </c>
       <c r="R228" t="n">
         <v>0</v>
@@ -21337,7 +21337,7 @@
       <c r="X228" t="inlineStr"/>
       <c r="Y228" t="inlineStr"/>
       <c r="Z228" t="n">
-        <v>2380952.38</v>
+        <v>2173913.04</v>
       </c>
       <c r="AA228" t="inlineStr"/>
       <c r="AB228" t="inlineStr"/>
@@ -21412,7 +21412,7 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>2857142.86</v>
+        <v>2826086.96</v>
       </c>
       <c r="R229" t="n">
         <v>0</v>
@@ -21427,7 +21427,7 @@
       <c r="X229" t="inlineStr"/>
       <c r="Y229" t="inlineStr"/>
       <c r="Z229" t="n">
-        <v>2857142.86</v>
+        <v>2826086.96</v>
       </c>
       <c r="AA229" t="inlineStr"/>
       <c r="AB229" t="inlineStr"/>
@@ -21502,7 +21502,7 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>1666666.67</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
         <v>0</v>
@@ -21517,7 +21517,7 @@
       <c r="X230" t="inlineStr"/>
       <c r="Y230" t="inlineStr"/>
       <c r="Z230" t="n">
-        <v>1666666.67</v>
+        <v>0</v>
       </c>
       <c r="AA230" t="inlineStr"/>
       <c r="AB230" t="inlineStr"/>
@@ -21592,7 +21592,7 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>238095.24</v>
+        <v>217391.3</v>
       </c>
       <c r="R231" t="n">
         <v>0</v>
@@ -21607,7 +21607,7 @@
       <c r="X231" t="inlineStr"/>
       <c r="Y231" t="inlineStr"/>
       <c r="Z231" t="n">
-        <v>238095.24</v>
+        <v>217391.3</v>
       </c>
       <c r="AA231" t="inlineStr"/>
       <c r="AB231" t="inlineStr"/>
@@ -21682,7 +21682,7 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>2380952.38</v>
+        <v>2173913.04</v>
       </c>
       <c r="R232" t="n">
         <v>0</v>
@@ -21697,7 +21697,7 @@
       <c r="X232" t="inlineStr"/>
       <c r="Y232" t="inlineStr"/>
       <c r="Z232" t="n">
-        <v>2380952.38</v>
+        <v>2173913.04</v>
       </c>
       <c r="AA232" t="inlineStr"/>
       <c r="AB232" t="inlineStr"/>
@@ -21772,7 +21772,7 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>476190.47</v>
+        <v>0</v>
       </c>
       <c r="R233" t="n">
         <v>0</v>
@@ -21787,7 +21787,7 @@
       <c r="X233" t="inlineStr"/>
       <c r="Y233" t="inlineStr"/>
       <c r="Z233" t="n">
-        <v>476190.47</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="inlineStr"/>
       <c r="AB233" t="inlineStr"/>
@@ -36586,7 +36586,7 @@
         <v>1583.48</v>
       </c>
       <c r="S397" t="n">
-        <v>0</v>
+        <v>1583.48</v>
       </c>
       <c r="T397" t="inlineStr"/>
       <c r="U397" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
       <c r="AB397" t="inlineStr"/>
       <c r="AC397" t="inlineStr"/>
       <c r="AD397" t="n">
-        <v>0</v>
+        <v>1583.48</v>
       </c>
     </row>
     <row r="398">
@@ -36680,7 +36680,7 @@
         <v>57506.44</v>
       </c>
       <c r="S398" t="n">
-        <v>0</v>
+        <v>51180.73</v>
       </c>
       <c r="T398" t="inlineStr"/>
       <c r="U398" t="inlineStr"/>
@@ -36699,7 +36699,7 @@
       <c r="AB398" t="inlineStr"/>
       <c r="AC398" t="inlineStr"/>
       <c r="AD398" t="n">
-        <v>0</v>
+        <v>51180.73</v>
       </c>
     </row>
     <row r="399">
@@ -36774,7 +36774,7 @@
         <v>33755.73</v>
       </c>
       <c r="S399" t="n">
-        <v>0</v>
+        <v>30113.19</v>
       </c>
       <c r="T399" t="inlineStr"/>
       <c r="U399" t="inlineStr"/>
@@ -36793,7 +36793,7 @@
       <c r="AB399" t="inlineStr"/>
       <c r="AC399" t="inlineStr"/>
       <c r="AD399" t="n">
-        <v>0</v>
+        <v>30113.19</v>
       </c>
     </row>
     <row r="400">
@@ -36962,7 +36962,7 @@
         <v>77101.56</v>
       </c>
       <c r="S401" t="n">
-        <v>0</v>
+        <v>25305.6</v>
       </c>
       <c r="T401" t="inlineStr"/>
       <c r="U401" t="inlineStr"/>
@@ -36981,7 +36981,7 @@
       <c r="AB401" t="inlineStr"/>
       <c r="AC401" t="inlineStr"/>
       <c r="AD401" t="n">
-        <v>0</v>
+        <v>25305.6</v>
       </c>
     </row>
     <row r="402">
@@ -37150,7 +37150,7 @@
         <v>55389.54</v>
       </c>
       <c r="S403" t="n">
-        <v>0</v>
+        <v>49402.17</v>
       </c>
       <c r="T403" t="inlineStr"/>
       <c r="U403" t="inlineStr"/>
@@ -37169,7 +37169,7 @@
       <c r="AB403" t="inlineStr"/>
       <c r="AC403" t="inlineStr"/>
       <c r="AD403" t="n">
-        <v>0</v>
+        <v>49402.17</v>
       </c>
     </row>
     <row r="404">
@@ -37338,7 +37338,7 @@
         <v>3079.52</v>
       </c>
       <c r="S405" t="n">
-        <v>0</v>
+        <v>2748.89</v>
       </c>
       <c r="T405" t="inlineStr"/>
       <c r="U405" t="inlineStr"/>
@@ -37357,7 +37357,7 @@
       <c r="AB405" t="inlineStr"/>
       <c r="AC405" t="inlineStr"/>
       <c r="AD405" t="n">
-        <v>0</v>
+        <v>2748.89</v>
       </c>
     </row>
     <row r="406">
@@ -37540,6 +37540,276 @@
         <v>0</v>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B408" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="C408" t="n">
+        <v>4291</v>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>25</v>
+      </c>
+      <c r="F408" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>42</v>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K408" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M408" t="n">
+        <v>80</v>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>01.311.508/0001-73</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>CIS VALE DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="Q408" t="n">
+        <v>1739130.44</v>
+      </c>
+      <c r="R408" t="n">
+        <v>0</v>
+      </c>
+      <c r="S408" t="n">
+        <v>0</v>
+      </c>
+      <c r="T408" t="inlineStr"/>
+      <c r="U408" t="inlineStr"/>
+      <c r="V408" t="inlineStr"/>
+      <c r="W408" t="inlineStr"/>
+      <c r="X408" t="inlineStr"/>
+      <c r="Y408" t="inlineStr"/>
+      <c r="Z408" t="n">
+        <v>1739130.44</v>
+      </c>
+      <c r="AA408" t="inlineStr"/>
+      <c r="AB408" t="inlineStr"/>
+      <c r="AC408" t="inlineStr"/>
+      <c r="AD408" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B409" t="n">
+        <v>9445683</v>
+      </c>
+      <c r="C409" t="n">
+        <v>4291</v>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE SAUDE</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>26</v>
+      </c>
+      <c r="F409" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>42</v>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K409" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M409" t="n">
+        <v>80</v>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>05.802.877/0001-10</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>INSTITUICAO DE COOPERACAO INTERMUNICIPAL DO MEDIO PARAOPEBA</t>
+        </is>
+      </c>
+      <c r="Q409" t="n">
+        <v>869565.22</v>
+      </c>
+      <c r="R409" t="n">
+        <v>0</v>
+      </c>
+      <c r="S409" t="n">
+        <v>0</v>
+      </c>
+      <c r="T409" t="inlineStr"/>
+      <c r="U409" t="inlineStr"/>
+      <c r="V409" t="inlineStr"/>
+      <c r="W409" t="inlineStr"/>
+      <c r="X409" t="inlineStr"/>
+      <c r="Y409" t="inlineStr"/>
+      <c r="Z409" t="n">
+        <v>869565.22</v>
+      </c>
+      <c r="AA409" t="inlineStr"/>
+      <c r="AB409" t="inlineStr"/>
+      <c r="AC409" t="inlineStr"/>
+      <c r="AD409" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B410" t="n">
+        <v>9480259</v>
+      </c>
+      <c r="C410" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>157</v>
+      </c>
+      <c r="F410" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>1221002 000013/2026</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>INEXIGIBILIDADE - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>39</v>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>OUTROS SERVICOS DE TERCEIROS - PESSOA JURIDICA</t>
+        </is>
+      </c>
+      <c r="K410" t="n">
+        <v>3919</v>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAQUINAS E EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="M410" t="n">
+        <v>80</v>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>17.511.734/0001-38</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>AMIS ASSOCIACAO MINEIRA DE SUPERMERCADOS</t>
+        </is>
+      </c>
+      <c r="Q410" t="n">
+        <v>79560.25</v>
+      </c>
+      <c r="R410" t="n">
+        <v>0</v>
+      </c>
+      <c r="S410" t="n">
+        <v>0</v>
+      </c>
+      <c r="T410" t="inlineStr"/>
+      <c r="U410" t="inlineStr"/>
+      <c r="V410" t="inlineStr"/>
+      <c r="W410" t="inlineStr"/>
+      <c r="X410" t="inlineStr"/>
+      <c r="Y410" t="inlineStr"/>
+      <c r="Z410" t="n">
+        <v>79560.25</v>
+      </c>
+      <c r="AA410" t="inlineStr"/>
+      <c r="AB410" t="inlineStr"/>
+      <c r="AC410" t="inlineStr"/>
+      <c r="AD410" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD410"/>
+  <dimension ref="A1:AD413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14602,13 +14602,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>25000</v>
+        <v>45000</v>
       </c>
       <c r="R156" t="n">
-        <v>11625.2</v>
+        <v>13209.7</v>
       </c>
       <c r="S156" t="n">
-        <v>11625.2</v>
+        <v>13209.7</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14621,13 +14621,13 @@
       </c>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="n">
-        <v>25000</v>
+        <v>45000</v>
       </c>
       <c r="AA156" t="inlineStr"/>
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>11625.2</v>
+        <v>13209.7</v>
       </c>
     </row>
     <row r="157">
@@ -22045,10 +22045,10 @@
         <v>29600</v>
       </c>
       <c r="R236" t="n">
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="S236" t="n">
-        <v>0</v>
+        <v>29600</v>
       </c>
       <c r="T236" t="inlineStr"/>
       <c r="U236" t="inlineStr"/>
@@ -22063,7 +22063,7 @@
       <c r="AB236" t="inlineStr"/>
       <c r="AC236" t="inlineStr"/>
       <c r="AD236" t="n">
-        <v>0</v>
+        <v>29600</v>
       </c>
     </row>
     <row r="237">
@@ -29378,7 +29378,7 @@
         <v>26315.79</v>
       </c>
       <c r="S317" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T317" t="inlineStr"/>
       <c r="U317" t="inlineStr"/>
@@ -29393,7 +29393,7 @@
       <c r="AB317" t="inlineStr"/>
       <c r="AC317" t="inlineStr"/>
       <c r="AD317" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="318">
@@ -29468,7 +29468,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S318" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T318" t="inlineStr"/>
       <c r="U318" t="inlineStr"/>
@@ -29483,7 +29483,7 @@
       <c r="AB318" t="inlineStr"/>
       <c r="AC318" t="inlineStr"/>
       <c r="AD318" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="319">
@@ -29558,7 +29558,7 @@
         <v>26315.79</v>
       </c>
       <c r="S319" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T319" t="inlineStr"/>
       <c r="U319" t="inlineStr"/>
@@ -29573,7 +29573,7 @@
       <c r="AB319" t="inlineStr"/>
       <c r="AC319" t="inlineStr"/>
       <c r="AD319" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="320">
@@ -29648,7 +29648,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S320" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T320" t="inlineStr"/>
       <c r="U320" t="inlineStr"/>
@@ -29663,7 +29663,7 @@
       <c r="AB320" t="inlineStr"/>
       <c r="AC320" t="inlineStr"/>
       <c r="AD320" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="321">
@@ -29738,7 +29738,7 @@
         <v>26315.79</v>
       </c>
       <c r="S321" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T321" t="inlineStr"/>
       <c r="U321" t="inlineStr"/>
@@ -29753,7 +29753,7 @@
       <c r="AB321" t="inlineStr"/>
       <c r="AC321" t="inlineStr"/>
       <c r="AD321" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="322">
@@ -29828,7 +29828,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S322" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T322" t="inlineStr"/>
       <c r="U322" t="inlineStr"/>
@@ -29843,7 +29843,7 @@
       <c r="AB322" t="inlineStr"/>
       <c r="AC322" t="inlineStr"/>
       <c r="AD322" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="323">
@@ -29918,7 +29918,7 @@
         <v>26315.79</v>
       </c>
       <c r="S323" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T323" t="inlineStr"/>
       <c r="U323" t="inlineStr"/>
@@ -29933,7 +29933,7 @@
       <c r="AB323" t="inlineStr"/>
       <c r="AC323" t="inlineStr"/>
       <c r="AD323" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="324">
@@ -30008,7 +30008,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S324" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T324" t="inlineStr"/>
       <c r="U324" t="inlineStr"/>
@@ -30023,7 +30023,7 @@
       <c r="AB324" t="inlineStr"/>
       <c r="AC324" t="inlineStr"/>
       <c r="AD324" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="325">
@@ -30098,7 +30098,7 @@
         <v>26315.79</v>
       </c>
       <c r="S325" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T325" t="inlineStr"/>
       <c r="U325" t="inlineStr"/>
@@ -30113,7 +30113,7 @@
       <c r="AB325" t="inlineStr"/>
       <c r="AC325" t="inlineStr"/>
       <c r="AD325" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="326">
@@ -30188,7 +30188,7 @@
         <v>75433.53</v>
       </c>
       <c r="S326" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T326" t="inlineStr"/>
       <c r="U326" t="inlineStr"/>
@@ -30203,7 +30203,7 @@
       <c r="AB326" t="inlineStr"/>
       <c r="AC326" t="inlineStr"/>
       <c r="AD326" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="327">
@@ -30278,7 +30278,7 @@
         <v>26315.79</v>
       </c>
       <c r="S327" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T327" t="inlineStr"/>
       <c r="U327" t="inlineStr"/>
@@ -30293,7 +30293,7 @@
       <c r="AB327" t="inlineStr"/>
       <c r="AC327" t="inlineStr"/>
       <c r="AD327" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="328">
@@ -30368,7 +30368,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S328" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T328" t="inlineStr"/>
       <c r="U328" t="inlineStr"/>
@@ -30383,7 +30383,7 @@
       <c r="AB328" t="inlineStr"/>
       <c r="AC328" t="inlineStr"/>
       <c r="AD328" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="329">
@@ -30458,7 +30458,7 @@
         <v>26315.79</v>
       </c>
       <c r="S329" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T329" t="inlineStr"/>
       <c r="U329" t="inlineStr"/>
@@ -30473,7 +30473,7 @@
       <c r="AB329" t="inlineStr"/>
       <c r="AC329" t="inlineStr"/>
       <c r="AD329" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="330">
@@ -30548,7 +30548,7 @@
         <v>69075.14</v>
       </c>
       <c r="S330" t="n">
-        <v>0</v>
+        <v>69075.14</v>
       </c>
       <c r="T330" t="inlineStr"/>
       <c r="U330" t="inlineStr"/>
@@ -30563,7 +30563,7 @@
       <c r="AB330" t="inlineStr"/>
       <c r="AC330" t="inlineStr"/>
       <c r="AD330" t="n">
-        <v>0</v>
+        <v>69075.14</v>
       </c>
     </row>
     <row r="331">
@@ -30638,7 +30638,7 @@
         <v>26315.79</v>
       </c>
       <c r="S331" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T331" t="inlineStr"/>
       <c r="U331" t="inlineStr"/>
@@ -30653,7 +30653,7 @@
       <c r="AB331" t="inlineStr"/>
       <c r="AC331" t="inlineStr"/>
       <c r="AD331" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="332">
@@ -30728,7 +30728,7 @@
         <v>75433.53</v>
       </c>
       <c r="S332" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T332" t="inlineStr"/>
       <c r="U332" t="inlineStr"/>
@@ -30743,7 +30743,7 @@
       <c r="AB332" t="inlineStr"/>
       <c r="AC332" t="inlineStr"/>
       <c r="AD332" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="333">
@@ -30818,7 +30818,7 @@
         <v>26315.79</v>
       </c>
       <c r="S333" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T333" t="inlineStr"/>
       <c r="U333" t="inlineStr"/>
@@ -30833,7 +30833,7 @@
       <c r="AB333" t="inlineStr"/>
       <c r="AC333" t="inlineStr"/>
       <c r="AD333" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="334">
@@ -30908,7 +30908,7 @@
         <v>75433.53</v>
       </c>
       <c r="S334" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T334" t="inlineStr"/>
       <c r="U334" t="inlineStr"/>
@@ -30923,7 +30923,7 @@
       <c r="AB334" t="inlineStr"/>
       <c r="AC334" t="inlineStr"/>
       <c r="AD334" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="335">
@@ -30998,7 +30998,7 @@
         <v>26315.79</v>
       </c>
       <c r="S335" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T335" t="inlineStr"/>
       <c r="U335" t="inlineStr"/>
@@ -31013,7 +31013,7 @@
       <c r="AB335" t="inlineStr"/>
       <c r="AC335" t="inlineStr"/>
       <c r="AD335" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="336">
@@ -31088,7 +31088,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S336" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T336" t="inlineStr"/>
       <c r="U336" t="inlineStr"/>
@@ -31103,7 +31103,7 @@
       <c r="AB336" t="inlineStr"/>
       <c r="AC336" t="inlineStr"/>
       <c r="AD336" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="337">
@@ -31178,7 +31178,7 @@
         <v>26315.79</v>
       </c>
       <c r="S337" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T337" t="inlineStr"/>
       <c r="U337" t="inlineStr"/>
@@ -31193,7 +31193,7 @@
       <c r="AB337" t="inlineStr"/>
       <c r="AC337" t="inlineStr"/>
       <c r="AD337" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="338">
@@ -31268,7 +31268,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S338" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T338" t="inlineStr"/>
       <c r="U338" t="inlineStr"/>
@@ -31283,7 +31283,7 @@
       <c r="AB338" t="inlineStr"/>
       <c r="AC338" t="inlineStr"/>
       <c r="AD338" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="339">
@@ -31358,7 +31358,7 @@
         <v>26315.79</v>
       </c>
       <c r="S339" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T339" t="inlineStr"/>
       <c r="U339" t="inlineStr"/>
@@ -31373,7 +31373,7 @@
       <c r="AB339" t="inlineStr"/>
       <c r="AC339" t="inlineStr"/>
       <c r="AD339" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="340">
@@ -31448,7 +31448,7 @@
         <v>75433.53</v>
       </c>
       <c r="S340" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T340" t="inlineStr"/>
       <c r="U340" t="inlineStr"/>
@@ -31463,7 +31463,7 @@
       <c r="AB340" t="inlineStr"/>
       <c r="AC340" t="inlineStr"/>
       <c r="AD340" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="341">
@@ -31538,7 +31538,7 @@
         <v>26315.79</v>
       </c>
       <c r="S341" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T341" t="inlineStr"/>
       <c r="U341" t="inlineStr"/>
@@ -31553,7 +31553,7 @@
       <c r="AB341" t="inlineStr"/>
       <c r="AC341" t="inlineStr"/>
       <c r="AD341" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="342">
@@ -31628,7 +31628,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S342" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T342" t="inlineStr"/>
       <c r="U342" t="inlineStr"/>
@@ -31643,7 +31643,7 @@
       <c r="AB342" t="inlineStr"/>
       <c r="AC342" t="inlineStr"/>
       <c r="AD342" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="343">
@@ -31718,7 +31718,7 @@
         <v>26315.79</v>
       </c>
       <c r="S343" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T343" t="inlineStr"/>
       <c r="U343" t="inlineStr"/>
@@ -31733,7 +31733,7 @@
       <c r="AB343" t="inlineStr"/>
       <c r="AC343" t="inlineStr"/>
       <c r="AD343" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="344">
@@ -31808,7 +31808,7 @@
         <v>75433.53</v>
       </c>
       <c r="S344" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T344" t="inlineStr"/>
       <c r="U344" t="inlineStr"/>
@@ -31823,7 +31823,7 @@
       <c r="AB344" t="inlineStr"/>
       <c r="AC344" t="inlineStr"/>
       <c r="AD344" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="345">
@@ -31898,7 +31898,7 @@
         <v>26315.79</v>
       </c>
       <c r="S345" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T345" t="inlineStr"/>
       <c r="U345" t="inlineStr"/>
@@ -31913,7 +31913,7 @@
       <c r="AB345" t="inlineStr"/>
       <c r="AC345" t="inlineStr"/>
       <c r="AD345" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="346">
@@ -31988,7 +31988,7 @@
         <v>75433.53</v>
       </c>
       <c r="S346" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T346" t="inlineStr"/>
       <c r="U346" t="inlineStr"/>
@@ -32003,7 +32003,7 @@
       <c r="AB346" t="inlineStr"/>
       <c r="AC346" t="inlineStr"/>
       <c r="AD346" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="347">
@@ -32078,7 +32078,7 @@
         <v>26315.79</v>
       </c>
       <c r="S347" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T347" t="inlineStr"/>
       <c r="U347" t="inlineStr"/>
@@ -32093,7 +32093,7 @@
       <c r="AB347" t="inlineStr"/>
       <c r="AC347" t="inlineStr"/>
       <c r="AD347" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="348">
@@ -32168,7 +32168,7 @@
         <v>75433.53</v>
       </c>
       <c r="S348" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T348" t="inlineStr"/>
       <c r="U348" t="inlineStr"/>
@@ -32183,7 +32183,7 @@
       <c r="AB348" t="inlineStr"/>
       <c r="AC348" t="inlineStr"/>
       <c r="AD348" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="349">
@@ -32258,7 +32258,7 @@
         <v>26315.79</v>
       </c>
       <c r="S349" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T349" t="inlineStr"/>
       <c r="U349" t="inlineStr"/>
@@ -32273,7 +32273,7 @@
       <c r="AB349" t="inlineStr"/>
       <c r="AC349" t="inlineStr"/>
       <c r="AD349" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="350">
@@ -32348,7 +32348,7 @@
         <v>75433.53</v>
       </c>
       <c r="S350" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T350" t="inlineStr"/>
       <c r="U350" t="inlineStr"/>
@@ -32363,7 +32363,7 @@
       <c r="AB350" t="inlineStr"/>
       <c r="AC350" t="inlineStr"/>
       <c r="AD350" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="351">
@@ -32438,7 +32438,7 @@
         <v>26315.79</v>
       </c>
       <c r="S351" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T351" t="inlineStr"/>
       <c r="U351" t="inlineStr"/>
@@ -32453,7 +32453,7 @@
       <c r="AB351" t="inlineStr"/>
       <c r="AC351" t="inlineStr"/>
       <c r="AD351" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="352">
@@ -32528,7 +32528,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S352" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T352" t="inlineStr"/>
       <c r="U352" t="inlineStr"/>
@@ -32543,7 +32543,7 @@
       <c r="AB352" t="inlineStr"/>
       <c r="AC352" t="inlineStr"/>
       <c r="AD352" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="353">
@@ -32618,7 +32618,7 @@
         <v>26315.79</v>
       </c>
       <c r="S353" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T353" t="inlineStr"/>
       <c r="U353" t="inlineStr"/>
@@ -32633,7 +32633,7 @@
       <c r="AB353" t="inlineStr"/>
       <c r="AC353" t="inlineStr"/>
       <c r="AD353" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="354">
@@ -32708,7 +32708,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S354" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T354" t="inlineStr"/>
       <c r="U354" t="inlineStr"/>
@@ -32723,7 +32723,7 @@
       <c r="AB354" t="inlineStr"/>
       <c r="AC354" t="inlineStr"/>
       <c r="AD354" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="355">
@@ -32798,7 +32798,7 @@
         <v>26315.79</v>
       </c>
       <c r="S355" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T355" t="inlineStr"/>
       <c r="U355" t="inlineStr"/>
@@ -32813,7 +32813,7 @@
       <c r="AB355" t="inlineStr"/>
       <c r="AC355" t="inlineStr"/>
       <c r="AD355" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="356">
@@ -32888,7 +32888,7 @@
         <v>81791.89999999999</v>
       </c>
       <c r="S356" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
       <c r="T356" t="inlineStr"/>
       <c r="U356" t="inlineStr"/>
@@ -32903,7 +32903,7 @@
       <c r="AB356" t="inlineStr"/>
       <c r="AC356" t="inlineStr"/>
       <c r="AD356" t="n">
-        <v>0</v>
+        <v>81791.89999999999</v>
       </c>
     </row>
     <row r="357">
@@ -32978,7 +32978,7 @@
         <v>26315.79</v>
       </c>
       <c r="S357" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T357" t="inlineStr"/>
       <c r="U357" t="inlineStr"/>
@@ -32993,7 +32993,7 @@
       <c r="AB357" t="inlineStr"/>
       <c r="AC357" t="inlineStr"/>
       <c r="AD357" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="358">
@@ -33068,7 +33068,7 @@
         <v>81791.91</v>
       </c>
       <c r="S358" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="T358" t="inlineStr"/>
       <c r="U358" t="inlineStr"/>
@@ -33083,7 +33083,7 @@
       <c r="AB358" t="inlineStr"/>
       <c r="AC358" t="inlineStr"/>
       <c r="AD358" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
     </row>
     <row r="359">
@@ -33158,7 +33158,7 @@
         <v>26315.79</v>
       </c>
       <c r="S359" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T359" t="inlineStr"/>
       <c r="U359" t="inlineStr"/>
@@ -33173,7 +33173,7 @@
       <c r="AB359" t="inlineStr"/>
       <c r="AC359" t="inlineStr"/>
       <c r="AD359" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="360">
@@ -33248,7 +33248,7 @@
         <v>75433.53</v>
       </c>
       <c r="S360" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T360" t="inlineStr"/>
       <c r="U360" t="inlineStr"/>
@@ -33263,7 +33263,7 @@
       <c r="AB360" t="inlineStr"/>
       <c r="AC360" t="inlineStr"/>
       <c r="AD360" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="361">
@@ -33338,7 +33338,7 @@
         <v>26315.79</v>
       </c>
       <c r="S361" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T361" t="inlineStr"/>
       <c r="U361" t="inlineStr"/>
@@ -33353,7 +33353,7 @@
       <c r="AB361" t="inlineStr"/>
       <c r="AC361" t="inlineStr"/>
       <c r="AD361" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="362">
@@ -33428,7 +33428,7 @@
         <v>81791.91</v>
       </c>
       <c r="S362" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="T362" t="inlineStr"/>
       <c r="U362" t="inlineStr"/>
@@ -33443,7 +33443,7 @@
       <c r="AB362" t="inlineStr"/>
       <c r="AC362" t="inlineStr"/>
       <c r="AD362" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
     </row>
     <row r="363">
@@ -33518,7 +33518,7 @@
         <v>26315.79</v>
       </c>
       <c r="S363" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T363" t="inlineStr"/>
       <c r="U363" t="inlineStr"/>
@@ -33533,7 +33533,7 @@
       <c r="AB363" t="inlineStr"/>
       <c r="AC363" t="inlineStr"/>
       <c r="AD363" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="364">
@@ -33608,7 +33608,7 @@
         <v>81791.91</v>
       </c>
       <c r="S364" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="T364" t="inlineStr"/>
       <c r="U364" t="inlineStr"/>
@@ -33623,7 +33623,7 @@
       <c r="AB364" t="inlineStr"/>
       <c r="AC364" t="inlineStr"/>
       <c r="AD364" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
     </row>
     <row r="365">
@@ -33698,7 +33698,7 @@
         <v>26315.79</v>
       </c>
       <c r="S365" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T365" t="inlineStr"/>
       <c r="U365" t="inlineStr"/>
@@ -33713,7 +33713,7 @@
       <c r="AB365" t="inlineStr"/>
       <c r="AC365" t="inlineStr"/>
       <c r="AD365" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="366">
@@ -33788,7 +33788,7 @@
         <v>75433.53</v>
       </c>
       <c r="S366" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T366" t="inlineStr"/>
       <c r="U366" t="inlineStr"/>
@@ -33803,7 +33803,7 @@
       <c r="AB366" t="inlineStr"/>
       <c r="AC366" t="inlineStr"/>
       <c r="AD366" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="367">
@@ -33878,7 +33878,7 @@
         <v>26315.79</v>
       </c>
       <c r="S367" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T367" t="inlineStr"/>
       <c r="U367" t="inlineStr"/>
@@ -33893,7 +33893,7 @@
       <c r="AB367" t="inlineStr"/>
       <c r="AC367" t="inlineStr"/>
       <c r="AD367" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="368">
@@ -33968,7 +33968,7 @@
         <v>75433.53</v>
       </c>
       <c r="S368" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T368" t="inlineStr"/>
       <c r="U368" t="inlineStr"/>
@@ -33983,7 +33983,7 @@
       <c r="AB368" t="inlineStr"/>
       <c r="AC368" t="inlineStr"/>
       <c r="AD368" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="369">
@@ -34058,7 +34058,7 @@
         <v>26315.79</v>
       </c>
       <c r="S369" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T369" t="inlineStr"/>
       <c r="U369" t="inlineStr"/>
@@ -34073,7 +34073,7 @@
       <c r="AB369" t="inlineStr"/>
       <c r="AC369" t="inlineStr"/>
       <c r="AD369" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="370">
@@ -34148,7 +34148,7 @@
         <v>81791.91</v>
       </c>
       <c r="S370" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="T370" t="inlineStr"/>
       <c r="U370" t="inlineStr"/>
@@ -34163,7 +34163,7 @@
       <c r="AB370" t="inlineStr"/>
       <c r="AC370" t="inlineStr"/>
       <c r="AD370" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
     </row>
     <row r="371">
@@ -34238,7 +34238,7 @@
         <v>26315.79</v>
       </c>
       <c r="S371" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T371" t="inlineStr"/>
       <c r="U371" t="inlineStr"/>
@@ -34253,7 +34253,7 @@
       <c r="AB371" t="inlineStr"/>
       <c r="AC371" t="inlineStr"/>
       <c r="AD371" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="372">
@@ -34328,7 +34328,7 @@
         <v>75433.53</v>
       </c>
       <c r="S372" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T372" t="inlineStr"/>
       <c r="U372" t="inlineStr"/>
@@ -34343,7 +34343,7 @@
       <c r="AB372" t="inlineStr"/>
       <c r="AC372" t="inlineStr"/>
       <c r="AD372" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="373">
@@ -34418,7 +34418,7 @@
         <v>26315.78</v>
       </c>
       <c r="S373" t="n">
-        <v>0</v>
+        <v>26315.78</v>
       </c>
       <c r="T373" t="inlineStr"/>
       <c r="U373" t="inlineStr"/>
@@ -34433,7 +34433,7 @@
       <c r="AB373" t="inlineStr"/>
       <c r="AC373" t="inlineStr"/>
       <c r="AD373" t="n">
-        <v>0</v>
+        <v>26315.78</v>
       </c>
     </row>
     <row r="374">
@@ -34508,7 +34508,7 @@
         <v>88150.28999999999</v>
       </c>
       <c r="S374" t="n">
-        <v>0</v>
+        <v>88150.28999999999</v>
       </c>
       <c r="T374" t="inlineStr"/>
       <c r="U374" t="inlineStr"/>
@@ -34523,7 +34523,7 @@
       <c r="AB374" t="inlineStr"/>
       <c r="AC374" t="inlineStr"/>
       <c r="AD374" t="n">
-        <v>0</v>
+        <v>88150.28999999999</v>
       </c>
     </row>
     <row r="375">
@@ -34598,7 +34598,7 @@
         <v>26315.79</v>
       </c>
       <c r="S375" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T375" t="inlineStr"/>
       <c r="U375" t="inlineStr"/>
@@ -34613,7 +34613,7 @@
       <c r="AB375" t="inlineStr"/>
       <c r="AC375" t="inlineStr"/>
       <c r="AD375" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="376">
@@ -34688,7 +34688,7 @@
         <v>81791.91</v>
       </c>
       <c r="S376" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="T376" t="inlineStr"/>
       <c r="U376" t="inlineStr"/>
@@ -34703,7 +34703,7 @@
       <c r="AB376" t="inlineStr"/>
       <c r="AC376" t="inlineStr"/>
       <c r="AD376" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
     </row>
     <row r="377">
@@ -34778,7 +34778,7 @@
         <v>26315.79</v>
       </c>
       <c r="S377" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T377" t="inlineStr"/>
       <c r="U377" t="inlineStr"/>
@@ -34793,7 +34793,7 @@
       <c r="AB377" t="inlineStr"/>
       <c r="AC377" t="inlineStr"/>
       <c r="AD377" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="378">
@@ -34868,7 +34868,7 @@
         <v>81791.91</v>
       </c>
       <c r="S378" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="T378" t="inlineStr"/>
       <c r="U378" t="inlineStr"/>
@@ -34883,7 +34883,7 @@
       <c r="AB378" t="inlineStr"/>
       <c r="AC378" t="inlineStr"/>
       <c r="AD378" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
     </row>
     <row r="379">
@@ -34958,7 +34958,7 @@
         <v>26315.79</v>
       </c>
       <c r="S379" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T379" t="inlineStr"/>
       <c r="U379" t="inlineStr"/>
@@ -34973,7 +34973,7 @@
       <c r="AB379" t="inlineStr"/>
       <c r="AC379" t="inlineStr"/>
       <c r="AD379" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="380">
@@ -35048,7 +35048,7 @@
         <v>75433.53</v>
       </c>
       <c r="S380" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T380" t="inlineStr"/>
       <c r="U380" t="inlineStr"/>
@@ -35063,7 +35063,7 @@
       <c r="AB380" t="inlineStr"/>
       <c r="AC380" t="inlineStr"/>
       <c r="AD380" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="381">
@@ -35138,7 +35138,7 @@
         <v>26315.79</v>
       </c>
       <c r="S381" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T381" t="inlineStr"/>
       <c r="U381" t="inlineStr"/>
@@ -35153,7 +35153,7 @@
       <c r="AB381" t="inlineStr"/>
       <c r="AC381" t="inlineStr"/>
       <c r="AD381" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="382">
@@ -35228,7 +35228,7 @@
         <v>88150.28999999999</v>
       </c>
       <c r="S382" t="n">
-        <v>0</v>
+        <v>88150.28999999999</v>
       </c>
       <c r="T382" t="inlineStr"/>
       <c r="U382" t="inlineStr"/>
@@ -35243,7 +35243,7 @@
       <c r="AB382" t="inlineStr"/>
       <c r="AC382" t="inlineStr"/>
       <c r="AD382" t="n">
-        <v>0</v>
+        <v>88150.28999999999</v>
       </c>
     </row>
     <row r="383">
@@ -35318,7 +35318,7 @@
         <v>26315.79</v>
       </c>
       <c r="S383" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T383" t="inlineStr"/>
       <c r="U383" t="inlineStr"/>
@@ -35333,7 +35333,7 @@
       <c r="AB383" t="inlineStr"/>
       <c r="AC383" t="inlineStr"/>
       <c r="AD383" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="384">
@@ -35408,7 +35408,7 @@
         <v>75433.53</v>
       </c>
       <c r="S384" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T384" t="inlineStr"/>
       <c r="U384" t="inlineStr"/>
@@ -35423,7 +35423,7 @@
       <c r="AB384" t="inlineStr"/>
       <c r="AC384" t="inlineStr"/>
       <c r="AD384" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="385">
@@ -35498,7 +35498,7 @@
         <v>26315.78</v>
       </c>
       <c r="S385" t="n">
-        <v>0</v>
+        <v>26315.78</v>
       </c>
       <c r="T385" t="inlineStr"/>
       <c r="U385" t="inlineStr"/>
@@ -35513,7 +35513,7 @@
       <c r="AB385" t="inlineStr"/>
       <c r="AC385" t="inlineStr"/>
       <c r="AD385" t="n">
-        <v>0</v>
+        <v>26315.78</v>
       </c>
     </row>
     <row r="386">
@@ -35588,7 +35588,7 @@
         <v>75433.53</v>
       </c>
       <c r="S386" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T386" t="inlineStr"/>
       <c r="U386" t="inlineStr"/>
@@ -35603,7 +35603,7 @@
       <c r="AB386" t="inlineStr"/>
       <c r="AC386" t="inlineStr"/>
       <c r="AD386" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="387">
@@ -35678,7 +35678,7 @@
         <v>26315.79</v>
       </c>
       <c r="S387" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T387" t="inlineStr"/>
       <c r="U387" t="inlineStr"/>
@@ -35693,7 +35693,7 @@
       <c r="AB387" t="inlineStr"/>
       <c r="AC387" t="inlineStr"/>
       <c r="AD387" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="388">
@@ -35768,7 +35768,7 @@
         <v>75433.53</v>
       </c>
       <c r="S388" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T388" t="inlineStr"/>
       <c r="U388" t="inlineStr"/>
@@ -35783,7 +35783,7 @@
       <c r="AB388" t="inlineStr"/>
       <c r="AC388" t="inlineStr"/>
       <c r="AD388" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="389">
@@ -35858,7 +35858,7 @@
         <v>26315.79</v>
       </c>
       <c r="S389" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T389" t="inlineStr"/>
       <c r="U389" t="inlineStr"/>
@@ -35873,7 +35873,7 @@
       <c r="AB389" t="inlineStr"/>
       <c r="AC389" t="inlineStr"/>
       <c r="AD389" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="390">
@@ -35948,7 +35948,7 @@
         <v>81791.91</v>
       </c>
       <c r="S390" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
       <c r="T390" t="inlineStr"/>
       <c r="U390" t="inlineStr"/>
@@ -35963,7 +35963,7 @@
       <c r="AB390" t="inlineStr"/>
       <c r="AC390" t="inlineStr"/>
       <c r="AD390" t="n">
-        <v>0</v>
+        <v>81791.91</v>
       </c>
     </row>
     <row r="391">
@@ -36038,7 +36038,7 @@
         <v>26315.79</v>
       </c>
       <c r="S391" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
       <c r="T391" t="inlineStr"/>
       <c r="U391" t="inlineStr"/>
@@ -36053,7 +36053,7 @@
       <c r="AB391" t="inlineStr"/>
       <c r="AC391" t="inlineStr"/>
       <c r="AD391" t="n">
-        <v>0</v>
+        <v>26315.79</v>
       </c>
     </row>
     <row r="392">
@@ -36128,7 +36128,7 @@
         <v>75433.53</v>
       </c>
       <c r="S392" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
       <c r="T392" t="inlineStr"/>
       <c r="U392" t="inlineStr"/>
@@ -36143,7 +36143,7 @@
       <c r="AB392" t="inlineStr"/>
       <c r="AC392" t="inlineStr"/>
       <c r="AD392" t="n">
-        <v>0</v>
+        <v>75433.53</v>
       </c>
     </row>
     <row r="393">
@@ -36406,7 +36406,7 @@
         <v>1500000</v>
       </c>
       <c r="S395" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="T395" t="inlineStr"/>
       <c r="U395" t="inlineStr"/>
@@ -36421,7 +36421,7 @@
       <c r="AB395" t="inlineStr"/>
       <c r="AC395" t="inlineStr"/>
       <c r="AD395" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="396">
@@ -36496,7 +36496,7 @@
         <v>550000</v>
       </c>
       <c r="S396" t="n">
-        <v>0</v>
+        <v>550000</v>
       </c>
       <c r="T396" t="inlineStr"/>
       <c r="U396" t="inlineStr"/>
@@ -36511,7 +36511,7 @@
       <c r="AB396" t="inlineStr"/>
       <c r="AC396" t="inlineStr"/>
       <c r="AD396" t="n">
-        <v>0</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="397">
@@ -37810,6 +37810,288 @@
         <v>0</v>
       </c>
     </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B411" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C411" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>27</v>
+      </c>
+      <c r="F411" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>37</v>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K411" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M411" t="n">
+        <v>80</v>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q411" t="n">
+        <v>9418.49</v>
+      </c>
+      <c r="R411" t="n">
+        <v>0</v>
+      </c>
+      <c r="S411" t="n">
+        <v>0</v>
+      </c>
+      <c r="T411" t="inlineStr"/>
+      <c r="U411" t="inlineStr"/>
+      <c r="V411" t="n">
+        <v>0</v>
+      </c>
+      <c r="W411" t="inlineStr"/>
+      <c r="X411" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y411" t="inlineStr"/>
+      <c r="Z411" t="n">
+        <v>9418.49</v>
+      </c>
+      <c r="AA411" t="inlineStr"/>
+      <c r="AB411" t="inlineStr"/>
+      <c r="AC411" t="inlineStr"/>
+      <c r="AD411" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B412" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C412" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>28</v>
+      </c>
+      <c r="F412" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>37</v>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K412" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M412" t="n">
+        <v>80</v>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q412" t="n">
+        <v>29040.66</v>
+      </c>
+      <c r="R412" t="n">
+        <v>0</v>
+      </c>
+      <c r="S412" t="n">
+        <v>0</v>
+      </c>
+      <c r="T412" t="inlineStr"/>
+      <c r="U412" t="inlineStr"/>
+      <c r="V412" t="n">
+        <v>0</v>
+      </c>
+      <c r="W412" t="inlineStr"/>
+      <c r="X412" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y412" t="inlineStr"/>
+      <c r="Z412" t="n">
+        <v>29040.66</v>
+      </c>
+      <c r="AA412" t="inlineStr"/>
+      <c r="AB412" t="inlineStr"/>
+      <c r="AC412" t="inlineStr"/>
+      <c r="AD412" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B413" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C413" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>29</v>
+      </c>
+      <c r="F413" s="2" t="n">
+        <v>46182</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>37</v>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K413" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M413" t="n">
+        <v>80</v>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q413" t="n">
+        <v>72267.23</v>
+      </c>
+      <c r="R413" t="n">
+        <v>0</v>
+      </c>
+      <c r="S413" t="n">
+        <v>0</v>
+      </c>
+      <c r="T413" t="inlineStr"/>
+      <c r="U413" t="inlineStr"/>
+      <c r="V413" t="n">
+        <v>0</v>
+      </c>
+      <c r="W413" t="inlineStr"/>
+      <c r="X413" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y413" t="inlineStr"/>
+      <c r="Z413" t="n">
+        <v>72267.23</v>
+      </c>
+      <c r="AA413" t="inlineStr"/>
+      <c r="AB413" t="inlineStr"/>
+      <c r="AC413" t="inlineStr"/>
+      <c r="AD413" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD413"/>
+  <dimension ref="A1:AD427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13101,10 +13101,10 @@
         <v>5891.4</v>
       </c>
       <c r="R140" t="n">
-        <v>3780.28</v>
+        <v>4835.94</v>
       </c>
       <c r="S140" t="n">
-        <v>3598.83</v>
+        <v>4603.82</v>
       </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
@@ -13123,7 +13123,7 @@
       <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="n">
-        <v>3598.83</v>
+        <v>4603.82</v>
       </c>
     </row>
     <row r="141">
@@ -13756,13 +13756,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
+        <v>179052.97</v>
+      </c>
+      <c r="R147" t="n">
         <v>162683.18</v>
       </c>
-      <c r="R147" t="n">
-        <v>120750.72</v>
-      </c>
       <c r="S147" t="n">
-        <v>101672.09</v>
+        <v>136979.22</v>
       </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
@@ -13775,13 +13775,13 @@
       </c>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="n">
-        <v>162683.18</v>
+        <v>179052.97</v>
       </c>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="n">
-        <v>101672.09</v>
+        <v>136979.22</v>
       </c>
     </row>
     <row r="148">
@@ -13853,10 +13853,10 @@
         <v>9641.92</v>
       </c>
       <c r="R148" t="n">
-        <v>3755.73</v>
+        <v>6641.91</v>
       </c>
       <c r="S148" t="n">
-        <v>3575.46</v>
+        <v>6152.99</v>
       </c>
       <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr"/>
@@ -13875,7 +13875,7 @@
       <c r="AB148" t="inlineStr"/>
       <c r="AC148" t="inlineStr"/>
       <c r="AD148" t="n">
-        <v>3575.46</v>
+        <v>6152.99</v>
       </c>
     </row>
     <row r="149">
@@ -13947,7 +13947,7 @@
         <v>58000.01</v>
       </c>
       <c r="R149" t="n">
-        <v>37583.73</v>
+        <v>43144.66</v>
       </c>
       <c r="S149" t="n">
         <v>34563.3</v>
@@ -14038,13 +14038,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>327810.84</v>
+        <v>415793.46</v>
       </c>
       <c r="R150" t="n">
-        <v>314764.05</v>
+        <v>385355.31</v>
       </c>
       <c r="S150" t="n">
-        <v>203337.81</v>
+        <v>260913.96</v>
       </c>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
@@ -14057,13 +14057,13 @@
       </c>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="n">
-        <v>327810.84</v>
+        <v>415793.46</v>
       </c>
       <c r="AA150" t="inlineStr"/>
       <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr"/>
       <c r="AD150" t="n">
-        <v>203337.81</v>
+        <v>260913.96</v>
       </c>
     </row>
     <row r="151">
@@ -14132,10 +14132,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>942502.41</v>
+        <v>1181540.53</v>
       </c>
       <c r="R151" t="n">
-        <v>899921.0600000001</v>
+        <v>1129581.26</v>
       </c>
       <c r="S151" t="n">
         <v>749422.04</v>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="n">
-        <v>942502.41</v>
+        <v>1181540.53</v>
       </c>
       <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="inlineStr"/>
@@ -14226,10 +14226,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>66200</v>
+        <v>78802.64999999999</v>
       </c>
       <c r="R152" t="n">
-        <v>39719.26</v>
+        <v>71246.27</v>
       </c>
       <c r="S152" t="n">
         <v>38270</v>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="n">
-        <v>66200</v>
+        <v>78802.64999999999</v>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
@@ -14320,10 +14320,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>7400.03</v>
+        <v>7560.85</v>
       </c>
       <c r="R153" t="n">
-        <v>5449.49</v>
+        <v>7560.81</v>
       </c>
       <c r="S153" t="n">
         <v>5275.1</v>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="n">
-        <v>7400.03</v>
+        <v>7560.85</v>
       </c>
       <c r="AA153" t="inlineStr"/>
       <c r="AB153" t="inlineStr"/>
@@ -14414,10 +14414,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>214322.25</v>
+        <v>275791.53</v>
       </c>
       <c r="R154" t="n">
-        <v>167580.85</v>
+        <v>228954.73</v>
       </c>
       <c r="S154" t="n">
         <v>150122.64</v>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="n">
-        <v>214322.25</v>
+        <v>275791.53</v>
       </c>
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="inlineStr"/>
@@ -14508,7 +14508,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>8998606.85</v>
+        <v>14718780.63</v>
       </c>
       <c r="R155" t="n">
         <v>3153036.27</v>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="n">
-        <v>8998606.85</v>
+        <v>14718780.63</v>
       </c>
       <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="inlineStr"/>
@@ -14605,10 +14605,10 @@
         <v>45000</v>
       </c>
       <c r="R156" t="n">
-        <v>13209.7</v>
+        <v>17714.4</v>
       </c>
       <c r="S156" t="n">
-        <v>13209.7</v>
+        <v>17714.4</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14627,7 +14627,7 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>13209.7</v>
+        <v>17714.4</v>
       </c>
     </row>
     <row r="157">
@@ -17699,7 +17699,7 @@
         <v>32800</v>
       </c>
       <c r="R189" t="n">
-        <v>24403.98</v>
+        <v>30912.24</v>
       </c>
       <c r="S189" t="n">
         <v>21131.31</v>
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>2559351.59</v>
+        <v>8193722.76</v>
       </c>
       <c r="R200" t="n">
         <v>2349004.86</v>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="Y200" t="inlineStr"/>
       <c r="Z200" t="n">
-        <v>2559351.59</v>
+        <v>8193722.76</v>
       </c>
       <c r="AA200" t="inlineStr"/>
       <c r="AB200" t="inlineStr"/>
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>38974.9</v>
+        <v>124777.51</v>
       </c>
       <c r="R201" t="n">
         <v>35771.66</v>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="Y201" t="inlineStr"/>
       <c r="Z201" t="n">
-        <v>38974.9</v>
+        <v>124777.51</v>
       </c>
       <c r="AA201" t="inlineStr"/>
       <c r="AB201" t="inlineStr"/>
@@ -18914,7 +18914,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>1499893.53</v>
+        <v>6076032.55</v>
       </c>
       <c r="R202" t="n">
         <v>1499893.53</v>
@@ -18933,7 +18933,7 @@
       </c>
       <c r="Y202" t="inlineStr"/>
       <c r="Z202" t="n">
-        <v>1499893.53</v>
+        <v>6076032.55</v>
       </c>
       <c r="AA202" t="inlineStr"/>
       <c r="AB202" t="inlineStr"/>
@@ -19008,10 +19008,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>374973.38</v>
+        <v>1519008.14</v>
       </c>
       <c r="R203" t="n">
-        <v>374973.38</v>
+        <v>614585.9300000001</v>
       </c>
       <c r="S203" t="n">
         <v>370473.7</v>
@@ -19027,7 +19027,7 @@
       </c>
       <c r="Y203" t="inlineStr"/>
       <c r="Z203" t="n">
-        <v>374973.38</v>
+        <v>1519008.14</v>
       </c>
       <c r="AA203" t="inlineStr"/>
       <c r="AB203" t="inlineStr"/>
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>3990374.93</v>
+        <v>4743053.83</v>
       </c>
       <c r="R204" t="n">
         <v>1288879.4</v>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="Y204" t="inlineStr"/>
       <c r="Z204" t="n">
-        <v>3990374.93</v>
+        <v>4743053.83</v>
       </c>
       <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="inlineStr"/>
@@ -22135,10 +22135,10 @@
         <v>60682.6</v>
       </c>
       <c r="R237" t="n">
-        <v>0</v>
+        <v>60682.6</v>
       </c>
       <c r="S237" t="n">
-        <v>0</v>
+        <v>60682.6</v>
       </c>
       <c r="T237" t="inlineStr"/>
       <c r="U237" t="inlineStr"/>
@@ -22153,7 +22153,7 @@
       <c r="AB237" t="inlineStr"/>
       <c r="AC237" t="inlineStr"/>
       <c r="AD237" t="n">
-        <v>0</v>
+        <v>60682.6</v>
       </c>
     </row>
     <row r="238">
@@ -26295,10 +26295,10 @@
         <v>15000000</v>
       </c>
       <c r="R283" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
       <c r="S283" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
       <c r="T283" t="inlineStr"/>
       <c r="U283" t="inlineStr"/>
@@ -26313,7 +26313,7 @@
       <c r="AB283" t="inlineStr"/>
       <c r="AC283" t="inlineStr"/>
       <c r="AD283" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
     </row>
     <row r="284">
@@ -26749,10 +26749,10 @@
         <v>4000</v>
       </c>
       <c r="R288" t="n">
-        <v>0</v>
+        <v>726.75</v>
       </c>
       <c r="S288" t="n">
-        <v>0</v>
+        <v>726.75</v>
       </c>
       <c r="T288" t="inlineStr"/>
       <c r="U288" t="inlineStr"/>
@@ -26767,7 +26767,7 @@
       <c r="AB288" t="inlineStr"/>
       <c r="AC288" t="inlineStr"/>
       <c r="AD288" t="n">
-        <v>0</v>
+        <v>726.75</v>
       </c>
     </row>
     <row r="289">
@@ -36215,10 +36215,10 @@
         <v>32739.58</v>
       </c>
       <c r="R393" t="n">
-        <v>0</v>
+        <v>32656.87</v>
       </c>
       <c r="S393" t="n">
-        <v>0</v>
+        <v>27497.08</v>
       </c>
       <c r="T393" t="inlineStr"/>
       <c r="U393" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       <c r="AB393" t="inlineStr"/>
       <c r="AC393" t="inlineStr"/>
       <c r="AD393" t="n">
-        <v>0</v>
+        <v>27497.08</v>
       </c>
     </row>
     <row r="394">
@@ -36309,10 +36309,10 @@
         <v>9462.459999999999</v>
       </c>
       <c r="R394" t="n">
-        <v>0</v>
+        <v>9462.459999999999</v>
       </c>
       <c r="S394" t="n">
-        <v>0</v>
+        <v>7998.63</v>
       </c>
       <c r="T394" t="inlineStr"/>
       <c r="U394" t="inlineStr"/>
@@ -36331,7 +36331,7 @@
       <c r="AB394" t="inlineStr"/>
       <c r="AC394" t="inlineStr"/>
       <c r="AD394" t="n">
-        <v>0</v>
+        <v>7998.63</v>
       </c>
     </row>
     <row r="395">
@@ -37879,7 +37879,7 @@
         <v>9418.49</v>
       </c>
       <c r="R411" t="n">
-        <v>0</v>
+        <v>8618.49</v>
       </c>
       <c r="S411" t="n">
         <v>0</v>
@@ -37973,7 +37973,7 @@
         <v>29040.66</v>
       </c>
       <c r="R412" t="n">
-        <v>0</v>
+        <v>28840.66</v>
       </c>
       <c r="S412" t="n">
         <v>0</v>
@@ -38067,7 +38067,7 @@
         <v>72267.23</v>
       </c>
       <c r="R413" t="n">
-        <v>0</v>
+        <v>72067.23</v>
       </c>
       <c r="S413" t="n">
         <v>0</v>
@@ -38092,6 +38092,1298 @@
         <v>0</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B414" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C414" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>244</v>
+      </c>
+      <c r="F414" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>CONCORRENCIA</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>51</v>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K414" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M414" t="n">
+        <v>80</v>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>42.875.401/0001-35</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>ABRIL CONSTRUCOES E SERVICOS LTDA</t>
+        </is>
+      </c>
+      <c r="Q414" t="n">
+        <v>0</v>
+      </c>
+      <c r="R414" t="n">
+        <v>0</v>
+      </c>
+      <c r="S414" t="n">
+        <v>0</v>
+      </c>
+      <c r="T414" t="inlineStr"/>
+      <c r="U414" t="inlineStr"/>
+      <c r="V414" t="n">
+        <v>0</v>
+      </c>
+      <c r="W414" t="inlineStr"/>
+      <c r="X414" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y414" t="inlineStr"/>
+      <c r="Z414" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA414" t="inlineStr"/>
+      <c r="AB414" t="inlineStr"/>
+      <c r="AC414" t="inlineStr"/>
+      <c r="AD414" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B415" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C415" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>245</v>
+      </c>
+      <c r="F415" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>CONCORRENCIA</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>51</v>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K415" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M415" t="n">
+        <v>80</v>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>42.875.401/0001-35</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>ABRIL CONSTRUCOES E SERVICOS LTDA</t>
+        </is>
+      </c>
+      <c r="Q415" t="n">
+        <v>119678.32</v>
+      </c>
+      <c r="R415" t="n">
+        <v>0</v>
+      </c>
+      <c r="S415" t="n">
+        <v>0</v>
+      </c>
+      <c r="T415" t="inlineStr"/>
+      <c r="U415" t="inlineStr"/>
+      <c r="V415" t="n">
+        <v>0</v>
+      </c>
+      <c r="W415" t="inlineStr"/>
+      <c r="X415" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y415" t="inlineStr"/>
+      <c r="Z415" t="n">
+        <v>119678.32</v>
+      </c>
+      <c r="AA415" t="inlineStr"/>
+      <c r="AB415" t="inlineStr"/>
+      <c r="AC415" t="inlineStr"/>
+      <c r="AD415" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B416" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C416" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>248</v>
+      </c>
+      <c r="F416" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>CONCORRENCIA</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>51</v>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K416" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M416" t="n">
+        <v>80</v>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>25.955.246/0001-48</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>IPE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="Q416" t="n">
+        <v>6719082.76</v>
+      </c>
+      <c r="R416" t="n">
+        <v>0</v>
+      </c>
+      <c r="S416" t="n">
+        <v>0</v>
+      </c>
+      <c r="T416" t="inlineStr"/>
+      <c r="U416" t="inlineStr"/>
+      <c r="V416" t="n">
+        <v>0</v>
+      </c>
+      <c r="W416" t="inlineStr"/>
+      <c r="X416" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y416" t="inlineStr"/>
+      <c r="Z416" t="n">
+        <v>6719082.76</v>
+      </c>
+      <c r="AA416" t="inlineStr"/>
+      <c r="AB416" t="inlineStr"/>
+      <c r="AC416" t="inlineStr"/>
+      <c r="AD416" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B417" t="n">
+        <v>9456622</v>
+      </c>
+      <c r="C417" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>1376</v>
+      </c>
+      <c r="F417" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>37</v>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K417" t="n">
+        <v>3704</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
+        </is>
+      </c>
+      <c r="M417" t="n">
+        <v>80</v>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q417" t="n">
+        <v>23010.54</v>
+      </c>
+      <c r="R417" t="n">
+        <v>0</v>
+      </c>
+      <c r="S417" t="n">
+        <v>0</v>
+      </c>
+      <c r="T417" t="inlineStr"/>
+      <c r="U417" t="inlineStr"/>
+      <c r="V417" t="inlineStr"/>
+      <c r="W417" t="inlineStr"/>
+      <c r="X417" t="inlineStr"/>
+      <c r="Y417" t="inlineStr"/>
+      <c r="Z417" t="n">
+        <v>23010.54</v>
+      </c>
+      <c r="AA417" t="inlineStr"/>
+      <c r="AB417" t="inlineStr"/>
+      <c r="AC417" t="inlineStr"/>
+      <c r="AD417" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B418" t="n">
+        <v>9456622</v>
+      </c>
+      <c r="C418" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>1377</v>
+      </c>
+      <c r="F418" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>37</v>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K418" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M418" t="n">
+        <v>80</v>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q418" t="n">
+        <v>1160.87</v>
+      </c>
+      <c r="R418" t="n">
+        <v>0</v>
+      </c>
+      <c r="S418" t="n">
+        <v>0</v>
+      </c>
+      <c r="T418" t="inlineStr"/>
+      <c r="U418" t="inlineStr"/>
+      <c r="V418" t="inlineStr"/>
+      <c r="W418" t="inlineStr"/>
+      <c r="X418" t="inlineStr"/>
+      <c r="Y418" t="inlineStr"/>
+      <c r="Z418" t="n">
+        <v>1160.87</v>
+      </c>
+      <c r="AA418" t="inlineStr"/>
+      <c r="AB418" t="inlineStr"/>
+      <c r="AC418" t="inlineStr"/>
+      <c r="AD418" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B419" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C419" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>1378</v>
+      </c>
+      <c r="F419" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>37</v>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K419" t="n">
+        <v>3704</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
+        </is>
+      </c>
+      <c r="M419" t="n">
+        <v>80</v>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q419" t="n">
+        <v>27770.9</v>
+      </c>
+      <c r="R419" t="n">
+        <v>0</v>
+      </c>
+      <c r="S419" t="n">
+        <v>0</v>
+      </c>
+      <c r="T419" t="inlineStr"/>
+      <c r="U419" t="inlineStr"/>
+      <c r="V419" t="inlineStr"/>
+      <c r="W419" t="inlineStr"/>
+      <c r="X419" t="inlineStr"/>
+      <c r="Y419" t="inlineStr"/>
+      <c r="Z419" t="n">
+        <v>27770.9</v>
+      </c>
+      <c r="AA419" t="inlineStr"/>
+      <c r="AB419" t="inlineStr"/>
+      <c r="AC419" t="inlineStr"/>
+      <c r="AD419" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B420" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C420" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>1391</v>
+      </c>
+      <c r="F420" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>37</v>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K420" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M420" t="n">
+        <v>80</v>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q420" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="R420" t="n">
+        <v>0</v>
+      </c>
+      <c r="S420" t="n">
+        <v>0</v>
+      </c>
+      <c r="T420" t="inlineStr"/>
+      <c r="U420" t="inlineStr"/>
+      <c r="V420" t="inlineStr"/>
+      <c r="W420" t="inlineStr"/>
+      <c r="X420" t="inlineStr"/>
+      <c r="Y420" t="inlineStr"/>
+      <c r="Z420" t="n">
+        <v>96.58</v>
+      </c>
+      <c r="AA420" t="inlineStr"/>
+      <c r="AB420" t="inlineStr"/>
+      <c r="AC420" t="inlineStr"/>
+      <c r="AD420" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B421" t="n">
+        <v>9456622</v>
+      </c>
+      <c r="C421" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>1392</v>
+      </c>
+      <c r="F421" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I421" t="n">
+        <v>37</v>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K421" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M421" t="n">
+        <v>80</v>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q421" t="n">
+        <v>979.04</v>
+      </c>
+      <c r="R421" t="n">
+        <v>0</v>
+      </c>
+      <c r="S421" t="n">
+        <v>0</v>
+      </c>
+      <c r="T421" t="inlineStr"/>
+      <c r="U421" t="inlineStr"/>
+      <c r="V421" t="inlineStr"/>
+      <c r="W421" t="inlineStr"/>
+      <c r="X421" t="inlineStr"/>
+      <c r="Y421" t="inlineStr"/>
+      <c r="Z421" t="n">
+        <v>979.04</v>
+      </c>
+      <c r="AA421" t="inlineStr"/>
+      <c r="AB421" t="inlineStr"/>
+      <c r="AC421" t="inlineStr"/>
+      <c r="AD421" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B422" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C422" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>1395</v>
+      </c>
+      <c r="F422" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>37</v>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K422" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M422" t="n">
+        <v>80</v>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q422" t="n">
+        <v>490.09</v>
+      </c>
+      <c r="R422" t="n">
+        <v>0</v>
+      </c>
+      <c r="S422" t="n">
+        <v>0</v>
+      </c>
+      <c r="T422" t="inlineStr"/>
+      <c r="U422" t="inlineStr"/>
+      <c r="V422" t="inlineStr"/>
+      <c r="W422" t="inlineStr"/>
+      <c r="X422" t="inlineStr"/>
+      <c r="Y422" t="inlineStr"/>
+      <c r="Z422" t="n">
+        <v>490.09</v>
+      </c>
+      <c r="AA422" t="inlineStr"/>
+      <c r="AB422" t="inlineStr"/>
+      <c r="AC422" t="inlineStr"/>
+      <c r="AD422" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B423" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C423" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>249</v>
+      </c>
+      <c r="F423" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I423" t="n">
+        <v>93</v>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K423" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M423" t="n">
+        <v>80</v>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q423" t="n">
+        <v>295000</v>
+      </c>
+      <c r="R423" t="n">
+        <v>0</v>
+      </c>
+      <c r="S423" t="n">
+        <v>0</v>
+      </c>
+      <c r="T423" t="inlineStr"/>
+      <c r="U423" t="inlineStr"/>
+      <c r="V423" t="n">
+        <v>0</v>
+      </c>
+      <c r="W423" t="inlineStr"/>
+      <c r="X423" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y423" t="inlineStr"/>
+      <c r="Z423" t="n">
+        <v>295000</v>
+      </c>
+      <c r="AA423" t="inlineStr"/>
+      <c r="AB423" t="inlineStr"/>
+      <c r="AC423" t="inlineStr"/>
+      <c r="AD423" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B424" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C424" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>250</v>
+      </c>
+      <c r="F424" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I424" t="n">
+        <v>93</v>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K424" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M424" t="n">
+        <v>80</v>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q424" t="n">
+        <v>35000</v>
+      </c>
+      <c r="R424" t="n">
+        <v>0</v>
+      </c>
+      <c r="S424" t="n">
+        <v>0</v>
+      </c>
+      <c r="T424" t="inlineStr"/>
+      <c r="U424" t="inlineStr"/>
+      <c r="V424" t="n">
+        <v>0</v>
+      </c>
+      <c r="W424" t="inlineStr"/>
+      <c r="X424" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y424" t="inlineStr"/>
+      <c r="Z424" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AA424" t="inlineStr"/>
+      <c r="AB424" t="inlineStr"/>
+      <c r="AC424" t="inlineStr"/>
+      <c r="AD424" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B425" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C425" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>251</v>
+      </c>
+      <c r="F425" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>2301762 000027/2025</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>CONCORRENCIA - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I425" t="n">
+        <v>51</v>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K425" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M425" t="n">
+        <v>80</v>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>66.418.765/0001-54</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>CONSTRUTORA CENTRO LESTE ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="Q425" t="n">
+        <v>14124998.39</v>
+      </c>
+      <c r="R425" t="n">
+        <v>0</v>
+      </c>
+      <c r="S425" t="n">
+        <v>0</v>
+      </c>
+      <c r="T425" t="inlineStr"/>
+      <c r="U425" t="inlineStr"/>
+      <c r="V425" t="n">
+        <v>0</v>
+      </c>
+      <c r="W425" t="inlineStr"/>
+      <c r="X425" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y425" t="inlineStr"/>
+      <c r="Z425" t="n">
+        <v>14124998.39</v>
+      </c>
+      <c r="AA425" t="inlineStr"/>
+      <c r="AB425" t="inlineStr"/>
+      <c r="AC425" t="inlineStr"/>
+      <c r="AD425" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B426" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C426" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>252</v>
+      </c>
+      <c r="F426" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I426" t="n">
+        <v>51</v>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K426" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M426" t="n">
+        <v>80</v>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q426" t="n">
+        <v>3648519</v>
+      </c>
+      <c r="R426" t="n">
+        <v>0</v>
+      </c>
+      <c r="S426" t="n">
+        <v>0</v>
+      </c>
+      <c r="T426" t="inlineStr"/>
+      <c r="U426" t="inlineStr"/>
+      <c r="V426" t="n">
+        <v>0</v>
+      </c>
+      <c r="W426" t="inlineStr"/>
+      <c r="X426" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y426" t="inlineStr"/>
+      <c r="Z426" t="n">
+        <v>3648519</v>
+      </c>
+      <c r="AA426" t="inlineStr"/>
+      <c r="AB426" t="inlineStr"/>
+      <c r="AC426" t="inlineStr"/>
+      <c r="AD426" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B427" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C427" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>253</v>
+      </c>
+      <c r="F427" s="2" t="n">
+        <v>46189</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I427" t="n">
+        <v>51</v>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K427" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M427" t="n">
+        <v>80</v>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q427" t="n">
+        <v>380415.6</v>
+      </c>
+      <c r="R427" t="n">
+        <v>0</v>
+      </c>
+      <c r="S427" t="n">
+        <v>0</v>
+      </c>
+      <c r="T427" t="inlineStr"/>
+      <c r="U427" t="inlineStr"/>
+      <c r="V427" t="n">
+        <v>0</v>
+      </c>
+      <c r="W427" t="inlineStr"/>
+      <c r="X427" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y427" t="inlineStr"/>
+      <c r="Z427" t="n">
+        <v>380415.6</v>
+      </c>
+      <c r="AA427" t="inlineStr"/>
+      <c r="AB427" t="inlineStr"/>
+      <c r="AC427" t="inlineStr"/>
+      <c r="AD427" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD427"/>
+  <dimension ref="A1:AD453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13950,7 +13950,7 @@
         <v>43144.66</v>
       </c>
       <c r="S149" t="n">
-        <v>34563.3</v>
+        <v>38117.53</v>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
@@ -13969,7 +13969,7 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr"/>
       <c r="AD149" t="n">
-        <v>34563.3</v>
+        <v>38117.53</v>
       </c>
     </row>
     <row r="150">
@@ -14138,7 +14138,7 @@
         <v>1129581.26</v>
       </c>
       <c r="S151" t="n">
-        <v>749422.04</v>
+        <v>942258.29</v>
       </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
@@ -14157,7 +14157,7 @@
       <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="n">
-        <v>749422.04</v>
+        <v>942258.29</v>
       </c>
     </row>
     <row r="152">
@@ -14232,7 +14232,7 @@
         <v>71246.27</v>
       </c>
       <c r="S152" t="n">
-        <v>38270</v>
+        <v>66180.75</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
@@ -14251,7 +14251,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="n">
-        <v>38270</v>
+        <v>66180.75</v>
       </c>
     </row>
     <row r="153">
@@ -14326,7 +14326,7 @@
         <v>7560.81</v>
       </c>
       <c r="S153" t="n">
-        <v>5275.1</v>
+        <v>7285.08</v>
       </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
@@ -14345,7 +14345,7 @@
       <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="n">
-        <v>5275.1</v>
+        <v>7285.08</v>
       </c>
     </row>
     <row r="154">
@@ -14420,7 +14420,7 @@
         <v>228954.73</v>
       </c>
       <c r="S154" t="n">
-        <v>150122.64</v>
+        <v>201799.44</v>
       </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
@@ -14439,7 +14439,7 @@
       <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr"/>
       <c r="AD154" t="n">
-        <v>150122.64</v>
+        <v>201799.44</v>
       </c>
     </row>
     <row r="155">
@@ -14508,10 +14508,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>14718780.63</v>
+        <v>33466718.46</v>
       </c>
       <c r="R155" t="n">
-        <v>3153036.27</v>
+        <v>4653543.42</v>
       </c>
       <c r="S155" t="n">
         <v>3115199.85</v>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="n">
-        <v>14718780.63</v>
+        <v>33466718.46</v>
       </c>
       <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="inlineStr"/>
@@ -14605,10 +14605,10 @@
         <v>45000</v>
       </c>
       <c r="R156" t="n">
-        <v>17714.4</v>
+        <v>17852.2</v>
       </c>
       <c r="S156" t="n">
-        <v>17714.4</v>
+        <v>17852.2</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14627,7 +14627,7 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>17714.4</v>
+        <v>17852.2</v>
       </c>
     </row>
     <row r="157">
@@ -16105,7 +16105,7 @@
         <v>11000</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>3929.86</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -16199,10 +16199,10 @@
         <v>67763</v>
       </c>
       <c r="R173" t="n">
-        <v>3380.8</v>
+        <v>6321.4</v>
       </c>
       <c r="S173" t="n">
-        <v>3742.8</v>
+        <v>6683.4</v>
       </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr"/>
       <c r="AD173" t="n">
-        <v>3742.8</v>
+        <v>6683.4</v>
       </c>
     </row>
     <row r="174">
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>7602.33</v>
+        <v>9112.059999999999</v>
       </c>
       <c r="R175" t="n">
         <v>7602.3</v>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="n">
-        <v>7602.33</v>
+        <v>9112.059999999999</v>
       </c>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr"/>
@@ -16756,7 +16756,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>5781.1</v>
+        <v>7364.59</v>
       </c>
       <c r="R179" t="n">
         <v>5781.07</v>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="n">
-        <v>5781.1</v>
+        <v>7364.59</v>
       </c>
       <c r="AA179" t="inlineStr"/>
       <c r="AB179" t="inlineStr"/>
@@ -17041,7 +17041,7 @@
         <v>17683.8</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>316.2</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -17132,7 +17132,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>489186</v>
+        <v>618435.35</v>
       </c>
       <c r="R183" t="n">
         <v>489138.54</v>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="n">
-        <v>489186</v>
+        <v>618435.35</v>
       </c>
       <c r="AA183" t="inlineStr"/>
       <c r="AB183" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>271448.09</v>
+        <v>348827.24</v>
       </c>
       <c r="R184" t="n">
         <v>271408.09</v>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="n">
-        <v>271448.09</v>
+        <v>348827.24</v>
       </c>
       <c r="AA184" t="inlineStr"/>
       <c r="AB184" t="inlineStr"/>
@@ -17320,7 +17320,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>1109262.91</v>
+        <v>1396844.69</v>
       </c>
       <c r="R185" t="n">
         <v>1109258.91</v>
@@ -17339,7 +17339,7 @@
       </c>
       <c r="Y185" t="inlineStr"/>
       <c r="Z185" t="n">
-        <v>1109262.91</v>
+        <v>1396844.69</v>
       </c>
       <c r="AA185" t="inlineStr"/>
       <c r="AB185" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>1010484.55</v>
+        <v>1287702.95</v>
       </c>
       <c r="R186" t="n">
         <v>1010482.55</v>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="Y186" t="inlineStr"/>
       <c r="Z186" t="n">
-        <v>1010484.55</v>
+        <v>1287702.95</v>
       </c>
       <c r="AA186" t="inlineStr"/>
       <c r="AB186" t="inlineStr"/>
@@ -17508,7 +17508,7 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>777688.27</v>
+        <v>960793.26</v>
       </c>
       <c r="R187" t="n">
         <v>777684.27</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Y187" t="inlineStr"/>
       <c r="Z187" t="n">
-        <v>777688.27</v>
+        <v>960793.26</v>
       </c>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr"/>
@@ -17602,7 +17602,7 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>212903.3</v>
+        <v>267391.5</v>
       </c>
       <c r="R188" t="n">
         <v>212899.3</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="n">
-        <v>212903.3</v>
+        <v>267391.5</v>
       </c>
       <c r="AA188" t="inlineStr"/>
       <c r="AB188" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
         <v>30912.24</v>
       </c>
       <c r="S189" t="n">
-        <v>21131.31</v>
+        <v>23814.69</v>
       </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
@@ -17721,7 +17721,7 @@
       <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr"/>
       <c r="AD189" t="n">
-        <v>21131.31</v>
+        <v>23814.69</v>
       </c>
     </row>
     <row r="190">
@@ -18444,7 +18444,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>1245.84</v>
+        <v>1720.89</v>
       </c>
       <c r="R197" t="n">
         <v>1245.81</v>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="Y197" t="inlineStr"/>
       <c r="Z197" t="n">
-        <v>1245.84</v>
+        <v>1720.89</v>
       </c>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr"/>
@@ -18538,7 +18538,7 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>51565.56</v>
+        <v>68798.59</v>
       </c>
       <c r="R198" t="n">
         <v>51565.51</v>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="Y198" t="inlineStr"/>
       <c r="Z198" t="n">
-        <v>51565.56</v>
+        <v>68798.59</v>
       </c>
       <c r="AA198" t="inlineStr"/>
       <c r="AB198" t="inlineStr"/>
@@ -18632,7 +18632,7 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>955001.36</v>
+        <v>13797201.02</v>
       </c>
       <c r="R199" t="n">
         <v>955001.36</v>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="Y199" t="inlineStr"/>
       <c r="Z199" t="n">
-        <v>955001.36</v>
+        <v>13797201.02</v>
       </c>
       <c r="AA199" t="inlineStr"/>
       <c r="AB199" t="inlineStr"/>
@@ -18726,10 +18726,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>8193722.76</v>
+        <v>16914580.43</v>
       </c>
       <c r="R200" t="n">
-        <v>2349004.86</v>
+        <v>3880593.18</v>
       </c>
       <c r="S200" t="n">
         <v>2320816.81</v>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="Y200" t="inlineStr"/>
       <c r="Z200" t="n">
-        <v>8193722.76</v>
+        <v>16914580.43</v>
       </c>
       <c r="AA200" t="inlineStr"/>
       <c r="AB200" t="inlineStr"/>
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>124777.51</v>
+        <v>257582.45</v>
       </c>
       <c r="R201" t="n">
         <v>35771.66</v>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="Y201" t="inlineStr"/>
       <c r="Z201" t="n">
-        <v>124777.51</v>
+        <v>257582.45</v>
       </c>
       <c r="AA201" t="inlineStr"/>
       <c r="AB201" t="inlineStr"/>
@@ -18914,13 +18914,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>6076032.55</v>
+        <v>9349434.27</v>
       </c>
       <c r="R202" t="n">
-        <v>1499893.53</v>
+        <v>2458343.75</v>
       </c>
       <c r="S202" t="n">
-        <v>1481894.81</v>
+        <v>2428843.63</v>
       </c>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
@@ -18933,13 +18933,13 @@
       </c>
       <c r="Y202" t="inlineStr"/>
       <c r="Z202" t="n">
-        <v>6076032.55</v>
+        <v>9349434.27</v>
       </c>
       <c r="AA202" t="inlineStr"/>
       <c r="AB202" t="inlineStr"/>
       <c r="AC202" t="inlineStr"/>
       <c r="AD202" t="n">
-        <v>1481894.81</v>
+        <v>2428843.63</v>
       </c>
     </row>
     <row r="203">
@@ -19008,13 +19008,13 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>1519008.14</v>
+        <v>2337358.56</v>
       </c>
       <c r="R203" t="n">
         <v>614585.9300000001</v>
       </c>
       <c r="S203" t="n">
-        <v>370473.7</v>
+        <v>607210.9</v>
       </c>
       <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr"/>
@@ -19027,13 +19027,13 @@
       </c>
       <c r="Y203" t="inlineStr"/>
       <c r="Z203" t="n">
-        <v>1519008.14</v>
+        <v>2337358.56</v>
       </c>
       <c r="AA203" t="inlineStr"/>
       <c r="AB203" t="inlineStr"/>
       <c r="AC203" t="inlineStr"/>
       <c r="AD203" t="n">
-        <v>370473.7</v>
+        <v>607210.9</v>
       </c>
     </row>
     <row r="204">
@@ -19102,10 +19102,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>4743053.83</v>
+        <v>9101988.42</v>
       </c>
       <c r="R204" t="n">
-        <v>1288879.4</v>
+        <v>1750936.02</v>
       </c>
       <c r="S204" t="n">
         <v>1273412.82</v>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="Y204" t="inlineStr"/>
       <c r="Z204" t="n">
-        <v>4743053.83</v>
+        <v>9101988.42</v>
       </c>
       <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="inlineStr"/>
@@ -20409,10 +20409,10 @@
         <v>114954.87</v>
       </c>
       <c r="R218" t="n">
-        <v>56668.17</v>
+        <v>114954.87</v>
       </c>
       <c r="S218" t="n">
-        <v>56668.17</v>
+        <v>114954.87</v>
       </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
@@ -20431,7 +20431,7 @@
       <c r="AB218" t="inlineStr"/>
       <c r="AC218" t="inlineStr"/>
       <c r="AD218" t="n">
-        <v>56668.17</v>
+        <v>114954.87</v>
       </c>
     </row>
     <row r="219">
@@ -20503,10 +20503,10 @@
         <v>3035.92</v>
       </c>
       <c r="R219" t="n">
-        <v>1418.75</v>
+        <v>3035.91</v>
       </c>
       <c r="S219" t="n">
-        <v>1418.75</v>
+        <v>3035.91</v>
       </c>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
@@ -20525,7 +20525,7 @@
       <c r="AB219" t="inlineStr"/>
       <c r="AC219" t="inlineStr"/>
       <c r="AD219" t="n">
-        <v>1418.75</v>
+        <v>3035.91</v>
       </c>
     </row>
     <row r="220">
@@ -26749,10 +26749,10 @@
         <v>4000</v>
       </c>
       <c r="R288" t="n">
-        <v>726.75</v>
+        <v>1930.55</v>
       </c>
       <c r="S288" t="n">
-        <v>726.75</v>
+        <v>1930.55</v>
       </c>
       <c r="T288" t="inlineStr"/>
       <c r="U288" t="inlineStr"/>
@@ -26767,7 +26767,7 @@
       <c r="AB288" t="inlineStr"/>
       <c r="AC288" t="inlineStr"/>
       <c r="AD288" t="n">
-        <v>726.75</v>
+        <v>1930.55</v>
       </c>
     </row>
     <row r="289">
@@ -36580,7 +36580,7 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>1583.51</v>
+        <v>3167</v>
       </c>
       <c r="R397" t="n">
         <v>1583.48</v>
@@ -36599,7 +36599,7 @@
       </c>
       <c r="Y397" t="inlineStr"/>
       <c r="Z397" t="n">
-        <v>1583.51</v>
+        <v>3167</v>
       </c>
       <c r="AA397" t="inlineStr"/>
       <c r="AB397" t="inlineStr"/>
@@ -36674,7 +36674,7 @@
         </is>
       </c>
       <c r="Q398" t="n">
-        <v>57506.47</v>
+        <v>122514.31</v>
       </c>
       <c r="R398" t="n">
         <v>57506.44</v>
@@ -36693,7 +36693,7 @@
       </c>
       <c r="Y398" t="inlineStr"/>
       <c r="Z398" t="n">
-        <v>57506.47</v>
+        <v>122514.31</v>
       </c>
       <c r="AA398" t="inlineStr"/>
       <c r="AB398" t="inlineStr"/>
@@ -37429,10 +37429,10 @@
         <v>45068.98</v>
       </c>
       <c r="R406" t="n">
-        <v>0</v>
+        <v>24991.21</v>
       </c>
       <c r="S406" t="n">
-        <v>0</v>
+        <v>24991.21</v>
       </c>
       <c r="T406" t="inlineStr"/>
       <c r="U406" t="inlineStr"/>
@@ -37447,7 +37447,7 @@
       <c r="AB406" t="inlineStr"/>
       <c r="AC406" t="inlineStr"/>
       <c r="AD406" t="n">
-        <v>0</v>
+        <v>24991.21</v>
       </c>
     </row>
     <row r="407">
@@ -37519,10 +37519,10 @@
         <v>974.33</v>
       </c>
       <c r="R407" t="n">
-        <v>0</v>
+        <v>974.3200000000001</v>
       </c>
       <c r="S407" t="n">
-        <v>0</v>
+        <v>974.3200000000001</v>
       </c>
       <c r="T407" t="inlineStr"/>
       <c r="U407" t="inlineStr"/>
@@ -37537,7 +37537,7 @@
       <c r="AB407" t="inlineStr"/>
       <c r="AC407" t="inlineStr"/>
       <c r="AD407" t="n">
-        <v>0</v>
+        <v>974.3200000000001</v>
       </c>
     </row>
     <row r="408">
@@ -37882,7 +37882,7 @@
         <v>8618.49</v>
       </c>
       <c r="S411" t="n">
-        <v>0</v>
+        <v>7286.79</v>
       </c>
       <c r="T411" t="inlineStr"/>
       <c r="U411" t="inlineStr"/>
@@ -37901,7 +37901,7 @@
       <c r="AB411" t="inlineStr"/>
       <c r="AC411" t="inlineStr"/>
       <c r="AD411" t="n">
-        <v>0</v>
+        <v>7286.79</v>
       </c>
     </row>
     <row r="412">
@@ -37976,7 +37976,7 @@
         <v>28840.66</v>
       </c>
       <c r="S412" t="n">
-        <v>0</v>
+        <v>24372.04</v>
       </c>
       <c r="T412" t="inlineStr"/>
       <c r="U412" t="inlineStr"/>
@@ -37995,7 +37995,7 @@
       <c r="AB412" t="inlineStr"/>
       <c r="AC412" t="inlineStr"/>
       <c r="AD412" t="n">
-        <v>0</v>
+        <v>24372.04</v>
       </c>
     </row>
     <row r="413">
@@ -38070,7 +38070,7 @@
         <v>72067.23</v>
       </c>
       <c r="S413" t="n">
-        <v>0</v>
+        <v>60926.65</v>
       </c>
       <c r="T413" t="inlineStr"/>
       <c r="U413" t="inlineStr"/>
@@ -38089,7 +38089,7 @@
       <c r="AB413" t="inlineStr"/>
       <c r="AC413" t="inlineStr"/>
       <c r="AD413" t="n">
-        <v>0</v>
+        <v>60926.65</v>
       </c>
     </row>
     <row r="414">
@@ -38252,7 +38252,7 @@
         </is>
       </c>
       <c r="Q415" t="n">
-        <v>119678.32</v>
+        <v>274617.42</v>
       </c>
       <c r="R415" t="n">
         <v>0</v>
@@ -38271,7 +38271,7 @@
       </c>
       <c r="Y415" t="inlineStr"/>
       <c r="Z415" t="n">
-        <v>119678.32</v>
+        <v>274617.42</v>
       </c>
       <c r="AA415" t="inlineStr"/>
       <c r="AB415" t="inlineStr"/>
@@ -38346,7 +38346,7 @@
         </is>
       </c>
       <c r="Q416" t="n">
-        <v>6719082.76</v>
+        <v>15417806.27</v>
       </c>
       <c r="R416" t="n">
         <v>0</v>
@@ -38365,7 +38365,7 @@
       </c>
       <c r="Y416" t="inlineStr"/>
       <c r="Z416" t="n">
-        <v>6719082.76</v>
+        <v>15417806.27</v>
       </c>
       <c r="AA416" t="inlineStr"/>
       <c r="AB416" t="inlineStr"/>
@@ -38443,7 +38443,7 @@
         <v>23010.54</v>
       </c>
       <c r="R417" t="n">
-        <v>0</v>
+        <v>11978.1</v>
       </c>
       <c r="S417" t="n">
         <v>0</v>
@@ -38623,7 +38623,7 @@
         <v>27770.9</v>
       </c>
       <c r="R419" t="n">
-        <v>0</v>
+        <v>27770.9</v>
       </c>
       <c r="S419" t="n">
         <v>0</v>
@@ -38713,7 +38713,7 @@
         <v>96.58</v>
       </c>
       <c r="R420" t="n">
-        <v>0</v>
+        <v>94.87</v>
       </c>
       <c r="S420" t="n">
         <v>0</v>
@@ -38803,7 +38803,7 @@
         <v>979.04</v>
       </c>
       <c r="R421" t="n">
-        <v>0</v>
+        <v>945.66</v>
       </c>
       <c r="S421" t="n">
         <v>0</v>
@@ -39384,6 +39384,2422 @@
         <v>0</v>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B428" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C428" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>35</v>
+      </c>
+      <c r="F428" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I428" t="n">
+        <v>37</v>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K428" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M428" t="n">
+        <v>80</v>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q428" t="n">
+        <v>4738.43</v>
+      </c>
+      <c r="R428" t="n">
+        <v>4738.43</v>
+      </c>
+      <c r="S428" t="n">
+        <v>0</v>
+      </c>
+      <c r="T428" t="inlineStr"/>
+      <c r="U428" t="inlineStr"/>
+      <c r="V428" t="n">
+        <v>0</v>
+      </c>
+      <c r="W428" t="inlineStr"/>
+      <c r="X428" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y428" t="inlineStr"/>
+      <c r="Z428" t="n">
+        <v>4738.43</v>
+      </c>
+      <c r="AA428" t="inlineStr"/>
+      <c r="AB428" t="inlineStr"/>
+      <c r="AC428" t="inlineStr"/>
+      <c r="AD428" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B429" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C429" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>36</v>
+      </c>
+      <c r="F429" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I429" t="n">
+        <v>37</v>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K429" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M429" t="n">
+        <v>80</v>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q429" t="n">
+        <v>528.83</v>
+      </c>
+      <c r="R429" t="n">
+        <v>527.83</v>
+      </c>
+      <c r="S429" t="n">
+        <v>0</v>
+      </c>
+      <c r="T429" t="inlineStr"/>
+      <c r="U429" t="inlineStr"/>
+      <c r="V429" t="n">
+        <v>0</v>
+      </c>
+      <c r="W429" t="inlineStr"/>
+      <c r="X429" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y429" t="inlineStr"/>
+      <c r="Z429" t="n">
+        <v>528.83</v>
+      </c>
+      <c r="AA429" t="inlineStr"/>
+      <c r="AB429" t="inlineStr"/>
+      <c r="AC429" t="inlineStr"/>
+      <c r="AD429" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B430" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C430" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>38</v>
+      </c>
+      <c r="F430" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I430" t="n">
+        <v>37</v>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K430" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M430" t="n">
+        <v>80</v>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q430" t="n">
+        <v>9482.379999999999</v>
+      </c>
+      <c r="R430" t="n">
+        <v>9482.379999999999</v>
+      </c>
+      <c r="S430" t="n">
+        <v>0</v>
+      </c>
+      <c r="T430" t="inlineStr"/>
+      <c r="U430" t="inlineStr"/>
+      <c r="V430" t="n">
+        <v>0</v>
+      </c>
+      <c r="W430" t="inlineStr"/>
+      <c r="X430" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y430" t="inlineStr"/>
+      <c r="Z430" t="n">
+        <v>9482.379999999999</v>
+      </c>
+      <c r="AA430" t="inlineStr"/>
+      <c r="AB430" t="inlineStr"/>
+      <c r="AC430" t="inlineStr"/>
+      <c r="AD430" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B431" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C431" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>1412</v>
+      </c>
+      <c r="F431" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I431" t="n">
+        <v>37</v>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K431" t="n">
+        <v>3704</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
+        </is>
+      </c>
+      <c r="M431" t="n">
+        <v>80</v>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q431" t="n">
+        <v>0</v>
+      </c>
+      <c r="R431" t="n">
+        <v>0</v>
+      </c>
+      <c r="S431" t="n">
+        <v>0</v>
+      </c>
+      <c r="T431" t="inlineStr"/>
+      <c r="U431" t="inlineStr"/>
+      <c r="V431" t="n">
+        <v>0</v>
+      </c>
+      <c r="W431" t="inlineStr"/>
+      <c r="X431" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y431" t="inlineStr"/>
+      <c r="Z431" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA431" t="inlineStr"/>
+      <c r="AB431" t="inlineStr"/>
+      <c r="AC431" t="inlineStr"/>
+      <c r="AD431" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B432" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C432" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>1413</v>
+      </c>
+      <c r="F432" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I432" t="n">
+        <v>37</v>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K432" t="n">
+        <v>3704</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
+        </is>
+      </c>
+      <c r="M432" t="n">
+        <v>80</v>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q432" t="n">
+        <v>0</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0</v>
+      </c>
+      <c r="S432" t="n">
+        <v>0</v>
+      </c>
+      <c r="T432" t="inlineStr"/>
+      <c r="U432" t="inlineStr"/>
+      <c r="V432" t="n">
+        <v>0</v>
+      </c>
+      <c r="W432" t="inlineStr"/>
+      <c r="X432" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y432" t="inlineStr"/>
+      <c r="Z432" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA432" t="inlineStr"/>
+      <c r="AB432" t="inlineStr"/>
+      <c r="AC432" t="inlineStr"/>
+      <c r="AD432" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B433" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C433" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>1414</v>
+      </c>
+      <c r="F433" s="2" t="n">
+        <v>46191</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I433" t="n">
+        <v>37</v>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K433" t="n">
+        <v>3704</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
+        </is>
+      </c>
+      <c r="M433" t="n">
+        <v>80</v>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q433" t="n">
+        <v>49109.37</v>
+      </c>
+      <c r="R433" t="n">
+        <v>32739.58</v>
+      </c>
+      <c r="S433" t="n">
+        <v>0</v>
+      </c>
+      <c r="T433" t="inlineStr"/>
+      <c r="U433" t="inlineStr"/>
+      <c r="V433" t="n">
+        <v>0</v>
+      </c>
+      <c r="W433" t="inlineStr"/>
+      <c r="X433" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y433" t="inlineStr"/>
+      <c r="Z433" t="n">
+        <v>49109.37</v>
+      </c>
+      <c r="AA433" t="inlineStr"/>
+      <c r="AB433" t="inlineStr"/>
+      <c r="AC433" t="inlineStr"/>
+      <c r="AD433" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B434" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C434" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>37</v>
+      </c>
+      <c r="F434" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I434" t="n">
+        <v>37</v>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K434" t="n">
+        <v>3704</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
+        </is>
+      </c>
+      <c r="M434" t="n">
+        <v>80</v>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q434" t="n">
+        <v>16369.79</v>
+      </c>
+      <c r="R434" t="n">
+        <v>16369.79</v>
+      </c>
+      <c r="S434" t="n">
+        <v>0</v>
+      </c>
+      <c r="T434" t="inlineStr"/>
+      <c r="U434" t="inlineStr"/>
+      <c r="V434" t="n">
+        <v>0</v>
+      </c>
+      <c r="W434" t="inlineStr"/>
+      <c r="X434" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y434" t="inlineStr"/>
+      <c r="Z434" t="n">
+        <v>16369.79</v>
+      </c>
+      <c r="AA434" t="inlineStr"/>
+      <c r="AB434" t="inlineStr"/>
+      <c r="AC434" t="inlineStr"/>
+      <c r="AD434" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B435" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C435" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>259</v>
+      </c>
+      <c r="F435" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I435" t="n">
+        <v>51</v>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K435" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M435" t="n">
+        <v>80</v>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q435" t="n">
+        <v>938190.6</v>
+      </c>
+      <c r="R435" t="n">
+        <v>0</v>
+      </c>
+      <c r="S435" t="n">
+        <v>0</v>
+      </c>
+      <c r="T435" t="inlineStr"/>
+      <c r="U435" t="inlineStr"/>
+      <c r="V435" t="n">
+        <v>0</v>
+      </c>
+      <c r="W435" t="inlineStr"/>
+      <c r="X435" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y435" t="inlineStr"/>
+      <c r="Z435" t="n">
+        <v>938190.6</v>
+      </c>
+      <c r="AA435" t="inlineStr"/>
+      <c r="AB435" t="inlineStr"/>
+      <c r="AC435" t="inlineStr"/>
+      <c r="AD435" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B436" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C436" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>260</v>
+      </c>
+      <c r="F436" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I436" t="n">
+        <v>93</v>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K436" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M436" t="n">
+        <v>80</v>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q436" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R436" t="n">
+        <v>0</v>
+      </c>
+      <c r="S436" t="n">
+        <v>0</v>
+      </c>
+      <c r="T436" t="inlineStr"/>
+      <c r="U436" t="inlineStr"/>
+      <c r="V436" t="n">
+        <v>0</v>
+      </c>
+      <c r="W436" t="inlineStr"/>
+      <c r="X436" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y436" t="inlineStr"/>
+      <c r="Z436" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AA436" t="inlineStr"/>
+      <c r="AB436" t="inlineStr"/>
+      <c r="AC436" t="inlineStr"/>
+      <c r="AD436" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B437" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C437" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>261</v>
+      </c>
+      <c r="F437" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I437" t="n">
+        <v>51</v>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K437" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M437" t="n">
+        <v>80</v>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q437" t="n">
+        <v>95103.89999999999</v>
+      </c>
+      <c r="R437" t="n">
+        <v>0</v>
+      </c>
+      <c r="S437" t="n">
+        <v>0</v>
+      </c>
+      <c r="T437" t="inlineStr"/>
+      <c r="U437" t="inlineStr"/>
+      <c r="V437" t="n">
+        <v>0</v>
+      </c>
+      <c r="W437" t="inlineStr"/>
+      <c r="X437" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y437" t="inlineStr"/>
+      <c r="Z437" t="n">
+        <v>95103.89999999999</v>
+      </c>
+      <c r="AA437" t="inlineStr"/>
+      <c r="AB437" t="inlineStr"/>
+      <c r="AC437" t="inlineStr"/>
+      <c r="AD437" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B438" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C438" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>262</v>
+      </c>
+      <c r="F438" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I438" t="n">
+        <v>93</v>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K438" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M438" t="n">
+        <v>80</v>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q438" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0</v>
+      </c>
+      <c r="S438" t="n">
+        <v>0</v>
+      </c>
+      <c r="T438" t="inlineStr"/>
+      <c r="U438" t="inlineStr"/>
+      <c r="V438" t="n">
+        <v>0</v>
+      </c>
+      <c r="W438" t="inlineStr"/>
+      <c r="X438" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y438" t="inlineStr"/>
+      <c r="Z438" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AA438" t="inlineStr"/>
+      <c r="AB438" t="inlineStr"/>
+      <c r="AC438" t="inlineStr"/>
+      <c r="AD438" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B439" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C439" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>1425</v>
+      </c>
+      <c r="F439" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I439" t="n">
+        <v>37</v>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K439" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M439" t="n">
+        <v>80</v>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q439" t="n">
+        <v>14215.29</v>
+      </c>
+      <c r="R439" t="n">
+        <v>14215.29</v>
+      </c>
+      <c r="S439" t="n">
+        <v>0</v>
+      </c>
+      <c r="T439" t="inlineStr"/>
+      <c r="U439" t="inlineStr"/>
+      <c r="V439" t="n">
+        <v>0</v>
+      </c>
+      <c r="W439" t="inlineStr"/>
+      <c r="X439" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y439" t="inlineStr"/>
+      <c r="Z439" t="n">
+        <v>14215.29</v>
+      </c>
+      <c r="AA439" t="inlineStr"/>
+      <c r="AB439" t="inlineStr"/>
+      <c r="AC439" t="inlineStr"/>
+      <c r="AD439" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B440" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C440" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>1426</v>
+      </c>
+      <c r="F440" s="2" t="n">
+        <v>46192</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I440" t="n">
+        <v>37</v>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K440" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M440" t="n">
+        <v>80</v>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q440" t="n">
+        <v>1535.39</v>
+      </c>
+      <c r="R440" t="n">
+        <v>1534.39</v>
+      </c>
+      <c r="S440" t="n">
+        <v>0</v>
+      </c>
+      <c r="T440" t="inlineStr"/>
+      <c r="U440" t="inlineStr"/>
+      <c r="V440" t="n">
+        <v>0</v>
+      </c>
+      <c r="W440" t="inlineStr"/>
+      <c r="X440" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y440" t="inlineStr"/>
+      <c r="Z440" t="n">
+        <v>1535.39</v>
+      </c>
+      <c r="AA440" t="inlineStr"/>
+      <c r="AB440" t="inlineStr"/>
+      <c r="AC440" t="inlineStr"/>
+      <c r="AD440" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B441" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C441" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>39</v>
+      </c>
+      <c r="F441" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I441" t="n">
+        <v>37</v>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K441" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M441" t="n">
+        <v>80</v>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q441" t="n">
+        <v>1056.66</v>
+      </c>
+      <c r="R441" t="n">
+        <v>1055.66</v>
+      </c>
+      <c r="S441" t="n">
+        <v>0</v>
+      </c>
+      <c r="T441" t="inlineStr"/>
+      <c r="U441" t="inlineStr"/>
+      <c r="V441" t="n">
+        <v>0</v>
+      </c>
+      <c r="W441" t="inlineStr"/>
+      <c r="X441" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y441" t="inlineStr"/>
+      <c r="Z441" t="n">
+        <v>1056.66</v>
+      </c>
+      <c r="AA441" t="inlineStr"/>
+      <c r="AB441" t="inlineStr"/>
+      <c r="AC441" t="inlineStr"/>
+      <c r="AD441" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B442" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C442" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>40</v>
+      </c>
+      <c r="F442" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I442" t="n">
+        <v>37</v>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K442" t="n">
+        <v>3704</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>LOCACAO DE SERVICOS DE APOIO ADMINISTRATIVO REALIZADOS PELA MGS</t>
+        </is>
+      </c>
+      <c r="M442" t="n">
+        <v>80</v>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q442" t="n">
+        <v>32739.58</v>
+      </c>
+      <c r="R442" t="n">
+        <v>32739.58</v>
+      </c>
+      <c r="S442" t="n">
+        <v>0</v>
+      </c>
+      <c r="T442" t="inlineStr"/>
+      <c r="U442" t="inlineStr"/>
+      <c r="V442" t="n">
+        <v>0</v>
+      </c>
+      <c r="W442" t="inlineStr"/>
+      <c r="X442" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y442" t="inlineStr"/>
+      <c r="Z442" t="n">
+        <v>32739.58</v>
+      </c>
+      <c r="AA442" t="inlineStr"/>
+      <c r="AB442" t="inlineStr"/>
+      <c r="AC442" t="inlineStr"/>
+      <c r="AD442" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B443" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C443" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>55</v>
+      </c>
+      <c r="F443" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>1511189 000132/2026</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I443" t="n">
+        <v>52</v>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K443" t="n">
+        <v>5207</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS DE INFORMATICA</t>
+        </is>
+      </c>
+      <c r="M443" t="n">
+        <v>80</v>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>51.527.662/0001-55</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>KONER INFORMATICA LTDA</t>
+        </is>
+      </c>
+      <c r="Q443" t="n">
+        <v>7064.85</v>
+      </c>
+      <c r="R443" t="n">
+        <v>0</v>
+      </c>
+      <c r="S443" t="n">
+        <v>0</v>
+      </c>
+      <c r="T443" t="inlineStr"/>
+      <c r="U443" t="inlineStr"/>
+      <c r="V443" t="inlineStr"/>
+      <c r="W443" t="inlineStr"/>
+      <c r="X443" t="inlineStr"/>
+      <c r="Y443" t="inlineStr"/>
+      <c r="Z443" t="n">
+        <v>7064.85</v>
+      </c>
+      <c r="AA443" t="inlineStr"/>
+      <c r="AB443" t="inlineStr"/>
+      <c r="AC443" t="inlineStr"/>
+      <c r="AD443" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B444" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C444" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>56</v>
+      </c>
+      <c r="F444" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>1511189 000133/2026</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I444" t="n">
+        <v>52</v>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K444" t="n">
+        <v>5207</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS DE INFORMATICA</t>
+        </is>
+      </c>
+      <c r="M444" t="n">
+        <v>80</v>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>04.602.789/0001-01</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>DATEN TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="Q444" t="n">
+        <v>85161.58</v>
+      </c>
+      <c r="R444" t="n">
+        <v>0</v>
+      </c>
+      <c r="S444" t="n">
+        <v>0</v>
+      </c>
+      <c r="T444" t="inlineStr"/>
+      <c r="U444" t="inlineStr"/>
+      <c r="V444" t="inlineStr"/>
+      <c r="W444" t="inlineStr"/>
+      <c r="X444" t="inlineStr"/>
+      <c r="Y444" t="inlineStr"/>
+      <c r="Z444" t="n">
+        <v>85161.58</v>
+      </c>
+      <c r="AA444" t="inlineStr"/>
+      <c r="AB444" t="inlineStr"/>
+      <c r="AC444" t="inlineStr"/>
+      <c r="AD444" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B445" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C445" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>265</v>
+      </c>
+      <c r="F445" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>2301762 000001/2026</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>CONCORRENCIA - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I445" t="n">
+        <v>51</v>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K445" t="n">
+        <v>5107</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>EXECUCAO DE OBRAS POR CONTRATO DE BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M445" t="n">
+        <v>80</v>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>19.256.565/0001-62</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>HWN ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="Q445" t="n">
+        <v>4408324.83</v>
+      </c>
+      <c r="R445" t="n">
+        <v>0</v>
+      </c>
+      <c r="S445" t="n">
+        <v>0</v>
+      </c>
+      <c r="T445" t="inlineStr"/>
+      <c r="U445" t="inlineStr"/>
+      <c r="V445" t="n">
+        <v>0</v>
+      </c>
+      <c r="W445" t="inlineStr"/>
+      <c r="X445" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y445" t="inlineStr"/>
+      <c r="Z445" t="n">
+        <v>4408324.83</v>
+      </c>
+      <c r="AA445" t="inlineStr"/>
+      <c r="AB445" t="inlineStr"/>
+      <c r="AC445" t="inlineStr"/>
+      <c r="AD445" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B446" t="n">
+        <v>9501917</v>
+      </c>
+      <c r="C446" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE GOVERNO</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>724</v>
+      </c>
+      <c r="F446" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I446" t="n">
+        <v>42</v>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K446" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M446" t="n">
+        <v>80</v>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>22.678.874/0001-35</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>PM MONTES CLAROS</t>
+        </is>
+      </c>
+      <c r="Q446" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="R446" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="S446" t="n">
+        <v>0</v>
+      </c>
+      <c r="T446" t="inlineStr"/>
+      <c r="U446" t="inlineStr"/>
+      <c r="V446" t="inlineStr"/>
+      <c r="W446" t="inlineStr"/>
+      <c r="X446" t="inlineStr"/>
+      <c r="Y446" t="inlineStr"/>
+      <c r="Z446" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="AA446" t="inlineStr"/>
+      <c r="AB446" t="inlineStr"/>
+      <c r="AC446" t="inlineStr"/>
+      <c r="AD446" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B447" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C447" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>30</v>
+      </c>
+      <c r="F447" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I447" t="n">
+        <v>33</v>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>PASSAGENS E DESPESAS COM LOCOMOCAO</t>
+        </is>
+      </c>
+      <c r="K447" t="n">
+        <v>3302</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>DESPESAS COM TRANSPORTE URBANO, PEDAGIO E ESTACIONAMETO PESSOA FISICA</t>
+        </is>
+      </c>
+      <c r="M447" t="n">
+        <v>80</v>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>120.225.986/36</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>JULIA PESSOA REIS</t>
+        </is>
+      </c>
+      <c r="Q447" t="n">
+        <v>398.32</v>
+      </c>
+      <c r="R447" t="n">
+        <v>398.32</v>
+      </c>
+      <c r="S447" t="n">
+        <v>398.32</v>
+      </c>
+      <c r="T447" t="inlineStr"/>
+      <c r="U447" t="inlineStr"/>
+      <c r="V447" t="n">
+        <v>0</v>
+      </c>
+      <c r="W447" t="inlineStr"/>
+      <c r="X447" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y447" t="inlineStr"/>
+      <c r="Z447" t="n">
+        <v>398.32</v>
+      </c>
+      <c r="AA447" t="inlineStr"/>
+      <c r="AB447" t="inlineStr"/>
+      <c r="AC447" t="inlineStr"/>
+      <c r="AD447" t="n">
+        <v>398.32</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B448" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C448" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>57</v>
+      </c>
+      <c r="F448" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>1511189 000175/2026</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I448" t="n">
+        <v>52</v>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K448" t="n">
+        <v>5207</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS DE INFORMATICA</t>
+        </is>
+      </c>
+      <c r="M448" t="n">
+        <v>80</v>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>07.500.596/0001-38</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>AIDC TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="Q448" t="n">
+        <v>3700</v>
+      </c>
+      <c r="R448" t="n">
+        <v>0</v>
+      </c>
+      <c r="S448" t="n">
+        <v>0</v>
+      </c>
+      <c r="T448" t="inlineStr"/>
+      <c r="U448" t="inlineStr"/>
+      <c r="V448" t="inlineStr"/>
+      <c r="W448" t="inlineStr"/>
+      <c r="X448" t="inlineStr"/>
+      <c r="Y448" t="inlineStr"/>
+      <c r="Z448" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AA448" t="inlineStr"/>
+      <c r="AB448" t="inlineStr"/>
+      <c r="AC448" t="inlineStr"/>
+      <c r="AD448" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B449" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C449" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>60</v>
+      </c>
+      <c r="F449" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>1511189 000176/2026</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I449" t="n">
+        <v>52</v>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K449" t="n">
+        <v>5208</v>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS DE SOM, VIDEO, FOTOGRAFICO E CINEMATOGRAFICO</t>
+        </is>
+      </c>
+      <c r="M449" t="n">
+        <v>80</v>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>18.152.404/0001-66</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>MAQNETE COMERCIO E SERVICOS LTDA -ME</t>
+        </is>
+      </c>
+      <c r="Q449" t="n">
+        <v>85.45999999999999</v>
+      </c>
+      <c r="R449" t="n">
+        <v>0</v>
+      </c>
+      <c r="S449" t="n">
+        <v>0</v>
+      </c>
+      <c r="T449" t="inlineStr"/>
+      <c r="U449" t="inlineStr"/>
+      <c r="V449" t="inlineStr"/>
+      <c r="W449" t="inlineStr"/>
+      <c r="X449" t="inlineStr"/>
+      <c r="Y449" t="inlineStr"/>
+      <c r="Z449" t="n">
+        <v>85.45999999999999</v>
+      </c>
+      <c r="AA449" t="inlineStr"/>
+      <c r="AB449" t="inlineStr"/>
+      <c r="AC449" t="inlineStr"/>
+      <c r="AD449" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B450" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C450" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>64</v>
+      </c>
+      <c r="F450" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>1511189 000164/2026</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I450" t="n">
+        <v>52</v>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K450" t="n">
+        <v>5213</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>MATERIAL ESPORTIVO E RECREATIVO</t>
+        </is>
+      </c>
+      <c r="M450" t="n">
+        <v>80</v>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>18.905.288/0001-09</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>AQUARELA COMERCIO E SERVICOS LTDA</t>
+        </is>
+      </c>
+      <c r="Q450" t="n">
+        <v>5100</v>
+      </c>
+      <c r="R450" t="n">
+        <v>0</v>
+      </c>
+      <c r="S450" t="n">
+        <v>0</v>
+      </c>
+      <c r="T450" t="inlineStr"/>
+      <c r="U450" t="inlineStr"/>
+      <c r="V450" t="inlineStr"/>
+      <c r="W450" t="inlineStr"/>
+      <c r="X450" t="inlineStr"/>
+      <c r="Y450" t="inlineStr"/>
+      <c r="Z450" t="n">
+        <v>5100</v>
+      </c>
+      <c r="AA450" t="inlineStr"/>
+      <c r="AB450" t="inlineStr"/>
+      <c r="AC450" t="inlineStr"/>
+      <c r="AD450" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B451" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C451" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>79</v>
+      </c>
+      <c r="F451" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>1511189 000131/2026</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I451" t="n">
+        <v>52</v>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K451" t="n">
+        <v>5214</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>MOBILIARIO</t>
+        </is>
+      </c>
+      <c r="M451" t="n">
+        <v>80</v>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>60.657.624/0001-08</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>RHODES S/A</t>
+        </is>
+      </c>
+      <c r="Q451" t="n">
+        <v>20375.85</v>
+      </c>
+      <c r="R451" t="n">
+        <v>0</v>
+      </c>
+      <c r="S451" t="n">
+        <v>0</v>
+      </c>
+      <c r="T451" t="inlineStr"/>
+      <c r="U451" t="inlineStr"/>
+      <c r="V451" t="inlineStr"/>
+      <c r="W451" t="inlineStr"/>
+      <c r="X451" t="inlineStr"/>
+      <c r="Y451" t="inlineStr"/>
+      <c r="Z451" t="n">
+        <v>20375.85</v>
+      </c>
+      <c r="AA451" t="inlineStr"/>
+      <c r="AB451" t="inlineStr"/>
+      <c r="AC451" t="inlineStr"/>
+      <c r="AD451" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B452" t="n">
+        <v>9473171</v>
+      </c>
+      <c r="C452" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>167</v>
+      </c>
+      <c r="F452" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I452" t="n">
+        <v>41</v>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K452" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M452" t="n">
+        <v>80</v>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>17.095.043/0001-09</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>PM BARBACENA</t>
+        </is>
+      </c>
+      <c r="Q452" t="n">
+        <v>795041.08</v>
+      </c>
+      <c r="R452" t="n">
+        <v>0</v>
+      </c>
+      <c r="S452" t="n">
+        <v>0</v>
+      </c>
+      <c r="T452" t="inlineStr"/>
+      <c r="U452" t="inlineStr"/>
+      <c r="V452" t="n">
+        <v>0</v>
+      </c>
+      <c r="W452" t="inlineStr"/>
+      <c r="X452" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y452" t="inlineStr"/>
+      <c r="Z452" t="n">
+        <v>795041.08</v>
+      </c>
+      <c r="AA452" t="inlineStr"/>
+      <c r="AB452" t="inlineStr"/>
+      <c r="AC452" t="inlineStr"/>
+      <c r="AD452" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B453" t="n">
+        <v>9473171</v>
+      </c>
+      <c r="C453" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>168</v>
+      </c>
+      <c r="F453" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I453" t="n">
+        <v>41</v>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K453" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M453" t="n">
+        <v>80</v>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>17.947.581/0001-76</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>PM MURIAE</t>
+        </is>
+      </c>
+      <c r="Q453" t="n">
+        <v>840474.27</v>
+      </c>
+      <c r="R453" t="n">
+        <v>0</v>
+      </c>
+      <c r="S453" t="n">
+        <v>0</v>
+      </c>
+      <c r="T453" t="inlineStr"/>
+      <c r="U453" t="inlineStr"/>
+      <c r="V453" t="n">
+        <v>0</v>
+      </c>
+      <c r="W453" t="inlineStr"/>
+      <c r="X453" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y453" t="inlineStr"/>
+      <c r="Z453" t="n">
+        <v>840474.27</v>
+      </c>
+      <c r="AA453" t="inlineStr"/>
+      <c r="AB453" t="inlineStr"/>
+      <c r="AC453" t="inlineStr"/>
+      <c r="AD453" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD453"/>
+  <dimension ref="A1:AD472"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>5891.4</v>
+        <v>5891.6</v>
       </c>
       <c r="R140" t="n">
         <v>4835.94</v>
@@ -13117,7 +13117,7 @@
       </c>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="n">
-        <v>5891.4</v>
+        <v>5891.6</v>
       </c>
       <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr"/>
@@ -14044,7 +14044,7 @@
         <v>385355.31</v>
       </c>
       <c r="S150" t="n">
-        <v>260913.96</v>
+        <v>320103.29</v>
       </c>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
@@ -14063,7 +14063,7 @@
       <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr"/>
       <c r="AD150" t="n">
-        <v>260913.96</v>
+        <v>320103.29</v>
       </c>
     </row>
     <row r="151">
@@ -14138,7 +14138,7 @@
         <v>1129581.26</v>
       </c>
       <c r="S151" t="n">
-        <v>942258.29</v>
+        <v>749422.04</v>
       </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
@@ -14157,7 +14157,7 @@
       <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="n">
-        <v>942258.29</v>
+        <v>749422.04</v>
       </c>
     </row>
     <row r="152">
@@ -14232,7 +14232,7 @@
         <v>71246.27</v>
       </c>
       <c r="S152" t="n">
-        <v>66180.75</v>
+        <v>45430.54</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
@@ -14251,7 +14251,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="n">
-        <v>66180.75</v>
+        <v>45430.54</v>
       </c>
     </row>
     <row r="153">
@@ -14326,7 +14326,7 @@
         <v>7560.81</v>
       </c>
       <c r="S153" t="n">
-        <v>7285.08</v>
+        <v>5275.1</v>
       </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
@@ -14345,7 +14345,7 @@
       <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="n">
-        <v>7285.08</v>
+        <v>5275.1</v>
       </c>
     </row>
     <row r="154">
@@ -14514,7 +14514,7 @@
         <v>4653543.42</v>
       </c>
       <c r="S155" t="n">
-        <v>3115199.85</v>
+        <v>4597700.91</v>
       </c>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
@@ -14533,7 +14533,7 @@
       <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="inlineStr"/>
       <c r="AD155" t="n">
-        <v>3115199.85</v>
+        <v>4597700.91</v>
       </c>
     </row>
     <row r="156">
@@ -14605,10 +14605,10 @@
         <v>45000</v>
       </c>
       <c r="R156" t="n">
-        <v>17852.2</v>
+        <v>18315.7</v>
       </c>
       <c r="S156" t="n">
-        <v>17852.2</v>
+        <v>18315.7</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14627,7 +14627,7 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>17852.2</v>
+        <v>18315.7</v>
       </c>
     </row>
     <row r="157">
@@ -16108,7 +16108,7 @@
         <v>3929.86</v>
       </c>
       <c r="S172" t="n">
-        <v>0</v>
+        <v>2297.73</v>
       </c>
       <c r="T172" t="inlineStr"/>
       <c r="U172" t="inlineStr"/>
@@ -16127,7 +16127,7 @@
       <c r="AB172" t="inlineStr"/>
       <c r="AC172" t="inlineStr"/>
       <c r="AD172" t="n">
-        <v>0</v>
+        <v>2297.73</v>
       </c>
     </row>
     <row r="173">
@@ -16286,10 +16286,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>20401.41</v>
+        <v>24515.1</v>
       </c>
       <c r="R174" t="n">
-        <v>20401.39</v>
+        <v>24515.08</v>
       </c>
       <c r="S174" t="n">
         <v>20036.2</v>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="n">
-        <v>20401.41</v>
+        <v>24515.1</v>
       </c>
       <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr"/>
@@ -16383,7 +16383,7 @@
         <v>9112.059999999999</v>
       </c>
       <c r="R175" t="n">
-        <v>7602.3</v>
+        <v>9112.030000000001</v>
       </c>
       <c r="S175" t="n">
         <v>7322.73</v>
@@ -16474,10 +16474,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>56971.47</v>
+        <v>71269.75999999999</v>
       </c>
       <c r="R176" t="n">
-        <v>56971.45</v>
+        <v>71269.74000000001</v>
       </c>
       <c r="S176" t="n">
         <v>53665.01</v>
@@ -16493,7 +16493,7 @@
       </c>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="n">
-        <v>56971.47</v>
+        <v>71269.75999999999</v>
       </c>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
@@ -16568,10 +16568,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>43093.1</v>
+        <v>57253.87</v>
       </c>
       <c r="R177" t="n">
-        <v>43093.08</v>
+        <v>57253.85</v>
       </c>
       <c r="S177" t="n">
         <v>41207.95</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="n">
-        <v>43093.1</v>
+        <v>57253.87</v>
       </c>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr"/>
@@ -16662,10 +16662,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>20845.26</v>
+        <v>25486.78</v>
       </c>
       <c r="R178" t="n">
-        <v>20845.24</v>
+        <v>25486.76</v>
       </c>
       <c r="S178" t="n">
         <v>20845.24</v>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="n">
-        <v>20845.26</v>
+        <v>25486.78</v>
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
@@ -16759,7 +16759,7 @@
         <v>7364.59</v>
       </c>
       <c r="R179" t="n">
-        <v>5781.07</v>
+        <v>7364.56</v>
       </c>
       <c r="S179" t="n">
         <v>5781.07</v>
@@ -17044,7 +17044,7 @@
         <v>316.2</v>
       </c>
       <c r="S182" t="n">
-        <v>0</v>
+        <v>266.24</v>
       </c>
       <c r="T182" t="inlineStr"/>
       <c r="U182" t="inlineStr"/>
@@ -17063,7 +17063,7 @@
       <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="inlineStr"/>
       <c r="AD182" t="n">
-        <v>0</v>
+        <v>266.24</v>
       </c>
     </row>
     <row r="183">
@@ -17135,7 +17135,7 @@
         <v>618435.35</v>
       </c>
       <c r="R183" t="n">
-        <v>489138.54</v>
+        <v>618387.89</v>
       </c>
       <c r="S183" t="n">
         <v>386505.74</v>
@@ -17696,7 +17696,7 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>32800</v>
+        <v>60100</v>
       </c>
       <c r="R189" t="n">
         <v>30912.24</v>
@@ -17715,7 +17715,7 @@
       </c>
       <c r="Y189" t="inlineStr"/>
       <c r="Z189" t="n">
-        <v>32800</v>
+        <v>60100</v>
       </c>
       <c r="AA189" t="inlineStr"/>
       <c r="AB189" t="inlineStr"/>
@@ -18353,7 +18353,7 @@
         <v>521640</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>69000</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -18447,7 +18447,7 @@
         <v>1720.89</v>
       </c>
       <c r="R197" t="n">
-        <v>1245.81</v>
+        <v>1694.47</v>
       </c>
       <c r="S197" t="n">
         <v>1245.81</v>
@@ -18635,7 +18635,7 @@
         <v>13797201.02</v>
       </c>
       <c r="R199" t="n">
-        <v>955001.36</v>
+        <v>2163567.83</v>
       </c>
       <c r="S199" t="n">
         <v>943541.35</v>
@@ -18823,7 +18823,7 @@
         <v>257582.45</v>
       </c>
       <c r="R201" t="n">
-        <v>35771.66</v>
+        <v>59095.34</v>
       </c>
       <c r="S201" t="n">
         <v>35342.41</v>
@@ -19108,7 +19108,7 @@
         <v>1750936.02</v>
       </c>
       <c r="S204" t="n">
-        <v>1273412.82</v>
+        <v>1729924.76</v>
       </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
@@ -19127,7 +19127,7 @@
       <c r="AB204" t="inlineStr"/>
       <c r="AC204" t="inlineStr"/>
       <c r="AD204" t="n">
-        <v>1273412.82</v>
+        <v>1729924.76</v>
       </c>
     </row>
     <row r="205">
@@ -21325,10 +21325,10 @@
         <v>2173913.04</v>
       </c>
       <c r="R228" t="n">
-        <v>0</v>
+        <v>2173913.04</v>
       </c>
       <c r="S228" t="n">
-        <v>0</v>
+        <v>2173913.04</v>
       </c>
       <c r="T228" t="inlineStr"/>
       <c r="U228" t="inlineStr"/>
@@ -21343,7 +21343,7 @@
       <c r="AB228" t="inlineStr"/>
       <c r="AC228" t="inlineStr"/>
       <c r="AD228" t="n">
-        <v>0</v>
+        <v>2173913.04</v>
       </c>
     </row>
     <row r="229">
@@ -21415,10 +21415,10 @@
         <v>2826086.96</v>
       </c>
       <c r="R229" t="n">
-        <v>0</v>
+        <v>2018712</v>
       </c>
       <c r="S229" t="n">
-        <v>0</v>
+        <v>2018712</v>
       </c>
       <c r="T229" t="inlineStr"/>
       <c r="U229" t="inlineStr"/>
@@ -21433,7 +21433,7 @@
       <c r="AB229" t="inlineStr"/>
       <c r="AC229" t="inlineStr"/>
       <c r="AD229" t="n">
-        <v>0</v>
+        <v>2018712</v>
       </c>
     </row>
     <row r="230">
@@ -21595,10 +21595,10 @@
         <v>217391.3</v>
       </c>
       <c r="R231" t="n">
-        <v>0</v>
+        <v>217391.3</v>
       </c>
       <c r="S231" t="n">
-        <v>0</v>
+        <v>217391.3</v>
       </c>
       <c r="T231" t="inlineStr"/>
       <c r="U231" t="inlineStr"/>
@@ -21613,7 +21613,7 @@
       <c r="AB231" t="inlineStr"/>
       <c r="AC231" t="inlineStr"/>
       <c r="AD231" t="n">
-        <v>0</v>
+        <v>217391.3</v>
       </c>
     </row>
     <row r="232">
@@ -21685,10 +21685,10 @@
         <v>2173913.04</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>1254137</v>
       </c>
       <c r="S232" t="n">
-        <v>0</v>
+        <v>1254137</v>
       </c>
       <c r="T232" t="inlineStr"/>
       <c r="U232" t="inlineStr"/>
@@ -21703,7 +21703,7 @@
       <c r="AB232" t="inlineStr"/>
       <c r="AC232" t="inlineStr"/>
       <c r="AD232" t="n">
-        <v>0</v>
+        <v>1254137</v>
       </c>
     </row>
     <row r="233">
@@ -22695,7 +22695,7 @@
         <v>4184317</v>
       </c>
       <c r="R243" t="n">
-        <v>0</v>
+        <v>4184317</v>
       </c>
       <c r="S243" t="n">
         <v>0</v>
@@ -26025,7 +26025,7 @@
         <v>5500000</v>
       </c>
       <c r="R280" t="n">
-        <v>0</v>
+        <v>5500000</v>
       </c>
       <c r="S280" t="n">
         <v>0</v>
@@ -26115,7 +26115,7 @@
         <v>7000000</v>
       </c>
       <c r="R281" t="n">
-        <v>0</v>
+        <v>7000000</v>
       </c>
       <c r="S281" t="n">
         <v>0</v>
@@ -26385,7 +26385,7 @@
         <v>1500000</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="S284" t="n">
         <v>0</v>
@@ -26475,10 +26475,10 @@
         <v>476625</v>
       </c>
       <c r="R285" t="n">
-        <v>0</v>
+        <v>476625</v>
       </c>
       <c r="S285" t="n">
-        <v>0</v>
+        <v>476625</v>
       </c>
       <c r="T285" t="inlineStr"/>
       <c r="U285" t="inlineStr"/>
@@ -26493,7 +26493,7 @@
       <c r="AB285" t="inlineStr"/>
       <c r="AC285" t="inlineStr"/>
       <c r="AD285" t="n">
-        <v>0</v>
+        <v>476625</v>
       </c>
     </row>
     <row r="286">
@@ -26565,7 +26565,7 @@
         <v>1850000</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>627500</v>
       </c>
       <c r="S286" t="n">
         <v>0</v>
@@ -26839,10 +26839,10 @@
         <v>300000</v>
       </c>
       <c r="R289" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="S289" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="T289" t="inlineStr"/>
       <c r="U289" t="inlineStr"/>
@@ -26857,7 +26857,7 @@
       <c r="AB289" t="inlineStr"/>
       <c r="AC289" t="inlineStr"/>
       <c r="AD289" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="290">
@@ -26929,10 +26929,10 @@
         <v>300000</v>
       </c>
       <c r="R290" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="S290" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="T290" t="inlineStr"/>
       <c r="U290" t="inlineStr"/>
@@ -26947,7 +26947,7 @@
       <c r="AB290" t="inlineStr"/>
       <c r="AC290" t="inlineStr"/>
       <c r="AD290" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="291">
@@ -27019,10 +27019,10 @@
         <v>1000000</v>
       </c>
       <c r="R291" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="S291" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="T291" t="inlineStr"/>
       <c r="U291" t="inlineStr"/>
@@ -27037,7 +27037,7 @@
       <c r="AB291" t="inlineStr"/>
       <c r="AC291" t="inlineStr"/>
       <c r="AD291" t="n">
-        <v>0</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="292">
@@ -27109,10 +27109,10 @@
         <v>6000000</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="S292" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="T292" t="inlineStr"/>
       <c r="U292" t="inlineStr"/>
@@ -27127,7 +27127,7 @@
       <c r="AB292" t="inlineStr"/>
       <c r="AC292" t="inlineStr"/>
       <c r="AD292" t="n">
-        <v>0</v>
+        <v>6000000</v>
       </c>
     </row>
     <row r="293">
@@ -27199,10 +27199,10 @@
         <v>1434006</v>
       </c>
       <c r="R293" t="n">
-        <v>0</v>
+        <v>1434006</v>
       </c>
       <c r="S293" t="n">
-        <v>0</v>
+        <v>1434006</v>
       </c>
       <c r="T293" t="inlineStr"/>
       <c r="U293" t="inlineStr"/>
@@ -27217,7 +27217,7 @@
       <c r="AB293" t="inlineStr"/>
       <c r="AC293" t="inlineStr"/>
       <c r="AD293" t="n">
-        <v>0</v>
+        <v>1434006</v>
       </c>
     </row>
     <row r="294">
@@ -36583,7 +36583,7 @@
         <v>3167</v>
       </c>
       <c r="R397" t="n">
-        <v>1583.48</v>
+        <v>3166.97</v>
       </c>
       <c r="S397" t="n">
         <v>1583.48</v>
@@ -36768,7 +36768,7 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>33755.74</v>
+        <v>37200.58</v>
       </c>
       <c r="R399" t="n">
         <v>33755.73</v>
@@ -36787,7 +36787,7 @@
       </c>
       <c r="Y399" t="inlineStr"/>
       <c r="Z399" t="n">
-        <v>33755.74</v>
+        <v>37200.58</v>
       </c>
       <c r="AA399" t="inlineStr"/>
       <c r="AB399" t="inlineStr"/>
@@ -36862,7 +36862,7 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>20455.24</v>
+        <v>20831.63</v>
       </c>
       <c r="R400" t="n">
         <v>20455.23</v>
@@ -36881,7 +36881,7 @@
       </c>
       <c r="Y400" t="inlineStr"/>
       <c r="Z400" t="n">
-        <v>20455.24</v>
+        <v>20831.63</v>
       </c>
       <c r="AA400" t="inlineStr"/>
       <c r="AB400" t="inlineStr"/>
@@ -36956,7 +36956,7 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>77101.57000000001</v>
+        <v>83870.03999999999</v>
       </c>
       <c r="R401" t="n">
         <v>77101.56</v>
@@ -36975,7 +36975,7 @@
       </c>
       <c r="Y401" t="inlineStr"/>
       <c r="Z401" t="n">
-        <v>77101.57000000001</v>
+        <v>83870.03999999999</v>
       </c>
       <c r="AA401" t="inlineStr"/>
       <c r="AB401" t="inlineStr"/>
@@ -37050,7 +37050,7 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>75875.06</v>
+        <v>82956.12</v>
       </c>
       <c r="R402" t="n">
         <v>75875.05</v>
@@ -37069,7 +37069,7 @@
       </c>
       <c r="Y402" t="inlineStr"/>
       <c r="Z402" t="n">
-        <v>75875.06</v>
+        <v>82956.12</v>
       </c>
       <c r="AA402" t="inlineStr"/>
       <c r="AB402" t="inlineStr"/>
@@ -37144,7 +37144,7 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>55389.55</v>
+        <v>60486.65</v>
       </c>
       <c r="R403" t="n">
         <v>55389.54</v>
@@ -37163,7 +37163,7 @@
       </c>
       <c r="Y403" t="inlineStr"/>
       <c r="Z403" t="n">
-        <v>55389.55</v>
+        <v>60486.65</v>
       </c>
       <c r="AA403" t="inlineStr"/>
       <c r="AB403" t="inlineStr"/>
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>12237.7</v>
+        <v>13909.09</v>
       </c>
       <c r="R404" t="n">
         <v>12237.69</v>
@@ -37257,7 +37257,7 @@
       </c>
       <c r="Y404" t="inlineStr"/>
       <c r="Z404" t="n">
-        <v>12237.7</v>
+        <v>13909.09</v>
       </c>
       <c r="AA404" t="inlineStr"/>
       <c r="AB404" t="inlineStr"/>
@@ -37332,7 +37332,7 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>3079.53</v>
+        <v>3462.29</v>
       </c>
       <c r="R405" t="n">
         <v>3079.52</v>
@@ -37351,7 +37351,7 @@
       </c>
       <c r="Y405" t="inlineStr"/>
       <c r="Z405" t="n">
-        <v>3079.53</v>
+        <v>3462.29</v>
       </c>
       <c r="AA405" t="inlineStr"/>
       <c r="AB405" t="inlineStr"/>
@@ -37699,10 +37699,10 @@
         <v>869565.22</v>
       </c>
       <c r="R409" t="n">
-        <v>0</v>
+        <v>265300</v>
       </c>
       <c r="S409" t="n">
-        <v>0</v>
+        <v>265300</v>
       </c>
       <c r="T409" t="inlineStr"/>
       <c r="U409" t="inlineStr"/>
@@ -37717,7 +37717,7 @@
       <c r="AB409" t="inlineStr"/>
       <c r="AC409" t="inlineStr"/>
       <c r="AD409" t="n">
-        <v>0</v>
+        <v>265300</v>
       </c>
     </row>
     <row r="410">
@@ -38349,7 +38349,7 @@
         <v>15417806.27</v>
       </c>
       <c r="R416" t="n">
-        <v>0</v>
+        <v>773832.3</v>
       </c>
       <c r="S416" t="n">
         <v>0</v>
@@ -38533,7 +38533,7 @@
         <v>1160.87</v>
       </c>
       <c r="R418" t="n">
-        <v>0</v>
+        <v>719.21</v>
       </c>
       <c r="S418" t="n">
         <v>0</v>
@@ -38713,7 +38713,7 @@
         <v>96.58</v>
       </c>
       <c r="R420" t="n">
-        <v>94.87</v>
+        <v>96.58</v>
       </c>
       <c r="S420" t="n">
         <v>0</v>
@@ -38803,7 +38803,7 @@
         <v>979.04</v>
       </c>
       <c r="R421" t="n">
-        <v>945.66</v>
+        <v>979.04</v>
       </c>
       <c r="S421" t="n">
         <v>0</v>
@@ -38893,7 +38893,7 @@
         <v>490.09</v>
       </c>
       <c r="R422" t="n">
-        <v>0</v>
+        <v>489.09</v>
       </c>
       <c r="S422" t="n">
         <v>0</v>
@@ -39456,7 +39456,7 @@
         <v>4738.43</v>
       </c>
       <c r="S428" t="n">
-        <v>0</v>
+        <v>4005.37</v>
       </c>
       <c r="T428" t="inlineStr"/>
       <c r="U428" t="inlineStr"/>
@@ -39475,7 +39475,7 @@
       <c r="AB428" t="inlineStr"/>
       <c r="AC428" t="inlineStr"/>
       <c r="AD428" t="n">
-        <v>0</v>
+        <v>4005.37</v>
       </c>
     </row>
     <row r="429">
@@ -39544,13 +39544,13 @@
         </is>
       </c>
       <c r="Q429" t="n">
-        <v>528.83</v>
+        <v>1822.18</v>
       </c>
       <c r="R429" t="n">
         <v>527.83</v>
       </c>
       <c r="S429" t="n">
-        <v>0</v>
+        <v>502.49</v>
       </c>
       <c r="T429" t="inlineStr"/>
       <c r="U429" t="inlineStr"/>
@@ -39563,13 +39563,13 @@
       </c>
       <c r="Y429" t="inlineStr"/>
       <c r="Z429" t="n">
-        <v>528.83</v>
+        <v>1822.18</v>
       </c>
       <c r="AA429" t="inlineStr"/>
       <c r="AB429" t="inlineStr"/>
       <c r="AC429" t="inlineStr"/>
       <c r="AD429" t="n">
-        <v>0</v>
+        <v>502.49</v>
       </c>
     </row>
     <row r="430">
@@ -39644,7 +39644,7 @@
         <v>9482.379999999999</v>
       </c>
       <c r="S430" t="n">
-        <v>0</v>
+        <v>9027.219999999999</v>
       </c>
       <c r="T430" t="inlineStr"/>
       <c r="U430" t="inlineStr"/>
@@ -39663,7 +39663,7 @@
       <c r="AB430" t="inlineStr"/>
       <c r="AC430" t="inlineStr"/>
       <c r="AD430" t="n">
-        <v>0</v>
+        <v>9027.219999999999</v>
       </c>
     </row>
     <row r="431">
@@ -39920,13 +39920,13 @@
         </is>
       </c>
       <c r="Q433" t="n">
+        <v>98218.74000000001</v>
+      </c>
+      <c r="R433" t="n">
         <v>49109.37</v>
       </c>
-      <c r="R433" t="n">
-        <v>32739.58</v>
-      </c>
       <c r="S433" t="n">
-        <v>0</v>
+        <v>39833.26</v>
       </c>
       <c r="T433" t="inlineStr"/>
       <c r="U433" t="inlineStr"/>
@@ -39939,13 +39939,13 @@
       </c>
       <c r="Y433" t="inlineStr"/>
       <c r="Z433" t="n">
-        <v>49109.37</v>
+        <v>98218.74000000001</v>
       </c>
       <c r="AA433" t="inlineStr"/>
       <c r="AB433" t="inlineStr"/>
       <c r="AC433" t="inlineStr"/>
       <c r="AD433" t="n">
-        <v>0</v>
+        <v>39833.26</v>
       </c>
     </row>
     <row r="434">
@@ -40014,13 +40014,13 @@
         </is>
       </c>
       <c r="Q434" t="n">
-        <v>16369.79</v>
+        <v>32739.58</v>
       </c>
       <c r="R434" t="n">
         <v>16369.79</v>
       </c>
       <c r="S434" t="n">
-        <v>0</v>
+        <v>13783.36</v>
       </c>
       <c r="T434" t="inlineStr"/>
       <c r="U434" t="inlineStr"/>
@@ -40033,13 +40033,13 @@
       </c>
       <c r="Y434" t="inlineStr"/>
       <c r="Z434" t="n">
-        <v>16369.79</v>
+        <v>32739.58</v>
       </c>
       <c r="AA434" t="inlineStr"/>
       <c r="AB434" t="inlineStr"/>
       <c r="AC434" t="inlineStr"/>
       <c r="AD434" t="n">
-        <v>0</v>
+        <v>13783.36</v>
       </c>
     </row>
     <row r="435">
@@ -40490,7 +40490,7 @@
         <v>14215.29</v>
       </c>
       <c r="S439" t="n">
-        <v>0</v>
+        <v>13532.95</v>
       </c>
       <c r="T439" t="inlineStr"/>
       <c r="U439" t="inlineStr"/>
@@ -40509,7 +40509,7 @@
       <c r="AB439" t="inlineStr"/>
       <c r="AC439" t="inlineStr"/>
       <c r="AD439" t="n">
-        <v>0</v>
+        <v>13532.95</v>
       </c>
     </row>
     <row r="440">
@@ -40578,13 +40578,13 @@
         </is>
       </c>
       <c r="Q440" t="n">
-        <v>1535.39</v>
+        <v>5415.44</v>
       </c>
       <c r="R440" t="n">
         <v>1534.39</v>
       </c>
       <c r="S440" t="n">
-        <v>0</v>
+        <v>1460.74</v>
       </c>
       <c r="T440" t="inlineStr"/>
       <c r="U440" t="inlineStr"/>
@@ -40597,13 +40597,13 @@
       </c>
       <c r="Y440" t="inlineStr"/>
       <c r="Z440" t="n">
-        <v>1535.39</v>
+        <v>5415.44</v>
       </c>
       <c r="AA440" t="inlineStr"/>
       <c r="AB440" t="inlineStr"/>
       <c r="AC440" t="inlineStr"/>
       <c r="AD440" t="n">
-        <v>0</v>
+        <v>1460.74</v>
       </c>
     </row>
     <row r="441">
@@ -40672,13 +40672,13 @@
         </is>
       </c>
       <c r="Q441" t="n">
-        <v>1056.66</v>
+        <v>3643.36</v>
       </c>
       <c r="R441" t="n">
         <v>1055.66</v>
       </c>
       <c r="S441" t="n">
-        <v>0</v>
+        <v>1004.99</v>
       </c>
       <c r="T441" t="inlineStr"/>
       <c r="U441" t="inlineStr"/>
@@ -40691,13 +40691,13 @@
       </c>
       <c r="Y441" t="inlineStr"/>
       <c r="Z441" t="n">
-        <v>1056.66</v>
+        <v>3643.36</v>
       </c>
       <c r="AA441" t="inlineStr"/>
       <c r="AB441" t="inlineStr"/>
       <c r="AC441" t="inlineStr"/>
       <c r="AD441" t="n">
-        <v>0</v>
+        <v>1004.99</v>
       </c>
     </row>
     <row r="442">
@@ -40766,13 +40766,13 @@
         </is>
       </c>
       <c r="Q442" t="n">
-        <v>32739.58</v>
+        <v>65479.16</v>
       </c>
       <c r="R442" t="n">
         <v>32739.58</v>
       </c>
       <c r="S442" t="n">
-        <v>0</v>
+        <v>27566.73</v>
       </c>
       <c r="T442" t="inlineStr"/>
       <c r="U442" t="inlineStr"/>
@@ -40785,13 +40785,13 @@
       </c>
       <c r="Y442" t="inlineStr"/>
       <c r="Z442" t="n">
-        <v>32739.58</v>
+        <v>65479.16</v>
       </c>
       <c r="AA442" t="inlineStr"/>
       <c r="AB442" t="inlineStr"/>
       <c r="AC442" t="inlineStr"/>
       <c r="AD442" t="n">
-        <v>0</v>
+        <v>27566.73</v>
       </c>
     </row>
     <row r="443">
@@ -41040,7 +41040,7 @@
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>4408324.83</v>
+        <v>5408324.83</v>
       </c>
       <c r="R445" t="n">
         <v>0</v>
@@ -41059,7 +41059,7 @@
       </c>
       <c r="Y445" t="inlineStr"/>
       <c r="Z445" t="n">
-        <v>4408324.83</v>
+        <v>5408324.83</v>
       </c>
       <c r="AA445" t="inlineStr"/>
       <c r="AB445" t="inlineStr"/>
@@ -41140,7 +41140,7 @@
         <v>7500000</v>
       </c>
       <c r="S446" t="n">
-        <v>0</v>
+        <v>3750000</v>
       </c>
       <c r="T446" t="inlineStr"/>
       <c r="U446" t="inlineStr"/>
@@ -41155,7 +41155,7 @@
       <c r="AB446" t="inlineStr"/>
       <c r="AC446" t="inlineStr"/>
       <c r="AD446" t="n">
-        <v>0</v>
+        <v>3750000</v>
       </c>
     </row>
     <row r="447">
@@ -41681,10 +41681,10 @@
         <v>795041.08</v>
       </c>
       <c r="R452" t="n">
-        <v>0</v>
+        <v>795041.08</v>
       </c>
       <c r="S452" t="n">
-        <v>0</v>
+        <v>795041.08</v>
       </c>
       <c r="T452" t="inlineStr"/>
       <c r="U452" t="inlineStr"/>
@@ -41703,7 +41703,7 @@
       <c r="AB452" t="inlineStr"/>
       <c r="AC452" t="inlineStr"/>
       <c r="AD452" t="n">
-        <v>0</v>
+        <v>795041.08</v>
       </c>
     </row>
     <row r="453">
@@ -41775,10 +41775,10 @@
         <v>840474.27</v>
       </c>
       <c r="R453" t="n">
-        <v>0</v>
+        <v>840474.27</v>
       </c>
       <c r="S453" t="n">
-        <v>0</v>
+        <v>840474.27</v>
       </c>
       <c r="T453" t="inlineStr"/>
       <c r="U453" t="inlineStr"/>
@@ -41797,6 +41797,1756 @@
       <c r="AB453" t="inlineStr"/>
       <c r="AC453" t="inlineStr"/>
       <c r="AD453" t="n">
+        <v>840474.27</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B454" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C454" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>38</v>
+      </c>
+      <c r="F454" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
+        <v>39</v>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>OUTROS SERVICOS DE TERCEIROS - PESSOA JURIDICA</t>
+        </is>
+      </c>
+      <c r="K454" t="n">
+        <v>3926</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>ENCARGOS FINANCEIROS</t>
+        </is>
+      </c>
+      <c r="M454" t="n">
+        <v>80</v>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>29.979.036/0001-40</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>INSS - INSTITUTO NACIONAL DE SEGURIDADE SOCIAL</t>
+        </is>
+      </c>
+      <c r="Q454" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="R454" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="S454" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="T454" t="inlineStr"/>
+      <c r="U454" t="inlineStr"/>
+      <c r="V454" t="n">
+        <v>0</v>
+      </c>
+      <c r="W454" t="inlineStr"/>
+      <c r="X454" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y454" t="inlineStr"/>
+      <c r="Z454" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="AA454" t="inlineStr"/>
+      <c r="AB454" t="inlineStr"/>
+      <c r="AC454" t="inlineStr"/>
+      <c r="AD454" t="n">
+        <v>38.05</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B455" t="n">
+        <v>9473171</v>
+      </c>
+      <c r="C455" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>171</v>
+      </c>
+      <c r="F455" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>41</v>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K455" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M455" t="n">
+        <v>80</v>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>16.784.720/0001-25</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>PM FORMIGA</t>
+        </is>
+      </c>
+      <c r="Q455" t="n">
+        <v>693533.1</v>
+      </c>
+      <c r="R455" t="n">
+        <v>693533.1</v>
+      </c>
+      <c r="S455" t="n">
+        <v>693533.1</v>
+      </c>
+      <c r="T455" t="inlineStr"/>
+      <c r="U455" t="inlineStr"/>
+      <c r="V455" t="n">
+        <v>0</v>
+      </c>
+      <c r="W455" t="inlineStr"/>
+      <c r="X455" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y455" t="inlineStr"/>
+      <c r="Z455" t="n">
+        <v>693533.1</v>
+      </c>
+      <c r="AA455" t="inlineStr"/>
+      <c r="AB455" t="inlineStr"/>
+      <c r="AC455" t="inlineStr"/>
+      <c r="AD455" t="n">
+        <v>693533.1</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B456" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C456" t="n">
+        <v>1481</v>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO SOCIAL</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>41</v>
+      </c>
+      <c r="F456" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>39</v>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>OUTROS SERVICOS DE TERCEIROS - PESSOA JURIDICA</t>
+        </is>
+      </c>
+      <c r="K456" t="n">
+        <v>3926</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>ENCARGOS FINANCEIROS</t>
+        </is>
+      </c>
+      <c r="M456" t="n">
+        <v>80</v>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>29.979.036/0001-40</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>INSS - INSTITUTO NACIONAL DE SEGURIDADE SOCIAL</t>
+        </is>
+      </c>
+      <c r="Q456" t="n">
+        <v>83.23999999999999</v>
+      </c>
+      <c r="R456" t="n">
+        <v>83.23999999999999</v>
+      </c>
+      <c r="S456" t="n">
+        <v>83.23999999999999</v>
+      </c>
+      <c r="T456" t="inlineStr"/>
+      <c r="U456" t="inlineStr"/>
+      <c r="V456" t="n">
+        <v>0</v>
+      </c>
+      <c r="W456" t="inlineStr"/>
+      <c r="X456" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y456" t="inlineStr"/>
+      <c r="Z456" t="n">
+        <v>83.23999999999999</v>
+      </c>
+      <c r="AA456" t="inlineStr"/>
+      <c r="AB456" t="inlineStr"/>
+      <c r="AC456" t="inlineStr"/>
+      <c r="AD456" t="n">
+        <v>83.23999999999999</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B457" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C457" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>82</v>
+      </c>
+      <c r="F457" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>1511189 000054/2026</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>52</v>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K457" t="n">
+        <v>5214</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>MOBILIARIO</t>
+        </is>
+      </c>
+      <c r="M457" t="n">
+        <v>80</v>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>44.216.778/0001-08</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>RIVERA MOVEIS INDUSTRIA E COMERCIO LTDA</t>
+        </is>
+      </c>
+      <c r="Q457" t="n">
+        <v>4470</v>
+      </c>
+      <c r="R457" t="n">
+        <v>0</v>
+      </c>
+      <c r="S457" t="n">
+        <v>0</v>
+      </c>
+      <c r="T457" t="inlineStr"/>
+      <c r="U457" t="inlineStr"/>
+      <c r="V457" t="inlineStr"/>
+      <c r="W457" t="inlineStr"/>
+      <c r="X457" t="inlineStr"/>
+      <c r="Y457" t="inlineStr"/>
+      <c r="Z457" t="n">
+        <v>4470</v>
+      </c>
+      <c r="AA457" t="inlineStr"/>
+      <c r="AB457" t="inlineStr"/>
+      <c r="AC457" t="inlineStr"/>
+      <c r="AD457" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B458" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C458" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>83</v>
+      </c>
+      <c r="F458" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>1511189 000054/2026</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>52</v>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K458" t="n">
+        <v>5214</v>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>MOBILIARIO</t>
+        </is>
+      </c>
+      <c r="M458" t="n">
+        <v>80</v>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>21.306.287/0001-52</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>TECNO 2000 INDUSTRIA E COMERCIO LTDA</t>
+        </is>
+      </c>
+      <c r="Q458" t="n">
+        <v>11676.5</v>
+      </c>
+      <c r="R458" t="n">
+        <v>0</v>
+      </c>
+      <c r="S458" t="n">
+        <v>0</v>
+      </c>
+      <c r="T458" t="inlineStr"/>
+      <c r="U458" t="inlineStr"/>
+      <c r="V458" t="inlineStr"/>
+      <c r="W458" t="inlineStr"/>
+      <c r="X458" t="inlineStr"/>
+      <c r="Y458" t="inlineStr"/>
+      <c r="Z458" t="n">
+        <v>11676.5</v>
+      </c>
+      <c r="AA458" t="inlineStr"/>
+      <c r="AB458" t="inlineStr"/>
+      <c r="AC458" t="inlineStr"/>
+      <c r="AD458" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B459" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C459" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>84</v>
+      </c>
+      <c r="F459" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>1511189 000035/2026</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>52</v>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K459" t="n">
+        <v>5225</v>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>APARELHOS E UTENSILIOS DOMESTICOS</t>
+        </is>
+      </c>
+      <c r="M459" t="n">
+        <v>80</v>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>18.132.510/0001-88</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>MARCELO EUSTAQUIO DE OLIVEIRA LTDA</t>
+        </is>
+      </c>
+      <c r="Q459" t="n">
+        <v>2986.8</v>
+      </c>
+      <c r="R459" t="n">
+        <v>0</v>
+      </c>
+      <c r="S459" t="n">
+        <v>0</v>
+      </c>
+      <c r="T459" t="inlineStr"/>
+      <c r="U459" t="inlineStr"/>
+      <c r="V459" t="inlineStr"/>
+      <c r="W459" t="inlineStr"/>
+      <c r="X459" t="inlineStr"/>
+      <c r="Y459" t="inlineStr"/>
+      <c r="Z459" t="n">
+        <v>2986.8</v>
+      </c>
+      <c r="AA459" t="inlineStr"/>
+      <c r="AB459" t="inlineStr"/>
+      <c r="AC459" t="inlineStr"/>
+      <c r="AD459" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B460" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C460" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>85</v>
+      </c>
+      <c r="F460" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>1511189 000047/2026</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I460" t="n">
+        <v>52</v>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K460" t="n">
+        <v>5214</v>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>MOBILIARIO</t>
+        </is>
+      </c>
+      <c r="M460" t="n">
+        <v>80</v>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>23.044.715/0002-22</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>DETTO MOBILIARIO CORPORATIVO LTDA</t>
+        </is>
+      </c>
+      <c r="Q460" t="n">
+        <v>4597.8</v>
+      </c>
+      <c r="R460" t="n">
+        <v>0</v>
+      </c>
+      <c r="S460" t="n">
+        <v>0</v>
+      </c>
+      <c r="T460" t="inlineStr"/>
+      <c r="U460" t="inlineStr"/>
+      <c r="V460" t="inlineStr"/>
+      <c r="W460" t="inlineStr"/>
+      <c r="X460" t="inlineStr"/>
+      <c r="Y460" t="inlineStr"/>
+      <c r="Z460" t="n">
+        <v>4597.8</v>
+      </c>
+      <c r="AA460" t="inlineStr"/>
+      <c r="AB460" t="inlineStr"/>
+      <c r="AC460" t="inlineStr"/>
+      <c r="AD460" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B461" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C461" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>269</v>
+      </c>
+      <c r="F461" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>51</v>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K461" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M461" t="n">
+        <v>80</v>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q461" t="n">
+        <v>5943495.38</v>
+      </c>
+      <c r="R461" t="n">
+        <v>0</v>
+      </c>
+      <c r="S461" t="n">
+        <v>0</v>
+      </c>
+      <c r="T461" t="inlineStr"/>
+      <c r="U461" t="inlineStr"/>
+      <c r="V461" t="n">
+        <v>0</v>
+      </c>
+      <c r="W461" t="inlineStr"/>
+      <c r="X461" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y461" t="inlineStr"/>
+      <c r="Z461" t="n">
+        <v>5943495.38</v>
+      </c>
+      <c r="AA461" t="inlineStr"/>
+      <c r="AB461" t="inlineStr"/>
+      <c r="AC461" t="inlineStr"/>
+      <c r="AD461" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B462" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C462" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>270</v>
+      </c>
+      <c r="F462" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>51</v>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K462" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M462" t="n">
+        <v>80</v>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q462" t="n">
+        <v>1886805.54</v>
+      </c>
+      <c r="R462" t="n">
+        <v>0</v>
+      </c>
+      <c r="S462" t="n">
+        <v>0</v>
+      </c>
+      <c r="T462" t="inlineStr"/>
+      <c r="U462" t="inlineStr"/>
+      <c r="V462" t="n">
+        <v>0</v>
+      </c>
+      <c r="W462" t="inlineStr"/>
+      <c r="X462" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y462" t="inlineStr"/>
+      <c r="Z462" t="n">
+        <v>1886805.54</v>
+      </c>
+      <c r="AA462" t="inlineStr"/>
+      <c r="AB462" t="inlineStr"/>
+      <c r="AC462" t="inlineStr"/>
+      <c r="AD462" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B463" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C463" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>271</v>
+      </c>
+      <c r="F463" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>51</v>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K463" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M463" t="n">
+        <v>80</v>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q463" t="n">
+        <v>554772.75</v>
+      </c>
+      <c r="R463" t="n">
+        <v>0</v>
+      </c>
+      <c r="S463" t="n">
+        <v>0</v>
+      </c>
+      <c r="T463" t="inlineStr"/>
+      <c r="U463" t="inlineStr"/>
+      <c r="V463" t="n">
+        <v>0</v>
+      </c>
+      <c r="W463" t="inlineStr"/>
+      <c r="X463" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y463" t="inlineStr"/>
+      <c r="Z463" t="n">
+        <v>554772.75</v>
+      </c>
+      <c r="AA463" t="inlineStr"/>
+      <c r="AB463" t="inlineStr"/>
+      <c r="AC463" t="inlineStr"/>
+      <c r="AD463" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B464" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C464" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>272</v>
+      </c>
+      <c r="F464" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>93</v>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K464" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M464" t="n">
+        <v>80</v>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q464" t="n">
+        <v>470000</v>
+      </c>
+      <c r="R464" t="n">
+        <v>0</v>
+      </c>
+      <c r="S464" t="n">
+        <v>0</v>
+      </c>
+      <c r="T464" t="inlineStr"/>
+      <c r="U464" t="inlineStr"/>
+      <c r="V464" t="n">
+        <v>0</v>
+      </c>
+      <c r="W464" t="inlineStr"/>
+      <c r="X464" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y464" t="inlineStr"/>
+      <c r="Z464" t="n">
+        <v>470000</v>
+      </c>
+      <c r="AA464" t="inlineStr"/>
+      <c r="AB464" t="inlineStr"/>
+      <c r="AC464" t="inlineStr"/>
+      <c r="AD464" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B465" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C465" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>273</v>
+      </c>
+      <c r="F465" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I465" t="n">
+        <v>93</v>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K465" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M465" t="n">
+        <v>80</v>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q465" t="n">
+        <v>55000</v>
+      </c>
+      <c r="R465" t="n">
+        <v>0</v>
+      </c>
+      <c r="S465" t="n">
+        <v>0</v>
+      </c>
+      <c r="T465" t="inlineStr"/>
+      <c r="U465" t="inlineStr"/>
+      <c r="V465" t="n">
+        <v>0</v>
+      </c>
+      <c r="W465" t="inlineStr"/>
+      <c r="X465" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y465" t="inlineStr"/>
+      <c r="Z465" t="n">
+        <v>55000</v>
+      </c>
+      <c r="AA465" t="inlineStr"/>
+      <c r="AB465" t="inlineStr"/>
+      <c r="AC465" t="inlineStr"/>
+      <c r="AD465" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B466" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C466" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>86</v>
+      </c>
+      <c r="F466" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>1511189 000163/2026</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I466" t="n">
+        <v>52</v>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K466" t="n">
+        <v>5214</v>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>MOBILIARIO</t>
+        </is>
+      </c>
+      <c r="M466" t="n">
+        <v>80</v>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>04.443.182/0001-26</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>UFFICIO INDUSTRIA E COMERCIO DE MOVEIS LTDA</t>
+        </is>
+      </c>
+      <c r="Q466" t="n">
+        <v>27159.78</v>
+      </c>
+      <c r="R466" t="n">
+        <v>0</v>
+      </c>
+      <c r="S466" t="n">
+        <v>0</v>
+      </c>
+      <c r="T466" t="inlineStr"/>
+      <c r="U466" t="inlineStr"/>
+      <c r="V466" t="inlineStr"/>
+      <c r="W466" t="inlineStr"/>
+      <c r="X466" t="inlineStr"/>
+      <c r="Y466" t="inlineStr"/>
+      <c r="Z466" t="n">
+        <v>27159.78</v>
+      </c>
+      <c r="AA466" t="inlineStr"/>
+      <c r="AB466" t="inlineStr"/>
+      <c r="AC466" t="inlineStr"/>
+      <c r="AD466" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B467" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C467" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>87</v>
+      </c>
+      <c r="F467" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>1511189 000163/2026</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I467" t="n">
+        <v>52</v>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K467" t="n">
+        <v>5214</v>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>MOBILIARIO</t>
+        </is>
+      </c>
+      <c r="M467" t="n">
+        <v>80</v>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>81.114.803/0001-79</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>W3 INDUSTRIAS REUNIDAS S/A</t>
+        </is>
+      </c>
+      <c r="Q467" t="n">
+        <v>14725.68</v>
+      </c>
+      <c r="R467" t="n">
+        <v>0</v>
+      </c>
+      <c r="S467" t="n">
+        <v>0</v>
+      </c>
+      <c r="T467" t="inlineStr"/>
+      <c r="U467" t="inlineStr"/>
+      <c r="V467" t="inlineStr"/>
+      <c r="W467" t="inlineStr"/>
+      <c r="X467" t="inlineStr"/>
+      <c r="Y467" t="inlineStr"/>
+      <c r="Z467" t="n">
+        <v>14725.68</v>
+      </c>
+      <c r="AA467" t="inlineStr"/>
+      <c r="AB467" t="inlineStr"/>
+      <c r="AC467" t="inlineStr"/>
+      <c r="AD467" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B468" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C468" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>91</v>
+      </c>
+      <c r="F468" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>1511189 000173/2026</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I468" t="n">
+        <v>52</v>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K468" t="n">
+        <v>5214</v>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>MOBILIARIO</t>
+        </is>
+      </c>
+      <c r="M468" t="n">
+        <v>80</v>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>65.149.197/0002-51</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>REPREMIG REPRESENTACAO E COMERCIO DE MINAS GERAIS LTDA</t>
+        </is>
+      </c>
+      <c r="Q468" t="n">
+        <v>896.3</v>
+      </c>
+      <c r="R468" t="n">
+        <v>0</v>
+      </c>
+      <c r="S468" t="n">
+        <v>0</v>
+      </c>
+      <c r="T468" t="inlineStr"/>
+      <c r="U468" t="inlineStr"/>
+      <c r="V468" t="inlineStr"/>
+      <c r="W468" t="inlineStr"/>
+      <c r="X468" t="inlineStr"/>
+      <c r="Y468" t="inlineStr"/>
+      <c r="Z468" t="n">
+        <v>896.3</v>
+      </c>
+      <c r="AA468" t="inlineStr"/>
+      <c r="AB468" t="inlineStr"/>
+      <c r="AC468" t="inlineStr"/>
+      <c r="AD468" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B469" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C469" t="n">
+        <v>1231</v>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>468</v>
+      </c>
+      <c r="F469" s="2" t="n">
+        <v>46200</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I469" t="n">
+        <v>37</v>
+      </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K469" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M469" t="n">
+        <v>80</v>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q469" t="n">
+        <v>1531.04</v>
+      </c>
+      <c r="R469" t="n">
+        <v>0</v>
+      </c>
+      <c r="S469" t="n">
+        <v>0</v>
+      </c>
+      <c r="T469" t="inlineStr"/>
+      <c r="U469" t="inlineStr"/>
+      <c r="V469" t="n">
+        <v>0</v>
+      </c>
+      <c r="W469" t="inlineStr"/>
+      <c r="X469" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y469" t="inlineStr"/>
+      <c r="Z469" t="n">
+        <v>1531.04</v>
+      </c>
+      <c r="AA469" t="inlineStr"/>
+      <c r="AB469" t="inlineStr"/>
+      <c r="AC469" t="inlineStr"/>
+      <c r="AD469" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B470" t="n">
+        <v>9473171</v>
+      </c>
+      <c r="C470" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>181</v>
+      </c>
+      <c r="F470" s="2" t="n">
+        <v>46202</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I470" t="n">
+        <v>41</v>
+      </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K470" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M470" t="n">
+        <v>80</v>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>17.694.860/0001-75</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>PM INIMUTABA</t>
+        </is>
+      </c>
+      <c r="Q470" t="n">
+        <v>842744.46</v>
+      </c>
+      <c r="R470" t="n">
+        <v>842744.46</v>
+      </c>
+      <c r="S470" t="n">
+        <v>842744.46</v>
+      </c>
+      <c r="T470" t="inlineStr"/>
+      <c r="U470" t="inlineStr"/>
+      <c r="V470" t="n">
+        <v>0</v>
+      </c>
+      <c r="W470" t="inlineStr"/>
+      <c r="X470" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y470" t="inlineStr"/>
+      <c r="Z470" t="n">
+        <v>842744.46</v>
+      </c>
+      <c r="AA470" t="inlineStr"/>
+      <c r="AB470" t="inlineStr"/>
+      <c r="AC470" t="inlineStr"/>
+      <c r="AD470" t="n">
+        <v>842744.46</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B471" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C471" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>1463</v>
+      </c>
+      <c r="F471" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I471" t="n">
+        <v>42</v>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K471" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M471" t="n">
+        <v>80</v>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>01.613.204/0001-60</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>PM PINGO D'AGUA</t>
+        </is>
+      </c>
+      <c r="Q471" t="n">
+        <v>692897.8</v>
+      </c>
+      <c r="R471" t="n">
+        <v>692897.8</v>
+      </c>
+      <c r="S471" t="n">
+        <v>0</v>
+      </c>
+      <c r="T471" t="inlineStr"/>
+      <c r="U471" t="inlineStr"/>
+      <c r="V471" t="inlineStr"/>
+      <c r="W471" t="inlineStr"/>
+      <c r="X471" t="inlineStr"/>
+      <c r="Y471" t="inlineStr"/>
+      <c r="Z471" t="n">
+        <v>692897.8</v>
+      </c>
+      <c r="AA471" t="inlineStr"/>
+      <c r="AB471" t="inlineStr"/>
+      <c r="AC471" t="inlineStr"/>
+      <c r="AD471" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B472" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C472" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>1464</v>
+      </c>
+      <c r="F472" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I472" t="n">
+        <v>42</v>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K472" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M472" t="n">
+        <v>80</v>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>01.613.204/0001-60</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>PM PINGO D'AGUA</t>
+        </is>
+      </c>
+      <c r="Q472" t="n">
+        <v>166966.67</v>
+      </c>
+      <c r="R472" t="n">
+        <v>166966.67</v>
+      </c>
+      <c r="S472" t="n">
+        <v>0</v>
+      </c>
+      <c r="T472" t="inlineStr"/>
+      <c r="U472" t="inlineStr"/>
+      <c r="V472" t="inlineStr"/>
+      <c r="W472" t="inlineStr"/>
+      <c r="X472" t="inlineStr"/>
+      <c r="Y472" t="inlineStr"/>
+      <c r="Z472" t="n">
+        <v>166966.67</v>
+      </c>
+      <c r="AA472" t="inlineStr"/>
+      <c r="AB472" t="inlineStr"/>
+      <c r="AC472" t="inlineStr"/>
+      <c r="AD472" t="n">
         <v>0</v>
       </c>
     </row>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD472"/>
+  <dimension ref="A1:AD495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13756,7 +13756,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>179052.97</v>
+        <v>211792.55</v>
       </c>
       <c r="R147" t="n">
         <v>162683.18</v>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="n">
-        <v>179052.97</v>
+        <v>211792.55</v>
       </c>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr"/>
@@ -13944,13 +13944,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>58000.01</v>
+        <v>62000.01</v>
       </c>
       <c r="R149" t="n">
         <v>43144.66</v>
       </c>
       <c r="S149" t="n">
-        <v>38117.53</v>
+        <v>39690.37</v>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
@@ -13963,13 +13963,13 @@
       </c>
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="n">
-        <v>58000.01</v>
+        <v>62000.01</v>
       </c>
       <c r="AA149" t="inlineStr"/>
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr"/>
       <c r="AD149" t="n">
-        <v>38117.53</v>
+        <v>39690.37</v>
       </c>
     </row>
     <row r="150">
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>415793.46</v>
+        <v>503776.08</v>
       </c>
       <c r="R150" t="n">
         <v>385355.31</v>
@@ -14057,7 +14057,7 @@
       </c>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="n">
-        <v>415793.46</v>
+        <v>503776.08</v>
       </c>
       <c r="AA150" t="inlineStr"/>
       <c r="AB150" t="inlineStr"/>
@@ -14132,13 +14132,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>1181540.53</v>
+        <v>1429064.13</v>
       </c>
       <c r="R151" t="n">
         <v>1129581.26</v>
       </c>
       <c r="S151" t="n">
-        <v>749422.04</v>
+        <v>942258.29</v>
       </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
@@ -14151,13 +14151,13 @@
       </c>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="n">
-        <v>1181540.53</v>
+        <v>1429064.13</v>
       </c>
       <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="n">
-        <v>749422.04</v>
+        <v>942258.29</v>
       </c>
     </row>
     <row r="152">
@@ -14226,13 +14226,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>78802.64999999999</v>
+        <v>111802.65</v>
       </c>
       <c r="R152" t="n">
         <v>71246.27</v>
       </c>
       <c r="S152" t="n">
-        <v>45430.54</v>
+        <v>66180.75</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
@@ -14245,13 +14245,13 @@
       </c>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="n">
-        <v>78802.64999999999</v>
+        <v>111802.65</v>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="n">
-        <v>45430.54</v>
+        <v>66180.75</v>
       </c>
     </row>
     <row r="153">
@@ -14320,13 +14320,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>7560.85</v>
+        <v>12560.85</v>
       </c>
       <c r="R153" t="n">
         <v>7560.81</v>
       </c>
       <c r="S153" t="n">
-        <v>5275.1</v>
+        <v>7285.08</v>
       </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
@@ -14339,13 +14339,13 @@
       </c>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="n">
-        <v>7560.85</v>
+        <v>12560.85</v>
       </c>
       <c r="AA153" t="inlineStr"/>
       <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="n">
-        <v>5275.1</v>
+        <v>7285.08</v>
       </c>
     </row>
     <row r="154">
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>275791.53</v>
+        <v>337260.81</v>
       </c>
       <c r="R154" t="n">
         <v>228954.73</v>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="n">
-        <v>275791.53</v>
+        <v>337260.81</v>
       </c>
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="inlineStr"/>
@@ -14508,7 +14508,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>33466718.46</v>
+        <v>29576226.46</v>
       </c>
       <c r="R155" t="n">
         <v>4653543.42</v>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="n">
-        <v>33466718.46</v>
+        <v>29576226.46</v>
       </c>
       <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="inlineStr"/>
@@ -14605,10 +14605,10 @@
         <v>45000</v>
       </c>
       <c r="R156" t="n">
-        <v>18315.7</v>
+        <v>36030.57</v>
       </c>
       <c r="S156" t="n">
-        <v>18315.7</v>
+        <v>36030.57</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14627,7 +14627,7 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>18315.7</v>
+        <v>36030.57</v>
       </c>
     </row>
     <row r="157">
@@ -17229,7 +17229,7 @@
         <v>348827.24</v>
       </c>
       <c r="R184" t="n">
-        <v>271408.09</v>
+        <v>348787.24</v>
       </c>
       <c r="S184" t="n">
         <v>241553.2</v>
@@ -17323,7 +17323,7 @@
         <v>1396844.69</v>
       </c>
       <c r="R185" t="n">
-        <v>1109258.91</v>
+        <v>1396840.69</v>
       </c>
       <c r="S185" t="n">
         <v>986429.4300000001</v>
@@ -17417,7 +17417,7 @@
         <v>1287702.95</v>
       </c>
       <c r="R186" t="n">
-        <v>1010482.55</v>
+        <v>1287700.95</v>
       </c>
       <c r="S186" t="n">
         <v>852437.58</v>
@@ -17511,7 +17511,7 @@
         <v>960793.26</v>
       </c>
       <c r="R187" t="n">
-        <v>777684.27</v>
+        <v>960789.26</v>
       </c>
       <c r="S187" t="n">
         <v>642569.49</v>
@@ -17605,7 +17605,7 @@
         <v>267391.5</v>
       </c>
       <c r="R188" t="n">
-        <v>212899.3</v>
+        <v>267387.5</v>
       </c>
       <c r="S188" t="n">
         <v>189480.38</v>
@@ -17702,7 +17702,7 @@
         <v>30912.24</v>
       </c>
       <c r="S189" t="n">
-        <v>23814.69</v>
+        <v>30164.95</v>
       </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
@@ -17721,7 +17721,7 @@
       <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr"/>
       <c r="AD189" t="n">
-        <v>23814.69</v>
+        <v>30164.95</v>
       </c>
     </row>
     <row r="190">
@@ -18353,10 +18353,10 @@
         <v>521640</v>
       </c>
       <c r="R196" t="n">
-        <v>69000</v>
+        <v>207000</v>
       </c>
       <c r="S196" t="n">
-        <v>0</v>
+        <v>67965</v>
       </c>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
@@ -18375,7 +18375,7 @@
       <c r="AB196" t="inlineStr"/>
       <c r="AC196" t="inlineStr"/>
       <c r="AD196" t="n">
-        <v>0</v>
+        <v>67965</v>
       </c>
     </row>
     <row r="197">
@@ -18541,7 +18541,7 @@
         <v>68798.59</v>
       </c>
       <c r="R198" t="n">
-        <v>51565.51</v>
+        <v>68798.53999999999</v>
       </c>
       <c r="S198" t="n">
         <v>45893.29</v>
@@ -18638,7 +18638,7 @@
         <v>2163567.83</v>
       </c>
       <c r="S199" t="n">
-        <v>943541.35</v>
+        <v>2137605.03</v>
       </c>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
@@ -18657,7 +18657,7 @@
       <c r="AB199" t="inlineStr"/>
       <c r="AC199" t="inlineStr"/>
       <c r="AD199" t="n">
-        <v>943541.35</v>
+        <v>2137605.03</v>
       </c>
     </row>
     <row r="200">
@@ -18732,7 +18732,7 @@
         <v>3880593.18</v>
       </c>
       <c r="S200" t="n">
-        <v>2320816.81</v>
+        <v>3834026.07</v>
       </c>
       <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
@@ -18751,7 +18751,7 @@
       <c r="AB200" t="inlineStr"/>
       <c r="AC200" t="inlineStr"/>
       <c r="AD200" t="n">
-        <v>2320816.81</v>
+        <v>3834026.07</v>
       </c>
     </row>
     <row r="201">
@@ -20406,7 +20406,7 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>114954.87</v>
+        <v>171017.71</v>
       </c>
       <c r="R218" t="n">
         <v>114954.87</v>
@@ -20425,7 +20425,7 @@
       </c>
       <c r="Y218" t="inlineStr"/>
       <c r="Z218" t="n">
-        <v>114954.87</v>
+        <v>171017.71</v>
       </c>
       <c r="AA218" t="inlineStr"/>
       <c r="AB218" t="inlineStr"/>
@@ -20500,7 +20500,7 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>3035.92</v>
+        <v>4578.33</v>
       </c>
       <c r="R219" t="n">
         <v>3035.91</v>
@@ -20519,7 +20519,7 @@
       </c>
       <c r="Y219" t="inlineStr"/>
       <c r="Z219" t="n">
-        <v>3035.92</v>
+        <v>4578.33</v>
       </c>
       <c r="AA219" t="inlineStr"/>
       <c r="AB219" t="inlineStr"/>
@@ -20691,7 +20691,7 @@
         <v>7132375.41</v>
       </c>
       <c r="R221" t="n">
-        <v>0</v>
+        <v>259286.23</v>
       </c>
       <c r="S221" t="n">
         <v>0</v>
@@ -22222,7 +22222,7 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>2612282.3</v>
+        <v>6435680.48</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
@@ -22241,7 +22241,7 @@
       </c>
       <c r="Y238" t="inlineStr"/>
       <c r="Z238" t="n">
-        <v>2612282.3</v>
+        <v>6435680.48</v>
       </c>
       <c r="AA238" t="inlineStr"/>
       <c r="AB238" t="inlineStr"/>
@@ -22316,7 +22316,7 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>90000</v>
+        <v>230000</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
@@ -22335,7 +22335,7 @@
       </c>
       <c r="Y239" t="inlineStr"/>
       <c r="Z239" t="n">
-        <v>90000</v>
+        <v>230000</v>
       </c>
       <c r="AA239" t="inlineStr"/>
       <c r="AB239" t="inlineStr"/>
@@ -22410,7 +22410,7 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>647687.6</v>
+        <v>698765.6</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
@@ -22429,7 +22429,7 @@
       </c>
       <c r="Y240" t="inlineStr"/>
       <c r="Z240" t="n">
-        <v>647687.6</v>
+        <v>698765.6</v>
       </c>
       <c r="AA240" t="inlineStr"/>
       <c r="AB240" t="inlineStr"/>
@@ -22504,7 +22504,7 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>330266.4</v>
+        <v>326805</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="Y241" t="inlineStr"/>
       <c r="Z241" t="n">
-        <v>330266.4</v>
+        <v>326805</v>
       </c>
       <c r="AA241" t="inlineStr"/>
       <c r="AB241" t="inlineStr"/>
@@ -22698,7 +22698,7 @@
         <v>4184317</v>
       </c>
       <c r="S243" t="n">
-        <v>0</v>
+        <v>4184317</v>
       </c>
       <c r="T243" t="inlineStr"/>
       <c r="U243" t="inlineStr"/>
@@ -22713,7 +22713,7 @@
       <c r="AB243" t="inlineStr"/>
       <c r="AC243" t="inlineStr"/>
       <c r="AD243" t="n">
-        <v>0</v>
+        <v>4184317</v>
       </c>
     </row>
     <row r="244">
@@ -26028,7 +26028,7 @@
         <v>5500000</v>
       </c>
       <c r="S280" t="n">
-        <v>0</v>
+        <v>5500000</v>
       </c>
       <c r="T280" t="inlineStr"/>
       <c r="U280" t="inlineStr"/>
@@ -26043,7 +26043,7 @@
       <c r="AB280" t="inlineStr"/>
       <c r="AC280" t="inlineStr"/>
       <c r="AD280" t="n">
-        <v>0</v>
+        <v>5500000</v>
       </c>
     </row>
     <row r="281">
@@ -26118,7 +26118,7 @@
         <v>7000000</v>
       </c>
       <c r="S281" t="n">
-        <v>0</v>
+        <v>7000000</v>
       </c>
       <c r="T281" t="inlineStr"/>
       <c r="U281" t="inlineStr"/>
@@ -26133,7 +26133,7 @@
       <c r="AB281" t="inlineStr"/>
       <c r="AC281" t="inlineStr"/>
       <c r="AD281" t="n">
-        <v>0</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="282">
@@ -26205,10 +26205,10 @@
         <v>1161804</v>
       </c>
       <c r="R282" t="n">
-        <v>0</v>
+        <v>640789</v>
       </c>
       <c r="S282" t="n">
-        <v>0</v>
+        <v>640789</v>
       </c>
       <c r="T282" t="inlineStr"/>
       <c r="U282" t="inlineStr"/>
@@ -26223,7 +26223,7 @@
       <c r="AB282" t="inlineStr"/>
       <c r="AC282" t="inlineStr"/>
       <c r="AD282" t="n">
-        <v>0</v>
+        <v>640789</v>
       </c>
     </row>
     <row r="283">
@@ -26388,7 +26388,7 @@
         <v>1500000</v>
       </c>
       <c r="S284" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="T284" t="inlineStr"/>
       <c r="U284" t="inlineStr"/>
@@ -26403,7 +26403,7 @@
       <c r="AB284" t="inlineStr"/>
       <c r="AC284" t="inlineStr"/>
       <c r="AD284" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
     </row>
     <row r="285">
@@ -26568,7 +26568,7 @@
         <v>627500</v>
       </c>
       <c r="S286" t="n">
-        <v>0</v>
+        <v>627500</v>
       </c>
       <c r="T286" t="inlineStr"/>
       <c r="U286" t="inlineStr"/>
@@ -26583,7 +26583,7 @@
       <c r="AB286" t="inlineStr"/>
       <c r="AC286" t="inlineStr"/>
       <c r="AD286" t="n">
-        <v>0</v>
+        <v>627500</v>
       </c>
     </row>
     <row r="287">
@@ -27574,7 +27574,7 @@
         <v>54521.23</v>
       </c>
       <c r="S297" t="n">
-        <v>27722.66</v>
+        <v>54521.23</v>
       </c>
       <c r="T297" t="inlineStr"/>
       <c r="U297" t="inlineStr"/>
@@ -27589,7 +27589,7 @@
       <c r="AB297" t="inlineStr"/>
       <c r="AC297" t="inlineStr"/>
       <c r="AD297" t="n">
-        <v>27722.66</v>
+        <v>54521.23</v>
       </c>
     </row>
     <row r="298">
@@ -27664,7 +27664,7 @@
         <v>952.01</v>
       </c>
       <c r="S298" t="n">
-        <v>439.39</v>
+        <v>952.01</v>
       </c>
       <c r="T298" t="inlineStr"/>
       <c r="U298" t="inlineStr"/>
@@ -27679,7 +27679,7 @@
       <c r="AB298" t="inlineStr"/>
       <c r="AC298" t="inlineStr"/>
       <c r="AD298" t="n">
-        <v>439.39</v>
+        <v>952.01</v>
       </c>
     </row>
     <row r="299">
@@ -36212,7 +36212,7 @@
         </is>
       </c>
       <c r="Q393" t="n">
-        <v>32739.58</v>
+        <v>98218.74000000001</v>
       </c>
       <c r="R393" t="n">
         <v>32656.87</v>
@@ -36231,7 +36231,7 @@
       </c>
       <c r="Y393" t="inlineStr"/>
       <c r="Z393" t="n">
-        <v>32739.58</v>
+        <v>98218.74000000001</v>
       </c>
       <c r="AA393" t="inlineStr"/>
       <c r="AB393" t="inlineStr"/>
@@ -36677,7 +36677,7 @@
         <v>122514.31</v>
       </c>
       <c r="R398" t="n">
-        <v>57506.44</v>
+        <v>122514.28</v>
       </c>
       <c r="S398" t="n">
         <v>51180.73</v>
@@ -36771,7 +36771,7 @@
         <v>37200.58</v>
       </c>
       <c r="R399" t="n">
-        <v>33755.73</v>
+        <v>37200.57</v>
       </c>
       <c r="S399" t="n">
         <v>30113.19</v>
@@ -36865,7 +36865,7 @@
         <v>20831.63</v>
       </c>
       <c r="R400" t="n">
-        <v>20455.23</v>
+        <v>20831.62</v>
       </c>
       <c r="S400" t="n">
         <v>18243.88</v>
@@ -36959,7 +36959,7 @@
         <v>83870.03999999999</v>
       </c>
       <c r="R401" t="n">
-        <v>77101.56</v>
+        <v>83870.03</v>
       </c>
       <c r="S401" t="n">
         <v>25305.6</v>
@@ -37053,7 +37053,7 @@
         <v>82956.12</v>
       </c>
       <c r="R402" t="n">
-        <v>75875.05</v>
+        <v>82956.11</v>
       </c>
       <c r="S402" t="n">
         <v>42058.91</v>
@@ -37147,7 +37147,7 @@
         <v>60486.65</v>
       </c>
       <c r="R403" t="n">
-        <v>55389.54</v>
+        <v>60486.64</v>
       </c>
       <c r="S403" t="n">
         <v>49402.17</v>
@@ -37241,7 +37241,7 @@
         <v>13909.09</v>
       </c>
       <c r="R404" t="n">
-        <v>12237.69</v>
+        <v>13909.08</v>
       </c>
       <c r="S404" t="n">
         <v>10926.23</v>
@@ -37335,7 +37335,7 @@
         <v>3462.29</v>
       </c>
       <c r="R405" t="n">
-        <v>3079.52</v>
+        <v>3462.28</v>
       </c>
       <c r="S405" t="n">
         <v>2748.89</v>
@@ -37426,7 +37426,7 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>45068.98</v>
+        <v>73360.92</v>
       </c>
       <c r="R406" t="n">
         <v>24991.21</v>
@@ -37441,7 +37441,7 @@
       <c r="X406" t="inlineStr"/>
       <c r="Y406" t="inlineStr"/>
       <c r="Z406" t="n">
-        <v>45068.98</v>
+        <v>73360.92</v>
       </c>
       <c r="AA406" t="inlineStr"/>
       <c r="AB406" t="inlineStr"/>
@@ -37516,7 +37516,7 @@
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>974.33</v>
+        <v>2027.65</v>
       </c>
       <c r="R407" t="n">
         <v>974.3200000000001</v>
@@ -37531,7 +37531,7 @@
       <c r="X407" t="inlineStr"/>
       <c r="Y407" t="inlineStr"/>
       <c r="Z407" t="n">
-        <v>974.33</v>
+        <v>2027.65</v>
       </c>
       <c r="AA407" t="inlineStr"/>
       <c r="AB407" t="inlineStr"/>
@@ -37789,10 +37789,10 @@
         <v>79560.25</v>
       </c>
       <c r="R410" t="n">
-        <v>0</v>
+        <v>79560.25</v>
       </c>
       <c r="S410" t="n">
-        <v>0</v>
+        <v>79560.25</v>
       </c>
       <c r="T410" t="inlineStr"/>
       <c r="U410" t="inlineStr"/>
@@ -37807,7 +37807,7 @@
       <c r="AB410" t="inlineStr"/>
       <c r="AC410" t="inlineStr"/>
       <c r="AD410" t="n">
-        <v>0</v>
+        <v>79560.25</v>
       </c>
     </row>
     <row r="411">
@@ -37876,7 +37876,7 @@
         </is>
       </c>
       <c r="Q411" t="n">
-        <v>9418.49</v>
+        <v>12892.12</v>
       </c>
       <c r="R411" t="n">
         <v>8618.49</v>
@@ -37895,7 +37895,7 @@
       </c>
       <c r="Y411" t="inlineStr"/>
       <c r="Z411" t="n">
-        <v>9418.49</v>
+        <v>12892.12</v>
       </c>
       <c r="AA411" t="inlineStr"/>
       <c r="AB411" t="inlineStr"/>
@@ -37970,7 +37970,7 @@
         </is>
       </c>
       <c r="Q412" t="n">
-        <v>29040.66</v>
+        <v>34485.5</v>
       </c>
       <c r="R412" t="n">
         <v>28840.66</v>
@@ -37989,7 +37989,7 @@
       </c>
       <c r="Y412" t="inlineStr"/>
       <c r="Z412" t="n">
-        <v>29040.66</v>
+        <v>34485.5</v>
       </c>
       <c r="AA412" t="inlineStr"/>
       <c r="AB412" t="inlineStr"/>
@@ -38064,7 +38064,7 @@
         </is>
       </c>
       <c r="Q413" t="n">
-        <v>72267.23</v>
+        <v>83169.53</v>
       </c>
       <c r="R413" t="n">
         <v>72067.23</v>
@@ -38083,7 +38083,7 @@
       </c>
       <c r="Y413" t="inlineStr"/>
       <c r="Z413" t="n">
-        <v>72267.23</v>
+        <v>83169.53</v>
       </c>
       <c r="AA413" t="inlineStr"/>
       <c r="AB413" t="inlineStr"/>
@@ -38255,7 +38255,7 @@
         <v>274617.42</v>
       </c>
       <c r="R415" t="n">
-        <v>0</v>
+        <v>13783.27</v>
       </c>
       <c r="S415" t="n">
         <v>0</v>
@@ -38352,7 +38352,7 @@
         <v>773832.3</v>
       </c>
       <c r="S416" t="n">
-        <v>0</v>
+        <v>764546.3</v>
       </c>
       <c r="T416" t="inlineStr"/>
       <c r="U416" t="inlineStr"/>
@@ -38371,7 +38371,7 @@
       <c r="AB416" t="inlineStr"/>
       <c r="AC416" t="inlineStr"/>
       <c r="AD416" t="n">
-        <v>0</v>
+        <v>764546.3</v>
       </c>
     </row>
     <row r="417">
@@ -38440,13 +38440,13 @@
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>23010.54</v>
+        <v>23956.2</v>
       </c>
       <c r="R417" t="n">
         <v>11978.1</v>
       </c>
       <c r="S417" t="n">
-        <v>0</v>
+        <v>11978.1</v>
       </c>
       <c r="T417" t="inlineStr"/>
       <c r="U417" t="inlineStr"/>
@@ -38455,13 +38455,13 @@
       <c r="X417" t="inlineStr"/>
       <c r="Y417" t="inlineStr"/>
       <c r="Z417" t="n">
-        <v>23010.54</v>
+        <v>23956.2</v>
       </c>
       <c r="AA417" t="inlineStr"/>
       <c r="AB417" t="inlineStr"/>
       <c r="AC417" t="inlineStr"/>
       <c r="AD417" t="n">
-        <v>0</v>
+        <v>11978.1</v>
       </c>
     </row>
     <row r="418">
@@ -38530,13 +38530,13 @@
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>1160.87</v>
+        <v>1688.7</v>
       </c>
       <c r="R418" t="n">
         <v>719.21</v>
       </c>
       <c r="S418" t="n">
-        <v>0</v>
+        <v>191.38</v>
       </c>
       <c r="T418" t="inlineStr"/>
       <c r="U418" t="inlineStr"/>
@@ -38545,13 +38545,13 @@
       <c r="X418" t="inlineStr"/>
       <c r="Y418" t="inlineStr"/>
       <c r="Z418" t="n">
-        <v>1160.87</v>
+        <v>1688.7</v>
       </c>
       <c r="AA418" t="inlineStr"/>
       <c r="AB418" t="inlineStr"/>
       <c r="AC418" t="inlineStr"/>
       <c r="AD418" t="n">
-        <v>0</v>
+        <v>191.38</v>
       </c>
     </row>
     <row r="419">
@@ -38620,13 +38620,13 @@
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>27770.9</v>
+        <v>55541.8</v>
       </c>
       <c r="R419" t="n">
         <v>27770.9</v>
       </c>
       <c r="S419" t="n">
-        <v>0</v>
+        <v>27770.9</v>
       </c>
       <c r="T419" t="inlineStr"/>
       <c r="U419" t="inlineStr"/>
@@ -38635,13 +38635,13 @@
       <c r="X419" t="inlineStr"/>
       <c r="Y419" t="inlineStr"/>
       <c r="Z419" t="n">
-        <v>27770.9</v>
+        <v>55541.8</v>
       </c>
       <c r="AA419" t="inlineStr"/>
       <c r="AB419" t="inlineStr"/>
       <c r="AC419" t="inlineStr"/>
       <c r="AD419" t="n">
-        <v>0</v>
+        <v>27770.9</v>
       </c>
     </row>
     <row r="420">
@@ -38716,7 +38716,7 @@
         <v>96.58</v>
       </c>
       <c r="S420" t="n">
-        <v>0</v>
+        <v>96.58</v>
       </c>
       <c r="T420" t="inlineStr"/>
       <c r="U420" t="inlineStr"/>
@@ -38731,7 +38731,7 @@
       <c r="AB420" t="inlineStr"/>
       <c r="AC420" t="inlineStr"/>
       <c r="AD420" t="n">
-        <v>0</v>
+        <v>96.58</v>
       </c>
     </row>
     <row r="421">
@@ -38806,7 +38806,7 @@
         <v>979.04</v>
       </c>
       <c r="S421" t="n">
-        <v>0</v>
+        <v>979.04</v>
       </c>
       <c r="T421" t="inlineStr"/>
       <c r="U421" t="inlineStr"/>
@@ -38821,7 +38821,7 @@
       <c r="AB421" t="inlineStr"/>
       <c r="AC421" t="inlineStr"/>
       <c r="AD421" t="n">
-        <v>0</v>
+        <v>979.04</v>
       </c>
     </row>
     <row r="422">
@@ -38890,7 +38890,7 @@
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>490.09</v>
+        <v>979.1799999999999</v>
       </c>
       <c r="R422" t="n">
         <v>489.09</v>
@@ -38905,7 +38905,7 @@
       <c r="X422" t="inlineStr"/>
       <c r="Y422" t="inlineStr"/>
       <c r="Z422" t="n">
-        <v>490.09</v>
+        <v>979.1799999999999</v>
       </c>
       <c r="AA422" t="inlineStr"/>
       <c r="AB422" t="inlineStr"/>
@@ -39262,7 +39262,7 @@
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>3648519</v>
+        <v>3653077.24</v>
       </c>
       <c r="R426" t="n">
         <v>0</v>
@@ -39281,7 +39281,7 @@
       </c>
       <c r="Y426" t="inlineStr"/>
       <c r="Z426" t="n">
-        <v>3648519</v>
+        <v>3653077.24</v>
       </c>
       <c r="AA426" t="inlineStr"/>
       <c r="AB426" t="inlineStr"/>
@@ -39356,7 +39356,7 @@
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>380415.6</v>
+        <v>375825.75</v>
       </c>
       <c r="R427" t="n">
         <v>0</v>
@@ -39375,7 +39375,7 @@
       </c>
       <c r="Y427" t="inlineStr"/>
       <c r="Z427" t="n">
-        <v>380415.6</v>
+        <v>375825.75</v>
       </c>
       <c r="AA427" t="inlineStr"/>
       <c r="AB427" t="inlineStr"/>
@@ -40108,7 +40108,7 @@
         </is>
       </c>
       <c r="Q435" t="n">
-        <v>938190.6</v>
+        <v>4233573.04</v>
       </c>
       <c r="R435" t="n">
         <v>0</v>
@@ -40127,7 +40127,7 @@
       </c>
       <c r="Y435" t="inlineStr"/>
       <c r="Z435" t="n">
-        <v>938190.6</v>
+        <v>4233573.04</v>
       </c>
       <c r="AA435" t="inlineStr"/>
       <c r="AB435" t="inlineStr"/>
@@ -40202,7 +40202,7 @@
         </is>
       </c>
       <c r="Q436" t="n">
-        <v>50000</v>
+        <v>220000</v>
       </c>
       <c r="R436" t="n">
         <v>0</v>
@@ -40221,7 +40221,7 @@
       </c>
       <c r="Y436" t="inlineStr"/>
       <c r="Z436" t="n">
-        <v>50000</v>
+        <v>220000</v>
       </c>
       <c r="AA436" t="inlineStr"/>
       <c r="AB436" t="inlineStr"/>
@@ -40296,7 +40296,7 @@
         </is>
       </c>
       <c r="Q437" t="n">
-        <v>95103.89999999999</v>
+        <v>490207.5</v>
       </c>
       <c r="R437" t="n">
         <v>0</v>
@@ -40315,7 +40315,7 @@
       </c>
       <c r="Y437" t="inlineStr"/>
       <c r="Z437" t="n">
-        <v>95103.89999999999</v>
+        <v>490207.5</v>
       </c>
       <c r="AA437" t="inlineStr"/>
       <c r="AB437" t="inlineStr"/>
@@ -40390,7 +40390,7 @@
         </is>
       </c>
       <c r="Q438" t="n">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="R438" t="n">
         <v>0</v>
@@ -40409,7 +40409,7 @@
       </c>
       <c r="Y438" t="inlineStr"/>
       <c r="Z438" t="n">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="AA438" t="inlineStr"/>
       <c r="AB438" t="inlineStr"/>
@@ -41862,7 +41862,7 @@
       </c>
       <c r="P454" t="inlineStr">
         <is>
-          <t>INSS - INSTITUTO NACIONAL DE SEGURIDADE SOCIAL</t>
+          <t>INSTITUTO NACIONAL DO SEGURO SOCIAL</t>
         </is>
       </c>
       <c r="Q454" t="n">
@@ -42050,7 +42050,7 @@
       </c>
       <c r="P456" t="inlineStr">
         <is>
-          <t>INSS - INSTITUTO NACIONAL DE SEGURIDADE SOCIAL</t>
+          <t>INSTITUTO NACIONAL DO SEGURO SOCIAL</t>
         </is>
       </c>
       <c r="Q456" t="n">
@@ -42508,7 +42508,7 @@
         </is>
       </c>
       <c r="Q461" t="n">
-        <v>5943495.38</v>
+        <v>5947766.41</v>
       </c>
       <c r="R461" t="n">
         <v>0</v>
@@ -42527,7 +42527,7 @@
       </c>
       <c r="Y461" t="inlineStr"/>
       <c r="Z461" t="n">
-        <v>5943495.38</v>
+        <v>5947766.41</v>
       </c>
       <c r="AA461" t="inlineStr"/>
       <c r="AB461" t="inlineStr"/>
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="Q462" t="n">
-        <v>1886805.54</v>
+        <v>1884995.3</v>
       </c>
       <c r="R462" t="n">
         <v>0</v>
@@ -42621,7 +42621,7 @@
       </c>
       <c r="Y462" t="inlineStr"/>
       <c r="Z462" t="n">
-        <v>1886805.54</v>
+        <v>1884995.3</v>
       </c>
       <c r="AA462" t="inlineStr"/>
       <c r="AB462" t="inlineStr"/>
@@ -42696,7 +42696,7 @@
         </is>
       </c>
       <c r="Q463" t="n">
-        <v>554772.75</v>
+        <v>552300.45</v>
       </c>
       <c r="R463" t="n">
         <v>0</v>
@@ -42715,7 +42715,7 @@
       </c>
       <c r="Y463" t="inlineStr"/>
       <c r="Z463" t="n">
-        <v>554772.75</v>
+        <v>552300.45</v>
       </c>
       <c r="AA463" t="inlineStr"/>
       <c r="AB463" t="inlineStr"/>
@@ -43436,10 +43436,10 @@
         </is>
       </c>
       <c r="Q471" t="n">
-        <v>692897.8</v>
+        <v>0</v>
       </c>
       <c r="R471" t="n">
-        <v>692897.8</v>
+        <v>0</v>
       </c>
       <c r="S471" t="n">
         <v>0</v>
@@ -43451,7 +43451,7 @@
       <c r="X471" t="inlineStr"/>
       <c r="Y471" t="inlineStr"/>
       <c r="Z471" t="n">
-        <v>692897.8</v>
+        <v>0</v>
       </c>
       <c r="AA471" t="inlineStr"/>
       <c r="AB471" t="inlineStr"/>
@@ -43532,7 +43532,7 @@
         <v>166966.67</v>
       </c>
       <c r="S472" t="n">
-        <v>0</v>
+        <v>166966.67</v>
       </c>
       <c r="T472" t="inlineStr"/>
       <c r="U472" t="inlineStr"/>
@@ -43547,6 +43547,2096 @@
       <c r="AB472" t="inlineStr"/>
       <c r="AC472" t="inlineStr"/>
       <c r="AD472" t="n">
+        <v>166966.67</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B473" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C473" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>1469</v>
+      </c>
+      <c r="F473" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I473" t="n">
+        <v>41</v>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K473" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M473" t="n">
+        <v>80</v>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>14.836.495/0001-06</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>FUNDO MUNICIPAL DE ASSIST. SOCIAL - TIMOTEO</t>
+        </is>
+      </c>
+      <c r="Q473" t="n">
+        <v>996836.97</v>
+      </c>
+      <c r="R473" t="n">
+        <v>996836.97</v>
+      </c>
+      <c r="S473" t="n">
+        <v>996836.97</v>
+      </c>
+      <c r="T473" t="inlineStr"/>
+      <c r="U473" t="inlineStr"/>
+      <c r="V473" t="inlineStr"/>
+      <c r="W473" t="inlineStr"/>
+      <c r="X473" t="inlineStr"/>
+      <c r="Y473" t="inlineStr"/>
+      <c r="Z473" t="n">
+        <v>996836.97</v>
+      </c>
+      <c r="AA473" t="inlineStr"/>
+      <c r="AB473" t="inlineStr"/>
+      <c r="AC473" t="inlineStr"/>
+      <c r="AD473" t="n">
+        <v>996836.97</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B474" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C474" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F474" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I474" t="n">
+        <v>41</v>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K474" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M474" t="n">
+        <v>80</v>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>13.516.483/0001-23</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>FUNDO MUNICIPAL DE ASSIST. SOCIAL - CONSELHEIRO PENA</t>
+        </is>
+      </c>
+      <c r="Q474" t="n">
+        <v>12000</v>
+      </c>
+      <c r="R474" t="n">
+        <v>12000</v>
+      </c>
+      <c r="S474" t="n">
+        <v>12000</v>
+      </c>
+      <c r="T474" t="inlineStr"/>
+      <c r="U474" t="inlineStr"/>
+      <c r="V474" t="inlineStr"/>
+      <c r="W474" t="inlineStr"/>
+      <c r="X474" t="inlineStr"/>
+      <c r="Y474" t="inlineStr"/>
+      <c r="Z474" t="n">
+        <v>12000</v>
+      </c>
+      <c r="AA474" t="inlineStr"/>
+      <c r="AB474" t="inlineStr"/>
+      <c r="AC474" t="inlineStr"/>
+      <c r="AD474" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B475" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C475" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>1471</v>
+      </c>
+      <c r="F475" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I475" t="n">
+        <v>41</v>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K475" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M475" t="n">
+        <v>80</v>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>14.787.516/0001-32</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>FUNDO MUNICIPAL DE ASSIST. SOCIAL - ITUETA</t>
+        </is>
+      </c>
+      <c r="Q475" t="n">
+        <v>161009.98</v>
+      </c>
+      <c r="R475" t="n">
+        <v>161009.98</v>
+      </c>
+      <c r="S475" t="n">
+        <v>161009.98</v>
+      </c>
+      <c r="T475" t="inlineStr"/>
+      <c r="U475" t="inlineStr"/>
+      <c r="V475" t="inlineStr"/>
+      <c r="W475" t="inlineStr"/>
+      <c r="X475" t="inlineStr"/>
+      <c r="Y475" t="inlineStr"/>
+      <c r="Z475" t="n">
+        <v>161009.98</v>
+      </c>
+      <c r="AA475" t="inlineStr"/>
+      <c r="AB475" t="inlineStr"/>
+      <c r="AC475" t="inlineStr"/>
+      <c r="AD475" t="n">
+        <v>161009.98</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B476" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C476" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>1472</v>
+      </c>
+      <c r="F476" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I476" t="n">
+        <v>41</v>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K476" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M476" t="n">
+        <v>80</v>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>13.579.485/0001-61</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>FUNDO MUNICIPAL DE ASSIST. SOCIAL - OURO PRETO</t>
+        </is>
+      </c>
+      <c r="Q476" t="n">
+        <v>365905.71</v>
+      </c>
+      <c r="R476" t="n">
+        <v>365905.71</v>
+      </c>
+      <c r="S476" t="n">
+        <v>365905.71</v>
+      </c>
+      <c r="T476" t="inlineStr"/>
+      <c r="U476" t="inlineStr"/>
+      <c r="V476" t="inlineStr"/>
+      <c r="W476" t="inlineStr"/>
+      <c r="X476" t="inlineStr"/>
+      <c r="Y476" t="inlineStr"/>
+      <c r="Z476" t="n">
+        <v>365905.71</v>
+      </c>
+      <c r="AA476" t="inlineStr"/>
+      <c r="AB476" t="inlineStr"/>
+      <c r="AC476" t="inlineStr"/>
+      <c r="AD476" t="n">
+        <v>365905.71</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B477" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C477" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>1473</v>
+      </c>
+      <c r="F477" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I477" t="n">
+        <v>42</v>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K477" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M477" t="n">
+        <v>80</v>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>18.401.018/0001-60</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>PM SAO DOMINGOS DO PRATA</t>
+        </is>
+      </c>
+      <c r="Q477" t="n">
+        <v>0</v>
+      </c>
+      <c r="R477" t="n">
+        <v>0</v>
+      </c>
+      <c r="S477" t="n">
+        <v>0</v>
+      </c>
+      <c r="T477" t="inlineStr"/>
+      <c r="U477" t="inlineStr"/>
+      <c r="V477" t="inlineStr"/>
+      <c r="W477" t="inlineStr"/>
+      <c r="X477" t="inlineStr"/>
+      <c r="Y477" t="inlineStr"/>
+      <c r="Z477" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA477" t="inlineStr"/>
+      <c r="AB477" t="inlineStr"/>
+      <c r="AC477" t="inlineStr"/>
+      <c r="AD477" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B478" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C478" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>1474</v>
+      </c>
+      <c r="F478" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I478" t="n">
+        <v>41</v>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K478" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M478" t="n">
+        <v>80</v>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>17.993.780/0001-10</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>FUNDO MUNICIPAL DE ASSIST. SOCIAL - TUMIRITINGA</t>
+        </is>
+      </c>
+      <c r="Q478" t="n">
+        <v>40000</v>
+      </c>
+      <c r="R478" t="n">
+        <v>40000</v>
+      </c>
+      <c r="S478" t="n">
+        <v>40000</v>
+      </c>
+      <c r="T478" t="inlineStr"/>
+      <c r="U478" t="inlineStr"/>
+      <c r="V478" t="inlineStr"/>
+      <c r="W478" t="inlineStr"/>
+      <c r="X478" t="inlineStr"/>
+      <c r="Y478" t="inlineStr"/>
+      <c r="Z478" t="n">
+        <v>40000</v>
+      </c>
+      <c r="AA478" t="inlineStr"/>
+      <c r="AB478" t="inlineStr"/>
+      <c r="AC478" t="inlineStr"/>
+      <c r="AD478" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B479" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C479" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>1476</v>
+      </c>
+      <c r="F479" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I479" t="n">
+        <v>42</v>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K479" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M479" t="n">
+        <v>80</v>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>01.613.208/0001-49</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>PM NAQUE</t>
+        </is>
+      </c>
+      <c r="Q479" t="n">
+        <v>0</v>
+      </c>
+      <c r="R479" t="n">
+        <v>0</v>
+      </c>
+      <c r="S479" t="n">
+        <v>0</v>
+      </c>
+      <c r="T479" t="inlineStr"/>
+      <c r="U479" t="inlineStr"/>
+      <c r="V479" t="inlineStr"/>
+      <c r="W479" t="inlineStr"/>
+      <c r="X479" t="inlineStr"/>
+      <c r="Y479" t="inlineStr"/>
+      <c r="Z479" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA479" t="inlineStr"/>
+      <c r="AB479" t="inlineStr"/>
+      <c r="AC479" t="inlineStr"/>
+      <c r="AD479" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B480" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C480" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>1477</v>
+      </c>
+      <c r="F480" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I480" t="n">
+        <v>42</v>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K480" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M480" t="n">
+        <v>80</v>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>18.413.179/0001-74</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>PM ITUETA</t>
+        </is>
+      </c>
+      <c r="Q480" t="n">
+        <v>0</v>
+      </c>
+      <c r="R480" t="n">
+        <v>0</v>
+      </c>
+      <c r="S480" t="n">
+        <v>0</v>
+      </c>
+      <c r="T480" t="inlineStr"/>
+      <c r="U480" t="inlineStr"/>
+      <c r="V480" t="inlineStr"/>
+      <c r="W480" t="inlineStr"/>
+      <c r="X480" t="inlineStr"/>
+      <c r="Y480" t="inlineStr"/>
+      <c r="Z480" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA480" t="inlineStr"/>
+      <c r="AB480" t="inlineStr"/>
+      <c r="AC480" t="inlineStr"/>
+      <c r="AD480" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B481" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C481" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>1482</v>
+      </c>
+      <c r="F481" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I481" t="n">
+        <v>42</v>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K481" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M481" t="n">
+        <v>80</v>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>18.401.018/0001-60</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>PM SAO DOMINGOS DO PRATA</t>
+        </is>
+      </c>
+      <c r="Q481" t="n">
+        <v>374030.18</v>
+      </c>
+      <c r="R481" t="n">
+        <v>374030.18</v>
+      </c>
+      <c r="S481" t="n">
+        <v>374030.18</v>
+      </c>
+      <c r="T481" t="inlineStr"/>
+      <c r="U481" t="inlineStr"/>
+      <c r="V481" t="inlineStr"/>
+      <c r="W481" t="inlineStr"/>
+      <c r="X481" t="inlineStr"/>
+      <c r="Y481" t="inlineStr"/>
+      <c r="Z481" t="n">
+        <v>374030.18</v>
+      </c>
+      <c r="AA481" t="inlineStr"/>
+      <c r="AB481" t="inlineStr"/>
+      <c r="AC481" t="inlineStr"/>
+      <c r="AD481" t="n">
+        <v>374030.18</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B482" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C482" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>1488</v>
+      </c>
+      <c r="F482" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I482" t="n">
+        <v>42</v>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K482" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M482" t="n">
+        <v>80</v>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>19.243.500/0001-82</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>PM SAO PEDRO DOS FERROS</t>
+        </is>
+      </c>
+      <c r="Q482" t="n">
+        <v>666604.48</v>
+      </c>
+      <c r="R482" t="n">
+        <v>666604.48</v>
+      </c>
+      <c r="S482" t="n">
+        <v>666604.48</v>
+      </c>
+      <c r="T482" t="inlineStr"/>
+      <c r="U482" t="inlineStr"/>
+      <c r="V482" t="inlineStr"/>
+      <c r="W482" t="inlineStr"/>
+      <c r="X482" t="inlineStr"/>
+      <c r="Y482" t="inlineStr"/>
+      <c r="Z482" t="n">
+        <v>666604.48</v>
+      </c>
+      <c r="AA482" t="inlineStr"/>
+      <c r="AB482" t="inlineStr"/>
+      <c r="AC482" t="inlineStr"/>
+      <c r="AD482" t="n">
+        <v>666604.48</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B483" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C483" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F483" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I483" t="n">
+        <v>42</v>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K483" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M483" t="n">
+        <v>80</v>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>18.836.957/0001-38</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>PM RIO CASCA</t>
+        </is>
+      </c>
+      <c r="Q483" t="n">
+        <v>500000</v>
+      </c>
+      <c r="R483" t="n">
+        <v>500000</v>
+      </c>
+      <c r="S483" t="n">
+        <v>0</v>
+      </c>
+      <c r="T483" t="inlineStr"/>
+      <c r="U483" t="inlineStr"/>
+      <c r="V483" t="inlineStr"/>
+      <c r="W483" t="inlineStr"/>
+      <c r="X483" t="inlineStr"/>
+      <c r="Y483" t="inlineStr"/>
+      <c r="Z483" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AA483" t="inlineStr"/>
+      <c r="AB483" t="inlineStr"/>
+      <c r="AC483" t="inlineStr"/>
+      <c r="AD483" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B484" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C484" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>1491</v>
+      </c>
+      <c r="F484" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I484" t="n">
+        <v>42</v>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K484" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M484" t="n">
+        <v>80</v>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>18.338.830/0001-99</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>PM IAPU</t>
+        </is>
+      </c>
+      <c r="Q484" t="n">
+        <v>421991.97</v>
+      </c>
+      <c r="R484" t="n">
+        <v>421991.97</v>
+      </c>
+      <c r="S484" t="n">
+        <v>421991.97</v>
+      </c>
+      <c r="T484" t="inlineStr"/>
+      <c r="U484" t="inlineStr"/>
+      <c r="V484" t="inlineStr"/>
+      <c r="W484" t="inlineStr"/>
+      <c r="X484" t="inlineStr"/>
+      <c r="Y484" t="inlineStr"/>
+      <c r="Z484" t="n">
+        <v>421991.97</v>
+      </c>
+      <c r="AA484" t="inlineStr"/>
+      <c r="AB484" t="inlineStr"/>
+      <c r="AC484" t="inlineStr"/>
+      <c r="AD484" t="n">
+        <v>421991.97</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B485" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C485" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>1493</v>
+      </c>
+      <c r="F485" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I485" t="n">
+        <v>42</v>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K485" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M485" t="n">
+        <v>80</v>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>01.613.208/0001-49</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>PM NAQUE</t>
+        </is>
+      </c>
+      <c r="Q485" t="n">
+        <v>775163.33</v>
+      </c>
+      <c r="R485" t="n">
+        <v>775163.33</v>
+      </c>
+      <c r="S485" t="n">
+        <v>775163.33</v>
+      </c>
+      <c r="T485" t="inlineStr"/>
+      <c r="U485" t="inlineStr"/>
+      <c r="V485" t="inlineStr"/>
+      <c r="W485" t="inlineStr"/>
+      <c r="X485" t="inlineStr"/>
+      <c r="Y485" t="inlineStr"/>
+      <c r="Z485" t="n">
+        <v>775163.33</v>
+      </c>
+      <c r="AA485" t="inlineStr"/>
+      <c r="AB485" t="inlineStr"/>
+      <c r="AC485" t="inlineStr"/>
+      <c r="AD485" t="n">
+        <v>775163.33</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B486" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C486" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>1494</v>
+      </c>
+      <c r="F486" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I486" t="n">
+        <v>42</v>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K486" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M486" t="n">
+        <v>80</v>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>19.769.660/0001-60</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>PM CONSELHEIRO PENA</t>
+        </is>
+      </c>
+      <c r="Q486" t="n">
+        <v>543266</v>
+      </c>
+      <c r="R486" t="n">
+        <v>543266</v>
+      </c>
+      <c r="S486" t="n">
+        <v>543266</v>
+      </c>
+      <c r="T486" t="inlineStr"/>
+      <c r="U486" t="inlineStr"/>
+      <c r="V486" t="inlineStr"/>
+      <c r="W486" t="inlineStr"/>
+      <c r="X486" t="inlineStr"/>
+      <c r="Y486" t="inlineStr"/>
+      <c r="Z486" t="n">
+        <v>543266</v>
+      </c>
+      <c r="AA486" t="inlineStr"/>
+      <c r="AB486" t="inlineStr"/>
+      <c r="AC486" t="inlineStr"/>
+      <c r="AD486" t="n">
+        <v>543266</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B487" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C487" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>1495</v>
+      </c>
+      <c r="F487" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I487" t="n">
+        <v>42</v>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K487" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M487" t="n">
+        <v>80</v>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>01.613.204/0001-60</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>PM PINGO D'AGUA</t>
+        </is>
+      </c>
+      <c r="Q487" t="n">
+        <v>346448.9</v>
+      </c>
+      <c r="R487" t="n">
+        <v>346448.9</v>
+      </c>
+      <c r="S487" t="n">
+        <v>346448.9</v>
+      </c>
+      <c r="T487" t="inlineStr"/>
+      <c r="U487" t="inlineStr"/>
+      <c r="V487" t="inlineStr"/>
+      <c r="W487" t="inlineStr"/>
+      <c r="X487" t="inlineStr"/>
+      <c r="Y487" t="inlineStr"/>
+      <c r="Z487" t="n">
+        <v>346448.9</v>
+      </c>
+      <c r="AA487" t="inlineStr"/>
+      <c r="AB487" t="inlineStr"/>
+      <c r="AC487" t="inlineStr"/>
+      <c r="AD487" t="n">
+        <v>346448.9</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B488" t="n">
+        <v>9445718</v>
+      </c>
+      <c r="C488" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>1496</v>
+      </c>
+      <c r="F488" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I488" t="n">
+        <v>42</v>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="K488" t="n">
+        <v>4201</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>AUXILIOS</t>
+        </is>
+      </c>
+      <c r="M488" t="n">
+        <v>80</v>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>18.413.179/0001-74</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>PM ITUETA</t>
+        </is>
+      </c>
+      <c r="Q488" t="n">
+        <v>487538.62</v>
+      </c>
+      <c r="R488" t="n">
+        <v>487538.62</v>
+      </c>
+      <c r="S488" t="n">
+        <v>487538.62</v>
+      </c>
+      <c r="T488" t="inlineStr"/>
+      <c r="U488" t="inlineStr"/>
+      <c r="V488" t="inlineStr"/>
+      <c r="W488" t="inlineStr"/>
+      <c r="X488" t="inlineStr"/>
+      <c r="Y488" t="inlineStr"/>
+      <c r="Z488" t="n">
+        <v>487538.62</v>
+      </c>
+      <c r="AA488" t="inlineStr"/>
+      <c r="AB488" t="inlineStr"/>
+      <c r="AC488" t="inlineStr"/>
+      <c r="AD488" t="n">
+        <v>487538.62</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B489" t="n">
+        <v>9480259</v>
+      </c>
+      <c r="C489" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>195</v>
+      </c>
+      <c r="F489" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I489" t="n">
+        <v>41</v>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K489" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M489" t="n">
+        <v>80</v>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>25.944.455/0001-96</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>UNIVERSIDADE FEDERAL DE VICOSA</t>
+        </is>
+      </c>
+      <c r="Q489" t="n">
+        <v>0</v>
+      </c>
+      <c r="R489" t="n">
+        <v>0</v>
+      </c>
+      <c r="S489" t="n">
+        <v>0</v>
+      </c>
+      <c r="T489" t="inlineStr"/>
+      <c r="U489" t="inlineStr"/>
+      <c r="V489" t="inlineStr"/>
+      <c r="W489" t="inlineStr"/>
+      <c r="X489" t="inlineStr"/>
+      <c r="Y489" t="inlineStr"/>
+      <c r="Z489" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA489" t="inlineStr"/>
+      <c r="AB489" t="inlineStr"/>
+      <c r="AC489" t="inlineStr"/>
+      <c r="AD489" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B490" t="n">
+        <v>9480259</v>
+      </c>
+      <c r="C490" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>196</v>
+      </c>
+      <c r="F490" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I490" t="n">
+        <v>41</v>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="K490" t="n">
+        <v>4101</v>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>CONTRIBUICOES</t>
+        </is>
+      </c>
+      <c r="M490" t="n">
+        <v>80</v>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>20.320.503/0001-51</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>FUNDACAO ARTHUR BERNARDES</t>
+        </is>
+      </c>
+      <c r="Q490" t="n">
+        <v>4047625.86</v>
+      </c>
+      <c r="R490" t="n">
+        <v>4047625.86</v>
+      </c>
+      <c r="S490" t="n">
+        <v>4047625.86</v>
+      </c>
+      <c r="T490" t="inlineStr"/>
+      <c r="U490" t="inlineStr"/>
+      <c r="V490" t="inlineStr"/>
+      <c r="W490" t="inlineStr"/>
+      <c r="X490" t="inlineStr"/>
+      <c r="Y490" t="inlineStr"/>
+      <c r="Z490" t="n">
+        <v>4047625.86</v>
+      </c>
+      <c r="AA490" t="inlineStr"/>
+      <c r="AB490" t="inlineStr"/>
+      <c r="AC490" t="inlineStr"/>
+      <c r="AD490" t="n">
+        <v>4047625.86</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B491" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C491" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>32</v>
+      </c>
+      <c r="F491" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I491" t="n">
+        <v>33</v>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>PASSAGENS E DESPESAS COM LOCOMOCAO</t>
+        </is>
+      </c>
+      <c r="K491" t="n">
+        <v>3302</v>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>DESPESAS COM TRANSPORTE URBANO, PEDAGIO E ESTACIONAMETO PESSOA FISICA</t>
+        </is>
+      </c>
+      <c r="M491" t="n">
+        <v>80</v>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>120.754.126/50</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>MATHEUS FILLIPE LANGANKE DE CARVALHO</t>
+        </is>
+      </c>
+      <c r="Q491" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="R491" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="S491" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="T491" t="inlineStr"/>
+      <c r="U491" t="inlineStr"/>
+      <c r="V491" t="n">
+        <v>0</v>
+      </c>
+      <c r="W491" t="inlineStr"/>
+      <c r="X491" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y491" t="inlineStr"/>
+      <c r="Z491" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="AA491" t="inlineStr"/>
+      <c r="AB491" t="inlineStr"/>
+      <c r="AC491" t="inlineStr"/>
+      <c r="AD491" t="n">
+        <v>197.13</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B492" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C492" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>33</v>
+      </c>
+      <c r="F492" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I492" t="n">
+        <v>33</v>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>PASSAGENS E DESPESAS COM LOCOMOCAO</t>
+        </is>
+      </c>
+      <c r="K492" t="n">
+        <v>3302</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>DESPESAS COM TRANSPORTE URBANO, PEDAGIO E ESTACIONAMETO PESSOA FISICA</t>
+        </is>
+      </c>
+      <c r="M492" t="n">
+        <v>80</v>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>126.665.156/05</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>BRUNA BORONI DE PAIVA</t>
+        </is>
+      </c>
+      <c r="Q492" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="R492" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="S492" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="T492" t="inlineStr"/>
+      <c r="U492" t="inlineStr"/>
+      <c r="V492" t="n">
+        <v>0</v>
+      </c>
+      <c r="W492" t="inlineStr"/>
+      <c r="X492" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y492" t="inlineStr"/>
+      <c r="Z492" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="AA492" t="inlineStr"/>
+      <c r="AB492" t="inlineStr"/>
+      <c r="AC492" t="inlineStr"/>
+      <c r="AD492" t="n">
+        <v>137.91</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B493" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C493" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>34</v>
+      </c>
+      <c r="F493" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I493" t="n">
+        <v>33</v>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>PASSAGENS E DESPESAS COM LOCOMOCAO</t>
+        </is>
+      </c>
+      <c r="K493" t="n">
+        <v>3302</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>DESPESAS COM TRANSPORTE URBANO, PEDAGIO E ESTACIONAMETO PESSOA FISICA</t>
+        </is>
+      </c>
+      <c r="M493" t="n">
+        <v>80</v>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>103.900.616/70</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>ANA CLAUDIA MACHADO BOTELHO</t>
+        </is>
+      </c>
+      <c r="Q493" t="n">
+        <v>360</v>
+      </c>
+      <c r="R493" t="n">
+        <v>360</v>
+      </c>
+      <c r="S493" t="n">
+        <v>360</v>
+      </c>
+      <c r="T493" t="inlineStr"/>
+      <c r="U493" t="inlineStr"/>
+      <c r="V493" t="n">
+        <v>0</v>
+      </c>
+      <c r="W493" t="inlineStr"/>
+      <c r="X493" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y493" t="inlineStr"/>
+      <c r="Z493" t="n">
+        <v>360</v>
+      </c>
+      <c r="AA493" t="inlineStr"/>
+      <c r="AB493" t="inlineStr"/>
+      <c r="AC493" t="inlineStr"/>
+      <c r="AD493" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B494" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C494" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>35</v>
+      </c>
+      <c r="F494" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I494" t="n">
+        <v>33</v>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>PASSAGENS E DESPESAS COM LOCOMOCAO</t>
+        </is>
+      </c>
+      <c r="K494" t="n">
+        <v>3302</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>DESPESAS COM TRANSPORTE URBANO, PEDAGIO E ESTACIONAMETO PESSOA FISICA</t>
+        </is>
+      </c>
+      <c r="M494" t="n">
+        <v>80</v>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>120.225.986/36</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>JULIA PESSOA REIS</t>
+        </is>
+      </c>
+      <c r="Q494" t="n">
+        <v>148.96</v>
+      </c>
+      <c r="R494" t="n">
+        <v>148.96</v>
+      </c>
+      <c r="S494" t="n">
+        <v>148.96</v>
+      </c>
+      <c r="T494" t="inlineStr"/>
+      <c r="U494" t="inlineStr"/>
+      <c r="V494" t="n">
+        <v>0</v>
+      </c>
+      <c r="W494" t="inlineStr"/>
+      <c r="X494" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y494" t="inlineStr"/>
+      <c r="Z494" t="n">
+        <v>148.96</v>
+      </c>
+      <c r="AA494" t="inlineStr"/>
+      <c r="AB494" t="inlineStr"/>
+      <c r="AC494" t="inlineStr"/>
+      <c r="AD494" t="n">
+        <v>148.96</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B495" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C495" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>200</v>
+      </c>
+      <c r="F495" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I495" t="n">
+        <v>37</v>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K495" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M495" t="n">
+        <v>80</v>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q495" t="n">
+        <v>3744.37</v>
+      </c>
+      <c r="R495" t="n">
+        <v>0</v>
+      </c>
+      <c r="S495" t="n">
+        <v>0</v>
+      </c>
+      <c r="T495" t="inlineStr"/>
+      <c r="U495" t="inlineStr"/>
+      <c r="V495" t="n">
+        <v>0</v>
+      </c>
+      <c r="W495" t="inlineStr"/>
+      <c r="X495" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y495" t="inlineStr"/>
+      <c r="Z495" t="n">
+        <v>3744.37</v>
+      </c>
+      <c r="AA495" t="inlineStr"/>
+      <c r="AB495" t="inlineStr"/>
+      <c r="AC495" t="inlineStr"/>
+      <c r="AD495" t="n">
         <v>0</v>
       </c>
     </row>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD495"/>
+  <dimension ref="A1:AD500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13101,10 +13101,10 @@
         <v>5891.6</v>
       </c>
       <c r="R140" t="n">
-        <v>4835.94</v>
+        <v>5891.6</v>
       </c>
       <c r="S140" t="n">
-        <v>4603.82</v>
+        <v>5608.81</v>
       </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
@@ -13123,7 +13123,7 @@
       <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="n">
-        <v>4603.82</v>
+        <v>5608.81</v>
       </c>
     </row>
     <row r="141">
@@ -13759,10 +13759,10 @@
         <v>211792.55</v>
       </c>
       <c r="R147" t="n">
-        <v>162683.18</v>
+        <v>195422.76</v>
       </c>
       <c r="S147" t="n">
-        <v>136979.22</v>
+        <v>164545.95</v>
       </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
@@ -13781,7 +13781,7 @@
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="n">
-        <v>136979.22</v>
+        <v>164545.95</v>
       </c>
     </row>
     <row r="148">
@@ -13944,10 +13944,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>62000.01</v>
+        <v>67000.00999999999</v>
       </c>
       <c r="R149" t="n">
-        <v>43144.66</v>
+        <v>56330.67</v>
       </c>
       <c r="S149" t="n">
         <v>39690.37</v>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="n">
-        <v>62000.01</v>
+        <v>67000.00999999999</v>
       </c>
       <c r="AA149" t="inlineStr"/>
       <c r="AB149" t="inlineStr"/>
@@ -14041,7 +14041,7 @@
         <v>503776.08</v>
       </c>
       <c r="R150" t="n">
-        <v>385355.31</v>
+        <v>458955.45</v>
       </c>
       <c r="S150" t="n">
         <v>320103.29</v>
@@ -14135,7 +14135,7 @@
         <v>1429064.13</v>
       </c>
       <c r="R151" t="n">
-        <v>1129581.26</v>
+        <v>1372920.58</v>
       </c>
       <c r="S151" t="n">
         <v>942258.29</v>
@@ -14229,7 +14229,7 @@
         <v>111802.65</v>
       </c>
       <c r="R152" t="n">
-        <v>71246.27</v>
+        <v>90398.55</v>
       </c>
       <c r="S152" t="n">
         <v>66180.75</v>
@@ -14323,7 +14323,7 @@
         <v>12560.85</v>
       </c>
       <c r="R153" t="n">
-        <v>7560.81</v>
+        <v>9672.129999999999</v>
       </c>
       <c r="S153" t="n">
         <v>7285.08</v>
@@ -14417,7 +14417,7 @@
         <v>337260.81</v>
       </c>
       <c r="R154" t="n">
-        <v>228954.73</v>
+        <v>290318.01</v>
       </c>
       <c r="S154" t="n">
         <v>201799.44</v>
@@ -14508,7 +14508,7 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>29576226.46</v>
+        <v>30127671.46</v>
       </c>
       <c r="R155" t="n">
         <v>4653543.42</v>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="n">
-        <v>29576226.46</v>
+        <v>30127671.46</v>
       </c>
       <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="inlineStr"/>
@@ -16199,10 +16199,10 @@
         <v>67763</v>
       </c>
       <c r="R173" t="n">
-        <v>6321.4</v>
+        <v>6992.2</v>
       </c>
       <c r="S173" t="n">
-        <v>6683.4</v>
+        <v>7354.2</v>
       </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr"/>
       <c r="AD173" t="n">
-        <v>6683.4</v>
+        <v>7354.2</v>
       </c>
     </row>
     <row r="174">
@@ -16292,7 +16292,7 @@
         <v>24515.08</v>
       </c>
       <c r="S174" t="n">
-        <v>20036.2</v>
+        <v>24149.89</v>
       </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
@@ -16311,7 +16311,7 @@
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr"/>
       <c r="AD174" t="n">
-        <v>20036.2</v>
+        <v>24149.89</v>
       </c>
     </row>
     <row r="175">
@@ -16386,7 +16386,7 @@
         <v>9112.030000000001</v>
       </c>
       <c r="S175" t="n">
-        <v>7322.73</v>
+        <v>8832.459999999999</v>
       </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr"/>
       <c r="AD175" t="n">
-        <v>7322.73</v>
+        <v>8832.459999999999</v>
       </c>
     </row>
     <row r="176">
@@ -16480,7 +16480,7 @@
         <v>71269.74000000001</v>
       </c>
       <c r="S176" t="n">
-        <v>53665.01</v>
+        <v>67124.59</v>
       </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
@@ -16499,7 +16499,7 @@
       <c r="AB176" t="inlineStr"/>
       <c r="AC176" t="inlineStr"/>
       <c r="AD176" t="n">
-        <v>53665.01</v>
+        <v>67124.59</v>
       </c>
     </row>
     <row r="177">
@@ -16574,7 +16574,7 @@
         <v>57253.85</v>
       </c>
       <c r="S177" t="n">
-        <v>41207.95</v>
+        <v>54550.94</v>
       </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
@@ -16593,7 +16593,7 @@
       <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="n">
-        <v>41207.95</v>
+        <v>54550.94</v>
       </c>
     </row>
     <row r="178">
@@ -16668,7 +16668,7 @@
         <v>25486.76</v>
       </c>
       <c r="S178" t="n">
-        <v>20845.24</v>
+        <v>25486.76</v>
       </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
@@ -16687,7 +16687,7 @@
       <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="inlineStr"/>
       <c r="AD178" t="n">
-        <v>20845.24</v>
+        <v>25486.76</v>
       </c>
     </row>
     <row r="179">
@@ -16762,7 +16762,7 @@
         <v>7364.56</v>
       </c>
       <c r="S179" t="n">
-        <v>5781.07</v>
+        <v>7364.56</v>
       </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
@@ -16781,7 +16781,7 @@
       <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="inlineStr"/>
       <c r="AD179" t="n">
-        <v>5781.07</v>
+        <v>7364.56</v>
       </c>
     </row>
     <row r="180">
@@ -17138,7 +17138,7 @@
         <v>618387.89</v>
       </c>
       <c r="S183" t="n">
-        <v>386505.74</v>
+        <v>501375.46</v>
       </c>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
@@ -17157,7 +17157,7 @@
       <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="inlineStr"/>
       <c r="AD183" t="n">
-        <v>386505.74</v>
+        <v>501375.46</v>
       </c>
     </row>
     <row r="184">
@@ -17232,7 +17232,7 @@
         <v>348787.24</v>
       </c>
       <c r="S184" t="n">
-        <v>241553.2</v>
+        <v>310420.64</v>
       </c>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
@@ -17251,7 +17251,7 @@
       <c r="AB184" t="inlineStr"/>
       <c r="AC184" t="inlineStr"/>
       <c r="AD184" t="n">
-        <v>241553.2</v>
+        <v>310420.64</v>
       </c>
     </row>
     <row r="185">
@@ -17326,7 +17326,7 @@
         <v>1396840.69</v>
       </c>
       <c r="S185" t="n">
-        <v>986429.4300000001</v>
+        <v>1242215.01</v>
       </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="inlineStr"/>
       <c r="AD185" t="n">
-        <v>986429.4300000001</v>
+        <v>1242215.01</v>
       </c>
     </row>
     <row r="186">
@@ -17420,7 +17420,7 @@
         <v>1287700.95</v>
       </c>
       <c r="S186" t="n">
-        <v>852437.58</v>
+        <v>1043395.36</v>
       </c>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
@@ -17439,7 +17439,7 @@
       <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr"/>
       <c r="AD186" t="n">
-        <v>852437.58</v>
+        <v>1043395.36</v>
       </c>
     </row>
     <row r="187">
@@ -17514,7 +17514,7 @@
         <v>960789.26</v>
       </c>
       <c r="S187" t="n">
-        <v>642569.49</v>
+        <v>805370.73</v>
       </c>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
@@ -17533,7 +17533,7 @@
       <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="n">
-        <v>642569.49</v>
+        <v>805370.73</v>
       </c>
     </row>
     <row r="188">
@@ -17608,7 +17608,7 @@
         <v>267387.5</v>
       </c>
       <c r="S188" t="n">
-        <v>189480.38</v>
+        <v>237974.88</v>
       </c>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
@@ -17627,7 +17627,7 @@
       <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="inlineStr"/>
       <c r="AD188" t="n">
-        <v>189480.38</v>
+        <v>237974.88</v>
       </c>
     </row>
     <row r="189">
@@ -17699,7 +17699,7 @@
         <v>60100</v>
       </c>
       <c r="R189" t="n">
-        <v>30912.24</v>
+        <v>42581.89</v>
       </c>
       <c r="S189" t="n">
         <v>30164.95</v>
@@ -18356,7 +18356,7 @@
         <v>207000</v>
       </c>
       <c r="S196" t="n">
-        <v>67965</v>
+        <v>203895</v>
       </c>
       <c r="T196" t="inlineStr"/>
       <c r="U196" t="inlineStr"/>
@@ -18375,7 +18375,7 @@
       <c r="AB196" t="inlineStr"/>
       <c r="AC196" t="inlineStr"/>
       <c r="AD196" t="n">
-        <v>67965</v>
+        <v>203895</v>
       </c>
     </row>
     <row r="197">
@@ -18450,7 +18450,7 @@
         <v>1694.47</v>
       </c>
       <c r="S197" t="n">
-        <v>1245.81</v>
+        <v>1694.47</v>
       </c>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
@@ -18469,7 +18469,7 @@
       <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="n">
-        <v>1245.81</v>
+        <v>1694.47</v>
       </c>
     </row>
     <row r="198">
@@ -18544,7 +18544,7 @@
         <v>68798.53999999999</v>
       </c>
       <c r="S198" t="n">
-        <v>45893.29</v>
+        <v>61230.69</v>
       </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
@@ -18563,7 +18563,7 @@
       <c r="AB198" t="inlineStr"/>
       <c r="AC198" t="inlineStr"/>
       <c r="AD198" t="n">
-        <v>45893.29</v>
+        <v>61230.69</v>
       </c>
     </row>
     <row r="199">
@@ -18826,7 +18826,7 @@
         <v>59095.34</v>
       </c>
       <c r="S201" t="n">
-        <v>35342.41</v>
+        <v>58386.21</v>
       </c>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
@@ -18845,7 +18845,7 @@
       <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr"/>
       <c r="AD201" t="n">
-        <v>35342.41</v>
+        <v>58386.21</v>
       </c>
     </row>
     <row r="202">
@@ -18914,7 +18914,7 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>9349434.27</v>
+        <v>8675354.27</v>
       </c>
       <c r="R202" t="n">
         <v>2458343.75</v>
@@ -18933,7 +18933,7 @@
       </c>
       <c r="Y202" t="inlineStr"/>
       <c r="Z202" t="n">
-        <v>9349434.27</v>
+        <v>8675354.27</v>
       </c>
       <c r="AA202" t="inlineStr"/>
       <c r="AB202" t="inlineStr"/>
@@ -19008,7 +19008,7 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>2337358.56</v>
+        <v>2168838.56</v>
       </c>
       <c r="R203" t="n">
         <v>614585.9300000001</v>
@@ -19027,7 +19027,7 @@
       </c>
       <c r="Y203" t="inlineStr"/>
       <c r="Z203" t="n">
-        <v>2337358.56</v>
+        <v>2168838.56</v>
       </c>
       <c r="AA203" t="inlineStr"/>
       <c r="AB203" t="inlineStr"/>
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>9101988.42</v>
+        <v>8550543.42</v>
       </c>
       <c r="R204" t="n">
         <v>1750936.02</v>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="Y204" t="inlineStr"/>
       <c r="Z204" t="n">
-        <v>9101988.42</v>
+        <v>8550543.42</v>
       </c>
       <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="inlineStr"/>
@@ -20409,10 +20409,10 @@
         <v>171017.71</v>
       </c>
       <c r="R218" t="n">
-        <v>114954.87</v>
+        <v>171017.71</v>
       </c>
       <c r="S218" t="n">
-        <v>114954.87</v>
+        <v>171017.71</v>
       </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
@@ -20431,7 +20431,7 @@
       <c r="AB218" t="inlineStr"/>
       <c r="AC218" t="inlineStr"/>
       <c r="AD218" t="n">
-        <v>114954.87</v>
+        <v>171017.71</v>
       </c>
     </row>
     <row r="219">
@@ -20503,10 +20503,10 @@
         <v>4578.33</v>
       </c>
       <c r="R219" t="n">
-        <v>3035.91</v>
+        <v>4578.32</v>
       </c>
       <c r="S219" t="n">
-        <v>3035.91</v>
+        <v>4578.32</v>
       </c>
       <c r="T219" t="inlineStr"/>
       <c r="U219" t="inlineStr"/>
@@ -20525,7 +20525,7 @@
       <c r="AB219" t="inlineStr"/>
       <c r="AC219" t="inlineStr"/>
       <c r="AD219" t="n">
-        <v>3035.91</v>
+        <v>4578.32</v>
       </c>
     </row>
     <row r="220">
@@ -20694,7 +20694,7 @@
         <v>259286.23</v>
       </c>
       <c r="S221" t="n">
-        <v>0</v>
+        <v>256174.8</v>
       </c>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
@@ -20713,7 +20713,7 @@
       <c r="AB221" t="inlineStr"/>
       <c r="AC221" t="inlineStr"/>
       <c r="AD221" t="n">
-        <v>0</v>
+        <v>256174.8</v>
       </c>
     </row>
     <row r="222">
@@ -36215,10 +36215,10 @@
         <v>98218.74000000001</v>
       </c>
       <c r="R393" t="n">
-        <v>32656.87</v>
+        <v>65332.12</v>
       </c>
       <c r="S393" t="n">
-        <v>27497.08</v>
+        <v>55009.64</v>
       </c>
       <c r="T393" t="inlineStr"/>
       <c r="U393" t="inlineStr"/>
@@ -36237,7 +36237,7 @@
       <c r="AB393" t="inlineStr"/>
       <c r="AC393" t="inlineStr"/>
       <c r="AD393" t="n">
-        <v>27497.08</v>
+        <v>55009.64</v>
       </c>
     </row>
     <row r="394">
@@ -36586,7 +36586,7 @@
         <v>3166.97</v>
       </c>
       <c r="S397" t="n">
-        <v>1583.48</v>
+        <v>3166.97</v>
       </c>
       <c r="T397" t="inlineStr"/>
       <c r="U397" t="inlineStr"/>
@@ -36605,7 +36605,7 @@
       <c r="AB397" t="inlineStr"/>
       <c r="AC397" t="inlineStr"/>
       <c r="AD397" t="n">
-        <v>1583.48</v>
+        <v>3166.97</v>
       </c>
     </row>
     <row r="398">
@@ -36680,7 +36680,7 @@
         <v>122514.28</v>
       </c>
       <c r="S398" t="n">
-        <v>51180.73</v>
+        <v>109037.71</v>
       </c>
       <c r="T398" t="inlineStr"/>
       <c r="U398" t="inlineStr"/>
@@ -36699,7 +36699,7 @@
       <c r="AB398" t="inlineStr"/>
       <c r="AC398" t="inlineStr"/>
       <c r="AD398" t="n">
-        <v>51180.73</v>
+        <v>109037.71</v>
       </c>
     </row>
     <row r="399">
@@ -36774,7 +36774,7 @@
         <v>37200.57</v>
       </c>
       <c r="S399" t="n">
-        <v>30113.19</v>
+        <v>33558.03</v>
       </c>
       <c r="T399" t="inlineStr"/>
       <c r="U399" t="inlineStr"/>
@@ -36793,7 +36793,7 @@
       <c r="AB399" t="inlineStr"/>
       <c r="AC399" t="inlineStr"/>
       <c r="AD399" t="n">
-        <v>30113.19</v>
+        <v>33558.03</v>
       </c>
     </row>
     <row r="400">
@@ -36868,7 +36868,7 @@
         <v>20831.62</v>
       </c>
       <c r="S400" t="n">
-        <v>18243.88</v>
+        <v>18620.27</v>
       </c>
       <c r="T400" t="inlineStr"/>
       <c r="U400" t="inlineStr"/>
@@ -36887,7 +36887,7 @@
       <c r="AB400" t="inlineStr"/>
       <c r="AC400" t="inlineStr"/>
       <c r="AD400" t="n">
-        <v>18243.88</v>
+        <v>18620.27</v>
       </c>
     </row>
     <row r="401">
@@ -36962,7 +36962,7 @@
         <v>83870.03</v>
       </c>
       <c r="S401" t="n">
-        <v>25305.6</v>
+        <v>32074.07</v>
       </c>
       <c r="T401" t="inlineStr"/>
       <c r="U401" t="inlineStr"/>
@@ -36981,7 +36981,7 @@
       <c r="AB401" t="inlineStr"/>
       <c r="AC401" t="inlineStr"/>
       <c r="AD401" t="n">
-        <v>25305.6</v>
+        <v>32074.07</v>
       </c>
     </row>
     <row r="402">
@@ -37056,7 +37056,7 @@
         <v>82956.11</v>
       </c>
       <c r="S402" t="n">
-        <v>42058.91</v>
+        <v>49139.97</v>
       </c>
       <c r="T402" t="inlineStr"/>
       <c r="U402" t="inlineStr"/>
@@ -37075,7 +37075,7 @@
       <c r="AB402" t="inlineStr"/>
       <c r="AC402" t="inlineStr"/>
       <c r="AD402" t="n">
-        <v>42058.91</v>
+        <v>49139.97</v>
       </c>
     </row>
     <row r="403">
@@ -37150,7 +37150,7 @@
         <v>60486.64</v>
       </c>
       <c r="S403" t="n">
-        <v>49402.17</v>
+        <v>54499.27</v>
       </c>
       <c r="T403" t="inlineStr"/>
       <c r="U403" t="inlineStr"/>
@@ -37169,7 +37169,7 @@
       <c r="AB403" t="inlineStr"/>
       <c r="AC403" t="inlineStr"/>
       <c r="AD403" t="n">
-        <v>49402.17</v>
+        <v>54499.27</v>
       </c>
     </row>
     <row r="404">
@@ -37244,7 +37244,7 @@
         <v>13909.08</v>
       </c>
       <c r="S404" t="n">
-        <v>10926.23</v>
+        <v>12597.62</v>
       </c>
       <c r="T404" t="inlineStr"/>
       <c r="U404" t="inlineStr"/>
@@ -37263,7 +37263,7 @@
       <c r="AB404" t="inlineStr"/>
       <c r="AC404" t="inlineStr"/>
       <c r="AD404" t="n">
-        <v>10926.23</v>
+        <v>12597.62</v>
       </c>
     </row>
     <row r="405">
@@ -37338,7 +37338,7 @@
         <v>3462.28</v>
       </c>
       <c r="S405" t="n">
-        <v>2748.89</v>
+        <v>3131.65</v>
       </c>
       <c r="T405" t="inlineStr"/>
       <c r="U405" t="inlineStr"/>
@@ -37357,7 +37357,7 @@
       <c r="AB405" t="inlineStr"/>
       <c r="AC405" t="inlineStr"/>
       <c r="AD405" t="n">
-        <v>2748.89</v>
+        <v>3131.65</v>
       </c>
     </row>
     <row r="406">
@@ -37429,10 +37429,10 @@
         <v>73360.92</v>
       </c>
       <c r="R406" t="n">
-        <v>24991.21</v>
+        <v>53283.15</v>
       </c>
       <c r="S406" t="n">
-        <v>24991.21</v>
+        <v>53283.15</v>
       </c>
       <c r="T406" t="inlineStr"/>
       <c r="U406" t="inlineStr"/>
@@ -37447,7 +37447,7 @@
       <c r="AB406" t="inlineStr"/>
       <c r="AC406" t="inlineStr"/>
       <c r="AD406" t="n">
-        <v>24991.21</v>
+        <v>53283.15</v>
       </c>
     </row>
     <row r="407">
@@ -37519,10 +37519,10 @@
         <v>2027.65</v>
       </c>
       <c r="R407" t="n">
-        <v>974.3200000000001</v>
+        <v>2027.64</v>
       </c>
       <c r="S407" t="n">
-        <v>974.3200000000001</v>
+        <v>2027.64</v>
       </c>
       <c r="T407" t="inlineStr"/>
       <c r="U407" t="inlineStr"/>
@@ -37537,7 +37537,7 @@
       <c r="AB407" t="inlineStr"/>
       <c r="AC407" t="inlineStr"/>
       <c r="AD407" t="n">
-        <v>974.3200000000001</v>
+        <v>2027.64</v>
       </c>
     </row>
     <row r="408">
@@ -37879,7 +37879,7 @@
         <v>12892.12</v>
       </c>
       <c r="R411" t="n">
-        <v>8618.49</v>
+        <v>10092.12</v>
       </c>
       <c r="S411" t="n">
         <v>7286.79</v>
@@ -37973,7 +37973,7 @@
         <v>34485.5</v>
       </c>
       <c r="R412" t="n">
-        <v>28840.66</v>
+        <v>32285.5</v>
       </c>
       <c r="S412" t="n">
         <v>24372.04</v>
@@ -38067,7 +38067,7 @@
         <v>83169.53</v>
       </c>
       <c r="R413" t="n">
-        <v>72067.23</v>
+        <v>82969.53</v>
       </c>
       <c r="S413" t="n">
         <v>60926.65</v>
@@ -38440,10 +38440,10 @@
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>23956.2</v>
+        <v>34988.64</v>
       </c>
       <c r="R417" t="n">
-        <v>11978.1</v>
+        <v>23010.54</v>
       </c>
       <c r="S417" t="n">
         <v>11978.1</v>
@@ -38455,7 +38455,7 @@
       <c r="X417" t="inlineStr"/>
       <c r="Y417" t="inlineStr"/>
       <c r="Z417" t="n">
-        <v>23956.2</v>
+        <v>34988.64</v>
       </c>
       <c r="AA417" t="inlineStr"/>
       <c r="AB417" t="inlineStr"/>
@@ -38533,7 +38533,7 @@
         <v>1688.7</v>
       </c>
       <c r="R418" t="n">
-        <v>719.21</v>
+        <v>1160.87</v>
       </c>
       <c r="S418" t="n">
         <v>191.38</v>
@@ -39547,7 +39547,7 @@
         <v>1822.18</v>
       </c>
       <c r="R429" t="n">
-        <v>527.83</v>
+        <v>1821.18</v>
       </c>
       <c r="S429" t="n">
         <v>502.49</v>
@@ -39923,7 +39923,7 @@
         <v>98218.74000000001</v>
       </c>
       <c r="R433" t="n">
-        <v>49109.37</v>
+        <v>98218.74000000001</v>
       </c>
       <c r="S433" t="n">
         <v>39833.26</v>
@@ -40017,7 +40017,7 @@
         <v>32739.58</v>
       </c>
       <c r="R434" t="n">
-        <v>16369.79</v>
+        <v>32739.58</v>
       </c>
       <c r="S434" t="n">
         <v>13783.36</v>
@@ -40581,7 +40581,7 @@
         <v>5415.44</v>
       </c>
       <c r="R440" t="n">
-        <v>1534.39</v>
+        <v>5414.44</v>
       </c>
       <c r="S440" t="n">
         <v>1460.74</v>
@@ -40675,7 +40675,7 @@
         <v>3643.36</v>
       </c>
       <c r="R441" t="n">
-        <v>1055.66</v>
+        <v>3642.36</v>
       </c>
       <c r="S441" t="n">
         <v>1004.99</v>
@@ -40769,7 +40769,7 @@
         <v>65479.16</v>
       </c>
       <c r="R442" t="n">
-        <v>32739.58</v>
+        <v>65479.16</v>
       </c>
       <c r="S442" t="n">
         <v>27566.73</v>
@@ -43251,10 +43251,10 @@
         <v>1531.04</v>
       </c>
       <c r="R469" t="n">
-        <v>0</v>
+        <v>1531.04</v>
       </c>
       <c r="S469" t="n">
-        <v>0</v>
+        <v>1457.55</v>
       </c>
       <c r="T469" t="inlineStr"/>
       <c r="U469" t="inlineStr"/>
@@ -43273,7 +43273,7 @@
       <c r="AB469" t="inlineStr"/>
       <c r="AC469" t="inlineStr"/>
       <c r="AD469" t="n">
-        <v>0</v>
+        <v>1457.55</v>
       </c>
     </row>
     <row r="470">
@@ -45615,10 +45615,10 @@
         <v>3744.37</v>
       </c>
       <c r="R495" t="n">
-        <v>0</v>
+        <v>3744.36</v>
       </c>
       <c r="S495" t="n">
-        <v>0</v>
+        <v>3395.18</v>
       </c>
       <c r="T495" t="inlineStr"/>
       <c r="U495" t="inlineStr"/>
@@ -45637,6 +45637,472 @@
       <c r="AB495" t="inlineStr"/>
       <c r="AC495" t="inlineStr"/>
       <c r="AD495" t="n">
+        <v>3395.18</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B496" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C496" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>99</v>
+      </c>
+      <c r="F496" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>1511189 000188/2026</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I496" t="n">
+        <v>52</v>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K496" t="n">
+        <v>5214</v>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>MOBILIARIO</t>
+        </is>
+      </c>
+      <c r="M496" t="n">
+        <v>80</v>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>17.756.197/0001-96</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>PRENSAR MOVEIS LTDA</t>
+        </is>
+      </c>
+      <c r="Q496" t="n">
+        <v>7200</v>
+      </c>
+      <c r="R496" t="n">
+        <v>0</v>
+      </c>
+      <c r="S496" t="n">
+        <v>0</v>
+      </c>
+      <c r="T496" t="inlineStr"/>
+      <c r="U496" t="inlineStr"/>
+      <c r="V496" t="inlineStr"/>
+      <c r="W496" t="inlineStr"/>
+      <c r="X496" t="inlineStr"/>
+      <c r="Y496" t="inlineStr"/>
+      <c r="Z496" t="n">
+        <v>7200</v>
+      </c>
+      <c r="AA496" t="inlineStr"/>
+      <c r="AB496" t="inlineStr"/>
+      <c r="AC496" t="inlineStr"/>
+      <c r="AD496" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B497" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C497" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>279</v>
+      </c>
+      <c r="F497" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I497" t="n">
+        <v>93</v>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K497" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M497" t="n">
+        <v>80</v>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q497" t="n">
+        <v>35000</v>
+      </c>
+      <c r="R497" t="n">
+        <v>0</v>
+      </c>
+      <c r="S497" t="n">
+        <v>0</v>
+      </c>
+      <c r="T497" t="inlineStr"/>
+      <c r="U497" t="inlineStr"/>
+      <c r="V497" t="n">
+        <v>0</v>
+      </c>
+      <c r="W497" t="inlineStr"/>
+      <c r="X497" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y497" t="inlineStr"/>
+      <c r="Z497" t="n">
+        <v>35000</v>
+      </c>
+      <c r="AA497" t="inlineStr"/>
+      <c r="AB497" t="inlineStr"/>
+      <c r="AC497" t="inlineStr"/>
+      <c r="AD497" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B498" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C498" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>280</v>
+      </c>
+      <c r="F498" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I498" t="n">
+        <v>93</v>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K498" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M498" t="n">
+        <v>80</v>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q498" t="n">
+        <v>16000</v>
+      </c>
+      <c r="R498" t="n">
+        <v>0</v>
+      </c>
+      <c r="S498" t="n">
+        <v>0</v>
+      </c>
+      <c r="T498" t="inlineStr"/>
+      <c r="U498" t="inlineStr"/>
+      <c r="V498" t="n">
+        <v>0</v>
+      </c>
+      <c r="W498" t="inlineStr"/>
+      <c r="X498" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y498" t="inlineStr"/>
+      <c r="Z498" t="n">
+        <v>16000</v>
+      </c>
+      <c r="AA498" t="inlineStr"/>
+      <c r="AB498" t="inlineStr"/>
+      <c r="AC498" t="inlineStr"/>
+      <c r="AD498" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B499" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C499" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>281</v>
+      </c>
+      <c r="F499" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I499" t="n">
+        <v>51</v>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K499" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M499" t="n">
+        <v>80</v>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q499" t="n">
+        <v>644461.2</v>
+      </c>
+      <c r="R499" t="n">
+        <v>0</v>
+      </c>
+      <c r="S499" t="n">
+        <v>0</v>
+      </c>
+      <c r="T499" t="inlineStr"/>
+      <c r="U499" t="inlineStr"/>
+      <c r="V499" t="n">
+        <v>0</v>
+      </c>
+      <c r="W499" t="inlineStr"/>
+      <c r="X499" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y499" t="inlineStr"/>
+      <c r="Z499" t="n">
+        <v>644461.2</v>
+      </c>
+      <c r="AA499" t="inlineStr"/>
+      <c r="AB499" t="inlineStr"/>
+      <c r="AC499" t="inlineStr"/>
+      <c r="AD499" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B500" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C500" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>282</v>
+      </c>
+      <c r="F500" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I500" t="n">
+        <v>51</v>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K500" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M500" t="n">
+        <v>80</v>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q500" t="n">
+        <v>147062.25</v>
+      </c>
+      <c r="R500" t="n">
+        <v>0</v>
+      </c>
+      <c r="S500" t="n">
+        <v>0</v>
+      </c>
+      <c r="T500" t="inlineStr"/>
+      <c r="U500" t="inlineStr"/>
+      <c r="V500" t="n">
+        <v>0</v>
+      </c>
+      <c r="W500" t="inlineStr"/>
+      <c r="X500" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y500" t="inlineStr"/>
+      <c r="Z500" t="n">
+        <v>147062.25</v>
+      </c>
+      <c r="AA500" t="inlineStr"/>
+      <c r="AB500" t="inlineStr"/>
+      <c r="AC500" t="inlineStr"/>
+      <c r="AD500" t="n">
         <v>0</v>
       </c>
     </row>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD500"/>
+  <dimension ref="A1:AD505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14511,7 +14511,7 @@
         <v>30127671.46</v>
       </c>
       <c r="R155" t="n">
-        <v>4653543.42</v>
+        <v>6448835.68</v>
       </c>
       <c r="S155" t="n">
         <v>4597700.91</v>
@@ -14605,10 +14605,10 @@
         <v>45000</v>
       </c>
       <c r="R156" t="n">
-        <v>36030.57</v>
+        <v>37154.07</v>
       </c>
       <c r="S156" t="n">
-        <v>36030.57</v>
+        <v>37154.07</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14627,7 +14627,7 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>36030.57</v>
+        <v>37154.07</v>
       </c>
     </row>
     <row r="157">
@@ -16199,10 +16199,10 @@
         <v>67763</v>
       </c>
       <c r="R173" t="n">
-        <v>6992.2</v>
+        <v>8729</v>
       </c>
       <c r="S173" t="n">
-        <v>7354.2</v>
+        <v>9091</v>
       </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr"/>
       <c r="AD173" t="n">
-        <v>7354.2</v>
+        <v>9091</v>
       </c>
     </row>
     <row r="174">
@@ -16286,7 +16286,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>24515.1</v>
+        <v>29781.17</v>
       </c>
       <c r="R174" t="n">
         <v>24515.08</v>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="n">
-        <v>24515.1</v>
+        <v>29781.17</v>
       </c>
       <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr"/>
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>9112.059999999999</v>
+        <v>11194.7</v>
       </c>
       <c r="R175" t="n">
         <v>9112.030000000001</v>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="n">
-        <v>9112.059999999999</v>
+        <v>11194.7</v>
       </c>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr"/>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>71269.75999999999</v>
+        <v>79951.16</v>
       </c>
       <c r="R176" t="n">
         <v>71269.74000000001</v>
@@ -16493,7 +16493,7 @@
       </c>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="n">
-        <v>71269.75999999999</v>
+        <v>79951.16</v>
       </c>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>57253.87</v>
+        <v>68767.81</v>
       </c>
       <c r="R177" t="n">
         <v>57253.85</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="n">
-        <v>57253.87</v>
+        <v>68767.81</v>
       </c>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr"/>
@@ -16662,7 +16662,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>25486.78</v>
+        <v>31263.08</v>
       </c>
       <c r="R178" t="n">
         <v>25486.76</v>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="n">
-        <v>25486.78</v>
+        <v>31263.08</v>
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
@@ -16756,7 +16756,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>7364.59</v>
+        <v>8235.469999999999</v>
       </c>
       <c r="R179" t="n">
         <v>7364.56</v>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="n">
-        <v>7364.59</v>
+        <v>8235.469999999999</v>
       </c>
       <c r="AA179" t="inlineStr"/>
       <c r="AB179" t="inlineStr"/>
@@ -18444,7 +18444,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>1720.89</v>
+        <v>2301.47</v>
       </c>
       <c r="R197" t="n">
         <v>1694.47</v>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="Y197" t="inlineStr"/>
       <c r="Z197" t="n">
-        <v>1720.89</v>
+        <v>2301.47</v>
       </c>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr"/>
@@ -18726,7 +18726,7 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>16914580.43</v>
+        <v>15468600.43</v>
       </c>
       <c r="R200" t="n">
         <v>3880593.18</v>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="Y200" t="inlineStr"/>
       <c r="Z200" t="n">
-        <v>16914580.43</v>
+        <v>15468600.43</v>
       </c>
       <c r="AA200" t="inlineStr"/>
       <c r="AB200" t="inlineStr"/>
@@ -18820,7 +18820,7 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>257582.45</v>
+        <v>235562.45</v>
       </c>
       <c r="R201" t="n">
         <v>59095.34</v>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="Y201" t="inlineStr"/>
       <c r="Z201" t="n">
-        <v>257582.45</v>
+        <v>235562.45</v>
       </c>
       <c r="AA201" t="inlineStr"/>
       <c r="AB201" t="inlineStr"/>
@@ -19105,7 +19105,7 @@
         <v>8550543.42</v>
       </c>
       <c r="R204" t="n">
-        <v>1750936.02</v>
+        <v>2054047.02</v>
       </c>
       <c r="S204" t="n">
         <v>1729924.76</v>
@@ -36580,7 +36580,7 @@
         </is>
       </c>
       <c r="Q397" t="n">
-        <v>3167</v>
+        <v>4987.97</v>
       </c>
       <c r="R397" t="n">
         <v>3166.97</v>
@@ -36599,7 +36599,7 @@
       </c>
       <c r="Y397" t="inlineStr"/>
       <c r="Z397" t="n">
-        <v>3167</v>
+        <v>4987.97</v>
       </c>
       <c r="AA397" t="inlineStr"/>
       <c r="AB397" t="inlineStr"/>
@@ -36768,7 +36768,7 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>37200.58</v>
+        <v>38157.52</v>
       </c>
       <c r="R399" t="n">
         <v>37200.57</v>
@@ -36787,7 +36787,7 @@
       </c>
       <c r="Y399" t="inlineStr"/>
       <c r="Z399" t="n">
-        <v>37200.58</v>
+        <v>38157.52</v>
       </c>
       <c r="AA399" t="inlineStr"/>
       <c r="AB399" t="inlineStr"/>
@@ -36862,7 +36862,7 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>20831.63</v>
+        <v>21023.01</v>
       </c>
       <c r="R400" t="n">
         <v>20831.62</v>
@@ -36881,7 +36881,7 @@
       </c>
       <c r="Y400" t="inlineStr"/>
       <c r="Z400" t="n">
-        <v>20831.63</v>
+        <v>21023.01</v>
       </c>
       <c r="AA400" t="inlineStr"/>
       <c r="AB400" t="inlineStr"/>
@@ -36956,7 +36956,7 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>83870.03999999999</v>
+        <v>85783.92999999999</v>
       </c>
       <c r="R401" t="n">
         <v>83870.03</v>
@@ -36975,7 +36975,7 @@
       </c>
       <c r="Y401" t="inlineStr"/>
       <c r="Z401" t="n">
-        <v>83870.03999999999</v>
+        <v>85783.92999999999</v>
       </c>
       <c r="AA401" t="inlineStr"/>
       <c r="AB401" t="inlineStr"/>
@@ -37050,7 +37050,7 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>82956.12</v>
+        <v>84678.62</v>
       </c>
       <c r="R402" t="n">
         <v>82956.11</v>
@@ -37069,7 +37069,7 @@
       </c>
       <c r="Y402" t="inlineStr"/>
       <c r="Z402" t="n">
-        <v>82956.12</v>
+        <v>84678.62</v>
       </c>
       <c r="AA402" t="inlineStr"/>
       <c r="AB402" t="inlineStr"/>
@@ -37144,7 +37144,7 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>60486.65</v>
+        <v>61443.59</v>
       </c>
       <c r="R403" t="n">
         <v>60486.64</v>
@@ -37163,7 +37163,7 @@
       </c>
       <c r="Y403" t="inlineStr"/>
       <c r="Z403" t="n">
-        <v>60486.65</v>
+        <v>61443.59</v>
       </c>
       <c r="AA403" t="inlineStr"/>
       <c r="AB403" t="inlineStr"/>
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>13909.09</v>
+        <v>14291.86</v>
       </c>
       <c r="R404" t="n">
         <v>13909.08</v>
@@ -37257,7 +37257,7 @@
       </c>
       <c r="Y404" t="inlineStr"/>
       <c r="Z404" t="n">
-        <v>13909.09</v>
+        <v>14291.86</v>
       </c>
       <c r="AA404" t="inlineStr"/>
       <c r="AB404" t="inlineStr"/>
@@ -37332,7 +37332,7 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>3462.29</v>
+        <v>3570.73</v>
       </c>
       <c r="R405" t="n">
         <v>3462.28</v>
@@ -37351,7 +37351,7 @@
       </c>
       <c r="Y405" t="inlineStr"/>
       <c r="Z405" t="n">
-        <v>3462.29</v>
+        <v>3570.73</v>
       </c>
       <c r="AA405" t="inlineStr"/>
       <c r="AB405" t="inlineStr"/>
@@ -38258,7 +38258,7 @@
         <v>13783.27</v>
       </c>
       <c r="S415" t="n">
-        <v>0</v>
+        <v>13616.44</v>
       </c>
       <c r="T415" t="inlineStr"/>
       <c r="U415" t="inlineStr"/>
@@ -38277,7 +38277,7 @@
       <c r="AB415" t="inlineStr"/>
       <c r="AC415" t="inlineStr"/>
       <c r="AD415" t="n">
-        <v>0</v>
+        <v>13616.44</v>
       </c>
     </row>
     <row r="416">
@@ -38443,7 +38443,7 @@
         <v>34988.64</v>
       </c>
       <c r="R417" t="n">
-        <v>23010.54</v>
+        <v>34988.64</v>
       </c>
       <c r="S417" t="n">
         <v>11978.1</v>
@@ -38533,10 +38533,10 @@
         <v>1688.7</v>
       </c>
       <c r="R418" t="n">
-        <v>1160.87</v>
+        <v>1688.7</v>
       </c>
       <c r="S418" t="n">
-        <v>191.38</v>
+        <v>719.21</v>
       </c>
       <c r="T418" t="inlineStr"/>
       <c r="U418" t="inlineStr"/>
@@ -38551,7 +38551,7 @@
       <c r="AB418" t="inlineStr"/>
       <c r="AC418" t="inlineStr"/>
       <c r="AD418" t="n">
-        <v>191.38</v>
+        <v>719.21</v>
       </c>
     </row>
     <row r="419">
@@ -38623,7 +38623,7 @@
         <v>55541.8</v>
       </c>
       <c r="R419" t="n">
-        <v>27770.9</v>
+        <v>55541.8</v>
       </c>
       <c r="S419" t="n">
         <v>27770.9</v>
@@ -38893,10 +38893,10 @@
         <v>979.1799999999999</v>
       </c>
       <c r="R422" t="n">
+        <v>978.1799999999999</v>
+      </c>
+      <c r="S422" t="n">
         <v>489.09</v>
-      </c>
-      <c r="S422" t="n">
-        <v>0</v>
       </c>
       <c r="T422" t="inlineStr"/>
       <c r="U422" t="inlineStr"/>
@@ -38911,7 +38911,7 @@
       <c r="AB422" t="inlineStr"/>
       <c r="AC422" t="inlineStr"/>
       <c r="AD422" t="n">
-        <v>0</v>
+        <v>489.09</v>
       </c>
     </row>
     <row r="423">
@@ -39550,7 +39550,7 @@
         <v>1821.18</v>
       </c>
       <c r="S429" t="n">
-        <v>502.49</v>
+        <v>1733.76</v>
       </c>
       <c r="T429" t="inlineStr"/>
       <c r="U429" t="inlineStr"/>
@@ -39569,7 +39569,7 @@
       <c r="AB429" t="inlineStr"/>
       <c r="AC429" t="inlineStr"/>
       <c r="AD429" t="n">
-        <v>502.49</v>
+        <v>1733.76</v>
       </c>
     </row>
     <row r="430">
@@ -39926,7 +39926,7 @@
         <v>98218.74000000001</v>
       </c>
       <c r="S433" t="n">
-        <v>39833.26</v>
+        <v>81183.35000000001</v>
       </c>
       <c r="T433" t="inlineStr"/>
       <c r="U433" t="inlineStr"/>
@@ -39945,7 +39945,7 @@
       <c r="AB433" t="inlineStr"/>
       <c r="AC433" t="inlineStr"/>
       <c r="AD433" t="n">
-        <v>39833.26</v>
+        <v>81183.35000000001</v>
       </c>
     </row>
     <row r="434">
@@ -40020,7 +40020,7 @@
         <v>32739.58</v>
       </c>
       <c r="S434" t="n">
-        <v>13783.36</v>
+        <v>27566.72</v>
       </c>
       <c r="T434" t="inlineStr"/>
       <c r="U434" t="inlineStr"/>
@@ -40039,7 +40039,7 @@
       <c r="AB434" t="inlineStr"/>
       <c r="AC434" t="inlineStr"/>
       <c r="AD434" t="n">
-        <v>13783.36</v>
+        <v>27566.72</v>
       </c>
     </row>
     <row r="435">
@@ -40584,7 +40584,7 @@
         <v>5414.44</v>
       </c>
       <c r="S440" t="n">
-        <v>1460.74</v>
+        <v>5154.55</v>
       </c>
       <c r="T440" t="inlineStr"/>
       <c r="U440" t="inlineStr"/>
@@ -40603,7 +40603,7 @@
       <c r="AB440" t="inlineStr"/>
       <c r="AC440" t="inlineStr"/>
       <c r="AD440" t="n">
-        <v>1460.74</v>
+        <v>5154.55</v>
       </c>
     </row>
     <row r="441">
@@ -40678,7 +40678,7 @@
         <v>3642.36</v>
       </c>
       <c r="S441" t="n">
-        <v>1004.99</v>
+        <v>3467.53</v>
       </c>
       <c r="T441" t="inlineStr"/>
       <c r="U441" t="inlineStr"/>
@@ -40697,7 +40697,7 @@
       <c r="AB441" t="inlineStr"/>
       <c r="AC441" t="inlineStr"/>
       <c r="AD441" t="n">
-        <v>1004.99</v>
+        <v>3467.53</v>
       </c>
     </row>
     <row r="442">
@@ -40772,7 +40772,7 @@
         <v>65479.16</v>
       </c>
       <c r="S442" t="n">
-        <v>27566.73</v>
+        <v>55133.46</v>
       </c>
       <c r="T442" t="inlineStr"/>
       <c r="U442" t="inlineStr"/>
@@ -40791,7 +40791,7 @@
       <c r="AB442" t="inlineStr"/>
       <c r="AC442" t="inlineStr"/>
       <c r="AD442" t="n">
-        <v>27566.73</v>
+        <v>55133.46</v>
       </c>
     </row>
     <row r="443">
@@ -46106,6 +46106,468 @@
         <v>0</v>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B501" t="n">
+        <v>9468057</v>
+      </c>
+      <c r="C501" t="n">
+        <v>1371</v>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE MEIO AMBIENTE E DESENVOLVIMENTO SUSTENTAVEL</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>367</v>
+      </c>
+      <c r="F501" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>1501561 000038/2025</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I501" t="n">
+        <v>37</v>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K501" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M501" t="n">
+        <v>80</v>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q501" t="n">
+        <v>510.38</v>
+      </c>
+      <c r="R501" t="n">
+        <v>0</v>
+      </c>
+      <c r="S501" t="n">
+        <v>0</v>
+      </c>
+      <c r="T501" t="inlineStr"/>
+      <c r="U501" t="inlineStr"/>
+      <c r="V501" t="n">
+        <v>0</v>
+      </c>
+      <c r="W501" t="inlineStr"/>
+      <c r="X501" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y501" t="inlineStr"/>
+      <c r="Z501" t="n">
+        <v>510.38</v>
+      </c>
+      <c r="AA501" t="inlineStr"/>
+      <c r="AB501" t="inlineStr"/>
+      <c r="AC501" t="inlineStr"/>
+      <c r="AD501" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B502" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C502" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>28</v>
+      </c>
+      <c r="F502" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>1511189 000101/2026</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I502" t="n">
+        <v>52</v>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K502" t="n">
+        <v>5201</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>AERONAVES E COMPONENTES ESTRUTURAIS</t>
+        </is>
+      </c>
+      <c r="M502" t="n">
+        <v>80</v>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>13.373.898/0001-95</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>GOHOBBY FUTURE TECHNOLOGY LTDA</t>
+        </is>
+      </c>
+      <c r="Q502" t="n">
+        <v>48700</v>
+      </c>
+      <c r="R502" t="n">
+        <v>0</v>
+      </c>
+      <c r="S502" t="n">
+        <v>0</v>
+      </c>
+      <c r="T502" t="inlineStr"/>
+      <c r="U502" t="inlineStr"/>
+      <c r="V502" t="inlineStr"/>
+      <c r="W502" t="inlineStr"/>
+      <c r="X502" t="inlineStr"/>
+      <c r="Y502" t="inlineStr"/>
+      <c r="Z502" t="n">
+        <v>48700</v>
+      </c>
+      <c r="AA502" t="inlineStr"/>
+      <c r="AB502" t="inlineStr"/>
+      <c r="AC502" t="inlineStr"/>
+      <c r="AD502" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B503" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C503" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>36</v>
+      </c>
+      <c r="F503" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I503" t="n">
+        <v>33</v>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>PASSAGENS E DESPESAS COM LOCOMOCAO</t>
+        </is>
+      </c>
+      <c r="K503" t="n">
+        <v>3302</v>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>DESPESAS COM TRANSPORTE URBANO, PEDAGIO E ESTACIONAMETO PESSOA FISICA</t>
+        </is>
+      </c>
+      <c r="M503" t="n">
+        <v>80</v>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>015.033.486/95</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>MATHEUS EDUARDO BRAGA LOPES BRAGANCA SILVA</t>
+        </is>
+      </c>
+      <c r="Q503" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="R503" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="S503" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="T503" t="inlineStr"/>
+      <c r="U503" t="inlineStr"/>
+      <c r="V503" t="n">
+        <v>0</v>
+      </c>
+      <c r="W503" t="inlineStr"/>
+      <c r="X503" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y503" t="inlineStr"/>
+      <c r="Z503" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="AA503" t="inlineStr"/>
+      <c r="AB503" t="inlineStr"/>
+      <c r="AC503" t="inlineStr"/>
+      <c r="AD503" t="n">
+        <v>61.28</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B504" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C504" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>37</v>
+      </c>
+      <c r="F504" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I504" t="n">
+        <v>33</v>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>PASSAGENS E DESPESAS COM LOCOMOCAO</t>
+        </is>
+      </c>
+      <c r="K504" t="n">
+        <v>3302</v>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>DESPESAS COM TRANSPORTE URBANO, PEDAGIO E ESTACIONAMETO PESSOA FISICA</t>
+        </is>
+      </c>
+      <c r="M504" t="n">
+        <v>80</v>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>120.225.986/36</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>JULIA PESSOA REIS</t>
+        </is>
+      </c>
+      <c r="Q504" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="R504" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="S504" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="T504" t="inlineStr"/>
+      <c r="U504" t="inlineStr"/>
+      <c r="V504" t="n">
+        <v>0</v>
+      </c>
+      <c r="W504" t="inlineStr"/>
+      <c r="X504" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y504" t="inlineStr"/>
+      <c r="Z504" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="AA504" t="inlineStr"/>
+      <c r="AB504" t="inlineStr"/>
+      <c r="AC504" t="inlineStr"/>
+      <c r="AD504" t="n">
+        <v>18.26</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B505" t="n">
+        <v>9480259</v>
+      </c>
+      <c r="C505" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>210</v>
+      </c>
+      <c r="F505" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>1221002 000020/2026</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>INEXIGIBILIDADE - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I505" t="n">
+        <v>39</v>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>OUTROS SERVICOS DE TERCEIROS - PESSOA JURIDICA</t>
+        </is>
+      </c>
+      <c r="K505" t="n">
+        <v>3919</v>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAQUINAS E EQUIPAMENTOS</t>
+        </is>
+      </c>
+      <c r="M505" t="n">
+        <v>80</v>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>37.868.443/0001-09</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>BRASIL SPIRIT EVENTOS LTDA</t>
+        </is>
+      </c>
+      <c r="Q505" t="n">
+        <v>18571.42</v>
+      </c>
+      <c r="R505" t="n">
+        <v>0</v>
+      </c>
+      <c r="S505" t="n">
+        <v>0</v>
+      </c>
+      <c r="T505" t="inlineStr"/>
+      <c r="U505" t="inlineStr"/>
+      <c r="V505" t="inlineStr"/>
+      <c r="W505" t="inlineStr"/>
+      <c r="X505" t="inlineStr"/>
+      <c r="Y505" t="inlineStr"/>
+      <c r="Z505" t="n">
+        <v>18571.42</v>
+      </c>
+      <c r="AA505" t="inlineStr"/>
+      <c r="AB505" t="inlineStr"/>
+      <c r="AC505" t="inlineStr"/>
+      <c r="AD505" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD511"/>
+  <dimension ref="A1:AD514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13098,7 +13098,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>5891.6</v>
+        <v>9891.6</v>
       </c>
       <c r="R140" t="n">
         <v>5891.6</v>
@@ -13117,7 +13117,7 @@
       </c>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="n">
-        <v>5891.6</v>
+        <v>9891.6</v>
       </c>
       <c r="AA140" t="inlineStr"/>
       <c r="AB140" t="inlineStr"/>
@@ -14514,7 +14514,7 @@
         <v>6448835.68</v>
       </c>
       <c r="S155" t="n">
-        <v>4597700.91</v>
+        <v>6371449.66</v>
       </c>
       <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr"/>
@@ -14533,7 +14533,7 @@
       <c r="AB155" t="inlineStr"/>
       <c r="AC155" t="inlineStr"/>
       <c r="AD155" t="n">
-        <v>4597700.91</v>
+        <v>6371449.66</v>
       </c>
     </row>
     <row r="156">
@@ -16199,10 +16199,10 @@
         <v>67763</v>
       </c>
       <c r="R173" t="n">
-        <v>8729</v>
+        <v>10465.8</v>
       </c>
       <c r="S173" t="n">
-        <v>9091</v>
+        <v>10827.8</v>
       </c>
       <c r="T173" t="inlineStr"/>
       <c r="U173" t="inlineStr"/>
@@ -16217,7 +16217,7 @@
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr"/>
       <c r="AD173" t="n">
-        <v>9091</v>
+        <v>10827.8</v>
       </c>
     </row>
     <row r="174">
@@ -18823,7 +18823,7 @@
         <v>235562.45</v>
       </c>
       <c r="R201" t="n">
-        <v>59095.34</v>
+        <v>87926.27</v>
       </c>
       <c r="S201" t="n">
         <v>58386.21</v>
@@ -19108,7 +19108,7 @@
         <v>2054047.02</v>
       </c>
       <c r="S204" t="n">
-        <v>1729924.76</v>
+        <v>2029398.43</v>
       </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
@@ -19127,7 +19127,7 @@
       <c r="AB204" t="inlineStr"/>
       <c r="AC204" t="inlineStr"/>
       <c r="AD204" t="n">
-        <v>1729924.76</v>
+        <v>2029398.43</v>
       </c>
     </row>
     <row r="205">
@@ -20597,7 +20597,7 @@
         <v>7132375.41</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>259286.24</v>
       </c>
       <c r="S220" t="n">
         <v>0</v>
@@ -38438,7 +38438,7 @@
         <v>13783.27</v>
       </c>
       <c r="S417" t="n">
-        <v>13616.44</v>
+        <v>13617.87</v>
       </c>
       <c r="T417" t="inlineStr"/>
       <c r="U417" t="inlineStr"/>
@@ -38457,7 +38457,7 @@
       <c r="AB417" t="inlineStr"/>
       <c r="AC417" t="inlineStr"/>
       <c r="AD417" t="n">
-        <v>13616.44</v>
+        <v>13617.87</v>
       </c>
     </row>
     <row r="418">
@@ -38529,7 +38529,7 @@
         <v>15417806.27</v>
       </c>
       <c r="R418" t="n">
-        <v>773832.3</v>
+        <v>1232944.69</v>
       </c>
       <c r="S418" t="n">
         <v>764546.3</v>
@@ -38626,7 +38626,7 @@
         <v>34988.64</v>
       </c>
       <c r="S419" t="n">
-        <v>11978.1</v>
+        <v>23956.2</v>
       </c>
       <c r="T419" t="inlineStr"/>
       <c r="U419" t="inlineStr"/>
@@ -38641,7 +38641,7 @@
       <c r="AB419" t="inlineStr"/>
       <c r="AC419" t="inlineStr"/>
       <c r="AD419" t="n">
-        <v>11978.1</v>
+        <v>23956.2</v>
       </c>
     </row>
     <row r="420">
@@ -38716,7 +38716,7 @@
         <v>1688.7</v>
       </c>
       <c r="S420" t="n">
-        <v>719.21</v>
+        <v>1247.04</v>
       </c>
       <c r="T420" t="inlineStr"/>
       <c r="U420" t="inlineStr"/>
@@ -38731,7 +38731,7 @@
       <c r="AB420" t="inlineStr"/>
       <c r="AC420" t="inlineStr"/>
       <c r="AD420" t="n">
-        <v>719.21</v>
+        <v>1247.04</v>
       </c>
     </row>
     <row r="421">
@@ -38806,7 +38806,7 @@
         <v>55541.8</v>
       </c>
       <c r="S421" t="n">
-        <v>27770.9</v>
+        <v>55541.8</v>
       </c>
       <c r="T421" t="inlineStr"/>
       <c r="U421" t="inlineStr"/>
@@ -38821,7 +38821,7 @@
       <c r="AB421" t="inlineStr"/>
       <c r="AC421" t="inlineStr"/>
       <c r="AD421" t="n">
-        <v>27770.9</v>
+        <v>55541.8</v>
       </c>
     </row>
     <row r="422">
@@ -38896,7 +38896,7 @@
         <v>131856.3</v>
       </c>
       <c r="S422" t="n">
-        <v>59204.52</v>
+        <v>131856.3</v>
       </c>
       <c r="T422" t="inlineStr"/>
       <c r="U422" t="inlineStr"/>
@@ -38911,7 +38911,7 @@
       <c r="AB422" t="inlineStr"/>
       <c r="AC422" t="inlineStr"/>
       <c r="AD422" t="n">
-        <v>59204.52</v>
+        <v>131856.3</v>
       </c>
     </row>
     <row r="423">
@@ -39256,7 +39256,7 @@
         <v>978.1799999999999</v>
       </c>
       <c r="S426" t="n">
-        <v>489.09</v>
+        <v>978.1799999999999</v>
       </c>
       <c r="T426" t="inlineStr"/>
       <c r="U426" t="inlineStr"/>
@@ -39271,7 +39271,7 @@
       <c r="AB426" t="inlineStr"/>
       <c r="AC426" t="inlineStr"/>
       <c r="AD426" t="n">
-        <v>489.09</v>
+        <v>978.1799999999999</v>
       </c>
     </row>
     <row r="427">
@@ -39346,7 +39346,7 @@
         <v>6398.28</v>
       </c>
       <c r="S427" t="n">
-        <v>3200.29</v>
+        <v>6398.28</v>
       </c>
       <c r="T427" t="inlineStr"/>
       <c r="U427" t="inlineStr"/>
@@ -39361,7 +39361,7 @@
       <c r="AB427" t="inlineStr"/>
       <c r="AC427" t="inlineStr"/>
       <c r="AD427" t="n">
-        <v>3200.29</v>
+        <v>6398.28</v>
       </c>
     </row>
     <row r="428">
@@ -39433,7 +39433,7 @@
         <v>295000</v>
       </c>
       <c r="R428" t="n">
-        <v>0</v>
+        <v>45235.48</v>
       </c>
       <c r="S428" t="n">
         <v>0</v>
@@ -39621,7 +39621,7 @@
         <v>14124998.39</v>
       </c>
       <c r="R430" t="n">
-        <v>0</v>
+        <v>1063647.94</v>
       </c>
       <c r="S430" t="n">
         <v>0</v>
@@ -39712,10 +39712,10 @@
         </is>
       </c>
       <c r="Q431" t="n">
-        <v>3653045.85</v>
+        <v>4999967.85</v>
       </c>
       <c r="R431" t="n">
-        <v>0</v>
+        <v>951012.53</v>
       </c>
       <c r="S431" t="n">
         <v>0</v>
@@ -39731,7 +39731,7 @@
       </c>
       <c r="Y431" t="inlineStr"/>
       <c r="Z431" t="n">
-        <v>3653045.85</v>
+        <v>4999967.85</v>
       </c>
       <c r="AA431" t="inlineStr"/>
       <c r="AB431" t="inlineStr"/>
@@ -41313,7 +41313,7 @@
         <v>7064.85</v>
       </c>
       <c r="R448" t="n">
-        <v>0</v>
+        <v>7064.85</v>
       </c>
       <c r="S448" t="n">
         <v>0</v>
@@ -43698,7 +43698,7 @@
         </is>
       </c>
       <c r="Q474" t="n">
-        <v>1531.04</v>
+        <v>3531.04</v>
       </c>
       <c r="R474" t="n">
         <v>1531.04</v>
@@ -43717,7 +43717,7 @@
       </c>
       <c r="Y474" t="inlineStr"/>
       <c r="Z474" t="n">
-        <v>1531.04</v>
+        <v>3531.04</v>
       </c>
       <c r="AA474" t="inlineStr"/>
       <c r="AB474" t="inlineStr"/>
@@ -47108,6 +47108,288 @@
         <v>0</v>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B512" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C512" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>287</v>
+      </c>
+      <c r="F512" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I512" t="n">
+        <v>51</v>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K512" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M512" t="n">
+        <v>80</v>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q512" t="n">
+        <v>1288904.58</v>
+      </c>
+      <c r="R512" t="n">
+        <v>0</v>
+      </c>
+      <c r="S512" t="n">
+        <v>0</v>
+      </c>
+      <c r="T512" t="inlineStr"/>
+      <c r="U512" t="inlineStr"/>
+      <c r="V512" t="n">
+        <v>0</v>
+      </c>
+      <c r="W512" t="inlineStr"/>
+      <c r="X512" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y512" t="inlineStr"/>
+      <c r="Z512" t="n">
+        <v>1288904.58</v>
+      </c>
+      <c r="AA512" t="inlineStr"/>
+      <c r="AB512" t="inlineStr"/>
+      <c r="AC512" t="inlineStr"/>
+      <c r="AD512" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B513" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C513" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>288</v>
+      </c>
+      <c r="F513" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I513" t="n">
+        <v>93</v>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K513" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M513" t="n">
+        <v>80</v>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q513" t="n">
+        <v>30000</v>
+      </c>
+      <c r="R513" t="n">
+        <v>0</v>
+      </c>
+      <c r="S513" t="n">
+        <v>0</v>
+      </c>
+      <c r="T513" t="inlineStr"/>
+      <c r="U513" t="inlineStr"/>
+      <c r="V513" t="n">
+        <v>0</v>
+      </c>
+      <c r="W513" t="inlineStr"/>
+      <c r="X513" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y513" t="inlineStr"/>
+      <c r="Z513" t="n">
+        <v>30000</v>
+      </c>
+      <c r="AA513" t="inlineStr"/>
+      <c r="AB513" t="inlineStr"/>
+      <c r="AC513" t="inlineStr"/>
+      <c r="AD513" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B514" t="n">
+        <v>9468055</v>
+      </c>
+      <c r="C514" t="n">
+        <v>1501</v>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE PLANEJAMENTO E GESTAO</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>38</v>
+      </c>
+      <c r="F514" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I514" t="n">
+        <v>33</v>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>PASSAGENS E DESPESAS COM LOCOMOCAO</t>
+        </is>
+      </c>
+      <c r="K514" t="n">
+        <v>3302</v>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>DESPESAS COM TRANSPORTE URBANO, PEDAGIO E ESTACIONAMETO PESSOA FISICA</t>
+        </is>
+      </c>
+      <c r="M514" t="n">
+        <v>80</v>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>120.754.126/50</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>MATHEUS FILLIPE LANGANKE DE CARVALHO</t>
+        </is>
+      </c>
+      <c r="Q514" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="R514" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="S514" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="T514" t="inlineStr"/>
+      <c r="U514" t="inlineStr"/>
+      <c r="V514" t="n">
+        <v>0</v>
+      </c>
+      <c r="W514" t="inlineStr"/>
+      <c r="X514" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y514" t="inlineStr"/>
+      <c r="Z514" t="n">
+        <v>38.26</v>
+      </c>
+      <c r="AA514" t="inlineStr"/>
+      <c r="AB514" t="inlineStr"/>
+      <c r="AC514" t="inlineStr"/>
+      <c r="AD514" t="n">
+        <v>38.26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD514"/>
+  <dimension ref="A1:AD517"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>503776.08</v>
+        <v>591758.7</v>
       </c>
       <c r="R150" t="n">
         <v>458955.45</v>
@@ -14057,7 +14057,7 @@
       </c>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="n">
-        <v>503776.08</v>
+        <v>591758.7</v>
       </c>
       <c r="AA150" t="inlineStr"/>
       <c r="AB150" t="inlineStr"/>
@@ -14132,7 +14132,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>1429064.13</v>
+        <v>1735475.63</v>
       </c>
       <c r="R151" t="n">
         <v>1372920.58</v>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="n">
-        <v>1429064.13</v>
+        <v>1735475.63</v>
       </c>
       <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="inlineStr"/>
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>337260.81</v>
+        <v>398730.09</v>
       </c>
       <c r="R154" t="n">
         <v>290318.01</v>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="n">
-        <v>337260.81</v>
+        <v>398730.09</v>
       </c>
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="inlineStr"/>
@@ -14602,10 +14602,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>45000</v>
+        <v>74230</v>
       </c>
       <c r="R156" t="n">
-        <v>37154.07</v>
+        <v>36384.07</v>
       </c>
       <c r="S156" t="n">
         <v>37154.07</v>
@@ -14621,7 +14621,7 @@
       </c>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="n">
-        <v>45000</v>
+        <v>74230</v>
       </c>
       <c r="AA156" t="inlineStr"/>
       <c r="AB156" t="inlineStr"/>
@@ -16286,10 +16286,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
+        <v>29781.19</v>
+      </c>
+      <c r="R174" t="n">
         <v>29781.17</v>
-      </c>
-      <c r="R174" t="n">
-        <v>24515.08</v>
       </c>
       <c r="S174" t="n">
         <v>24149.89</v>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="n">
-        <v>29781.17</v>
+        <v>29781.19</v>
       </c>
       <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr"/>
@@ -16380,10 +16380,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
+        <v>11194.73</v>
+      </c>
+      <c r="R175" t="n">
         <v>11194.7</v>
-      </c>
-      <c r="R175" t="n">
-        <v>9112.030000000001</v>
       </c>
       <c r="S175" t="n">
         <v>8832.459999999999</v>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="n">
-        <v>11194.7</v>
+        <v>11194.73</v>
       </c>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr"/>
@@ -16474,10 +16474,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
+        <v>79951.17999999999</v>
+      </c>
+      <c r="R176" t="n">
         <v>79951.16</v>
-      </c>
-      <c r="R176" t="n">
-        <v>71269.74000000001</v>
       </c>
       <c r="S176" t="n">
         <v>67124.59</v>
@@ -16493,7 +16493,7 @@
       </c>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="n">
-        <v>79951.16</v>
+        <v>79951.17999999999</v>
       </c>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
@@ -16568,10 +16568,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
+        <v>68767.83</v>
+      </c>
+      <c r="R177" t="n">
         <v>68767.81</v>
-      </c>
-      <c r="R177" t="n">
-        <v>57253.85</v>
       </c>
       <c r="S177" t="n">
         <v>54550.94</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="n">
-        <v>68767.81</v>
+        <v>68767.83</v>
       </c>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr"/>
@@ -16662,10 +16662,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
+        <v>31263.1</v>
+      </c>
+      <c r="R178" t="n">
         <v>31263.08</v>
-      </c>
-      <c r="R178" t="n">
-        <v>25486.76</v>
       </c>
       <c r="S178" t="n">
         <v>25486.76</v>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="n">
-        <v>31263.08</v>
+        <v>31263.1</v>
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
@@ -16756,10 +16756,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
+        <v>8235.5</v>
+      </c>
+      <c r="R179" t="n">
         <v>8235.469999999999</v>
-      </c>
-      <c r="R179" t="n">
-        <v>7364.56</v>
       </c>
       <c r="S179" t="n">
         <v>7364.56</v>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="n">
-        <v>8235.469999999999</v>
+        <v>8235.5</v>
       </c>
       <c r="AA179" t="inlineStr"/>
       <c r="AB179" t="inlineStr"/>
@@ -17132,10 +17132,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>618435.35</v>
+        <v>747684.7</v>
       </c>
       <c r="R183" t="n">
-        <v>618387.89</v>
+        <v>747637.24</v>
       </c>
       <c r="S183" t="n">
         <v>501375.46</v>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="n">
-        <v>618435.35</v>
+        <v>747684.7</v>
       </c>
       <c r="AA183" t="inlineStr"/>
       <c r="AB183" t="inlineStr"/>
@@ -17226,10 +17226,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>348827.24</v>
+        <v>423414.5</v>
       </c>
       <c r="R184" t="n">
-        <v>348787.24</v>
+        <v>423374.5</v>
       </c>
       <c r="S184" t="n">
         <v>310420.64</v>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="n">
-        <v>348827.24</v>
+        <v>423414.5</v>
       </c>
       <c r="AA184" t="inlineStr"/>
       <c r="AB184" t="inlineStr"/>
@@ -17320,10 +17320,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>1396844.69</v>
+        <v>1687657.74</v>
       </c>
       <c r="R185" t="n">
-        <v>1396840.69</v>
+        <v>1687653.74</v>
       </c>
       <c r="S185" t="n">
         <v>1242215.01</v>
@@ -17339,7 +17339,7 @@
       </c>
       <c r="Y185" t="inlineStr"/>
       <c r="Z185" t="n">
-        <v>1396844.69</v>
+        <v>1687657.74</v>
       </c>
       <c r="AA185" t="inlineStr"/>
       <c r="AB185" t="inlineStr"/>
@@ -17414,10 +17414,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>1287702.95</v>
+        <v>1559471.71</v>
       </c>
       <c r="R186" t="n">
-        <v>1287700.95</v>
+        <v>1559469.71</v>
       </c>
       <c r="S186" t="n">
         <v>1043395.36</v>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="Y186" t="inlineStr"/>
       <c r="Z186" t="n">
-        <v>1287702.95</v>
+        <v>1559471.71</v>
       </c>
       <c r="AA186" t="inlineStr"/>
       <c r="AB186" t="inlineStr"/>
@@ -17508,10 +17508,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>960793.26</v>
+        <v>1166875.46</v>
       </c>
       <c r="R187" t="n">
-        <v>960789.26</v>
+        <v>1166871.46</v>
       </c>
       <c r="S187" t="n">
         <v>805370.73</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Y187" t="inlineStr"/>
       <c r="Z187" t="n">
-        <v>960793.26</v>
+        <v>1166875.46</v>
       </c>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr"/>
@@ -17602,10 +17602,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>267391.5</v>
+        <v>303700.1</v>
       </c>
       <c r="R188" t="n">
-        <v>267387.5</v>
+        <v>303696.1</v>
       </c>
       <c r="S188" t="n">
         <v>237974.88</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="n">
-        <v>267391.5</v>
+        <v>303700.1</v>
       </c>
       <c r="AA188" t="inlineStr"/>
       <c r="AB188" t="inlineStr"/>
@@ -18444,10 +18444,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
+        <v>2301.5</v>
+      </c>
+      <c r="R197" t="n">
         <v>2301.47</v>
-      </c>
-      <c r="R197" t="n">
-        <v>1694.47</v>
       </c>
       <c r="S197" t="n">
         <v>1694.47</v>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="Y197" t="inlineStr"/>
       <c r="Z197" t="n">
-        <v>2301.47</v>
+        <v>2301.5</v>
       </c>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr"/>
@@ -18538,10 +18538,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>68798.59</v>
+        <v>90339.88</v>
       </c>
       <c r="R198" t="n">
-        <v>68798.53999999999</v>
+        <v>90339.83</v>
       </c>
       <c r="S198" t="n">
         <v>61230.69</v>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="Y198" t="inlineStr"/>
       <c r="Z198" t="n">
-        <v>68798.59</v>
+        <v>90339.88</v>
       </c>
       <c r="AA198" t="inlineStr"/>
       <c r="AB198" t="inlineStr"/>
@@ -18638,7 +18638,7 @@
         <v>3409725.72</v>
       </c>
       <c r="S199" t="n">
-        <v>2137605.03</v>
+        <v>3368809.03</v>
       </c>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
@@ -18657,7 +18657,7 @@
       <c r="AB199" t="inlineStr"/>
       <c r="AC199" t="inlineStr"/>
       <c r="AD199" t="n">
-        <v>2137605.03</v>
+        <v>3368809.03</v>
       </c>
     </row>
     <row r="200">
@@ -18729,7 +18729,7 @@
         <v>15468600.43</v>
       </c>
       <c r="R200" t="n">
-        <v>3880593.18</v>
+        <v>5773824.52</v>
       </c>
       <c r="S200" t="n">
         <v>3834026.07</v>
@@ -18826,7 +18826,7 @@
         <v>87926.27</v>
       </c>
       <c r="S201" t="n">
-        <v>58386.21</v>
+        <v>86871.17</v>
       </c>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
@@ -18845,7 +18845,7 @@
       <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr"/>
       <c r="AD201" t="n">
-        <v>58386.21</v>
+        <v>86871.17</v>
       </c>
     </row>
     <row r="202">
@@ -18917,10 +18917,10 @@
         <v>8675354.27</v>
       </c>
       <c r="R202" t="n">
-        <v>2458343.75</v>
+        <v>3083705.74</v>
       </c>
       <c r="S202" t="n">
-        <v>2428843.63</v>
+        <v>3046701.28</v>
       </c>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
@@ -18939,7 +18939,7 @@
       <c r="AB202" t="inlineStr"/>
       <c r="AC202" t="inlineStr"/>
       <c r="AD202" t="n">
-        <v>2428843.63</v>
+        <v>3046701.28</v>
       </c>
     </row>
     <row r="203">
@@ -19011,10 +19011,10 @@
         <v>2168838.56</v>
       </c>
       <c r="R203" t="n">
-        <v>614585.9300000001</v>
+        <v>770926.4300000001</v>
       </c>
       <c r="S203" t="n">
-        <v>607210.9</v>
+        <v>761675.3100000001</v>
       </c>
       <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr"/>
@@ -19033,7 +19033,7 @@
       <c r="AB203" t="inlineStr"/>
       <c r="AC203" t="inlineStr"/>
       <c r="AD203" t="n">
-        <v>607210.9</v>
+        <v>761675.3100000001</v>
       </c>
     </row>
     <row r="204">
@@ -20600,7 +20600,7 @@
         <v>259286.24</v>
       </c>
       <c r="S220" t="n">
-        <v>0</v>
+        <v>256174.81</v>
       </c>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
@@ -20619,7 +20619,7 @@
       <c r="AB220" t="inlineStr"/>
       <c r="AC220" t="inlineStr"/>
       <c r="AD220" t="n">
-        <v>0</v>
+        <v>256174.81</v>
       </c>
     </row>
     <row r="221">
@@ -36395,7 +36395,7 @@
         <v>98218.74000000001</v>
       </c>
       <c r="R395" t="n">
-        <v>65332.12</v>
+        <v>97998.17999999999</v>
       </c>
       <c r="S395" t="n">
         <v>55009.64</v>
@@ -36760,10 +36760,10 @@
         </is>
       </c>
       <c r="Q399" t="n">
+        <v>4988</v>
+      </c>
+      <c r="R399" t="n">
         <v>4987.97</v>
-      </c>
-      <c r="R399" t="n">
-        <v>3166.97</v>
       </c>
       <c r="S399" t="n">
         <v>3166.97</v>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="Y399" t="inlineStr"/>
       <c r="Z399" t="n">
-        <v>4987.97</v>
+        <v>4988</v>
       </c>
       <c r="AA399" t="inlineStr"/>
       <c r="AB399" t="inlineStr"/>
@@ -36854,10 +36854,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>122514.31</v>
+        <v>187522.15</v>
       </c>
       <c r="R400" t="n">
-        <v>122514.28</v>
+        <v>187522.12</v>
       </c>
       <c r="S400" t="n">
         <v>109037.71</v>
@@ -36873,7 +36873,7 @@
       </c>
       <c r="Y400" t="inlineStr"/>
       <c r="Z400" t="n">
-        <v>122514.31</v>
+        <v>187522.15</v>
       </c>
       <c r="AA400" t="inlineStr"/>
       <c r="AB400" t="inlineStr"/>
@@ -36951,7 +36951,7 @@
         <v>38157.52</v>
       </c>
       <c r="R401" t="n">
-        <v>37200.57</v>
+        <v>38157.52</v>
       </c>
       <c r="S401" t="n">
         <v>33558.03</v>
@@ -37045,7 +37045,7 @@
         <v>21023.01</v>
       </c>
       <c r="R402" t="n">
-        <v>20831.62</v>
+        <v>21023.01</v>
       </c>
       <c r="S402" t="n">
         <v>18620.27</v>
@@ -37139,7 +37139,7 @@
         <v>85783.92999999999</v>
       </c>
       <c r="R403" t="n">
-        <v>83870.03</v>
+        <v>85783.92999999999</v>
       </c>
       <c r="S403" t="n">
         <v>32074.07</v>
@@ -37233,7 +37233,7 @@
         <v>84678.62</v>
       </c>
       <c r="R404" t="n">
-        <v>82956.11</v>
+        <v>84678.62</v>
       </c>
       <c r="S404" t="n">
         <v>49139.97</v>
@@ -37327,7 +37327,7 @@
         <v>61443.59</v>
       </c>
       <c r="R405" t="n">
-        <v>60486.64</v>
+        <v>61443.59</v>
       </c>
       <c r="S405" t="n">
         <v>54499.27</v>
@@ -37421,7 +37421,7 @@
         <v>14291.86</v>
       </c>
       <c r="R406" t="n">
-        <v>13909.08</v>
+        <v>14291.86</v>
       </c>
       <c r="S406" t="n">
         <v>12597.62</v>
@@ -37515,7 +37515,7 @@
         <v>3570.73</v>
       </c>
       <c r="R407" t="n">
-        <v>3462.28</v>
+        <v>3570.73</v>
       </c>
       <c r="S407" t="n">
         <v>3131.65</v>
@@ -38532,7 +38532,7 @@
         <v>1232944.69</v>
       </c>
       <c r="S418" t="n">
-        <v>764546.3</v>
+        <v>1218149.35</v>
       </c>
       <c r="T418" t="inlineStr"/>
       <c r="U418" t="inlineStr"/>
@@ -38551,7 +38551,7 @@
       <c r="AB418" t="inlineStr"/>
       <c r="AC418" t="inlineStr"/>
       <c r="AD418" t="n">
-        <v>764546.3</v>
+        <v>1218149.35</v>
       </c>
     </row>
     <row r="419">
@@ -38716,7 +38716,7 @@
         <v>1688.7</v>
       </c>
       <c r="S420" t="n">
-        <v>1247.04</v>
+        <v>1688.7</v>
       </c>
       <c r="T420" t="inlineStr"/>
       <c r="U420" t="inlineStr"/>
@@ -38731,7 +38731,7 @@
       <c r="AB420" t="inlineStr"/>
       <c r="AC420" t="inlineStr"/>
       <c r="AD420" t="n">
-        <v>1247.04</v>
+        <v>1688.7</v>
       </c>
     </row>
     <row r="421">
@@ -39436,7 +39436,7 @@
         <v>45235.48</v>
       </c>
       <c r="S428" t="n">
-        <v>0</v>
+        <v>45235.48</v>
       </c>
       <c r="T428" t="inlineStr"/>
       <c r="U428" t="inlineStr"/>
@@ -39455,7 +39455,7 @@
       <c r="AB428" t="inlineStr"/>
       <c r="AC428" t="inlineStr"/>
       <c r="AD428" t="n">
-        <v>0</v>
+        <v>45235.48</v>
       </c>
     </row>
     <row r="429">
@@ -39624,7 +39624,7 @@
         <v>1063647.94</v>
       </c>
       <c r="S430" t="n">
-        <v>0</v>
+        <v>1050884.17</v>
       </c>
       <c r="T430" t="inlineStr"/>
       <c r="U430" t="inlineStr"/>
@@ -39643,7 +39643,7 @@
       <c r="AB430" t="inlineStr"/>
       <c r="AC430" t="inlineStr"/>
       <c r="AD430" t="n">
-        <v>0</v>
+        <v>1050884.17</v>
       </c>
     </row>
     <row r="431">
@@ -39718,7 +39718,7 @@
         <v>951012.53</v>
       </c>
       <c r="S431" t="n">
-        <v>0</v>
+        <v>948621.53</v>
       </c>
       <c r="T431" t="inlineStr"/>
       <c r="U431" t="inlineStr"/>
@@ -39737,7 +39737,7 @@
       <c r="AB431" t="inlineStr"/>
       <c r="AC431" t="inlineStr"/>
       <c r="AD431" t="n">
-        <v>0</v>
+        <v>948621.53</v>
       </c>
     </row>
     <row r="432">
@@ -39806,7 +39806,7 @@
         </is>
       </c>
       <c r="Q432" t="n">
-        <v>375825.75</v>
+        <v>496416.8</v>
       </c>
       <c r="R432" t="n">
         <v>0</v>
@@ -39825,7 +39825,7 @@
       </c>
       <c r="Y432" t="inlineStr"/>
       <c r="Z432" t="n">
-        <v>375825.75</v>
+        <v>496416.8</v>
       </c>
       <c r="AA432" t="inlineStr"/>
       <c r="AB432" t="inlineStr"/>
@@ -41316,7 +41316,7 @@
         <v>7064.85</v>
       </c>
       <c r="S448" t="n">
-        <v>0</v>
+        <v>7064.85</v>
       </c>
       <c r="T448" t="inlineStr"/>
       <c r="U448" t="inlineStr"/>
@@ -41331,7 +41331,7 @@
       <c r="AB448" t="inlineStr"/>
       <c r="AC448" t="inlineStr"/>
       <c r="AD448" t="n">
-        <v>0</v>
+        <v>7064.85</v>
       </c>
     </row>
     <row r="449">
@@ -43611,7 +43611,7 @@
         <v>896.3</v>
       </c>
       <c r="R473" t="n">
-        <v>0</v>
+        <v>896.3</v>
       </c>
       <c r="S473" t="n">
         <v>0</v>
@@ -46249,7 +46249,7 @@
         <v>7200</v>
       </c>
       <c r="R502" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="S502" t="n">
         <v>0</v>
@@ -46715,7 +46715,7 @@
         <v>510.38</v>
       </c>
       <c r="R507" t="n">
-        <v>0</v>
+        <v>510.37</v>
       </c>
       <c r="S507" t="n">
         <v>0</v>
@@ -47390,6 +47390,284 @@
         <v>38.26</v>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B515" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C515" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>289</v>
+      </c>
+      <c r="F515" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I515" t="n">
+        <v>51</v>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K515" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M515" t="n">
+        <v>80</v>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q515" t="n">
+        <v>196083</v>
+      </c>
+      <c r="R515" t="n">
+        <v>0</v>
+      </c>
+      <c r="S515" t="n">
+        <v>0</v>
+      </c>
+      <c r="T515" t="inlineStr"/>
+      <c r="U515" t="inlineStr"/>
+      <c r="V515" t="n">
+        <v>0</v>
+      </c>
+      <c r="W515" t="inlineStr"/>
+      <c r="X515" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y515" t="inlineStr"/>
+      <c r="Z515" t="n">
+        <v>196083</v>
+      </c>
+      <c r="AA515" t="inlineStr"/>
+      <c r="AB515" t="inlineStr"/>
+      <c r="AC515" t="inlineStr"/>
+      <c r="AD515" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B516" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C516" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>290</v>
+      </c>
+      <c r="F516" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I516" t="n">
+        <v>93</v>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K516" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M516" t="n">
+        <v>80</v>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q516" t="n">
+        <v>15000</v>
+      </c>
+      <c r="R516" t="n">
+        <v>0</v>
+      </c>
+      <c r="S516" t="n">
+        <v>0</v>
+      </c>
+      <c r="T516" t="inlineStr"/>
+      <c r="U516" t="inlineStr"/>
+      <c r="V516" t="n">
+        <v>0</v>
+      </c>
+      <c r="W516" t="inlineStr"/>
+      <c r="X516" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y516" t="inlineStr"/>
+      <c r="Z516" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AA516" t="inlineStr"/>
+      <c r="AB516" t="inlineStr"/>
+      <c r="AC516" t="inlineStr"/>
+      <c r="AD516" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B517" t="n">
+        <v>9445721</v>
+      </c>
+      <c r="C517" t="n">
+        <v>1231</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE AGRICULTURA, PECUARIA E ABASTECIMENTO</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>529</v>
+      </c>
+      <c r="F517" s="2" t="n">
+        <v>46232</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I517" t="n">
+        <v>14</v>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>DIARIAS - CIVIL</t>
+        </is>
+      </c>
+      <c r="K517" t="n">
+        <v>1401</v>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>DIARIAS - CIVIL</t>
+        </is>
+      </c>
+      <c r="M517" t="n">
+        <v>80</v>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>999.999.598/57</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>DIARIAS DE VIAGENS/PASSAGENS</t>
+        </is>
+      </c>
+      <c r="Q517" t="n">
+        <v>10125</v>
+      </c>
+      <c r="R517" t="n">
+        <v>0</v>
+      </c>
+      <c r="S517" t="n">
+        <v>0</v>
+      </c>
+      <c r="T517" t="inlineStr"/>
+      <c r="U517" t="inlineStr"/>
+      <c r="V517" t="inlineStr"/>
+      <c r="W517" t="inlineStr"/>
+      <c r="X517" t="inlineStr"/>
+      <c r="Y517" t="inlineStr"/>
+      <c r="Z517" t="n">
+        <v>10125</v>
+      </c>
+      <c r="AA517" t="inlineStr"/>
+      <c r="AB517" t="inlineStr"/>
+      <c r="AC517" t="inlineStr"/>
+      <c r="AD517" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -14226,7 +14226,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>111802.65</v>
+        <v>131802.65</v>
       </c>
       <c r="R152" t="n">
         <v>90398.55</v>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="n">
-        <v>111802.65</v>
+        <v>131802.65</v>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
@@ -20691,7 +20691,7 @@
         <v>7132375.41</v>
       </c>
       <c r="R221" t="n">
-        <v>259286.23</v>
+        <v>868789.0600000001</v>
       </c>
       <c r="S221" t="n">
         <v>256174.8</v>
@@ -22410,7 +22410,7 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>698765.6</v>
+        <v>696572.29</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
@@ -22429,7 +22429,7 @@
       </c>
       <c r="Y240" t="inlineStr"/>
       <c r="Z240" t="n">
-        <v>698765.6</v>
+        <v>696572.29</v>
       </c>
       <c r="AA240" t="inlineStr"/>
       <c r="AB240" t="inlineStr"/>
@@ -22504,7 +22504,7 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>326805</v>
+        <v>328992.35</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
@@ -22523,7 +22523,7 @@
       </c>
       <c r="Y241" t="inlineStr"/>
       <c r="Z241" t="n">
-        <v>326805</v>
+        <v>328992.35</v>
       </c>
       <c r="AA241" t="inlineStr"/>
       <c r="AB241" t="inlineStr"/>
@@ -38244,7 +38244,7 @@
         </is>
       </c>
       <c r="Q415" t="n">
-        <v>83169.53</v>
+        <v>89169.53</v>
       </c>
       <c r="R415" t="n">
         <v>82969.53</v>
@@ -38263,7 +38263,7 @@
       </c>
       <c r="Y415" t="inlineStr"/>
       <c r="Z415" t="n">
-        <v>83169.53</v>
+        <v>89169.53</v>
       </c>
       <c r="AA415" t="inlineStr"/>
       <c r="AB415" t="inlineStr"/>
@@ -39806,7 +39806,7 @@
         </is>
       </c>
       <c r="Q432" t="n">
-        <v>496416.8</v>
+        <v>496394.56</v>
       </c>
       <c r="R432" t="n">
         <v>0</v>
@@ -39825,7 +39825,7 @@
       </c>
       <c r="Y432" t="inlineStr"/>
       <c r="Z432" t="n">
-        <v>496416.8</v>
+        <v>496394.56</v>
       </c>
       <c r="AA432" t="inlineStr"/>
       <c r="AB432" t="inlineStr"/>
@@ -40746,7 +40746,7 @@
         </is>
       </c>
       <c r="Q442" t="n">
-        <v>490207.5</v>
+        <v>490207.03</v>
       </c>
       <c r="R442" t="n">
         <v>0</v>
@@ -40765,7 +40765,7 @@
       </c>
       <c r="Y442" t="inlineStr"/>
       <c r="Z442" t="n">
-        <v>490207.5</v>
+        <v>490207.03</v>
       </c>
       <c r="AA442" t="inlineStr"/>
       <c r="AB442" t="inlineStr"/>
@@ -43146,7 +43146,7 @@
         </is>
       </c>
       <c r="Q468" t="n">
-        <v>552300.45</v>
+        <v>552270.41</v>
       </c>
       <c r="R468" t="n">
         <v>0</v>
@@ -43165,7 +43165,7 @@
       </c>
       <c r="Y468" t="inlineStr"/>
       <c r="Z468" t="n">
-        <v>552300.45</v>
+        <v>552270.41</v>
       </c>
       <c r="AA468" t="inlineStr"/>
       <c r="AB468" t="inlineStr"/>
@@ -46618,7 +46618,7 @@
         </is>
       </c>
       <c r="Q506" t="n">
-        <v>147062.25</v>
+        <v>147031.61</v>
       </c>
       <c r="R506" t="n">
         <v>0</v>
@@ -46637,7 +46637,7 @@
       </c>
       <c r="Y506" t="inlineStr"/>
       <c r="Z506" t="n">
-        <v>147062.25</v>
+        <v>147031.61</v>
       </c>
       <c r="AA506" t="inlineStr"/>
       <c r="AB506" t="inlineStr"/>
@@ -47456,7 +47456,7 @@
         </is>
       </c>
       <c r="Q515" t="n">
-        <v>196083</v>
+        <v>196080.79</v>
       </c>
       <c r="R515" t="n">
         <v>0</v>
@@ -47475,7 +47475,7 @@
       </c>
       <c r="Y515" t="inlineStr"/>
       <c r="Z515" t="n">
-        <v>196083</v>
+        <v>196080.79</v>
       </c>
       <c r="AA515" t="inlineStr"/>
       <c r="AB515" t="inlineStr"/>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD517"/>
+  <dimension ref="A1:AD530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13101,10 +13101,10 @@
         <v>9891.6</v>
       </c>
       <c r="R140" t="n">
-        <v>5891.6</v>
+        <v>7105.6</v>
       </c>
       <c r="S140" t="n">
-        <v>5608.81</v>
+        <v>6764.54</v>
       </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
@@ -13123,7 +13123,7 @@
       <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="n">
-        <v>5608.81</v>
+        <v>6764.54</v>
       </c>
     </row>
     <row r="141">
@@ -13756,13 +13756,13 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>211792.55</v>
+        <v>244532.13</v>
       </c>
       <c r="R147" t="n">
-        <v>195422.76</v>
+        <v>228162.34</v>
       </c>
       <c r="S147" t="n">
-        <v>164545.95</v>
+        <v>192112.68</v>
       </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
@@ -13775,13 +13775,13 @@
       </c>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="n">
-        <v>211792.55</v>
+        <v>244532.13</v>
       </c>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr"/>
       <c r="AC147" t="inlineStr"/>
       <c r="AD147" t="n">
-        <v>164545.95</v>
+        <v>192112.68</v>
       </c>
     </row>
     <row r="148">
@@ -13947,7 +13947,7 @@
         <v>67000.00999999999</v>
       </c>
       <c r="R149" t="n">
-        <v>56330.67</v>
+        <v>60353.76</v>
       </c>
       <c r="S149" t="n">
         <v>51276.71</v>
@@ -14041,7 +14041,7 @@
         <v>591758.7</v>
       </c>
       <c r="R150" t="n">
-        <v>458955.45</v>
+        <v>532088</v>
       </c>
       <c r="S150" t="n">
         <v>381841.64</v>
@@ -14135,7 +14135,7 @@
         <v>1735475.63</v>
       </c>
       <c r="R151" t="n">
-        <v>1372920.58</v>
+        <v>1653787.16</v>
       </c>
       <c r="S151" t="n">
         <v>1146612.36</v>
@@ -14229,7 +14229,7 @@
         <v>131802.65</v>
       </c>
       <c r="R152" t="n">
-        <v>90398.55</v>
+        <v>103830.02</v>
       </c>
       <c r="S152" t="n">
         <v>83732.94</v>
@@ -14323,7 +14323,7 @@
         <v>12560.85</v>
       </c>
       <c r="R153" t="n">
-        <v>9672.129999999999</v>
+        <v>12100.13</v>
       </c>
       <c r="S153" t="n">
         <v>9295.059999999999</v>
@@ -14417,7 +14417,7 @@
         <v>398730.09</v>
       </c>
       <c r="R154" t="n">
-        <v>290318.01</v>
+        <v>351702.49</v>
       </c>
       <c r="S154" t="n">
         <v>201799.44</v>
@@ -16292,7 +16292,7 @@
         <v>29781.17</v>
       </c>
       <c r="S174" t="n">
-        <v>24149.89</v>
+        <v>29332.76</v>
       </c>
       <c r="T174" t="inlineStr"/>
       <c r="U174" t="inlineStr"/>
@@ -16311,7 +16311,7 @@
       <c r="AB174" t="inlineStr"/>
       <c r="AC174" t="inlineStr"/>
       <c r="AD174" t="n">
-        <v>24149.89</v>
+        <v>29332.76</v>
       </c>
     </row>
     <row r="175">
@@ -16386,7 +16386,7 @@
         <v>11194.7</v>
       </c>
       <c r="S175" t="n">
-        <v>8832.459999999999</v>
+        <v>10868.92</v>
       </c>
       <c r="T175" t="inlineStr"/>
       <c r="U175" t="inlineStr"/>
@@ -16405,7 +16405,7 @@
       <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr"/>
       <c r="AD175" t="n">
-        <v>8832.459999999999</v>
+        <v>10868.92</v>
       </c>
     </row>
     <row r="176">
@@ -16480,7 +16480,7 @@
         <v>79951.16</v>
       </c>
       <c r="S176" t="n">
-        <v>67124.59</v>
+        <v>75680.95</v>
       </c>
       <c r="T176" t="inlineStr"/>
       <c r="U176" t="inlineStr"/>
@@ -16499,7 +16499,7 @@
       <c r="AB176" t="inlineStr"/>
       <c r="AC176" t="inlineStr"/>
       <c r="AD176" t="n">
-        <v>67124.59</v>
+        <v>75680.95</v>
       </c>
     </row>
     <row r="177">
@@ -16574,7 +16574,7 @@
         <v>68767.81</v>
       </c>
       <c r="S177" t="n">
-        <v>54550.94</v>
+        <v>65605.03999999999</v>
       </c>
       <c r="T177" t="inlineStr"/>
       <c r="U177" t="inlineStr"/>
@@ -16593,7 +16593,7 @@
       <c r="AB177" t="inlineStr"/>
       <c r="AC177" t="inlineStr"/>
       <c r="AD177" t="n">
-        <v>54550.94</v>
+        <v>65605.03999999999</v>
       </c>
     </row>
     <row r="178">
@@ -16668,7 +16668,7 @@
         <v>31263.08</v>
       </c>
       <c r="S178" t="n">
-        <v>25486.76</v>
+        <v>31263.08</v>
       </c>
       <c r="T178" t="inlineStr"/>
       <c r="U178" t="inlineStr"/>
@@ -16687,7 +16687,7 @@
       <c r="AB178" t="inlineStr"/>
       <c r="AC178" t="inlineStr"/>
       <c r="AD178" t="n">
-        <v>25486.76</v>
+        <v>31263.08</v>
       </c>
     </row>
     <row r="179">
@@ -16762,7 +16762,7 @@
         <v>8235.469999999999</v>
       </c>
       <c r="S179" t="n">
-        <v>7364.56</v>
+        <v>8235.469999999999</v>
       </c>
       <c r="T179" t="inlineStr"/>
       <c r="U179" t="inlineStr"/>
@@ -16781,7 +16781,7 @@
       <c r="AB179" t="inlineStr"/>
       <c r="AC179" t="inlineStr"/>
       <c r="AD179" t="n">
-        <v>7364.56</v>
+        <v>8235.469999999999</v>
       </c>
     </row>
     <row r="180">
@@ -17138,7 +17138,7 @@
         <v>747637.24</v>
       </c>
       <c r="S183" t="n">
-        <v>501375.46</v>
+        <v>616245.1800000001</v>
       </c>
       <c r="T183" t="inlineStr"/>
       <c r="U183" t="inlineStr"/>
@@ -17157,7 +17157,7 @@
       <c r="AB183" t="inlineStr"/>
       <c r="AC183" t="inlineStr"/>
       <c r="AD183" t="n">
-        <v>501375.46</v>
+        <v>616245.1800000001</v>
       </c>
     </row>
     <row r="184">
@@ -17232,7 +17232,7 @@
         <v>423374.5</v>
       </c>
       <c r="S184" t="n">
-        <v>310420.64</v>
+        <v>376803.3</v>
       </c>
       <c r="T184" t="inlineStr"/>
       <c r="U184" t="inlineStr"/>
@@ -17251,7 +17251,7 @@
       <c r="AB184" t="inlineStr"/>
       <c r="AC184" t="inlineStr"/>
       <c r="AD184" t="n">
-        <v>310420.64</v>
+        <v>376803.3</v>
       </c>
     </row>
     <row r="185">
@@ -17326,7 +17326,7 @@
         <v>1687653.74</v>
       </c>
       <c r="S185" t="n">
-        <v>1242215.01</v>
+        <v>1446217.81</v>
       </c>
       <c r="T185" t="inlineStr"/>
       <c r="U185" t="inlineStr"/>
@@ -17345,7 +17345,7 @@
       <c r="AB185" t="inlineStr"/>
       <c r="AC185" t="inlineStr"/>
       <c r="AD185" t="n">
-        <v>1242215.01</v>
+        <v>1446217.81</v>
       </c>
     </row>
     <row r="186">
@@ -17420,7 +17420,7 @@
         <v>1559469.71</v>
       </c>
       <c r="S186" t="n">
-        <v>1043395.36</v>
+        <v>1285107.36</v>
       </c>
       <c r="T186" t="inlineStr"/>
       <c r="U186" t="inlineStr"/>
@@ -17439,7 +17439,7 @@
       <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr"/>
       <c r="AD186" t="n">
-        <v>1043395.36</v>
+        <v>1285107.36</v>
       </c>
     </row>
     <row r="187">
@@ -17514,7 +17514,7 @@
         <v>1166871.46</v>
       </c>
       <c r="S187" t="n">
-        <v>805370.73</v>
+        <v>988621.6899999999</v>
       </c>
       <c r="T187" t="inlineStr"/>
       <c r="U187" t="inlineStr"/>
@@ -17533,7 +17533,7 @@
       <c r="AB187" t="inlineStr"/>
       <c r="AC187" t="inlineStr"/>
       <c r="AD187" t="n">
-        <v>805370.73</v>
+        <v>988621.6899999999</v>
       </c>
     </row>
     <row r="188">
@@ -17608,7 +17608,7 @@
         <v>303696.1</v>
       </c>
       <c r="S188" t="n">
-        <v>237974.88</v>
+        <v>270289.53</v>
       </c>
       <c r="T188" t="inlineStr"/>
       <c r="U188" t="inlineStr"/>
@@ -17627,7 +17627,7 @@
       <c r="AB188" t="inlineStr"/>
       <c r="AC188" t="inlineStr"/>
       <c r="AD188" t="n">
-        <v>237974.88</v>
+        <v>270289.53</v>
       </c>
     </row>
     <row r="189">
@@ -18450,7 +18450,7 @@
         <v>2301.47</v>
       </c>
       <c r="S197" t="n">
-        <v>1694.47</v>
+        <v>2301.47</v>
       </c>
       <c r="T197" t="inlineStr"/>
       <c r="U197" t="inlineStr"/>
@@ -18469,7 +18469,7 @@
       <c r="AB197" t="inlineStr"/>
       <c r="AC197" t="inlineStr"/>
       <c r="AD197" t="n">
-        <v>1694.47</v>
+        <v>2301.47</v>
       </c>
     </row>
     <row r="198">
@@ -18544,7 +18544,7 @@
         <v>90339.83</v>
       </c>
       <c r="S198" t="n">
-        <v>61230.69</v>
+        <v>80402.44</v>
       </c>
       <c r="T198" t="inlineStr"/>
       <c r="U198" t="inlineStr"/>
@@ -18563,7 +18563,7 @@
       <c r="AB198" t="inlineStr"/>
       <c r="AC198" t="inlineStr"/>
       <c r="AD198" t="n">
-        <v>61230.69</v>
+        <v>80402.44</v>
       </c>
     </row>
     <row r="199">
@@ -18732,7 +18732,7 @@
         <v>5773824.52</v>
       </c>
       <c r="S200" t="n">
-        <v>3834026.07</v>
+        <v>5704538.62</v>
       </c>
       <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
@@ -18751,7 +18751,7 @@
       <c r="AB200" t="inlineStr"/>
       <c r="AC200" t="inlineStr"/>
       <c r="AD200" t="n">
-        <v>3834026.07</v>
+        <v>5704538.62</v>
       </c>
     </row>
     <row r="201">
@@ -20406,7 +20406,7 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>171017.71</v>
+        <v>211991.51</v>
       </c>
       <c r="R218" t="n">
         <v>171017.71</v>
@@ -20425,7 +20425,7 @@
       </c>
       <c r="Y218" t="inlineStr"/>
       <c r="Z218" t="n">
-        <v>171017.71</v>
+        <v>211991.51</v>
       </c>
       <c r="AA218" t="inlineStr"/>
       <c r="AB218" t="inlineStr"/>
@@ -20500,7 +20500,7 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>4578.33</v>
+        <v>4578.32</v>
       </c>
       <c r="R219" t="n">
         <v>4578.32</v>
@@ -20519,7 +20519,7 @@
       </c>
       <c r="Y219" t="inlineStr"/>
       <c r="Z219" t="n">
-        <v>4578.33</v>
+        <v>4578.32</v>
       </c>
       <c r="AA219" t="inlineStr"/>
       <c r="AB219" t="inlineStr"/>
@@ -20694,7 +20694,7 @@
         <v>868789.0600000001</v>
       </c>
       <c r="S221" t="n">
-        <v>256174.8</v>
+        <v>858363.59</v>
       </c>
       <c r="T221" t="inlineStr"/>
       <c r="U221" t="inlineStr"/>
@@ -20713,7 +20713,7 @@
       <c r="AB221" t="inlineStr"/>
       <c r="AC221" t="inlineStr"/>
       <c r="AD221" t="n">
-        <v>256174.8</v>
+        <v>858363.59</v>
       </c>
     </row>
     <row r="222">
@@ -36398,7 +36398,7 @@
         <v>97998.17999999999</v>
       </c>
       <c r="S395" t="n">
-        <v>55009.64</v>
+        <v>82514.46000000001</v>
       </c>
       <c r="T395" t="inlineStr"/>
       <c r="U395" t="inlineStr"/>
@@ -36417,7 +36417,7 @@
       <c r="AB395" t="inlineStr"/>
       <c r="AC395" t="inlineStr"/>
       <c r="AD395" t="n">
-        <v>55009.64</v>
+        <v>82514.46000000001</v>
       </c>
     </row>
     <row r="396">
@@ -36766,7 +36766,7 @@
         <v>4987.97</v>
       </c>
       <c r="S399" t="n">
-        <v>3166.97</v>
+        <v>4987.97</v>
       </c>
       <c r="T399" t="inlineStr"/>
       <c r="U399" t="inlineStr"/>
@@ -36785,7 +36785,7 @@
       <c r="AB399" t="inlineStr"/>
       <c r="AC399" t="inlineStr"/>
       <c r="AD399" t="n">
-        <v>3166.97</v>
+        <v>4987.97</v>
       </c>
     </row>
     <row r="400">
@@ -36860,7 +36860,7 @@
         <v>187522.12</v>
       </c>
       <c r="S400" t="n">
-        <v>109037.71</v>
+        <v>166894.69</v>
       </c>
       <c r="T400" t="inlineStr"/>
       <c r="U400" t="inlineStr"/>
@@ -36879,7 +36879,7 @@
       <c r="AB400" t="inlineStr"/>
       <c r="AC400" t="inlineStr"/>
       <c r="AD400" t="n">
-        <v>109037.71</v>
+        <v>166894.69</v>
       </c>
     </row>
     <row r="401">
@@ -36954,7 +36954,7 @@
         <v>38157.52</v>
       </c>
       <c r="S401" t="n">
-        <v>33558.03</v>
+        <v>34514.98</v>
       </c>
       <c r="T401" t="inlineStr"/>
       <c r="U401" t="inlineStr"/>
@@ -36973,7 +36973,7 @@
       <c r="AB401" t="inlineStr"/>
       <c r="AC401" t="inlineStr"/>
       <c r="AD401" t="n">
-        <v>33558.03</v>
+        <v>34514.98</v>
       </c>
     </row>
     <row r="402">
@@ -37048,7 +37048,7 @@
         <v>21023.01</v>
       </c>
       <c r="S402" t="n">
-        <v>18620.27</v>
+        <v>18811.66</v>
       </c>
       <c r="T402" t="inlineStr"/>
       <c r="U402" t="inlineStr"/>
@@ -37067,7 +37067,7 @@
       <c r="AB402" t="inlineStr"/>
       <c r="AC402" t="inlineStr"/>
       <c r="AD402" t="n">
-        <v>18620.27</v>
+        <v>18811.66</v>
       </c>
     </row>
     <row r="403">
@@ -37142,7 +37142,7 @@
         <v>85783.92999999999</v>
       </c>
       <c r="S403" t="n">
-        <v>32074.07</v>
+        <v>33987.97</v>
       </c>
       <c r="T403" t="inlineStr"/>
       <c r="U403" t="inlineStr"/>
@@ -37161,7 +37161,7 @@
       <c r="AB403" t="inlineStr"/>
       <c r="AC403" t="inlineStr"/>
       <c r="AD403" t="n">
-        <v>32074.07</v>
+        <v>33987.97</v>
       </c>
     </row>
     <row r="404">
@@ -37236,7 +37236,7 @@
         <v>84678.62</v>
       </c>
       <c r="S404" t="n">
-        <v>49139.97</v>
+        <v>50862.48</v>
       </c>
       <c r="T404" t="inlineStr"/>
       <c r="U404" t="inlineStr"/>
@@ -37255,7 +37255,7 @@
       <c r="AB404" t="inlineStr"/>
       <c r="AC404" t="inlineStr"/>
       <c r="AD404" t="n">
-        <v>49139.97</v>
+        <v>50862.48</v>
       </c>
     </row>
     <row r="405">
@@ -37330,7 +37330,7 @@
         <v>61443.59</v>
       </c>
       <c r="S405" t="n">
-        <v>54499.27</v>
+        <v>55456.22</v>
       </c>
       <c r="T405" t="inlineStr"/>
       <c r="U405" t="inlineStr"/>
@@ -37349,7 +37349,7 @@
       <c r="AB405" t="inlineStr"/>
       <c r="AC405" t="inlineStr"/>
       <c r="AD405" t="n">
-        <v>54499.27</v>
+        <v>55456.22</v>
       </c>
     </row>
     <row r="406">
@@ -37424,7 +37424,7 @@
         <v>14291.86</v>
       </c>
       <c r="S406" t="n">
-        <v>12597.62</v>
+        <v>12980.4</v>
       </c>
       <c r="T406" t="inlineStr"/>
       <c r="U406" t="inlineStr"/>
@@ -37443,7 +37443,7 @@
       <c r="AB406" t="inlineStr"/>
       <c r="AC406" t="inlineStr"/>
       <c r="AD406" t="n">
-        <v>12597.62</v>
+        <v>12980.4</v>
       </c>
     </row>
     <row r="407">
@@ -37518,7 +37518,7 @@
         <v>3570.73</v>
       </c>
       <c r="S407" t="n">
-        <v>3131.65</v>
+        <v>3240.1</v>
       </c>
       <c r="T407" t="inlineStr"/>
       <c r="U407" t="inlineStr"/>
@@ -37537,7 +37537,7 @@
       <c r="AB407" t="inlineStr"/>
       <c r="AC407" t="inlineStr"/>
       <c r="AD407" t="n">
-        <v>3131.65</v>
+        <v>3240.1</v>
       </c>
     </row>
     <row r="408">
@@ -37606,7 +37606,7 @@
         </is>
       </c>
       <c r="Q408" t="n">
-        <v>73360.92</v>
+        <v>81568.64999999999</v>
       </c>
       <c r="R408" t="n">
         <v>53283.15</v>
@@ -37621,7 +37621,7 @@
       <c r="X408" t="inlineStr"/>
       <c r="Y408" t="inlineStr"/>
       <c r="Z408" t="n">
-        <v>73360.92</v>
+        <v>81568.64999999999</v>
       </c>
       <c r="AA408" t="inlineStr"/>
       <c r="AB408" t="inlineStr"/>
@@ -37696,7 +37696,7 @@
         </is>
       </c>
       <c r="Q409" t="n">
-        <v>2027.65</v>
+        <v>2027.64</v>
       </c>
       <c r="R409" t="n">
         <v>2027.64</v>
@@ -37711,7 +37711,7 @@
       <c r="X409" t="inlineStr"/>
       <c r="Y409" t="inlineStr"/>
       <c r="Z409" t="n">
-        <v>2027.65</v>
+        <v>2027.64</v>
       </c>
       <c r="AA409" t="inlineStr"/>
       <c r="AB409" t="inlineStr"/>
@@ -38059,7 +38059,7 @@
         <v>12892.12</v>
       </c>
       <c r="R413" t="n">
-        <v>10092.12</v>
+        <v>10857.68</v>
       </c>
       <c r="S413" t="n">
         <v>7286.79</v>
@@ -38153,7 +38153,7 @@
         <v>34485.5</v>
       </c>
       <c r="R414" t="n">
-        <v>32285.5</v>
+        <v>32789.49</v>
       </c>
       <c r="S414" t="n">
         <v>24372.04</v>
@@ -38247,7 +38247,7 @@
         <v>89169.53</v>
       </c>
       <c r="R415" t="n">
-        <v>82969.53</v>
+        <v>85680.89</v>
       </c>
       <c r="S415" t="n">
         <v>60926.65</v>
@@ -38432,7 +38432,7 @@
         </is>
       </c>
       <c r="Q417" t="n">
-        <v>274617.42</v>
+        <v>223692.42</v>
       </c>
       <c r="R417" t="n">
         <v>13783.27</v>
@@ -38451,7 +38451,7 @@
       </c>
       <c r="Y417" t="inlineStr"/>
       <c r="Z417" t="n">
-        <v>274617.42</v>
+        <v>223692.42</v>
       </c>
       <c r="AA417" t="inlineStr"/>
       <c r="AB417" t="inlineStr"/>
@@ -38526,7 +38526,7 @@
         </is>
       </c>
       <c r="Q418" t="n">
-        <v>15417806.27</v>
+        <v>12558731.27</v>
       </c>
       <c r="R418" t="n">
         <v>1232944.69</v>
@@ -38545,7 +38545,7 @@
       </c>
       <c r="Y418" t="inlineStr"/>
       <c r="Z418" t="n">
-        <v>15417806.27</v>
+        <v>12558731.27</v>
       </c>
       <c r="AA418" t="inlineStr"/>
       <c r="AB418" t="inlineStr"/>
@@ -39994,7 +39994,7 @@
         </is>
       </c>
       <c r="Q434" t="n">
-        <v>1822.18</v>
+        <v>2619.57</v>
       </c>
       <c r="R434" t="n">
         <v>1821.18</v>
@@ -40013,7 +40013,7 @@
       </c>
       <c r="Y434" t="inlineStr"/>
       <c r="Z434" t="n">
-        <v>1822.18</v>
+        <v>2619.57</v>
       </c>
       <c r="AA434" t="inlineStr"/>
       <c r="AB434" t="inlineStr"/>
@@ -40370,7 +40370,7 @@
         </is>
       </c>
       <c r="Q438" t="n">
-        <v>98218.74000000001</v>
+        <v>147328.11</v>
       </c>
       <c r="R438" t="n">
         <v>98218.74000000001</v>
@@ -40389,7 +40389,7 @@
       </c>
       <c r="Y438" t="inlineStr"/>
       <c r="Z438" t="n">
-        <v>98218.74000000001</v>
+        <v>147328.11</v>
       </c>
       <c r="AA438" t="inlineStr"/>
       <c r="AB438" t="inlineStr"/>
@@ -40464,7 +40464,7 @@
         </is>
       </c>
       <c r="Q439" t="n">
-        <v>32739.58</v>
+        <v>49109.37</v>
       </c>
       <c r="R439" t="n">
         <v>32739.58</v>
@@ -40483,7 +40483,7 @@
       </c>
       <c r="Y439" t="inlineStr"/>
       <c r="Z439" t="n">
-        <v>32739.58</v>
+        <v>49109.37</v>
       </c>
       <c r="AA439" t="inlineStr"/>
       <c r="AB439" t="inlineStr"/>
@@ -41028,7 +41028,7 @@
         </is>
       </c>
       <c r="Q445" t="n">
-        <v>5415.44</v>
+        <v>7809.61</v>
       </c>
       <c r="R445" t="n">
         <v>5414.44</v>
@@ -41047,7 +41047,7 @@
       </c>
       <c r="Y445" t="inlineStr"/>
       <c r="Z445" t="n">
-        <v>5415.44</v>
+        <v>7809.61</v>
       </c>
       <c r="AA445" t="inlineStr"/>
       <c r="AB445" t="inlineStr"/>
@@ -41122,7 +41122,7 @@
         </is>
       </c>
       <c r="Q446" t="n">
-        <v>3643.36</v>
+        <v>5239.14</v>
       </c>
       <c r="R446" t="n">
         <v>3642.36</v>
@@ -41141,7 +41141,7 @@
       </c>
       <c r="Y446" t="inlineStr"/>
       <c r="Z446" t="n">
-        <v>3643.36</v>
+        <v>5239.14</v>
       </c>
       <c r="AA446" t="inlineStr"/>
       <c r="AB446" t="inlineStr"/>
@@ -41216,7 +41216,7 @@
         </is>
       </c>
       <c r="Q447" t="n">
-        <v>65479.16</v>
+        <v>98218.74000000001</v>
       </c>
       <c r="R447" t="n">
         <v>65479.16</v>
@@ -41235,7 +41235,7 @@
       </c>
       <c r="Y447" t="inlineStr"/>
       <c r="Z447" t="n">
-        <v>65479.16</v>
+        <v>98218.74000000001</v>
       </c>
       <c r="AA447" t="inlineStr"/>
       <c r="AB447" t="inlineStr"/>
@@ -41490,7 +41490,7 @@
         </is>
       </c>
       <c r="Q450" t="n">
-        <v>5408324.83</v>
+        <v>2424959.83</v>
       </c>
       <c r="R450" t="n">
         <v>0</v>
@@ -41509,7 +41509,7 @@
       </c>
       <c r="Y450" t="inlineStr"/>
       <c r="Z450" t="n">
-        <v>5408324.83</v>
+        <v>2424959.83</v>
       </c>
       <c r="AA450" t="inlineStr"/>
       <c r="AB450" t="inlineStr"/>
@@ -42601,7 +42601,7 @@
         <v>4470</v>
       </c>
       <c r="R462" t="n">
-        <v>0</v>
+        <v>4470</v>
       </c>
       <c r="S462" t="n">
         <v>0</v>
@@ -43614,7 +43614,7 @@
         <v>896.3</v>
       </c>
       <c r="S473" t="n">
-        <v>0</v>
+        <v>885.55</v>
       </c>
       <c r="T473" t="inlineStr"/>
       <c r="U473" t="inlineStr"/>
@@ -43629,7 +43629,7 @@
       <c r="AB473" t="inlineStr"/>
       <c r="AC473" t="inlineStr"/>
       <c r="AD473" t="n">
-        <v>0</v>
+        <v>885.55</v>
       </c>
     </row>
     <row r="474">
@@ -43701,10 +43701,10 @@
         <v>3531.04</v>
       </c>
       <c r="R474" t="n">
-        <v>1531.04</v>
+        <v>1913.82</v>
       </c>
       <c r="S474" t="n">
-        <v>1457.55</v>
+        <v>1821.96</v>
       </c>
       <c r="T474" t="inlineStr"/>
       <c r="U474" t="inlineStr"/>
@@ -43723,7 +43723,7 @@
       <c r="AB474" t="inlineStr"/>
       <c r="AC474" t="inlineStr"/>
       <c r="AD474" t="n">
-        <v>1457.55</v>
+        <v>1821.96</v>
       </c>
     </row>
     <row r="475">
@@ -46152,13 +46152,13 @@
         </is>
       </c>
       <c r="Q501" t="n">
-        <v>3744.37</v>
+        <v>5341.15</v>
       </c>
       <c r="R501" t="n">
-        <v>3744.36</v>
+        <v>5341.14</v>
       </c>
       <c r="S501" t="n">
-        <v>3395.18</v>
+        <v>4915.32</v>
       </c>
       <c r="T501" t="inlineStr"/>
       <c r="U501" t="inlineStr"/>
@@ -46171,13 +46171,13 @@
       </c>
       <c r="Y501" t="inlineStr"/>
       <c r="Z501" t="n">
-        <v>3744.37</v>
+        <v>5341.15</v>
       </c>
       <c r="AA501" t="inlineStr"/>
       <c r="AB501" t="inlineStr"/>
       <c r="AC501" t="inlineStr"/>
       <c r="AD501" t="n">
-        <v>3395.18</v>
+        <v>4915.32</v>
       </c>
     </row>
     <row r="502">
@@ -46718,7 +46718,7 @@
         <v>510.37</v>
       </c>
       <c r="S507" t="n">
-        <v>0</v>
+        <v>510.37</v>
       </c>
       <c r="T507" t="inlineStr"/>
       <c r="U507" t="inlineStr"/>
@@ -46737,7 +46737,7 @@
       <c r="AB507" t="inlineStr"/>
       <c r="AC507" t="inlineStr"/>
       <c r="AD507" t="n">
-        <v>0</v>
+        <v>510.37</v>
       </c>
     </row>
     <row r="508">
@@ -47668,6 +47668,1220 @@
         <v>0</v>
       </c>
     </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B518" t="n">
+        <v>9473171</v>
+      </c>
+      <c r="C518" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>226</v>
+      </c>
+      <c r="F518" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I518" t="n">
+        <v>37</v>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K518" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M518" t="n">
+        <v>80</v>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q518" t="n">
+        <v>1498.22</v>
+      </c>
+      <c r="R518" t="n">
+        <v>0</v>
+      </c>
+      <c r="S518" t="n">
+        <v>0</v>
+      </c>
+      <c r="T518" t="inlineStr"/>
+      <c r="U518" t="inlineStr"/>
+      <c r="V518" t="n">
+        <v>0</v>
+      </c>
+      <c r="W518" t="inlineStr"/>
+      <c r="X518" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y518" t="inlineStr"/>
+      <c r="Z518" t="n">
+        <v>1498.22</v>
+      </c>
+      <c r="AA518" t="inlineStr"/>
+      <c r="AB518" t="inlineStr"/>
+      <c r="AC518" t="inlineStr"/>
+      <c r="AD518" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B519" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C519" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>296</v>
+      </c>
+      <c r="F519" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I519" t="n">
+        <v>51</v>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K519" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M519" t="n">
+        <v>80</v>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q519" t="n">
+        <v>2245957.2</v>
+      </c>
+      <c r="R519" t="n">
+        <v>0</v>
+      </c>
+      <c r="S519" t="n">
+        <v>0</v>
+      </c>
+      <c r="T519" t="inlineStr"/>
+      <c r="U519" t="inlineStr"/>
+      <c r="V519" t="n">
+        <v>0</v>
+      </c>
+      <c r="W519" t="inlineStr"/>
+      <c r="X519" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y519" t="inlineStr"/>
+      <c r="Z519" t="n">
+        <v>2245957.2</v>
+      </c>
+      <c r="AA519" t="inlineStr"/>
+      <c r="AB519" t="inlineStr"/>
+      <c r="AC519" t="inlineStr"/>
+      <c r="AD519" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B520" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C520" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>297</v>
+      </c>
+      <c r="F520" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I520" t="n">
+        <v>93</v>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K520" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M520" t="n">
+        <v>80</v>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q520" t="n">
+        <v>80000</v>
+      </c>
+      <c r="R520" t="n">
+        <v>0</v>
+      </c>
+      <c r="S520" t="n">
+        <v>0</v>
+      </c>
+      <c r="T520" t="inlineStr"/>
+      <c r="U520" t="inlineStr"/>
+      <c r="V520" t="n">
+        <v>0</v>
+      </c>
+      <c r="W520" t="inlineStr"/>
+      <c r="X520" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y520" t="inlineStr"/>
+      <c r="Z520" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AA520" t="inlineStr"/>
+      <c r="AB520" t="inlineStr"/>
+      <c r="AC520" t="inlineStr"/>
+      <c r="AD520" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B521" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C521" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>298</v>
+      </c>
+      <c r="F521" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I521" t="n">
+        <v>51</v>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K521" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M521" t="n">
+        <v>80</v>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q521" t="n">
+        <v>417689.6</v>
+      </c>
+      <c r="R521" t="n">
+        <v>0</v>
+      </c>
+      <c r="S521" t="n">
+        <v>0</v>
+      </c>
+      <c r="T521" t="inlineStr"/>
+      <c r="U521" t="inlineStr"/>
+      <c r="V521" t="n">
+        <v>0</v>
+      </c>
+      <c r="W521" t="inlineStr"/>
+      <c r="X521" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y521" t="inlineStr"/>
+      <c r="Z521" t="n">
+        <v>417689.6</v>
+      </c>
+      <c r="AA521" t="inlineStr"/>
+      <c r="AB521" t="inlineStr"/>
+      <c r="AC521" t="inlineStr"/>
+      <c r="AD521" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B522" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C522" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>299</v>
+      </c>
+      <c r="F522" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I522" t="n">
+        <v>51</v>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K522" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M522" t="n">
+        <v>80</v>
+      </c>
+      <c r="N522" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q522" t="n">
+        <v>189718.2</v>
+      </c>
+      <c r="R522" t="n">
+        <v>0</v>
+      </c>
+      <c r="S522" t="n">
+        <v>0</v>
+      </c>
+      <c r="T522" t="inlineStr"/>
+      <c r="U522" t="inlineStr"/>
+      <c r="V522" t="n">
+        <v>0</v>
+      </c>
+      <c r="W522" t="inlineStr"/>
+      <c r="X522" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y522" t="inlineStr"/>
+      <c r="Z522" t="n">
+        <v>189718.2</v>
+      </c>
+      <c r="AA522" t="inlineStr"/>
+      <c r="AB522" t="inlineStr"/>
+      <c r="AC522" t="inlineStr"/>
+      <c r="AD522" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B523" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C523" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>300</v>
+      </c>
+      <c r="F523" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I523" t="n">
+        <v>93</v>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K523" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M523" t="n">
+        <v>80</v>
+      </c>
+      <c r="N523" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q523" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R523" t="n">
+        <v>0</v>
+      </c>
+      <c r="S523" t="n">
+        <v>0</v>
+      </c>
+      <c r="T523" t="inlineStr"/>
+      <c r="U523" t="inlineStr"/>
+      <c r="V523" t="n">
+        <v>0</v>
+      </c>
+      <c r="W523" t="inlineStr"/>
+      <c r="X523" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y523" t="inlineStr"/>
+      <c r="Z523" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AA523" t="inlineStr"/>
+      <c r="AB523" t="inlineStr"/>
+      <c r="AC523" t="inlineStr"/>
+      <c r="AD523" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B524" t="n">
+        <v>9480259</v>
+      </c>
+      <c r="C524" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>228</v>
+      </c>
+      <c r="F524" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I524" t="n">
+        <v>37</v>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K524" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M524" t="n">
+        <v>80</v>
+      </c>
+      <c r="N524" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q524" t="n">
+        <v>1984.05</v>
+      </c>
+      <c r="R524" t="n">
+        <v>0</v>
+      </c>
+      <c r="S524" t="n">
+        <v>0</v>
+      </c>
+      <c r="T524" t="inlineStr"/>
+      <c r="U524" t="inlineStr"/>
+      <c r="V524" t="inlineStr"/>
+      <c r="W524" t="inlineStr"/>
+      <c r="X524" t="inlineStr"/>
+      <c r="Y524" t="inlineStr"/>
+      <c r="Z524" t="n">
+        <v>1984.05</v>
+      </c>
+      <c r="AA524" t="inlineStr"/>
+      <c r="AB524" t="inlineStr"/>
+      <c r="AC524" t="inlineStr"/>
+      <c r="AD524" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B525" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C525" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>302</v>
+      </c>
+      <c r="F525" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I525" t="n">
+        <v>51</v>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K525" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M525" t="n">
+        <v>80</v>
+      </c>
+      <c r="N525" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q525" t="n">
+        <v>2394528</v>
+      </c>
+      <c r="R525" t="n">
+        <v>0</v>
+      </c>
+      <c r="S525" t="n">
+        <v>0</v>
+      </c>
+      <c r="T525" t="inlineStr"/>
+      <c r="U525" t="inlineStr"/>
+      <c r="V525" t="n">
+        <v>0</v>
+      </c>
+      <c r="W525" t="inlineStr"/>
+      <c r="X525" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y525" t="inlineStr"/>
+      <c r="Z525" t="n">
+        <v>2394528</v>
+      </c>
+      <c r="AA525" t="inlineStr"/>
+      <c r="AB525" t="inlineStr"/>
+      <c r="AC525" t="inlineStr"/>
+      <c r="AD525" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B526" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C526" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>303</v>
+      </c>
+      <c r="F526" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I526" t="n">
+        <v>93</v>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K526" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M526" t="n">
+        <v>80</v>
+      </c>
+      <c r="N526" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>02.351.006/0006-43</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>GRECA DISTRIBUIDORA DE ASFALTOS LTDA.</t>
+        </is>
+      </c>
+      <c r="Q526" t="n">
+        <v>150000</v>
+      </c>
+      <c r="R526" t="n">
+        <v>0</v>
+      </c>
+      <c r="S526" t="n">
+        <v>0</v>
+      </c>
+      <c r="T526" t="inlineStr"/>
+      <c r="U526" t="inlineStr"/>
+      <c r="V526" t="n">
+        <v>0</v>
+      </c>
+      <c r="W526" t="inlineStr"/>
+      <c r="X526" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y526" t="inlineStr"/>
+      <c r="Z526" t="n">
+        <v>150000</v>
+      </c>
+      <c r="AA526" t="inlineStr"/>
+      <c r="AB526" t="inlineStr"/>
+      <c r="AC526" t="inlineStr"/>
+      <c r="AD526" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B527" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C527" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>304</v>
+      </c>
+      <c r="F527" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I527" t="n">
+        <v>51</v>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K527" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M527" t="n">
+        <v>80</v>
+      </c>
+      <c r="N527" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q527" t="n">
+        <v>78316.8</v>
+      </c>
+      <c r="R527" t="n">
+        <v>0</v>
+      </c>
+      <c r="S527" t="n">
+        <v>0</v>
+      </c>
+      <c r="T527" t="inlineStr"/>
+      <c r="U527" t="inlineStr"/>
+      <c r="V527" t="n">
+        <v>0</v>
+      </c>
+      <c r="W527" t="inlineStr"/>
+      <c r="X527" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y527" t="inlineStr"/>
+      <c r="Z527" t="n">
+        <v>78316.8</v>
+      </c>
+      <c r="AA527" t="inlineStr"/>
+      <c r="AB527" t="inlineStr"/>
+      <c r="AC527" t="inlineStr"/>
+      <c r="AD527" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B528" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C528" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>305</v>
+      </c>
+      <c r="F528" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>2301762 000003/2026</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I528" t="n">
+        <v>51</v>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>OBRAS E INSTALACOES</t>
+        </is>
+      </c>
+      <c r="K528" t="n">
+        <v>5112</v>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>MATERIAL PARA OBRAS - BENS NAO PATRIMONIAVEIS</t>
+        </is>
+      </c>
+      <c r="M528" t="n">
+        <v>80</v>
+      </c>
+      <c r="N528" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q528" t="n">
+        <v>237147.75</v>
+      </c>
+      <c r="R528" t="n">
+        <v>0</v>
+      </c>
+      <c r="S528" t="n">
+        <v>0</v>
+      </c>
+      <c r="T528" t="inlineStr"/>
+      <c r="U528" t="inlineStr"/>
+      <c r="V528" t="n">
+        <v>0</v>
+      </c>
+      <c r="W528" t="inlineStr"/>
+      <c r="X528" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y528" t="inlineStr"/>
+      <c r="Z528" t="n">
+        <v>237147.75</v>
+      </c>
+      <c r="AA528" t="inlineStr"/>
+      <c r="AB528" t="inlineStr"/>
+      <c r="AC528" t="inlineStr"/>
+      <c r="AD528" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B529" t="n">
+        <v>9452379</v>
+      </c>
+      <c r="C529" t="n">
+        <v>2301</v>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>306</v>
+      </c>
+      <c r="F529" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I529" t="n">
+        <v>93</v>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="K529" t="n">
+        <v>9399</v>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>OUTRAS INDENIZACOES E RESTITUICOES</t>
+        </is>
+      </c>
+      <c r="M529" t="n">
+        <v>80</v>
+      </c>
+      <c r="N529" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>01.593.821/0010-32</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>CENTRO OESTE ASFALTOS S/A</t>
+        </is>
+      </c>
+      <c r="Q529" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R529" t="n">
+        <v>0</v>
+      </c>
+      <c r="S529" t="n">
+        <v>0</v>
+      </c>
+      <c r="T529" t="inlineStr"/>
+      <c r="U529" t="inlineStr"/>
+      <c r="V529" t="n">
+        <v>0</v>
+      </c>
+      <c r="W529" t="inlineStr"/>
+      <c r="X529" t="n">
+        <v>23767.08</v>
+      </c>
+      <c r="Y529" t="inlineStr"/>
+      <c r="Z529" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AA529" t="inlineStr"/>
+      <c r="AB529" t="inlineStr"/>
+      <c r="AC529" t="inlineStr"/>
+      <c r="AD529" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B530" t="n">
+        <v>9445684</v>
+      </c>
+      <c r="C530" t="n">
+        <v>4251</v>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>FUNDO ESTADUAL DE ASSISTENCIA SOCIAL</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>1591</v>
+      </c>
+      <c r="F530" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>1501561 000060/2025</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>DISPENSA DE LICITAÇÃO - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I530" t="n">
+        <v>37</v>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>LOCACAO DE MAO-DE-OBRA</t>
+        </is>
+      </c>
+      <c r="K530" t="n">
+        <v>3705</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>DESPESAS COM O PAGAMENTO DE ENCARGOS TRABALHISTAS A MGS</t>
+        </is>
+      </c>
+      <c r="M530" t="n">
+        <v>80</v>
+      </c>
+      <c r="N530" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>33.224.254/0001-42</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>MGS MINAS GERAIS ADMINISTRACAO E SERVICOS S/A</t>
+        </is>
+      </c>
+      <c r="Q530" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R530" t="n">
+        <v>0</v>
+      </c>
+      <c r="S530" t="n">
+        <v>0</v>
+      </c>
+      <c r="T530" t="inlineStr"/>
+      <c r="U530" t="inlineStr"/>
+      <c r="V530" t="inlineStr"/>
+      <c r="W530" t="inlineStr"/>
+      <c r="X530" t="inlineStr"/>
+      <c r="Y530" t="inlineStr"/>
+      <c r="Z530" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AA530" t="inlineStr"/>
+      <c r="AB530" t="inlineStr"/>
+      <c r="AC530" t="inlineStr"/>
+      <c r="AD530" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD530"/>
+  <dimension ref="A1:AD533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13950,7 +13950,7 @@
         <v>60353.76</v>
       </c>
       <c r="S149" t="n">
-        <v>51276.71</v>
+        <v>55191.63</v>
       </c>
       <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr"/>
@@ -13969,7 +13969,7 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr"/>
       <c r="AD149" t="n">
-        <v>51276.71</v>
+        <v>55191.63</v>
       </c>
     </row>
     <row r="150">
@@ -14044,7 +14044,7 @@
         <v>532088</v>
       </c>
       <c r="S150" t="n">
-        <v>381841.64</v>
+        <v>443139.67</v>
       </c>
       <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr"/>
@@ -14063,7 +14063,7 @@
       <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr"/>
       <c r="AD150" t="n">
-        <v>381841.64</v>
+        <v>443139.67</v>
       </c>
     </row>
     <row r="151">
@@ -14138,7 +14138,7 @@
         <v>1653787.16</v>
       </c>
       <c r="S151" t="n">
-        <v>1146612.36</v>
+        <v>1382564.38</v>
       </c>
       <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr"/>
@@ -14157,7 +14157,7 @@
       <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr"/>
       <c r="AD151" t="n">
-        <v>1146612.36</v>
+        <v>1382564.38</v>
       </c>
     </row>
     <row r="152">
@@ -14232,7 +14232,7 @@
         <v>103830.02</v>
       </c>
       <c r="S152" t="n">
-        <v>83732.94</v>
+        <v>96683.03</v>
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
@@ -14251,7 +14251,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr"/>
       <c r="AD152" t="n">
-        <v>83732.94</v>
+        <v>96683.03</v>
       </c>
     </row>
     <row r="153">
@@ -14326,7 +14326,7 @@
         <v>12100.13</v>
       </c>
       <c r="S153" t="n">
-        <v>9295.059999999999</v>
+        <v>11606.52</v>
       </c>
       <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr"/>
@@ -14345,7 +14345,7 @@
       <c r="AB153" t="inlineStr"/>
       <c r="AC153" t="inlineStr"/>
       <c r="AD153" t="n">
-        <v>9295.059999999999</v>
+        <v>11606.52</v>
       </c>
     </row>
     <row r="154">
@@ -14420,7 +14420,7 @@
         <v>351702.49</v>
       </c>
       <c r="S154" t="n">
-        <v>201799.44</v>
+        <v>253485.17</v>
       </c>
       <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr"/>
@@ -14439,7 +14439,7 @@
       <c r="AB154" t="inlineStr"/>
       <c r="AC154" t="inlineStr"/>
       <c r="AD154" t="n">
-        <v>201799.44</v>
+        <v>253485.17</v>
       </c>
     </row>
     <row r="155">
@@ -14605,10 +14605,10 @@
         <v>74230</v>
       </c>
       <c r="R156" t="n">
-        <v>36384.07</v>
+        <v>36872.47</v>
       </c>
       <c r="S156" t="n">
-        <v>37154.07</v>
+        <v>37642.47</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14627,7 +14627,7 @@
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>37154.07</v>
+        <v>37642.47</v>
       </c>
     </row>
     <row r="157">
@@ -17702,7 +17702,7 @@
         <v>42581.89</v>
       </c>
       <c r="S189" t="n">
-        <v>30164.95</v>
+        <v>41553.09</v>
       </c>
       <c r="T189" t="inlineStr"/>
       <c r="U189" t="inlineStr"/>
@@ -17721,7 +17721,7 @@
       <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr"/>
       <c r="AD189" t="n">
-        <v>30164.95</v>
+        <v>41553.09</v>
       </c>
     </row>
     <row r="190">
@@ -17793,10 +17793,10 @@
         <v>496800</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>138000</v>
       </c>
       <c r="S190" t="n">
-        <v>0</v>
+        <v>138000</v>
       </c>
       <c r="T190" t="inlineStr"/>
       <c r="U190" t="inlineStr"/>
@@ -17815,7 +17815,7 @@
       <c r="AB190" t="inlineStr"/>
       <c r="AC190" t="inlineStr"/>
       <c r="AD190" t="n">
-        <v>0</v>
+        <v>138000</v>
       </c>
     </row>
     <row r="191">
@@ -20409,10 +20409,10 @@
         <v>211991.51</v>
       </c>
       <c r="R218" t="n">
-        <v>171017.71</v>
+        <v>211991.51</v>
       </c>
       <c r="S218" t="n">
-        <v>171017.71</v>
+        <v>211991.51</v>
       </c>
       <c r="T218" t="inlineStr"/>
       <c r="U218" t="inlineStr"/>
@@ -20431,7 +20431,7 @@
       <c r="AB218" t="inlineStr"/>
       <c r="AC218" t="inlineStr"/>
       <c r="AD218" t="n">
-        <v>171017.71</v>
+        <v>211991.51</v>
       </c>
     </row>
     <row r="219">
@@ -20597,7 +20597,7 @@
         <v>7132375.41</v>
       </c>
       <c r="R220" t="n">
-        <v>259286.24</v>
+        <v>868789.0600000001</v>
       </c>
       <c r="S220" t="n">
         <v>256174.81</v>
@@ -22225,7 +22225,7 @@
         <v>6435668.8</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>1612436.99</v>
       </c>
       <c r="S238" t="n">
         <v>0</v>
@@ -22319,7 +22319,7 @@
         <v>230000</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>43235.45</v>
       </c>
       <c r="S239" t="n">
         <v>0</v>
@@ -37609,10 +37609,10 @@
         <v>81568.64999999999</v>
       </c>
       <c r="R408" t="n">
-        <v>53283.15</v>
+        <v>81568.64999999999</v>
       </c>
       <c r="S408" t="n">
-        <v>53283.15</v>
+        <v>81568.64999999999</v>
       </c>
       <c r="T408" t="inlineStr"/>
       <c r="U408" t="inlineStr"/>
@@ -37627,7 +37627,7 @@
       <c r="AB408" t="inlineStr"/>
       <c r="AC408" t="inlineStr"/>
       <c r="AD408" t="n">
-        <v>53283.15</v>
+        <v>81568.64999999999</v>
       </c>
     </row>
     <row r="409">
@@ -38062,7 +38062,7 @@
         <v>10857.68</v>
       </c>
       <c r="S413" t="n">
-        <v>7286.79</v>
+        <v>8015.6</v>
       </c>
       <c r="T413" t="inlineStr"/>
       <c r="U413" t="inlineStr"/>
@@ -38081,7 +38081,7 @@
       <c r="AB413" t="inlineStr"/>
       <c r="AC413" t="inlineStr"/>
       <c r="AD413" t="n">
-        <v>7286.79</v>
+        <v>8015.6</v>
       </c>
     </row>
     <row r="414">
@@ -38156,7 +38156,7 @@
         <v>32789.49</v>
       </c>
       <c r="S414" t="n">
-        <v>24372.04</v>
+        <v>24851.84</v>
       </c>
       <c r="T414" t="inlineStr"/>
       <c r="U414" t="inlineStr"/>
@@ -38175,7 +38175,7 @@
       <c r="AB414" t="inlineStr"/>
       <c r="AC414" t="inlineStr"/>
       <c r="AD414" t="n">
-        <v>24372.04</v>
+        <v>24851.84</v>
       </c>
     </row>
     <row r="415">
@@ -38250,7 +38250,7 @@
         <v>85680.89</v>
       </c>
       <c r="S415" t="n">
-        <v>60926.65</v>
+        <v>63507.86</v>
       </c>
       <c r="T415" t="inlineStr"/>
       <c r="U415" t="inlineStr"/>
@@ -38269,7 +38269,7 @@
       <c r="AB415" t="inlineStr"/>
       <c r="AC415" t="inlineStr"/>
       <c r="AD415" t="n">
-        <v>60926.65</v>
+        <v>63507.86</v>
       </c>
     </row>
     <row r="416">
@@ -38620,7 +38620,7 @@
         </is>
       </c>
       <c r="Q419" t="n">
-        <v>34988.64</v>
+        <v>46966.74</v>
       </c>
       <c r="R419" t="n">
         <v>34988.64</v>
@@ -38635,7 +38635,7 @@
       <c r="X419" t="inlineStr"/>
       <c r="Y419" t="inlineStr"/>
       <c r="Z419" t="n">
-        <v>34988.64</v>
+        <v>46966.74</v>
       </c>
       <c r="AA419" t="inlineStr"/>
       <c r="AB419" t="inlineStr"/>
@@ -38710,7 +38710,7 @@
         </is>
       </c>
       <c r="Q420" t="n">
-        <v>1688.7</v>
+        <v>2487.09</v>
       </c>
       <c r="R420" t="n">
         <v>1688.7</v>
@@ -38725,7 +38725,7 @@
       <c r="X420" t="inlineStr"/>
       <c r="Y420" t="inlineStr"/>
       <c r="Z420" t="n">
-        <v>1688.7</v>
+        <v>2487.09</v>
       </c>
       <c r="AA420" t="inlineStr"/>
       <c r="AB420" t="inlineStr"/>
@@ -38800,7 +38800,7 @@
         </is>
       </c>
       <c r="Q421" t="n">
-        <v>55541.8</v>
+        <v>83312.7</v>
       </c>
       <c r="R421" t="n">
         <v>55541.8</v>
@@ -38815,7 +38815,7 @@
       <c r="X421" t="inlineStr"/>
       <c r="Y421" t="inlineStr"/>
       <c r="Z421" t="n">
-        <v>55541.8</v>
+        <v>83312.7</v>
       </c>
       <c r="AA421" t="inlineStr"/>
       <c r="AB421" t="inlineStr"/>
@@ -38890,7 +38890,7 @@
         </is>
       </c>
       <c r="Q422" t="n">
-        <v>131856.3</v>
+        <v>190387.12</v>
       </c>
       <c r="R422" t="n">
         <v>131856.3</v>
@@ -38905,7 +38905,7 @@
       <c r="X422" t="inlineStr"/>
       <c r="Y422" t="inlineStr"/>
       <c r="Z422" t="n">
-        <v>131856.3</v>
+        <v>190387.12</v>
       </c>
       <c r="AA422" t="inlineStr"/>
       <c r="AB422" t="inlineStr"/>
@@ -39250,7 +39250,7 @@
         </is>
       </c>
       <c r="Q426" t="n">
-        <v>979.1799999999999</v>
+        <v>1541.63</v>
       </c>
       <c r="R426" t="n">
         <v>978.1799999999999</v>
@@ -39265,7 +39265,7 @@
       <c r="X426" t="inlineStr"/>
       <c r="Y426" t="inlineStr"/>
       <c r="Z426" t="n">
-        <v>979.1799999999999</v>
+        <v>1541.63</v>
       </c>
       <c r="AA426" t="inlineStr"/>
       <c r="AB426" t="inlineStr"/>
@@ -39340,7 +39340,7 @@
         </is>
       </c>
       <c r="Q427" t="n">
-        <v>6398.28</v>
+        <v>10063.48</v>
       </c>
       <c r="R427" t="n">
         <v>6398.28</v>
@@ -39355,7 +39355,7 @@
       <c r="X427" t="inlineStr"/>
       <c r="Y427" t="inlineStr"/>
       <c r="Z427" t="n">
-        <v>6398.28</v>
+        <v>10063.48</v>
       </c>
       <c r="AA427" t="inlineStr"/>
       <c r="AB427" t="inlineStr"/>
@@ -39433,7 +39433,7 @@
         <v>295000</v>
       </c>
       <c r="R428" t="n">
-        <v>45235.48</v>
+        <v>164415.59</v>
       </c>
       <c r="S428" t="n">
         <v>45235.48</v>
@@ -39715,7 +39715,7 @@
         <v>4999967.85</v>
       </c>
       <c r="R431" t="n">
-        <v>951012.53</v>
+        <v>3427611</v>
       </c>
       <c r="S431" t="n">
         <v>948621.53</v>
@@ -39997,7 +39997,7 @@
         <v>2619.57</v>
       </c>
       <c r="R434" t="n">
-        <v>1821.18</v>
+        <v>2619.57</v>
       </c>
       <c r="S434" t="n">
         <v>1733.76</v>
@@ -40373,7 +40373,7 @@
         <v>147328.11</v>
       </c>
       <c r="R438" t="n">
-        <v>98218.74000000001</v>
+        <v>147328.11</v>
       </c>
       <c r="S438" t="n">
         <v>81183.35000000001</v>
@@ -40467,7 +40467,7 @@
         <v>49109.37</v>
       </c>
       <c r="R439" t="n">
-        <v>32739.58</v>
+        <v>49109.37</v>
       </c>
       <c r="S439" t="n">
         <v>27566.72</v>
@@ -41031,7 +41031,7 @@
         <v>7809.61</v>
       </c>
       <c r="R445" t="n">
-        <v>5414.44</v>
+        <v>7235.44</v>
       </c>
       <c r="S445" t="n">
         <v>5154.55</v>
@@ -41125,7 +41125,7 @@
         <v>5239.14</v>
       </c>
       <c r="R446" t="n">
-        <v>3642.36</v>
+        <v>5239.14</v>
       </c>
       <c r="S446" t="n">
         <v>3467.53</v>
@@ -41219,7 +41219,7 @@
         <v>98218.74000000001</v>
       </c>
       <c r="R447" t="n">
-        <v>65479.16</v>
+        <v>98218.74000000001</v>
       </c>
       <c r="S447" t="n">
         <v>55133.46</v>
@@ -42961,7 +42961,7 @@
         <v>6076768.36</v>
       </c>
       <c r="R466" t="n">
-        <v>0</v>
+        <v>937347.08</v>
       </c>
       <c r="S466" t="n">
         <v>0</v>
@@ -43055,7 +43055,7 @@
         <v>1755987.2</v>
       </c>
       <c r="R467" t="n">
-        <v>0</v>
+        <v>147463.02</v>
       </c>
       <c r="S467" t="n">
         <v>0</v>
@@ -43243,7 +43243,7 @@
         <v>470000</v>
       </c>
       <c r="R469" t="n">
-        <v>0</v>
+        <v>55477.88</v>
       </c>
       <c r="S469" t="n">
         <v>0</v>
@@ -43521,10 +43521,10 @@
         <v>14725.68</v>
       </c>
       <c r="R472" t="n">
-        <v>0</v>
+        <v>14725.68</v>
       </c>
       <c r="S472" t="n">
-        <v>0</v>
+        <v>14548.97</v>
       </c>
       <c r="T472" t="inlineStr"/>
       <c r="U472" t="inlineStr"/>
@@ -43539,7 +43539,7 @@
       <c r="AB472" t="inlineStr"/>
       <c r="AC472" t="inlineStr"/>
       <c r="AD472" t="n">
-        <v>0</v>
+        <v>14548.97</v>
       </c>
     </row>
     <row r="473">
@@ -46252,7 +46252,7 @@
         <v>7200</v>
       </c>
       <c r="S502" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
       <c r="T502" t="inlineStr"/>
       <c r="U502" t="inlineStr"/>
@@ -46267,7 +46267,7 @@
       <c r="AB502" t="inlineStr"/>
       <c r="AC502" t="inlineStr"/>
       <c r="AD502" t="n">
-        <v>0</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="503">
@@ -47087,10 +47087,10 @@
         <v>18571.42</v>
       </c>
       <c r="R511" t="n">
-        <v>0</v>
+        <v>18571.42</v>
       </c>
       <c r="S511" t="n">
-        <v>0</v>
+        <v>18571.42</v>
       </c>
       <c r="T511" t="inlineStr"/>
       <c r="U511" t="inlineStr"/>
@@ -47105,7 +47105,7 @@
       <c r="AB511" t="inlineStr"/>
       <c r="AC511" t="inlineStr"/>
       <c r="AD511" t="n">
-        <v>0</v>
+        <v>18571.42</v>
       </c>
     </row>
     <row r="512">
@@ -47177,7 +47177,7 @@
         <v>1288904.58</v>
       </c>
       <c r="R512" t="n">
-        <v>0</v>
+        <v>162778.02</v>
       </c>
       <c r="S512" t="n">
         <v>0</v>
@@ -47271,7 +47271,7 @@
         <v>30000</v>
       </c>
       <c r="R513" t="n">
-        <v>0</v>
+        <v>1842.29</v>
       </c>
       <c r="S513" t="n">
         <v>0</v>
@@ -47737,10 +47737,10 @@
         <v>1498.22</v>
       </c>
       <c r="R518" t="n">
-        <v>0</v>
+        <v>1498.22</v>
       </c>
       <c r="S518" t="n">
-        <v>0</v>
+        <v>1498.22</v>
       </c>
       <c r="T518" t="inlineStr"/>
       <c r="U518" t="inlineStr"/>
@@ -47759,7 +47759,7 @@
       <c r="AB518" t="inlineStr"/>
       <c r="AC518" t="inlineStr"/>
       <c r="AD518" t="n">
-        <v>0</v>
+        <v>1498.22</v>
       </c>
     </row>
     <row r="519">
@@ -48301,10 +48301,10 @@
         <v>1984.05</v>
       </c>
       <c r="R524" t="n">
-        <v>0</v>
+        <v>1984.05</v>
       </c>
       <c r="S524" t="n">
-        <v>0</v>
+        <v>1984.05</v>
       </c>
       <c r="T524" t="inlineStr"/>
       <c r="U524" t="inlineStr"/>
@@ -48319,7 +48319,7 @@
       <c r="AB524" t="inlineStr"/>
       <c r="AC524" t="inlineStr"/>
       <c r="AD524" t="n">
-        <v>0</v>
+        <v>1984.05</v>
       </c>
     </row>
     <row r="525">
@@ -48861,7 +48861,7 @@
         <v>10000</v>
       </c>
       <c r="R530" t="n">
-        <v>0</v>
+        <v>2286.32</v>
       </c>
       <c r="S530" t="n">
         <v>0</v>
@@ -48882,6 +48882,280 @@
         <v>0</v>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B531" t="n">
+        <v>9480259</v>
+      </c>
+      <c r="C531" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>233</v>
+      </c>
+      <c r="F531" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>1221002 000024/2024</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECOS</t>
+        </is>
+      </c>
+      <c r="I531" t="n">
+        <v>39</v>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>OUTROS SERVICOS DE TERCEIROS - PESSOA JURIDICA</t>
+        </is>
+      </c>
+      <c r="K531" t="n">
+        <v>3917</v>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>LOCACAO DE VEICULOS</t>
+        </is>
+      </c>
+      <c r="M531" t="n">
+        <v>80</v>
+      </c>
+      <c r="N531" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>27.595.780/0001-16</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>CS BRASIL FROTAS S.A.</t>
+        </is>
+      </c>
+      <c r="Q531" t="n">
+        <v>24604.41</v>
+      </c>
+      <c r="R531" t="n">
+        <v>0</v>
+      </c>
+      <c r="S531" t="n">
+        <v>0</v>
+      </c>
+      <c r="T531" t="inlineStr"/>
+      <c r="U531" t="inlineStr"/>
+      <c r="V531" t="inlineStr"/>
+      <c r="W531" t="inlineStr"/>
+      <c r="X531" t="inlineStr"/>
+      <c r="Y531" t="inlineStr"/>
+      <c r="Z531" t="n">
+        <v>24604.41</v>
+      </c>
+      <c r="AA531" t="inlineStr"/>
+      <c r="AB531" t="inlineStr"/>
+      <c r="AC531" t="inlineStr"/>
+      <c r="AD531" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B532" t="n">
+        <v>9473171</v>
+      </c>
+      <c r="C532" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>SECRETARIA DE ESTADO DE DESENVOLVIMENTO ECONOMICO</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>234</v>
+      </c>
+      <c r="F532" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>1221002 000024/2024</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECOS</t>
+        </is>
+      </c>
+      <c r="I532" t="n">
+        <v>39</v>
+      </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>OUTROS SERVICOS DE TERCEIROS - PESSOA JURIDICA</t>
+        </is>
+      </c>
+      <c r="K532" t="n">
+        <v>3917</v>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>LOCACAO DE VEICULOS</t>
+        </is>
+      </c>
+      <c r="M532" t="n">
+        <v>80</v>
+      </c>
+      <c r="N532" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>27.595.780/0001-16</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>CS BRASIL FROTAS S.A.</t>
+        </is>
+      </c>
+      <c r="Q532" t="n">
+        <v>7304.7</v>
+      </c>
+      <c r="R532" t="n">
+        <v>0</v>
+      </c>
+      <c r="S532" t="n">
+        <v>0</v>
+      </c>
+      <c r="T532" t="inlineStr"/>
+      <c r="U532" t="inlineStr"/>
+      <c r="V532" t="n">
+        <v>0</v>
+      </c>
+      <c r="W532" t="inlineStr"/>
+      <c r="X532" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y532" t="inlineStr"/>
+      <c r="Z532" t="n">
+        <v>7304.7</v>
+      </c>
+      <c r="AA532" t="inlineStr"/>
+      <c r="AB532" t="inlineStr"/>
+      <c r="AC532" t="inlineStr"/>
+      <c r="AD532" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B533" t="n">
+        <v>9480440</v>
+      </c>
+      <c r="C533" t="n">
+        <v>2241</v>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>INSTITUTO MINEIRO DE GESTAO DAS AGUAS</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>318</v>
+      </c>
+      <c r="F533" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>0000000 000000/0000</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
+      <c r="I533" t="n">
+        <v>85</v>
+      </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>CONTRATO DE GESTAO</t>
+        </is>
+      </c>
+      <c r="K533" t="n">
+        <v>8501</v>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>CONTRATO DE GESTAO COM ORGANIZACAO SOCIAL - OS</t>
+        </is>
+      </c>
+      <c r="M533" t="n">
+        <v>80</v>
+      </c>
+      <c r="N533" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>70.945.209/0001-03</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>ASSOCIACAO PRO-CULTURA E PROMOCAO DAS ARTES</t>
+        </is>
+      </c>
+      <c r="Q533" t="n">
+        <v>8635921.619999999</v>
+      </c>
+      <c r="R533" t="n">
+        <v>8635921.619999999</v>
+      </c>
+      <c r="S533" t="n">
+        <v>8635921.619999999</v>
+      </c>
+      <c r="T533" t="inlineStr"/>
+      <c r="U533" t="inlineStr"/>
+      <c r="V533" t="inlineStr"/>
+      <c r="W533" t="inlineStr"/>
+      <c r="X533" t="inlineStr"/>
+      <c r="Y533" t="inlineStr"/>
+      <c r="Z533" t="n">
+        <v>8635921.619999999</v>
+      </c>
+      <c r="AA533" t="inlineStr"/>
+      <c r="AB533" t="inlineStr"/>
+      <c r="AC533" t="inlineStr"/>
+      <c r="AD533" t="n">
+        <v>8635921.619999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD533"/>
+  <dimension ref="A1:AD534"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13004,7 +13004,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>121765.44</v>
+        <v>121592.61</v>
       </c>
       <c r="R139" t="n">
         <v>121592.61</v>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="n">
-        <v>121765.44</v>
+        <v>121592.61</v>
       </c>
       <c r="AA139" t="inlineStr"/>
       <c r="AB139" t="inlineStr"/>
@@ -14602,13 +14602,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>74230</v>
+        <v>73900</v>
       </c>
       <c r="R156" t="n">
-        <v>36872.47</v>
+        <v>41633.27</v>
       </c>
       <c r="S156" t="n">
-        <v>37642.47</v>
+        <v>42733.27</v>
       </c>
       <c r="T156" t="inlineStr"/>
       <c r="U156" t="inlineStr"/>
@@ -14621,13 +14621,13 @@
       </c>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="n">
-        <v>74230</v>
+        <v>73900</v>
       </c>
       <c r="AA156" t="inlineStr"/>
       <c r="AB156" t="inlineStr"/>
       <c r="AC156" t="inlineStr"/>
       <c r="AD156" t="n">
-        <v>37642.47</v>
+        <v>42733.27</v>
       </c>
     </row>
     <row r="157">
@@ -16286,7 +16286,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>29781.19</v>
+        <v>35809.7</v>
       </c>
       <c r="R174" t="n">
         <v>29781.17</v>
@@ -16305,7 +16305,7 @@
       </c>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="n">
-        <v>29781.19</v>
+        <v>35809.7</v>
       </c>
       <c r="AA174" t="inlineStr"/>
       <c r="AB174" t="inlineStr"/>
@@ -16380,7 +16380,7 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>11194.73</v>
+        <v>15155.15</v>
       </c>
       <c r="R175" t="n">
         <v>11194.7</v>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="n">
-        <v>11194.73</v>
+        <v>15155.15</v>
       </c>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr"/>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>79951.17999999999</v>
+        <v>111539.89</v>
       </c>
       <c r="R176" t="n">
         <v>79951.16</v>
@@ -16493,7 +16493,7 @@
       </c>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="n">
-        <v>79951.17999999999</v>
+        <v>111539.89</v>
       </c>
       <c r="AA176" t="inlineStr"/>
       <c r="AB176" t="inlineStr"/>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>68767.83</v>
+        <v>86942.83</v>
       </c>
       <c r="R177" t="n">
         <v>68767.81</v>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="n">
-        <v>68767.83</v>
+        <v>86942.83</v>
       </c>
       <c r="AA177" t="inlineStr"/>
       <c r="AB177" t="inlineStr"/>
@@ -16662,7 +16662,7 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>31263.1</v>
+        <v>40443.6</v>
       </c>
       <c r="R178" t="n">
         <v>31263.08</v>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="n">
-        <v>31263.1</v>
+        <v>40443.6</v>
       </c>
       <c r="AA178" t="inlineStr"/>
       <c r="AB178" t="inlineStr"/>
@@ -16756,7 +16756,7 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>8235.5</v>
+        <v>9343.940000000001</v>
       </c>
       <c r="R179" t="n">
         <v>8235.469999999999</v>
@@ -16775,7 +16775,7 @@
       </c>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="n">
-        <v>8235.5</v>
+        <v>9343.940000000001</v>
       </c>
       <c r="AA179" t="inlineStr"/>
       <c r="AB179" t="inlineStr"/>
@@ -17132,7 +17132,7 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>747684.7</v>
+        <v>876934.05</v>
       </c>
       <c r="R183" t="n">
         <v>747637.24</v>
@@ -17151,7 +17151,7 @@
       </c>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="n">
-        <v>747684.7</v>
+        <v>876934.05</v>
       </c>
       <c r="AA183" t="inlineStr"/>
       <c r="AB183" t="inlineStr"/>
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>423414.5</v>
+        <v>500793.65</v>
       </c>
       <c r="R184" t="n">
         <v>423374.5</v>
@@ -17245,7 +17245,7 @@
       </c>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="n">
-        <v>423414.5</v>
+        <v>500793.65</v>
       </c>
       <c r="AA184" t="inlineStr"/>
       <c r="AB184" t="inlineStr"/>
@@ -17320,7 +17320,7 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>1687657.74</v>
+        <v>1977393.7</v>
       </c>
       <c r="R185" t="n">
         <v>1687653.74</v>
@@ -17339,7 +17339,7 @@
       </c>
       <c r="Y185" t="inlineStr"/>
       <c r="Z185" t="n">
-        <v>1687657.74</v>
+        <v>1977393.7</v>
       </c>
       <c r="AA185" t="inlineStr"/>
       <c r="AB185" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>1559471.71</v>
+        <v>1884590.14</v>
       </c>
       <c r="R186" t="n">
         <v>1559469.71</v>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="Y186" t="inlineStr"/>
       <c r="Z186" t="n">
-        <v>1559471.71</v>
+        <v>1884590.14</v>
       </c>
       <c r="AA186" t="inlineStr"/>
       <c r="AB186" t="inlineStr"/>
@@ -17508,7 +17508,7 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>1166875.46</v>
+        <v>1415682.48</v>
       </c>
       <c r="R187" t="n">
         <v>1166871.46</v>
@@ -17527,7 +17527,7 @@
       </c>
       <c r="Y187" t="inlineStr"/>
       <c r="Z187" t="n">
-        <v>1166875.46</v>
+        <v>1415682.48</v>
       </c>
       <c r="AA187" t="inlineStr"/>
       <c r="AB187" t="inlineStr"/>
@@ -17602,7 +17602,7 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>303700.1</v>
+        <v>347017.97</v>
       </c>
       <c r="R188" t="n">
         <v>303696.1</v>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="Y188" t="inlineStr"/>
       <c r="Z188" t="n">
-        <v>303700.1</v>
+        <v>347017.97</v>
       </c>
       <c r="AA188" t="inlineStr"/>
       <c r="AB188" t="inlineStr"/>
@@ -18444,7 +18444,7 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>2301.5</v>
+        <v>2855.72</v>
       </c>
       <c r="R197" t="n">
         <v>2301.47</v>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="Y197" t="inlineStr"/>
       <c r="Z197" t="n">
-        <v>2301.5</v>
+        <v>2855.72</v>
       </c>
       <c r="AA197" t="inlineStr"/>
       <c r="AB197" t="inlineStr"/>
@@ -18635,7 +18635,7 @@
         <v>12267201.02</v>
       </c>
       <c r="R199" t="n">
-        <v>3409725.72</v>
+        <v>5134400.23</v>
       </c>
       <c r="S199" t="n">
         <v>3368809.03</v>
@@ -18729,7 +18729,7 @@
         <v>15468600.43</v>
       </c>
       <c r="R200" t="n">
-        <v>5773824.52</v>
+        <v>9206332.279999999</v>
       </c>
       <c r="S200" t="n">
         <v>5704538.62</v>
@@ -19102,7 +19102,7 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>8550543.42</v>
+        <v>8085543.42</v>
       </c>
       <c r="R204" t="n">
         <v>2054047.02</v>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="Y204" t="inlineStr"/>
       <c r="Z204" t="n">
-        <v>8550543.42</v>
+        <v>8085543.42</v>
       </c>
       <c r="AA204" t="inlineStr"/>
       <c r="AB204" t="inlineStr"/>
@@ -20594,13 +20594,13 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>7132375.41</v>
+        <v>6977375.41</v>
       </c>
       <c r="R220" t="n">
         <v>868789.0600000001</v>
       </c>
       <c r="S220" t="n">
-        <v>256174.81</v>
+        <v>858363.6</v>
       </c>
       <c r="T220" t="inlineStr"/>
       <c r="U220" t="inlineStr"/>
@@ -20613,13 +20613,13 @@
       </c>
       <c r="Y220" t="inlineStr"/>
       <c r="Z220" t="n">
-        <v>7132375.41</v>
+        <v>6977375.41</v>
       </c>
       <c r="AA220" t="inlineStr"/>
       <c r="AB220" t="inlineStr"/>
       <c r="AC220" t="inlineStr"/>
       <c r="AD220" t="n">
-        <v>256174.81</v>
+        <v>858363.6</v>
       </c>
     </row>
     <row r="221">
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>7132375.41</v>
+        <v>6977375.41</v>
       </c>
       <c r="R221" t="n">
         <v>868789.0600000001</v>
@@ -20707,7 +20707,7 @@
       </c>
       <c r="Y221" t="inlineStr"/>
       <c r="Z221" t="n">
-        <v>7132375.41</v>
+        <v>6977375.41</v>
       </c>
       <c r="AA221" t="inlineStr"/>
       <c r="AB221" t="inlineStr"/>
@@ -22222,13 +22222,13 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>6435668.8</v>
+        <v>6745456</v>
       </c>
       <c r="R238" t="n">
         <v>1612436.99</v>
       </c>
       <c r="S238" t="n">
-        <v>0</v>
+        <v>1608463.38</v>
       </c>
       <c r="T238" t="inlineStr"/>
       <c r="U238" t="inlineStr"/>
@@ -22241,13 +22241,13 @@
       </c>
       <c r="Y238" t="inlineStr"/>
       <c r="Z238" t="n">
-        <v>6435668.8</v>
+        <v>6745456</v>
       </c>
       <c r="AA238" t="inlineStr"/>
       <c r="AB238" t="inlineStr"/>
       <c r="AC238" t="inlineStr"/>
       <c r="AD238" t="n">
-        <v>0</v>
+        <v>1608463.38</v>
       </c>
     </row>
     <row r="239">
@@ -22322,7 +22322,7 @@
         <v>43235.45</v>
       </c>
       <c r="S239" t="n">
-        <v>0</v>
+        <v>43235.45</v>
       </c>
       <c r="T239" t="inlineStr"/>
       <c r="U239" t="inlineStr"/>
@@ -22341,7 +22341,7 @@
       <c r="AB239" t="inlineStr"/>
       <c r="AC239" t="inlineStr"/>
       <c r="AD239" t="n">
-        <v>0</v>
+        <v>43235.45</v>
       </c>
     </row>
     <row r="240">
@@ -22413,7 +22413,7 @@
         <v>696572.29</v>
       </c>
       <c r="R240" t="n">
-        <v>0</v>
+        <v>231318.29</v>
       </c>
       <c r="S240" t="n">
         <v>0</v>
@@ -22507,7 +22507,7 @@
         <v>328992.35</v>
       </c>
       <c r="R241" t="n">
-        <v>0</v>
+        <v>186703.7</v>
       </c>
       <c r="S241" t="n">
         <v>0</v>
@@ -22601,7 +22601,7 @@
         <v>55000</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>18408.35</v>
       </c>
       <c r="S242" t="n">
         <v>0</v>
@@ -36392,7 +36392,7 @@
         </is>
       </c>
       <c r="Q395" t="n">
-        <v>98218.74000000001</v>
+        <v>130958.32</v>
       </c>
       <c r="R395" t="n">
         <v>97998.17999999999</v>
@@ -36411,7 +36411,7 @@
       </c>
       <c r="Y395" t="inlineStr"/>
       <c r="Z395" t="n">
-        <v>98218.74000000001</v>
+        <v>130958.32</v>
       </c>
       <c r="AA395" t="inlineStr"/>
       <c r="AB395" t="inlineStr"/>
@@ -36760,7 +36760,7 @@
         </is>
       </c>
       <c r="Q399" t="n">
-        <v>4988</v>
+        <v>8789.450000000001</v>
       </c>
       <c r="R399" t="n">
         <v>4987.97</v>
@@ -36779,7 +36779,7 @@
       </c>
       <c r="Y399" t="inlineStr"/>
       <c r="Z399" t="n">
-        <v>4988</v>
+        <v>8789.450000000001</v>
       </c>
       <c r="AA399" t="inlineStr"/>
       <c r="AB399" t="inlineStr"/>
@@ -36948,7 +36948,7 @@
         </is>
       </c>
       <c r="Q401" t="n">
-        <v>38157.52</v>
+        <v>39114.47</v>
       </c>
       <c r="R401" t="n">
         <v>38157.52</v>
@@ -36967,7 +36967,7 @@
       </c>
       <c r="Y401" t="inlineStr"/>
       <c r="Z401" t="n">
-        <v>38157.52</v>
+        <v>39114.47</v>
       </c>
       <c r="AA401" t="inlineStr"/>
       <c r="AB401" t="inlineStr"/>
@@ -37042,7 +37042,7 @@
         </is>
       </c>
       <c r="Q402" t="n">
-        <v>21023.01</v>
+        <v>21214.4</v>
       </c>
       <c r="R402" t="n">
         <v>21023.01</v>
@@ -37061,7 +37061,7 @@
       </c>
       <c r="Y402" t="inlineStr"/>
       <c r="Z402" t="n">
-        <v>21023.01</v>
+        <v>21214.4</v>
       </c>
       <c r="AA402" t="inlineStr"/>
       <c r="AB402" t="inlineStr"/>
@@ -37136,7 +37136,7 @@
         </is>
       </c>
       <c r="Q403" t="n">
-        <v>85783.92999999999</v>
+        <v>87506.44</v>
       </c>
       <c r="R403" t="n">
         <v>85783.92999999999</v>
@@ -37155,7 +37155,7 @@
       </c>
       <c r="Y403" t="inlineStr"/>
       <c r="Z403" t="n">
-        <v>85783.92999999999</v>
+        <v>87506.44</v>
       </c>
       <c r="AA403" t="inlineStr"/>
       <c r="AB403" t="inlineStr"/>
@@ -37230,7 +37230,7 @@
         </is>
       </c>
       <c r="Q404" t="n">
-        <v>84678.62</v>
+        <v>86503.2</v>
       </c>
       <c r="R404" t="n">
         <v>84678.62</v>
@@ -37249,7 +37249,7 @@
       </c>
       <c r="Y404" t="inlineStr"/>
       <c r="Z404" t="n">
-        <v>84678.62</v>
+        <v>86503.2</v>
       </c>
       <c r="AA404" t="inlineStr"/>
       <c r="AB404" t="inlineStr"/>
@@ -37324,7 +37324,7 @@
         </is>
       </c>
       <c r="Q405" t="n">
-        <v>61443.59</v>
+        <v>62694</v>
       </c>
       <c r="R405" t="n">
         <v>61443.59</v>
@@ -37343,7 +37343,7 @@
       </c>
       <c r="Y405" t="inlineStr"/>
       <c r="Z405" t="n">
-        <v>61443.59</v>
+        <v>62694</v>
       </c>
       <c r="AA405" t="inlineStr"/>
       <c r="AB405" t="inlineStr"/>
@@ -37418,7 +37418,7 @@
         </is>
       </c>
       <c r="Q406" t="n">
-        <v>14291.86</v>
+        <v>14763.95</v>
       </c>
       <c r="R406" t="n">
         <v>14291.86</v>
@@ -37437,7 +37437,7 @@
       </c>
       <c r="Y406" t="inlineStr"/>
       <c r="Z406" t="n">
-        <v>14291.86</v>
+        <v>14763.95</v>
       </c>
       <c r="AA406" t="inlineStr"/>
       <c r="AB406" t="inlineStr"/>
@@ -37512,7 +37512,7 @@
         </is>
       </c>
       <c r="Q407" t="n">
-        <v>3570.73</v>
+        <v>3723.84</v>
       </c>
       <c r="R407" t="n">
         <v>3570.73</v>
@@ -37531,7 +37531,7 @@
       </c>
       <c r="Y407" t="inlineStr"/>
       <c r="Z407" t="n">
-        <v>3570.73</v>
+        <v>3723.84</v>
       </c>
       <c r="AA407" t="inlineStr"/>
       <c r="AB407" t="inlineStr"/>
@@ -38529,7 +38529,7 @@
         <v>12558731.27</v>
       </c>
       <c r="R418" t="n">
-        <v>1232944.69</v>
+        <v>1589721.35</v>
       </c>
       <c r="S418" t="n">
         <v>1218149.35</v>
@@ -38623,7 +38623,7 @@
         <v>46966.74</v>
       </c>
       <c r="R419" t="n">
-        <v>34988.64</v>
+        <v>46966.74</v>
       </c>
       <c r="S419" t="n">
         <v>23956.2</v>
@@ -38713,7 +38713,7 @@
         <v>2487.09</v>
       </c>
       <c r="R420" t="n">
-        <v>1688.7</v>
+        <v>2487.09</v>
       </c>
       <c r="S420" t="n">
         <v>1688.7</v>
@@ -38803,7 +38803,7 @@
         <v>83312.7</v>
       </c>
       <c r="R421" t="n">
-        <v>55541.8</v>
+        <v>83312.7</v>
       </c>
       <c r="S421" t="n">
         <v>55541.8</v>
@@ -38893,7 +38893,7 @@
         <v>190387.12</v>
       </c>
       <c r="R422" t="n">
-        <v>131856.3</v>
+        <v>190387.12</v>
       </c>
       <c r="S422" t="n">
         <v>131856.3</v>
@@ -39253,7 +39253,7 @@
         <v>1541.63</v>
       </c>
       <c r="R426" t="n">
-        <v>978.1799999999999</v>
+        <v>1540.63</v>
       </c>
       <c r="S426" t="n">
         <v>978.1799999999999</v>
@@ -39343,7 +39343,7 @@
         <v>10063.48</v>
       </c>
       <c r="R427" t="n">
-        <v>6398.28</v>
+        <v>10063.48</v>
       </c>
       <c r="S427" t="n">
         <v>6398.28</v>
@@ -39436,7 +39436,7 @@
         <v>164415.59</v>
       </c>
       <c r="S428" t="n">
-        <v>45235.48</v>
+        <v>164415.59</v>
       </c>
       <c r="T428" t="inlineStr"/>
       <c r="U428" t="inlineStr"/>
@@ -39455,7 +39455,7 @@
       <c r="AB428" t="inlineStr"/>
       <c r="AC428" t="inlineStr"/>
       <c r="AD428" t="n">
-        <v>45235.48</v>
+        <v>164415.59</v>
       </c>
     </row>
     <row r="429">
@@ -39527,7 +39527,7 @@
         <v>35000</v>
       </c>
       <c r="R429" t="n">
-        <v>0</v>
+        <v>6638.9</v>
       </c>
       <c r="S429" t="n">
         <v>0</v>
@@ -39618,7 +39618,7 @@
         </is>
       </c>
       <c r="Q430" t="n">
-        <v>14124998.39</v>
+        <v>13762998.39</v>
       </c>
       <c r="R430" t="n">
         <v>1063647.94</v>
@@ -39637,7 +39637,7 @@
       </c>
       <c r="Y430" t="inlineStr"/>
       <c r="Z430" t="n">
-        <v>14124998.39</v>
+        <v>13762998.39</v>
       </c>
       <c r="AA430" t="inlineStr"/>
       <c r="AB430" t="inlineStr"/>
@@ -39718,7 +39718,7 @@
         <v>3427611</v>
       </c>
       <c r="S431" t="n">
-        <v>948621.53</v>
+        <v>3418990.12</v>
       </c>
       <c r="T431" t="inlineStr"/>
       <c r="U431" t="inlineStr"/>
@@ -39737,7 +39737,7 @@
       <c r="AB431" t="inlineStr"/>
       <c r="AC431" t="inlineStr"/>
       <c r="AD431" t="n">
-        <v>948621.53</v>
+        <v>3418990.12</v>
       </c>
     </row>
     <row r="432">
@@ -39809,7 +39809,7 @@
         <v>496394.56</v>
       </c>
       <c r="R432" t="n">
-        <v>0</v>
+        <v>96342.11</v>
       </c>
       <c r="S432" t="n">
         <v>0</v>
@@ -40000,7 +40000,7 @@
         <v>2619.57</v>
       </c>
       <c r="S434" t="n">
-        <v>1733.76</v>
+        <v>2493.82</v>
       </c>
       <c r="T434" t="inlineStr"/>
       <c r="U434" t="inlineStr"/>
@@ -40019,7 +40019,7 @@
       <c r="AB434" t="inlineStr"/>
       <c r="AC434" t="inlineStr"/>
       <c r="AD434" t="n">
-        <v>1733.76</v>
+        <v>2493.82</v>
       </c>
     </row>
     <row r="435">
@@ -40376,7 +40376,7 @@
         <v>147328.11</v>
       </c>
       <c r="S438" t="n">
-        <v>81183.35000000001</v>
+        <v>122533.44</v>
       </c>
       <c r="T438" t="inlineStr"/>
       <c r="U438" t="inlineStr"/>
@@ -40395,7 +40395,7 @@
       <c r="AB438" t="inlineStr"/>
       <c r="AC438" t="inlineStr"/>
       <c r="AD438" t="n">
-        <v>81183.35000000001</v>
+        <v>122533.44</v>
       </c>
     </row>
     <row r="439">
@@ -40470,7 +40470,7 @@
         <v>49109.37</v>
       </c>
       <c r="S439" t="n">
-        <v>27566.72</v>
+        <v>41350.08</v>
       </c>
       <c r="T439" t="inlineStr"/>
       <c r="U439" t="inlineStr"/>
@@ -40489,7 +40489,7 @@
       <c r="AB439" t="inlineStr"/>
       <c r="AC439" t="inlineStr"/>
       <c r="AD439" t="n">
-        <v>27566.72</v>
+        <v>41350.08</v>
       </c>
     </row>
     <row r="440">
@@ -40561,7 +40561,7 @@
         <v>4233596.13</v>
       </c>
       <c r="R440" t="n">
-        <v>0</v>
+        <v>779131.49</v>
       </c>
       <c r="S440" t="n">
         <v>0</v>
@@ -40655,7 +40655,7 @@
         <v>220000</v>
       </c>
       <c r="R441" t="n">
-        <v>0</v>
+        <v>34221.35</v>
       </c>
       <c r="S441" t="n">
         <v>0</v>
@@ -40749,7 +40749,7 @@
         <v>490207.03</v>
       </c>
       <c r="R442" t="n">
-        <v>0</v>
+        <v>47942.29</v>
       </c>
       <c r="S442" t="n">
         <v>0</v>
@@ -40843,7 +40843,7 @@
         <v>40000</v>
       </c>
       <c r="R443" t="n">
-        <v>0</v>
+        <v>3545.6</v>
       </c>
       <c r="S443" t="n">
         <v>0</v>
@@ -41031,10 +41031,10 @@
         <v>7809.61</v>
       </c>
       <c r="R445" t="n">
-        <v>7235.44</v>
+        <v>7809.61</v>
       </c>
       <c r="S445" t="n">
-        <v>5154.55</v>
+        <v>7434.75</v>
       </c>
       <c r="T445" t="inlineStr"/>
       <c r="U445" t="inlineStr"/>
@@ -41053,7 +41053,7 @@
       <c r="AB445" t="inlineStr"/>
       <c r="AC445" t="inlineStr"/>
       <c r="AD445" t="n">
-        <v>5154.55</v>
+        <v>7434.75</v>
       </c>
     </row>
     <row r="446">
@@ -41128,7 +41128,7 @@
         <v>5239.14</v>
       </c>
       <c r="S446" t="n">
-        <v>3467.53</v>
+        <v>4987.67</v>
       </c>
       <c r="T446" t="inlineStr"/>
       <c r="U446" t="inlineStr"/>
@@ -41147,7 +41147,7 @@
       <c r="AB446" t="inlineStr"/>
       <c r="AC446" t="inlineStr"/>
       <c r="AD446" t="n">
-        <v>3467.53</v>
+        <v>4987.67</v>
       </c>
     </row>
     <row r="447">
@@ -41222,7 +41222,7 @@
         <v>98218.74000000001</v>
       </c>
       <c r="S447" t="n">
-        <v>55133.46</v>
+        <v>82700.19</v>
       </c>
       <c r="T447" t="inlineStr"/>
       <c r="U447" t="inlineStr"/>
@@ -41241,7 +41241,7 @@
       <c r="AB447" t="inlineStr"/>
       <c r="AC447" t="inlineStr"/>
       <c r="AD447" t="n">
-        <v>55133.46</v>
+        <v>82700.19</v>
       </c>
     </row>
     <row r="448">
@@ -42604,7 +42604,7 @@
         <v>4470</v>
       </c>
       <c r="S462" t="n">
-        <v>0</v>
+        <v>4416.36</v>
       </c>
       <c r="T462" t="inlineStr"/>
       <c r="U462" t="inlineStr"/>
@@ -42619,7 +42619,7 @@
       <c r="AB462" t="inlineStr"/>
       <c r="AC462" t="inlineStr"/>
       <c r="AD462" t="n">
-        <v>0</v>
+        <v>4416.36</v>
       </c>
     </row>
     <row r="463">
@@ -42958,13 +42958,13 @@
         </is>
       </c>
       <c r="Q466" t="n">
-        <v>6076768.36</v>
+        <v>6438186.76</v>
       </c>
       <c r="R466" t="n">
         <v>937347.08</v>
       </c>
       <c r="S466" t="n">
-        <v>0</v>
+        <v>934983.12</v>
       </c>
       <c r="T466" t="inlineStr"/>
       <c r="U466" t="inlineStr"/>
@@ -42977,13 +42977,13 @@
       </c>
       <c r="Y466" t="inlineStr"/>
       <c r="Z466" t="n">
-        <v>6076768.36</v>
+        <v>6438186.76</v>
       </c>
       <c r="AA466" t="inlineStr"/>
       <c r="AB466" t="inlineStr"/>
       <c r="AC466" t="inlineStr"/>
       <c r="AD466" t="n">
-        <v>0</v>
+        <v>934983.12</v>
       </c>
     </row>
     <row r="467">
@@ -43058,7 +43058,7 @@
         <v>147463.02</v>
       </c>
       <c r="S467" t="n">
-        <v>0</v>
+        <v>147090.3</v>
       </c>
       <c r="T467" t="inlineStr"/>
       <c r="U467" t="inlineStr"/>
@@ -43077,7 +43077,7 @@
       <c r="AB467" t="inlineStr"/>
       <c r="AC467" t="inlineStr"/>
       <c r="AD467" t="n">
-        <v>0</v>
+        <v>147090.3</v>
       </c>
     </row>
     <row r="468">
@@ -43246,7 +43246,7 @@
         <v>55477.88</v>
       </c>
       <c r="S469" t="n">
-        <v>0</v>
+        <v>55477.88</v>
       </c>
       <c r="T469" t="inlineStr"/>
       <c r="U469" t="inlineStr"/>
@@ -43265,7 +43265,7 @@
       <c r="AB469" t="inlineStr"/>
       <c r="AC469" t="inlineStr"/>
       <c r="AD469" t="n">
-        <v>0</v>
+        <v>55477.88</v>
       </c>
     </row>
     <row r="470">
@@ -46339,7 +46339,7 @@
         <v>35000</v>
       </c>
       <c r="R503" t="n">
-        <v>0</v>
+        <v>5815.15</v>
       </c>
       <c r="S503" t="n">
         <v>0</v>
@@ -46527,7 +46527,7 @@
         <v>644461.2</v>
       </c>
       <c r="R505" t="n">
-        <v>0</v>
+        <v>154297.4</v>
       </c>
       <c r="S505" t="n">
         <v>0</v>
@@ -46712,7 +46712,7 @@
         </is>
       </c>
       <c r="Q507" t="n">
-        <v>510.38</v>
+        <v>1084.55</v>
       </c>
       <c r="R507" t="n">
         <v>510.37</v>
@@ -46731,7 +46731,7 @@
       </c>
       <c r="Y507" t="inlineStr"/>
       <c r="Z507" t="n">
-        <v>510.38</v>
+        <v>1084.55</v>
       </c>
       <c r="AA507" t="inlineStr"/>
       <c r="AB507" t="inlineStr"/>
@@ -47180,7 +47180,7 @@
         <v>162778.02</v>
       </c>
       <c r="S512" t="n">
-        <v>0</v>
+        <v>162382.93</v>
       </c>
       <c r="T512" t="inlineStr"/>
       <c r="U512" t="inlineStr"/>
@@ -47199,7 +47199,7 @@
       <c r="AB512" t="inlineStr"/>
       <c r="AC512" t="inlineStr"/>
       <c r="AD512" t="n">
-        <v>0</v>
+        <v>162382.93</v>
       </c>
     </row>
     <row r="513">
@@ -47274,7 +47274,7 @@
         <v>1842.29</v>
       </c>
       <c r="S513" t="n">
-        <v>0</v>
+        <v>1842.29</v>
       </c>
       <c r="T513" t="inlineStr"/>
       <c r="U513" t="inlineStr"/>
@@ -47293,7 +47293,7 @@
       <c r="AB513" t="inlineStr"/>
       <c r="AC513" t="inlineStr"/>
       <c r="AD513" t="n">
-        <v>0</v>
+        <v>1842.29</v>
       </c>
     </row>
     <row r="514">
@@ -47459,7 +47459,7 @@
         <v>196080.79</v>
       </c>
       <c r="R515" t="n">
-        <v>0</v>
+        <v>48922.71</v>
       </c>
       <c r="S515" t="n">
         <v>0</v>
@@ -47553,7 +47553,7 @@
         <v>15000</v>
       </c>
       <c r="R516" t="n">
-        <v>0</v>
+        <v>991.01</v>
       </c>
       <c r="S516" t="n">
         <v>0</v>
@@ -48951,10 +48951,10 @@
         <v>24604.41</v>
       </c>
       <c r="R531" t="n">
-        <v>0</v>
+        <v>6994.36</v>
       </c>
       <c r="S531" t="n">
-        <v>0</v>
+        <v>6994.36</v>
       </c>
       <c r="T531" t="inlineStr"/>
       <c r="U531" t="inlineStr"/>
@@ -48969,7 +48969,7 @@
       <c r="AB531" t="inlineStr"/>
       <c r="AC531" t="inlineStr"/>
       <c r="AD531" t="n">
-        <v>0</v>
+        <v>6994.36</v>
       </c>
     </row>
     <row r="532">
@@ -49041,10 +49041,10 @@
         <v>7304.7</v>
       </c>
       <c r="R532" t="n">
-        <v>0</v>
+        <v>1413.81</v>
       </c>
       <c r="S532" t="n">
-        <v>0</v>
+        <v>1413.81</v>
       </c>
       <c r="T532" t="inlineStr"/>
       <c r="U532" t="inlineStr"/>
@@ -49063,7 +49063,7 @@
       <c r="AB532" t="inlineStr"/>
       <c r="AC532" t="inlineStr"/>
       <c r="AD532" t="n">
-        <v>0</v>
+        <v>1413.81</v>
       </c>
     </row>
     <row r="533">
@@ -49156,6 +49156,96 @@
         <v>8635921.619999999</v>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B534" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C534" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>106</v>
+      </c>
+      <c r="F534" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>1511189 000243/2026</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I534" t="n">
+        <v>52</v>
+      </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K534" t="n">
+        <v>5207</v>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS DE INFORMATICA</t>
+        </is>
+      </c>
+      <c r="M534" t="n">
+        <v>80</v>
+      </c>
+      <c r="N534" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>18.476.349/0001-60</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>GP TRADE COMPANY ELETRONICOS IMPORTACAO E EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="Q534" t="n">
+        <v>1398.22</v>
+      </c>
+      <c r="R534" t="n">
+        <v>0</v>
+      </c>
+      <c r="S534" t="n">
+        <v>0</v>
+      </c>
+      <c r="T534" t="inlineStr"/>
+      <c r="U534" t="inlineStr"/>
+      <c r="V534" t="inlineStr"/>
+      <c r="W534" t="inlineStr"/>
+      <c r="X534" t="inlineStr"/>
+      <c r="Y534" t="inlineStr"/>
+      <c r="Z534" t="n">
+        <v>1398.22</v>
+      </c>
+      <c r="AA534" t="inlineStr"/>
+      <c r="AB534" t="inlineStr"/>
+      <c r="AC534" t="inlineStr"/>
+      <c r="AD534" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/upload/empenho.xlsx
+++ b/upload/empenho.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD534"/>
+  <dimension ref="A1:AD537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13101,10 +13101,10 @@
         <v>9891.6</v>
       </c>
       <c r="R140" t="n">
-        <v>7105.6</v>
+        <v>8214.040000000001</v>
       </c>
       <c r="S140" t="n">
-        <v>6764.54</v>
+        <v>7819.77</v>
       </c>
       <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr"/>
@@ -13123,7 +13123,7 @@
       <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="n">
-        <v>6764.54</v>
+        <v>7819.77</v>
       </c>
     </row>
     <row r="141">
@@ -13756,7 +13756,7 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>244532.13</v>
+        <v>275634.73</v>
       </c>
       <c r="R147" t="n">
         <v>228162.34</v>
@@ -13775,7 +13775,7 @@
       </c>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="n">
-        <v>244532.13</v>
+        <v>275634.73</v>
       </c>
       <c r="AA147" t="inlineStr"/>
       <c r="AB147" t="inlineStr"/>
@@ -13944,7 +13944,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>67000.00999999999</v>
+        <v>75000.00999999999</v>
       </c>
       <c r="R149" t="n">
         <v>60353.76</v>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="n">
-        <v>67000.00999999999</v>
+        <v>75000.00999999999</v>
       </c>
       <c r="AA149" t="inlineStr"/>
       <c r="AB149" t="inlineStr"/>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>591758.7</v>
+        <v>679741.3199999999</v>
       </c>
       <c r="R150" t="n">
         <v>532088</v>
@@ -14057,7 +14057,7 @@
       </c>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="n">
-        <v>591758.7</v>
+        <v>679741.3199999999</v>
       </c>
       <c r="AA150" t="inlineStr"/>
       <c r="AB150" t="inlineStr"/>
@@ -14132,7 +14132,7 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>1735475.63</v>
+        <v>2057254.45</v>
       </c>
       <c r="R151" t="n">
         <v>1653787.16</v>
@@ -14151,7 +14151,7 @@
       </c>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="n">
-        <v>1735475.63</v>
+        <v>2057254.45</v>
       </c>
       <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="inlineStr"/>
@@ -14226,7 +14226,7 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>131802.65</v>
+        <v>139802.65</v>
       </c>
       <c r="R152" t="n">
         <v>103830.02</v>
@@ -14245,7 +14245,7 @@
       </c>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="n">
-        <v>131802.65</v>
+        <v>139802.65</v>
       </c>
       <c r="AA152" t="inlineStr"/>
       <c r="AB152" t="inlineStr"/>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>12560.85</v>
+        <v>15560.85</v>
       </c>
       <c r="R153" t="n">
         <v>12100.13</v>
@@ -14339,7 +14339,7 @@
       </c>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="n">
-        <v>12560.85</v>
+        <v>15560.85</v>
       </c>
       <c r="AA153" t="inlineStr"/>
       <c r="AB153" t="inlineStr"/>
@@ -14414,7 +14414,7 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>398730.09</v>
+        <v>460199.37</v>
       </c>
       <c r="R154" t="n">
         <v>351702.49</v>
@@ -14433,7 +14433,7 @@
       </c>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="n">
-        <v>398730.09</v>
+        <v>460199.37</v>
       </c>
       <c r="AA154" t="inlineStr"/>
       <c r="AB154" t="inlineStr"/>
@@ -14508,10 +14508,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>30127671.46</v>
+        <v>28737066.86</v>
       </c>
       <c r="R155" t="n">
-        <v>6448835.68</v>
+        <v>9732274.390000001</v>
       </c>
       <c r="S155" t="n">
         <v>6371449.66</v>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="n">
-        <v>30127671.46</v>
+        <v>28737066.86</v>
       </c>
       <c r="AA155" t="inlineStr"/>
       <c r="AB155" t="inlineStr"/>
@@ -16289,7 +16289,7 @@
         <v>35809.7</v>
       </c>
       <c r="R174" t="n">
-        <v>29781.17</v>
+        <v>35809.68</v>
       </c>
       <c r="S174" t="n">
         <v>29332.76</v>
@@ -16383,7 +16383,7 @@
         <v>15155.15</v>
       </c>
       <c r="R175" t="n">
-        <v>11194.7</v>
+        <v>15155.12</v>
       </c>
       <c r="S175" t="n">
         <v>10868.92</v>
@@ -16477,7 +16477,7 @@
         <v>111539.89</v>
       </c>
       <c r="R176" t="n">
-        <v>79951.16</v>
+        <v>111539.87</v>
       </c>
       <c r="S176" t="n">
         <v>75680.95</v>
@@ -16571,7 +16571,7 @@
         <v>86942.83</v>
       </c>
       <c r="R177" t="n">
-        <v>68767.81</v>
+        <v>86942.81</v>
       </c>
       <c r="S177" t="n">
         <v>65605.03999999999</v>
@@ -16665,7 +16665,7 @@
         <v>40443.6</v>
       </c>
       <c r="R178" t="n">
-        <v>31263.08</v>
+        <v>40443.58</v>
       </c>
       <c r="S178" t="n">
         <v>31263.08</v>
@@ -16759,7 +16759,7 @@
         <v>9343.940000000001</v>
       </c>
       <c r="R179" t="n">
-        <v>8235.469999999999</v>
+        <v>9343.91</v>
       </c>
       <c r="S179" t="n">
         <v>8235.469999999999</v>
@@ -17135,7 +17135,7 @@
         <v>876934.05</v>
       </c>
       <c r="R183" t="n">
-        <v>747637.24</v>
+        <v>876886.59</v>
       </c>
       <c r="S183" t="n">
         <v>616245.1800000001</v>
@@ -17229,7 +17229,7 @@
         <v>500793.65</v>
       </c>
       <c r="R184" t="n">
-        <v>423374.5</v>
+        <v>500753.65</v>
       </c>
       <c r="S184" t="n">
         <v>376803.3</v>
@@ -17323,7 +17323,7 @@
         <v>1977393.7</v>
       </c>
       <c r="R185" t="n">
-        <v>1687653.74</v>
+        <v>1977389.7</v>
       </c>
       <c r="S185" t="n">
         <v>1446217.81</v>
@@ -17417,7 +17417,7 @@
         <v>1884590.14</v>
       </c>
       <c r="R186" t="n">
-        <v>1559469.71</v>
+        <v>1884588.14</v>
       </c>
       <c r="S186" t="n">
         <v>1285107.36</v>
@@ -17511,7 +17511,7 @@
         <v>1415682.48</v>
       </c>
       <c r="R187" t="n">
-        <v>1166871.46</v>
+        <v>1415678.48</v>
       </c>
       <c r="S187" t="n">
         <v>988621.6899999999</v>
@@ -17605,7 +17605,7 @@
         <v>347017.97</v>
       </c>
       <c r="R188" t="n">
-        <v>303696.1</v>
+        <v>347013.97</v>
       </c>
       <c r="S188" t="n">
         <v>270289.53</v>
@@ -17699,7 +17699,7 @@
         <v>60100</v>
       </c>
       <c r="R189" t="n">
-        <v>42581.89</v>
+        <v>42713.34</v>
       </c>
       <c r="S189" t="n">
         <v>41553.09</v>
@@ -18447,7 +18447,7 @@
         <v>2855.72</v>
       </c>
       <c r="R197" t="n">
-        <v>2301.47</v>
+        <v>2855.69</v>
       </c>
       <c r="S197" t="n">
         <v>2301.47</v>
@@ -18538,10 +18538,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>90339.88</v>
+        <v>111881.17</v>
       </c>
       <c r="R198" t="n">
-        <v>90339.83</v>
+        <v>111881.12</v>
       </c>
       <c r="S198" t="n">
         <v>80402.44</v>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="Y198" t="inlineStr"/>
       <c r="Z198" t="n">
-        <v>90339.88</v>
+        <v>111881.17</v>
       </c>
       <c r="AA198" t="inlineStr"/>
       <c r="AB198" t="inlineStr"/>
@@ -18638,7 +18638,7 @@
         <v>5134400.23</v>
       </c>
       <c r="S199" t="n">
-        <v>3368809.03</v>
+        <v>5072787.47</v>
       </c>
       <c r="T199" t="inlineStr"/>
       <c r="U199" t="inlineStr"/>
@@ -18657,7 +18657,7 @@
       <c r="AB199" t="inlineStr"/>
       <c r="AC199" t="inlineStr"/>
       <c r="AD199" t="n">
-        <v>3368809.03</v>
+        <v>5072787.47</v>
       </c>
     </row>
     <row r="200">
@@ -18732,7 +18732,7 @@
         <v>9206332.279999999</v>
       </c>
       <c r="S200" t="n">
-        <v>5704538.62</v>
+        <v>9095856.26</v>
       </c>
       <c r="T200" t="inlineStr"/>
       <c r="U200" t="inlineStr"/>
@@ -18751,7 +18751,7 @@
       <c r="AB200" t="inlineStr"/>
       <c r="AC200" t="inlineStr"/>
       <c r="AD200" t="n">
-        <v>5704538.62</v>
+        <v>9095856.26</v>
       </c>
     </row>
     <row r="201">
@@ -18823,10 +18823,10 @@
         <v>235562.45</v>
       </c>
       <c r="R201" t="n">
-        <v>87926.27</v>
+        <v>140197.96</v>
       </c>
       <c r="S201" t="n">
-        <v>86871.17</v>
+        <v>138515.6</v>
       </c>
       <c r="T201" t="inlineStr"/>
       <c r="U201" t="inlineStr"/>
@@ -18845,7 +18845,7 @@
       <c r="AB201" t="inlineStr"/>
       <c r="AC201" t="inlineStr"/>
       <c r="AD201" t="n">
-        <v>86871.17</v>
+        <v>138515.6</v>
       </c>
     </row>
     <row r="202">
@@ -18917,10 +18917,10 @@
         <v>8675354.27</v>
       </c>
       <c r="R202" t="n">
-        <v>3083705.74</v>
+        <v>3523181.65</v>
       </c>
       <c r="S202" t="n">
-        <v>3046701.28</v>
+        <v>3480903.48</v>
       </c>
       <c r="T202" t="inlineStr"/>
       <c r="U202" t="inlineStr"/>
@@ -18939,7 +18939,7 @@
       <c r="AB202" t="inlineStr"/>
       <c r="AC202" t="inlineStr"/>
       <c r="AD202" t="n">
-        <v>3046701.28</v>
+        <v>3480903.48</v>
       </c>
     </row>
     <row r="203">
@@ -19011,10 +19011,10 @@
         <v>2168838.56</v>
       </c>
       <c r="R203" t="n">
-        <v>770926.4300000001</v>
+        <v>880795.41</v>
       </c>
       <c r="S203" t="n">
-        <v>761675.3100000001</v>
+        <v>870225.86</v>
       </c>
       <c r="T203" t="inlineStr"/>
       <c r="U203" t="inlineStr"/>
@@ -19033,7 +19033,7 @@
       <c r="AB203" t="inlineStr"/>
       <c r="AC203" t="inlineStr"/>
       <c r="AD203" t="n">
-        <v>761675.3100000001</v>
+        <v>870225.86</v>
       </c>
     </row>
     <row r="204">
@@ -19105,10 +19105,10 @@
         <v>8085543.42</v>
       </c>
       <c r="R204" t="n">
-        <v>2054047.02</v>
+        <v>2529111.84</v>
       </c>
       <c r="S204" t="n">
-        <v>2029398.43</v>
+        <v>2498762.48</v>
       </c>
       <c r="T204" t="inlineStr"/>
       <c r="U204" t="inlineStr"/>
@@ -19127,7 +19127,7 @@
       <c r="AB204" t="inlineStr"/>
       <c r="AC204" t="inlineStr"/>
       <c r="AD204" t="n">
-        <v>2029398.43</v>
+        <v>2498762.48</v>
       </c>
     </row>
     <row r="205">
@@ -20406,7 +20406,7 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>211991.51</v>
+        <v>267582.82</v>
       </c>
       <c r="R218" t="n">
         <v>211991.51</v>
@@ -20425,7 +20425,7 @@
       </c>
       <c r="Y218" t="inlineStr"/>
       <c r="Z218" t="n">
-        <v>211991.51</v>
+        <v>267582.82</v>
       </c>
       <c r="AA218" t="inlineStr"/>
       <c r="AB218" t="inlineStr"/>
@@ -20691,7 +20691,7 @@
         <v>6977375.41</v>
       </c>
       <c r="R221" t="n">
-        <v>868789.0600000001</v>
+        <v>3356349.34</v>
       </c>
       <c r="S221" t="n">
         <v>858363.59</v>
@@ -22416,7 +22416,7 @@
         <v>231318.29</v>
       </c>
       <c r="S240" t="n">
-        <v>0</v>
+        <v>230736.57</v>
       </c>
       <c r="T240" t="inlineStr"/>
       <c r="U240" t="inlineStr"/>
@@ -22435,7 +22435,7 @@
       <c r="AB240" t="inlineStr"/>
       <c r="AC240" t="inlineStr"/>
       <c r="AD240" t="n">
-        <v>0</v>
+        <v>230736.57</v>
       </c>
     </row>
     <row r="241">
@@ -22510,7 +22510,7 @@
         <v>186703.7</v>
       </c>
       <c r="S241" t="n">
-        <v>0</v>
+        <v>186237.99</v>
       </c>
       <c r="T241" t="inlineStr"/>
       <c r="U241" t="inlineStr"/>
@@ -22529,7 +22529,7 @@
       <c r="AB241" t="inlineStr"/>
       <c r="AC241" t="inlineStr"/>
       <c r="AD241" t="n">
-        <v>0</v>
+        <v>186237.99</v>
       </c>
     </row>
     <row r="242">
@@ -22604,7 +22604,7 @@
         <v>18408.35</v>
       </c>
       <c r="S242" t="n">
-        <v>0</v>
+        <v>18408.35</v>
       </c>
       <c r="T242" t="inlineStr"/>
       <c r="U242" t="inlineStr"/>
@@ -22623,7 +22623,7 @@
       <c r="AB242" t="inlineStr"/>
       <c r="AC242" t="inlineStr"/>
       <c r="AD242" t="n">
-        <v>0</v>
+        <v>18408.35</v>
       </c>
     </row>
     <row r="243">
@@ -36395,10 +36395,10 @@
         <v>130958.32</v>
       </c>
       <c r="R395" t="n">
-        <v>97998.17999999999</v>
+        <v>130655.05</v>
       </c>
       <c r="S395" t="n">
-        <v>82514.46000000001</v>
+        <v>110011.54</v>
       </c>
       <c r="T395" t="inlineStr"/>
       <c r="U395" t="inlineStr"/>
@@ -36417,7 +36417,7 @@
       <c r="AB395" t="inlineStr"/>
       <c r="AC395" t="inlineStr"/>
       <c r="AD395" t="n">
-        <v>82514.46000000001</v>
+        <v>110011.54</v>
       </c>
     </row>
     <row r="396">
@@ -36763,7 +36763,7 @@
         <v>8789.450000000001</v>
       </c>
       <c r="R399" t="n">
-        <v>4987.97</v>
+        <v>8789.42</v>
       </c>
       <c r="S399" t="n">
         <v>4987.97</v>
@@ -36854,10 +36854,10 @@
         </is>
       </c>
       <c r="Q400" t="n">
-        <v>187522.15</v>
+        <v>252529.99</v>
       </c>
       <c r="R400" t="n">
-        <v>187522.12</v>
+        <v>252529.96</v>
       </c>
       <c r="S400" t="n">
         <v>166894.69</v>
@@ -36873,7 +36873,7 @@
       </c>
       <c r="Y400" t="inlineStr"/>
       <c r="Z400" t="n">
-        <v>187522.15</v>
+        <v>252529.99</v>
       </c>
       <c r="AA400" t="inlineStr"/>
       <c r="AB400" t="inlineStr"/>
@@ -36951,7 +36951,7 @@
         <v>39114.47</v>
       </c>
       <c r="R401" t="n">
-        <v>38157.52</v>
+        <v>39114.47</v>
       </c>
       <c r="S401" t="n">
         <v>34514.98</v>
@@ -37045,7 +37045,7 @@
         <v>21214.4</v>
       </c>
       <c r="R402" t="n">
-        <v>21023.01</v>
+        <v>21214.4</v>
       </c>
       <c r="S402" t="n">
         <v>18811.66</v>
@@ -37139,7 +37139,7 @@
         <v>87506.44</v>
       </c>
       <c r="R403" t="n">
-        <v>85783.92999999999</v>
+        <v>87506.44</v>
       </c>
       <c r="S403" t="n">
         <v>33987.97</v>
@@ -37233,7 +37233,7 @@
         <v>86503.2</v>
       </c>
       <c r="R404" t="n">
-        <v>84678.62</v>
+        <v>86503.2</v>
       </c>
       <c r="S404" t="n">
         <v>50862.48</v>
@@ -37327,7 +37327,7 @@
         <v>62694</v>
       </c>
       <c r="R405" t="n">
-        <v>61443.59</v>
+        <v>62694</v>
       </c>
       <c r="S405" t="n">
         <v>55456.22</v>
@@ -37421,7 +37421,7 @@
         <v>14763.95</v>
       </c>
       <c r="R406" t="n">
-        <v>14291.86</v>
+        <v>14763.95</v>
       </c>
       <c r="S406" t="n">
         <v>12980.4</v>
@@ -37515,7 +37515,7 @@
         <v>3723.84</v>
       </c>
       <c r="R407" t="n">
-        <v>3570.73</v>
+        <v>3723.84</v>
       </c>
       <c r="S407" t="n">
         <v>3240.1</v>
@@ -37606,7 +37606,7 @@
         </is>
       </c>
       <c r="Q408" t="n">
-        <v>81568.64999999999</v>
+        <v>109845.87</v>
       </c>
       <c r="R408" t="n">
         <v>81568.64999999999</v>
@@ -37621,7 +37621,7 @@
       <c r="X408" t="inlineStr"/>
       <c r="Y408" t="inlineStr"/>
       <c r="Z408" t="n">
-        <v>81568.64999999999</v>
+        <v>109845.87</v>
       </c>
       <c r="AA408" t="inlineStr"/>
       <c r="AB408" t="inlineStr"/>
@@ -38435,7 +38435,7 @@
         <v>223692.42</v>
       </c>
       <c r="R417" t="n">
-        <v>13783.27</v>
+        <v>28315.64</v>
       </c>
       <c r="S417" t="n">
         <v>13617.87</v>
@@ -38532,7 +38532,7 @@
         <v>1589721.35</v>
       </c>
       <c r="S418" t="n">
-        <v>1218149.35</v>
+        <v>1570644.68</v>
       </c>
       <c r="T418" t="inlineStr"/>
       <c r="U418" t="inlineStr"/>
@@ -38551,7 +38551,7 @@
       <c r="AB418" t="inlineStr"/>
       <c r="AC418" t="inlineStr"/>
       <c r="AD418" t="n">
-        <v>1218149.35</v>
+        <v>1570644.68</v>
       </c>
     </row>
     <row r="419">
@@ -38626,7 +38626,7 @@
         <v>46966.74</v>
       </c>
       <c r="S419" t="n">
-        <v>23956.2</v>
+        <v>35934.3</v>
       </c>
       <c r="T419" t="inlineStr"/>
       <c r="U419" t="inlineStr"/>
@@ -38641,7 +38641,7 @@
       <c r="AB419" t="inlineStr"/>
       <c r="AC419" t="inlineStr"/>
       <c r="AD419" t="n">
-        <v>23956.2</v>
+        <v>35934.3</v>
       </c>
     </row>
     <row r="420">
@@ -38716,7 +38716,7 @@
         <v>2487.09</v>
       </c>
       <c r="S420" t="n">
-        <v>1688.7</v>
+        <v>2487.09</v>
       </c>
       <c r="T420" t="inlineStr"/>
       <c r="U420" t="inlineStr"/>
@@ -38731,7 +38731,7 @@
       <c r="AB420" t="inlineStr"/>
       <c r="AC420" t="inlineStr"/>
       <c r="AD420" t="n">
-        <v>1688.7</v>
+        <v>2487.09</v>
       </c>
     </row>
     <row r="421">
@@ -38806,7 +38806,7 @@
         <v>83312.7</v>
       </c>
       <c r="S421" t="n">
-        <v>55541.8</v>
+        <v>83312.7</v>
       </c>
       <c r="T421" t="inlineStr"/>
       <c r="U421" t="inlineStr"/>
@@ -38821,7 +38821,7 @@
       <c r="AB421" t="inlineStr"/>
       <c r="AC421" t="inlineStr"/>
       <c r="AD421" t="n">
-        <v>55541.8</v>
+        <v>83312.7</v>
       </c>
     </row>
     <row r="422">
@@ -38896,7 +38896,7 @@
         <v>190387.12</v>
       </c>
       <c r="S422" t="n">
-        <v>131856.3</v>
+        <v>190387.12</v>
       </c>
       <c r="T422" t="inlineStr"/>
       <c r="U422" t="inlineStr"/>
@@ -38911,7 +38911,7 @@
       <c r="AB422" t="inlineStr"/>
       <c r="AC422" t="inlineStr"/>
       <c r="AD422" t="n">
-        <v>131856.3</v>
+        <v>190387.12</v>
       </c>
     </row>
     <row r="423">
@@ -39256,7 +39256,7 @@
         <v>1540.63</v>
       </c>
       <c r="S426" t="n">
-        <v>978.1799999999999</v>
+        <v>1540.63</v>
       </c>
       <c r="T426" t="inlineStr"/>
       <c r="U426" t="inlineStr"/>
@@ -39271,7 +39271,7 @@
       <c r="AB426" t="inlineStr"/>
       <c r="AC426" t="inlineStr"/>
       <c r="AD426" t="n">
-        <v>978.1799999999999</v>
+        <v>1540.63</v>
       </c>
     </row>
     <row r="427">
@@ -39346,7 +39346,7 @@
         <v>10063.48</v>
       </c>
       <c r="S427" t="n">
-        <v>6398.28</v>
+        <v>10063.48</v>
       </c>
       <c r="T427" t="inlineStr"/>
       <c r="U427" t="inlineStr"/>
@@ -39361,7 +39361,7 @@
       <c r="AB427" t="inlineStr"/>
       <c r="AC427" t="inlineStr"/>
       <c r="AD427" t="n">
-        <v>6398.28</v>
+        <v>10063.48</v>
       </c>
     </row>
     <row r="428">
@@ -39530,7 +39530,7 @@
         <v>6638.9</v>
       </c>
       <c r="S429" t="n">
-        <v>0</v>
+        <v>6638.9</v>
       </c>
       <c r="T429" t="inlineStr"/>
       <c r="U429" t="inlineStr"/>
@@ -39549,7 +39549,7 @@
       <c r="AB429" t="inlineStr"/>
       <c r="AC429" t="inlineStr"/>
       <c r="AD429" t="n">
-        <v>0</v>
+        <v>6638.9</v>
       </c>
     </row>
     <row r="430">
@@ -39621,10 +39621,10 @@
         <v>13762998.39</v>
       </c>
       <c r="R430" t="n">
-        <v>1063647.94</v>
+        <v>1750547.98</v>
       </c>
       <c r="S430" t="n">
-        <v>1050884.17</v>
+        <v>1729541.41</v>
       </c>
       <c r="T430" t="inlineStr"/>
       <c r="U430" t="inlineStr"/>
@@ -39643,7 +39643,7 @@
       <c r="AB430" t="inlineStr"/>
       <c r="AC430" t="inlineStr"/>
       <c r="AD430" t="n">
-        <v>1050884.17</v>
+        <v>1729541.41</v>
       </c>
     </row>
     <row r="431">
@@ -39812,7 +39812,7 @@
         <v>96342.11</v>
       </c>
       <c r="S432" t="n">
-        <v>0</v>
+        <v>96094.96000000001</v>
       </c>
       <c r="T432" t="inlineStr"/>
       <c r="U432" t="inlineStr"/>
@@ -39831,7 +39831,7 @@
       <c r="AB432" t="inlineStr"/>
       <c r="AC432" t="inlineStr"/>
       <c r="AD432" t="n">
-        <v>0</v>
+        <v>96094.96000000001</v>
       </c>
     </row>
     <row r="433">
@@ -40558,13 +40558,13 @@
         </is>
       </c>
       <c r="Q440" t="n">
-        <v>4233596.13</v>
+        <v>5369450.46</v>
       </c>
       <c r="R440" t="n">
         <v>779131.49</v>
       </c>
       <c r="S440" t="n">
-        <v>0</v>
+        <v>777179.45</v>
       </c>
       <c r="T440" t="inlineStr"/>
       <c r="U440" t="inlineStr"/>
@@ -40577,13 +40577,13 @@
       </c>
       <c r="Y440" t="inlineStr"/>
       <c r="Z440" t="n">
-        <v>4233596.13</v>
+        <v>5369450.46</v>
       </c>
       <c r="AA440" t="inlineStr"/>
       <c r="AB440" t="inlineStr"/>
       <c r="AC440" t="inlineStr"/>
       <c r="AD440" t="n">
-        <v>0</v>
+        <v>777179.45</v>
       </c>
     </row>
     <row r="441">
@@ -40652,13 +40652,13 @@
         </is>
       </c>
       <c r="Q441" t="n">
-        <v>220000</v>
+        <v>270000</v>
       </c>
       <c r="R441" t="n">
         <v>34221.35</v>
       </c>
       <c r="S441" t="n">
-        <v>0</v>
+        <v>34221.35</v>
       </c>
       <c r="T441" t="inlineStr"/>
       <c r="U441" t="inlineStr"/>
@@ -40671,13 +40671,13 @@
       </c>
       <c r="Y441" t="inlineStr"/>
       <c r="Z441" t="n">
-        <v>220000</v>
+        <v>270000</v>
       </c>
       <c r="AA441" t="inlineStr"/>
       <c r="AB441" t="inlineStr"/>
       <c r="AC441" t="inlineStr"/>
       <c r="AD441" t="n">
-        <v>0</v>
+        <v>34221.35</v>
       </c>
     </row>
     <row r="442">
@@ -40746,13 +40746,13 @@
         </is>
       </c>
       <c r="Q442" t="n">
-        <v>490207.03</v>
+        <v>679925.23</v>
       </c>
       <c r="R442" t="n">
         <v>47942.29</v>
       </c>
       <c r="S442" t="n">
-        <v>0</v>
+        <v>47818.72</v>
       </c>
       <c r="T442" t="inlineStr"/>
       <c r="U442" t="inlineStr"/>
@@ -40765,13 +40765,13 @@
       </c>
       <c r="Y442" t="inlineStr"/>
       <c r="Z442" t="n">
-        <v>490207.03</v>
+        <v>679925.23</v>
       </c>
       <c r="AA442" t="inlineStr"/>
       <c r="AB442" t="inlineStr"/>
       <c r="AC442" t="inlineStr"/>
       <c r="AD442" t="n">
-        <v>0</v>
+        <v>47818.72</v>
       </c>
     </row>
     <row r="443">
@@ -40840,13 +40840,13 @@
         </is>
       </c>
       <c r="Q443" t="n">
-        <v>40000</v>
+        <v>55000</v>
       </c>
       <c r="R443" t="n">
         <v>3545.6</v>
       </c>
       <c r="S443" t="n">
-        <v>0</v>
+        <v>3545.6</v>
       </c>
       <c r="T443" t="inlineStr"/>
       <c r="U443" t="inlineStr"/>
@@ -40859,13 +40859,13 @@
       </c>
       <c r="Y443" t="inlineStr"/>
       <c r="Z443" t="n">
-        <v>40000</v>
+        <v>55000</v>
       </c>
       <c r="AA443" t="inlineStr"/>
       <c r="AB443" t="inlineStr"/>
       <c r="AC443" t="inlineStr"/>
       <c r="AD443" t="n">
-        <v>0</v>
+        <v>3545.6</v>
       </c>
     </row>
     <row r="444">
@@ -41403,7 +41403,7 @@
         <v>85161.58</v>
       </c>
       <c r="R449" t="n">
-        <v>0</v>
+        <v>85161.58</v>
       </c>
       <c r="S449" t="n">
         <v>0</v>
@@ -41493,7 +41493,7 @@
         <v>2424959.83</v>
       </c>
       <c r="R450" t="n">
-        <v>0</v>
+        <v>217771.81</v>
       </c>
       <c r="S450" t="n">
         <v>0</v>
@@ -41771,7 +41771,7 @@
         <v>3700</v>
       </c>
       <c r="R453" t="n">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="S453" t="n">
         <v>0</v>
@@ -41861,7 +41861,7 @@
         <v>85.45999999999999</v>
       </c>
       <c r="R454" t="n">
-        <v>0</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="S454" t="n">
         <v>0</v>
@@ -43149,7 +43149,7 @@
         <v>552270.41</v>
       </c>
       <c r="R468" t="n">
-        <v>0</v>
+        <v>94512.00999999999</v>
       </c>
       <c r="S468" t="n">
         <v>0</v>
@@ -43337,7 +43337,7 @@
         <v>55000</v>
       </c>
       <c r="R470" t="n">
-        <v>0</v>
+        <v>6959.88</v>
       </c>
       <c r="S470" t="n">
         <v>0</v>
@@ -43701,10 +43701,10 @@
         <v>3531.04</v>
       </c>
       <c r="R474" t="n">
-        <v>1913.82</v>
+        <v>2296.6</v>
       </c>
       <c r="S474" t="n">
-        <v>1821.96</v>
+        <v>2186.37</v>
       </c>
       <c r="T474" t="inlineStr"/>
       <c r="U474" t="inlineStr"/>
@@ -43723,7 +43723,7 @@
       <c r="AB474" t="inlineStr"/>
       <c r="AC474" t="inlineStr"/>
       <c r="AD474" t="n">
-        <v>1821.96</v>
+        <v>2186.37</v>
       </c>
     </row>
     <row r="475">
@@ -46152,7 +46152,7 @@
         </is>
       </c>
       <c r="Q501" t="n">
-        <v>5341.15</v>
+        <v>6588.2</v>
       </c>
       <c r="R501" t="n">
         <v>5341.14</v>
@@ -46171,7 +46171,7 @@
       </c>
       <c r="Y501" t="inlineStr"/>
       <c r="Z501" t="n">
-        <v>5341.15</v>
+        <v>6588.2</v>
       </c>
       <c r="AA501" t="inlineStr"/>
       <c r="AB501" t="inlineStr"/>
@@ -46342,7 +46342,7 @@
         <v>5815.15</v>
       </c>
       <c r="S503" t="n">
-        <v>0</v>
+        <v>5815.15</v>
       </c>
       <c r="T503" t="inlineStr"/>
       <c r="U503" t="inlineStr"/>
@@ -46361,7 +46361,7 @@
       <c r="AB503" t="inlineStr"/>
       <c r="AC503" t="inlineStr"/>
       <c r="AD503" t="n">
-        <v>0</v>
+        <v>5815.15</v>
       </c>
     </row>
     <row r="504">
@@ -46530,7 +46530,7 @@
         <v>154297.4</v>
       </c>
       <c r="S505" t="n">
-        <v>0</v>
+        <v>153913.13</v>
       </c>
       <c r="T505" t="inlineStr"/>
       <c r="U505" t="inlineStr"/>
@@ -46549,7 +46549,7 @@
       <c r="AB505" t="inlineStr"/>
       <c r="AC505" t="inlineStr"/>
       <c r="AD505" t="n">
-        <v>0</v>
+        <v>153913.13</v>
       </c>
     </row>
     <row r="506">
@@ -46715,7 +46715,7 @@
         <v>1084.55</v>
       </c>
       <c r="R507" t="n">
-        <v>510.37</v>
+        <v>1084.54</v>
       </c>
       <c r="S507" t="n">
         <v>510.37</v>
@@ -47462,7 +47462,7 @@
         <v>48922.71</v>
       </c>
       <c r="S515" t="n">
-        <v>0</v>
+        <v>48802.92</v>
       </c>
       <c r="T515" t="inlineStr"/>
       <c r="U515" t="inlineStr"/>
@@ -47481,7 +47481,7 @@
       <c r="AB515" t="inlineStr"/>
       <c r="AC515" t="inlineStr"/>
       <c r="AD515" t="n">
-        <v>0</v>
+        <v>48802.92</v>
       </c>
     </row>
     <row r="516">
@@ -47556,7 +47556,7 @@
         <v>991.01</v>
       </c>
       <c r="S516" t="n">
-        <v>0</v>
+        <v>991.01</v>
       </c>
       <c r="T516" t="inlineStr"/>
       <c r="U516" t="inlineStr"/>
@@ -47575,7 +47575,7 @@
       <c r="AB516" t="inlineStr"/>
       <c r="AC516" t="inlineStr"/>
       <c r="AD516" t="n">
-        <v>0</v>
+        <v>991.01</v>
       </c>
     </row>
     <row r="517">
@@ -47734,7 +47734,7 @@
         </is>
       </c>
       <c r="Q518" t="n">
-        <v>1498.22</v>
+        <v>3309.12</v>
       </c>
       <c r="R518" t="n">
         <v>1498.22</v>
@@ -47753,7 +47753,7 @@
       </c>
       <c r="Y518" t="inlineStr"/>
       <c r="Z518" t="n">
-        <v>1498.22</v>
+        <v>3309.12</v>
       </c>
       <c r="AA518" t="inlineStr"/>
       <c r="AB518" t="inlineStr"/>
@@ -48298,7 +48298,7 @@
         </is>
       </c>
       <c r="Q524" t="n">
-        <v>1984.05</v>
+        <v>8485.08</v>
       </c>
       <c r="R524" t="n">
         <v>1984.05</v>
@@ -48313,7 +48313,7 @@
       <c r="X524" t="inlineStr"/>
       <c r="Y524" t="inlineStr"/>
       <c r="Z524" t="n">
-        <v>1984.05</v>
+        <v>8485.08</v>
       </c>
       <c r="AA524" t="inlineStr"/>
       <c r="AB524" t="inlineStr"/>
@@ -48864,7 +48864,7 @@
         <v>2286.32</v>
       </c>
       <c r="S530" t="n">
-        <v>0</v>
+        <v>2286.32</v>
       </c>
       <c r="T530" t="inlineStr"/>
       <c r="U530" t="inlineStr"/>
@@ -48879,7 +48879,7 @@
       <c r="AB530" t="inlineStr"/>
       <c r="AC530" t="inlineStr"/>
       <c r="AD530" t="n">
-        <v>0</v>
+        <v>2286.32</v>
       </c>
     </row>
     <row r="531">
@@ -49246,6 +49246,276 @@
         <v>0</v>
       </c>
     </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B535" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C535" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>107</v>
+      </c>
+      <c r="F535" s="2" t="n">
+        <v>46261</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>1511189 000136/2026</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I535" t="n">
+        <v>52</v>
+      </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K535" t="n">
+        <v>5203</v>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>ARMAMENTO E EQUIPAMENTO DE USO POLICIAL</t>
+        </is>
+      </c>
+      <c r="M535" t="n">
+        <v>80</v>
+      </c>
+      <c r="N535" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>07.831.740/0001-19</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>CANTARES MAGAZINE LTDA</t>
+        </is>
+      </c>
+      <c r="Q535" t="n">
+        <v>3470.69</v>
+      </c>
+      <c r="R535" t="n">
+        <v>0</v>
+      </c>
+      <c r="S535" t="n">
+        <v>0</v>
+      </c>
+      <c r="T535" t="inlineStr"/>
+      <c r="U535" t="inlineStr"/>
+      <c r="V535" t="inlineStr"/>
+      <c r="W535" t="inlineStr"/>
+      <c r="X535" t="inlineStr"/>
+      <c r="Y535" t="inlineStr"/>
+      <c r="Z535" t="n">
+        <v>3470.69</v>
+      </c>
+      <c r="AA535" t="inlineStr"/>
+      <c r="AB535" t="inlineStr"/>
+      <c r="AC535" t="inlineStr"/>
+      <c r="AD535" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B536" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C536" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>116</v>
+      </c>
+      <c r="F536" s="2" t="n">
+        <v>46265</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>1511189 000180/2026</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I536" t="n">
+        <v>52</v>
+      </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K536" t="n">
+        <v>5207</v>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS DE INFORMATICA</t>
+        </is>
+      </c>
+      <c r="M536" t="n">
+        <v>80</v>
+      </c>
+      <c r="N536" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>04.602.789/0001-01</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>DATEN TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="Q536" t="n">
+        <v>23424.68</v>
+      </c>
+      <c r="R536" t="n">
+        <v>0</v>
+      </c>
+      <c r="S536" t="n">
+        <v>0</v>
+      </c>
+      <c r="T536" t="inlineStr"/>
+      <c r="U536" t="inlineStr"/>
+      <c r="V536" t="inlineStr"/>
+      <c r="W536" t="inlineStr"/>
+      <c r="X536" t="inlineStr"/>
+      <c r="Y536" t="inlineStr"/>
+      <c r="Z536" t="n">
+        <v>23424.68</v>
+      </c>
+      <c r="AA536" t="inlineStr"/>
+      <c r="AB536" t="inlineStr"/>
+      <c r="AC536" t="inlineStr"/>
+      <c r="AD536" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B537" t="n">
+        <v>9456627</v>
+      </c>
+      <c r="C537" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>POLICIA CIVIL DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>127</v>
+      </c>
+      <c r="F537" s="2" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>1511189 000249/2026</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>REGISTRO DE PRECO REALIZADO NO SIRP - LEI 14.133</t>
+        </is>
+      </c>
+      <c r="I537" t="n">
+        <v>52</v>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS E MATERIAL PERMANENTE</t>
+        </is>
+      </c>
+      <c r="K537" t="n">
+        <v>5207</v>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>EQUIPAMENTOS DE INFORMATICA</t>
+        </is>
+      </c>
+      <c r="M537" t="n">
+        <v>80</v>
+      </c>
+      <c r="N537" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>04.602.789/0001-01</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>DATEN TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="Q537" t="n">
+        <v>15027.7</v>
+      </c>
+      <c r="R537" t="n">
+        <v>0</v>
+      </c>
+      <c r="S537" t="n">
+        <v>0</v>
+      </c>
+      <c r="T537" t="inlineStr"/>
+      <c r="U537" t="inlineStr"/>
+      <c r="V537" t="inlineStr"/>
+      <c r="W537" t="inlineStr"/>
+      <c r="X537" t="inlineStr"/>
+      <c r="Y537" t="inlineStr"/>
+      <c r="Z537" t="n">
+        <v>15027.7</v>
+      </c>
+      <c r="AA537" t="inlineStr"/>
+      <c r="AB537" t="inlineStr"/>
+      <c r="AC537" t="inlineStr"/>
+      <c r="AD537" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
